--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{87AD083B-D41F-654A-9282-24E83F6B0AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{88E5C103-F4AE-0E48-A72A-7FA7A8B97876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1132" uniqueCount="232">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1264" uniqueCount="250">
   <si>
     <t>reviewer</t>
   </si>
@@ -455,13 +455,7 @@
     <t>supersedes</t>
   </si>
   <si>
-    <t>Another implementation proposal has been written: BIP79 Bustapay.We decided to deviate from it for several reasons: [...] Other than that, our proposal is very similar.</t>
-  </si>
-  <si>
     <t>BIP78 is the proposed replacement of the BIP79.</t>
-  </si>
-  <si>
-    <t>This BIP is a modification and intended replacement of BIP 0021 to add information about the modern usage of bitcoin.</t>
   </si>
   <si>
     <t>Replaces: 151</t>
@@ -729,6 +723,66 @@
   </si>
   <si>
     <t>Registered coin types for BIP-0044</t>
+  </si>
+  <si>
+    <t>clients MUST understand the implications of the version they use (eg, comply with BIP 0034 for version 2) [...] This does not include the block height, which is required to be included in the scriptSig by BIP 0034.</t>
+  </si>
+  <si>
+    <t>This BIP defines the derivation scheme for HD wallets using the P2WPKH-nested-in-P2SH (BIP 141) serialization format. [...] References [...] BIP32 - Hierarchical Deterministic Wallets</t>
+  </si>
+  <si>
+    <t>References [....] BIP43 - Purpose Field for Deterministic Wallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference BIP16 - Pay to Script Hash </t>
+  </si>
+  <si>
+    <t>To derive a public key from the root account, this BIP uses the same account-structure as defined in BIP 44, but only uses a different purpose value to indicate the different transaction serialization method. [...] References [....] BIP44 - Multi-Account Hierarchy for Deterministic Wallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional registered version bytes are listed in SLIP-0132. </t>
+  </si>
+  <si>
+    <t>Payjoin URI Bitcoin URIs (BIP 21 or BIP 321) are a standard way to request bitcoin</t>
+  </si>
+  <si>
+    <t>Replaces: 79 [...] Another implementation proposal has been written: BIP79 Bustapay. We decided to deviate from it for several reasons: [...] Other than that, our proposal is very similar.</t>
+  </si>
+  <si>
+    <t>In a payjoin payment, the following steps happen: The receiver of the payment, presents a BIP 21 URI to the sender with a parameter [...] This proposal is defining the following new BIP 21 URI parameters</t>
+  </si>
+  <si>
+    <t>similar to the current witness commitment [6] [...] References [...] https://github.com/bitcoin/bips/blob/master/bip-0141.mediawiki</t>
+  </si>
+  <si>
+    <t>Replaces: 21 [...] This BIP is a modification and intended replacement of BIP 0021 to add information about the modern usage of bitcoin.</t>
+  </si>
+  <si>
+    <t>The following keys are currently defined for payment instructions of various forms: [...] sp: BIP 352 Silent Payment addresses</t>
+  </si>
+  <si>
+    <t>The following keys are currently defined for payment instructions of various forms: [...] pay: BIP 351 Private Payment addresses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: Scheme described in BIP44 should use 44' (or 0x8000002C) as purpose. </t>
+  </si>
+  <si>
+    <t>Example made to demonstrate purpose of BIP43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIP 21 was based on BIP 20, which was, in turn based on an earlier document by Nils Schneider. </t>
+  </si>
+  <si>
+    <t>Assuming a node sends only ping messages every 20 minutes (the timeout interval for post-BIP31 connections) on a connection</t>
+  </si>
+  <si>
+    <t>Trezor generates all keys from a BIP-0039 mnemonic or from a set of SLIP-0039 mnemonic shares and optionally a passphrase.</t>
+  </si>
+  <si>
+    <t>However, there does not exist any similar specification for the derivation of keys for symmetric-key algorithms, which are needed for example in password encryption or encryption of Bitcoin metadata. SLIP-0011 deals with this problem by first using BIP-0032 to derive a secp256k1 private key [...]</t>
+  </si>
+  <si>
+    <t>The checksum design is heavily inspired by Bech32 defined in BIP-0173.</t>
   </si>
 </sst>
 </file>
@@ -736,9 +790,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -878,6 +932,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1234,7 +1295,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1257,8 +1318,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1676,10 +1740,10 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -1729,7 +1793,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
@@ -1737,6 +1801,9 @@
       <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D2" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="E2" s="7" t="s">
         <v>33</v>
       </c>
@@ -1759,21 +1826,21 @@
         <v>2016-04-26</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B3" s="3">
         <v>12</v>
@@ -1823,7 +1890,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3">
         <v>14</v>
@@ -1873,7 +1940,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" s="3">
         <v>16</v>
@@ -1920,7 +1987,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
@@ -1970,7 +2037,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -2020,7 +2087,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B8" s="3">
         <v>21</v>
@@ -2028,6 +2095,9 @@
       <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D8" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="E8" s="7" t="s">
         <v>33</v>
       </c>
@@ -2050,21 +2120,21 @@
         <v>2019-06-25</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B9" s="3">
         <v>22</v>
@@ -2114,7 +2184,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B10" s="3">
         <v>30</v>
@@ -2164,7 +2234,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="3">
         <v>31</v>
@@ -2214,7 +2284,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B12" s="3">
         <v>39</v>
@@ -2264,7 +2334,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B13" s="3">
         <v>39</v>
@@ -2272,6 +2342,9 @@
       <c r="C13" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D13" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="E13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2294,21 +2367,21 @@
         <v>2017-12-18</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B14" s="3">
         <v>43</v>
@@ -2358,7 +2431,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B15" s="3">
         <v>44</v>
@@ -2408,7 +2481,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B16" s="3">
         <v>44</v>
@@ -2416,6 +2489,9 @@
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D16" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="E16" s="7" t="s">
         <v>33</v>
       </c>
@@ -2438,21 +2514,21 @@
         <v>2014-07-09</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B17" s="3">
         <v>49</v>
@@ -2502,7 +2578,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B18" s="3">
         <v>73</v>
@@ -2552,7 +2628,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B19" s="3">
         <v>74</v>
@@ -2602,7 +2678,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B20" s="3">
         <v>77</v>
@@ -2652,7 +2728,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B21" s="3">
         <v>78</v>
@@ -2702,7 +2778,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B22" s="3">
         <v>111</v>
@@ -2752,7 +2828,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B23" s="3">
         <v>112</v>
@@ -2802,7 +2878,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B24" s="3">
         <v>113</v>
@@ -2852,7 +2928,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B25" s="3">
         <v>114</v>
@@ -2902,7 +2978,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B26" s="3">
         <v>119</v>
@@ -2952,7 +3028,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B27" s="3">
         <v>122</v>
@@ -3002,7 +3078,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B28" s="3">
         <v>128</v>
@@ -3052,7 +3128,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B29" s="3">
         <v>142</v>
@@ -3102,7 +3178,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B30" s="3">
         <v>145</v>
@@ -3152,7 +3228,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B31" s="3">
         <v>158</v>
@@ -3202,7 +3278,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B32" s="3">
         <v>197</v>
@@ -3252,7 +3328,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B33" s="3">
         <v>320</v>
@@ -3296,7 +3372,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B34" s="3">
         <v>321</v>
@@ -3346,7 +3422,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B35" s="3">
         <v>324</v>
@@ -3396,7 +3472,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3">
         <v>330</v>
@@ -3443,7 +3519,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>331</v>
@@ -3490,7 +3566,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B38" s="3">
         <v>347</v>
@@ -3537,7 +3613,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B39" s="3">
         <v>353</v>
@@ -3584,7 +3660,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B40" s="3">
         <v>375</v>
@@ -3631,7 +3707,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B41" s="3">
         <v>392</v>
@@ -3678,7 +3754,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B42" s="3">
         <v>440</v>
@@ -3725,7 +3801,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B43" s="3">
         <v>443</v>
@@ -4099,7 +4175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -4118,13 +4194,13 @@
         <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>115</v>
@@ -4147,13 +4223,13 @@
     </row>
     <row r="2" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D2" s="3">
         <v>32</v>
@@ -4162,13 +4238,13 @@
         <v>118</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>15</v>
@@ -4177,47 +4253,47 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3" s="3">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>156</v>
+        <v>247</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D4" s="3">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>128</v>
@@ -4226,56 +4302,56 @@
         <v>37</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>156</v>
+        <v>247</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" s="3">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="3">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="3">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3">
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D6" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>128</v>
@@ -4284,7 +4360,7 @@
         <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>15</v>
@@ -4295,13 +4371,13 @@
     </row>
     <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D7" s="3">
         <v>12</v>
@@ -4310,27 +4386,27 @@
         <v>140</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B8" s="3">
-        <v>18</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D8" s="3">
         <v>13</v>
@@ -4339,45 +4415,39 @@
         <v>128</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D9" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>15</v>
@@ -4386,30 +4456,27 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B10" s="3">
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D10" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>140</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -4418,27 +4485,30 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="3">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="3">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D11" s="3">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>164</v>
+        <v>155</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>15</v>
@@ -4447,114 +4517,120 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B12" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D12" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B13" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D13" s="3">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>151</v>
+        <v>159</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B14" s="3">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="3">
         <v>21</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="3">
-        <v>39</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B15" s="3">
         <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D15" s="3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -4563,94 +4639,85 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B16" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D16" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B17" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D17" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" s="3">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D18" s="3">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>15</v>
@@ -4659,30 +4726,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B19" s="3">
+        <v>21</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="3">
         <v>39</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="3">
-        <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>15</v>
@@ -4691,105 +4755,111 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B20" s="3">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D20" s="3">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B21" s="3">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D21" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B22" s="3">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D22" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>123</v>
+        <v>230</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B23" s="3">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D23" s="3">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>118</v>
@@ -4798,10 +4868,10 @@
         <v>37</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>15</v>
@@ -4812,16 +4882,16 @@
     </row>
     <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B24" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D24" s="3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>118</v>
@@ -4830,10 +4900,10 @@
         <v>37</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>15</v>
@@ -4842,30 +4912,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D25" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -4874,27 +4941,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B26" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D26" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
@@ -4905,48 +4972,45 @@
     </row>
     <row r="27" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B27" s="3">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D27" s="3">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B28" s="3">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D28" s="3">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>118</v>
@@ -4955,27 +5019,27 @@
         <v>37</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="3">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" s="3">
         <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="3">
-        <v>73</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" s="3">
-        <v>70</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>128</v>
@@ -4984,30 +5048,30 @@
         <v>37</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B30" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="3">
-        <v>74</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D30" s="3">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>118</v>
@@ -5016,30 +5080,30 @@
         <v>37</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B31" s="3">
-        <v>77</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D31" s="3">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>118</v>
@@ -5048,10 +5112,10 @@
         <v>37</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>15</v>
@@ -5062,28 +5126,28 @@
     </row>
     <row r="32" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B32" s="3">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D32" s="3">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>15</v>
@@ -5092,18 +5156,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B33" s="3">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D33" s="3">
-        <v>173</v>
+        <v>44</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>118</v>
@@ -5112,10 +5176,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>15</v>
@@ -5124,50 +5185,47 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B34" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D34" s="3">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B35" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D35" s="3">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>118</v>
@@ -5176,68 +5234,68 @@
         <v>37</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>139</v>
+        <v>231</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D36" s="3">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D37" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>175</v>
+        <v>234</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>15</v>
@@ -5246,30 +5304,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B38" s="3">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>15</v>
@@ -5278,30 +5333,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B39" s="3">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D39" s="3">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>15</v>
@@ -5310,27 +5362,30 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B40" s="3">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D40" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>178</v>
+        <v>169</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>15</v>
@@ -5339,30 +5394,30 @@
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B41" s="3">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D41" s="3">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>15</v>
@@ -5371,18 +5426,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B42" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D42" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>118</v>
@@ -5391,126 +5446,126 @@
         <v>37</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B43" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D43" s="3">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B44" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D44" s="3">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B45" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D45" s="3">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B46" s="3">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D46" s="3">
-        <v>9</v>
+        <v>321</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>118</v>
@@ -5519,274 +5574,274 @@
         <v>37</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>189</v>
+        <v>236</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B47" s="3">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D47" s="3">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D48" s="3">
+        <v>21</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="3">
+        <v>78</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" s="3">
+        <v>79</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="3">
+        <v>111</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="3">
+        <v>37</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="3">
         <v>112</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B49" s="3">
-        <v>114</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D49" s="3">
-        <v>141</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" s="3">
+        <v>9</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B50" s="3">
-        <v>119</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D50" s="3">
+      <c r="F51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B52" s="3">
+        <v>112</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D52" s="3">
         <v>65</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B51" s="3">
-        <v>119</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D51" s="3">
-        <v>112</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B52" s="3">
-        <v>119</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D52" s="3">
-        <v>341</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B53" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D53" s="3">
-        <v>346</v>
+        <v>68</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B54" s="3">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D54" s="3">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B55" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D55" s="3">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>118</v>
@@ -5795,7 +5850,10 @@
         <v>37</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>199</v>
+        <v>174</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
@@ -5806,25 +5864,28 @@
     </row>
     <row r="56" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B56" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D56" s="3">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>197</v>
+        <v>180</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>15</v>
@@ -5833,27 +5894,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B57" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D57" s="3">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>198</v>
+        <v>180</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>15</v>
@@ -5862,27 +5926,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B58" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D58" s="3">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>200</v>
+        <v>180</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
@@ -5891,27 +5958,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B59" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D59" s="3">
-        <v>433</v>
+        <v>9</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>15</v>
@@ -5920,18 +5987,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B60" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D60" s="3">
-        <v>443</v>
+        <v>16</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>128</v>
@@ -5940,7 +6007,10 @@
         <v>37</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>15</v>
@@ -5949,30 +6019,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B61" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D61" s="3">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>15</v>
@@ -5981,27 +6051,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B62" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D62" s="3">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
@@ -6010,18 +6080,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B63" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D63" s="3">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>128</v>
@@ -6030,10 +6100,7 @@
         <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
@@ -6042,18 +6109,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B64" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D64" s="3">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>128</v>
@@ -6062,10 +6129,7 @@
         <v>37</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
@@ -6074,18 +6138,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B65" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D65" s="3">
-        <v>70</v>
+        <v>341</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>128</v>
@@ -6094,10 +6158,10 @@
         <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -6106,30 +6170,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B66" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D66" s="3">
-        <v>141</v>
+        <v>346</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
@@ -6138,30 +6202,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B67" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D67" s="3">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
@@ -6170,18 +6234,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B68" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D68" s="3">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>118</v>
@@ -6190,7 +6254,7 @@
         <v>37</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
@@ -6199,30 +6263,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B69" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D69" s="3">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
@@ -6231,18 +6292,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B70" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D70" s="3">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>128</v>
@@ -6251,7 +6312,7 @@
         <v>37</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
@@ -6260,27 +6321,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B71" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D71" s="3">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
@@ -6289,27 +6350,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B72" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D72" s="3">
-        <v>157</v>
+        <v>433</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>15</v>
@@ -6318,27 +6379,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B73" s="3">
-        <v>197</v>
+        <v>128</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D73" s="3">
-        <v>199</v>
+        <v>443</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
@@ -6347,79 +6408,79 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B74" s="3">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D74" s="3">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>143</v>
+        <v>202</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B75" s="3">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D75" s="3">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B76" s="3">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D76" s="3">
-        <v>340</v>
+        <v>47</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>128</v>
@@ -6428,25 +6489,568 @@
         <v>37</v>
       </c>
       <c r="G76" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" s="3">
+        <v>142</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="3">
+        <v>63</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B78" s="3">
+        <v>142</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D78" s="3">
+        <v>70</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B79" s="3">
+        <v>142</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" s="3">
+        <v>141</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B80" s="3">
+        <v>145</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" s="3">
+        <v>9</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B81" s="3">
+        <v>145</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D81" s="3">
+        <v>22</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" s="3">
+        <v>145</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" s="3">
+        <v>23</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H76" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="3" t="s">
+      <c r="G82" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B83" s="3">
+        <v>145</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" s="3">
+        <v>141</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B84" s="3">
+        <v>158</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D84" s="3">
+        <v>37</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B85" s="3">
+        <v>158</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D85" s="3">
+        <v>141</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B86" s="3">
+        <v>158</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D86" s="3">
+        <v>157</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" s="3">
+        <v>197</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D87" s="3">
+        <v>199</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" s="3">
+        <v>321</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D88" s="3">
+        <v>20</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="3">
+        <v>321</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" s="3">
+        <v>21</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" s="3" t="s">
         <v>50</v>
       </c>
     </row>
+    <row r="90" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B90" s="3">
+        <v>321</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" s="3">
+        <v>351</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B91" s="3">
+        <v>321</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D91" s="3">
+        <v>352</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B92" s="3">
+        <v>324</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D92" s="3">
+        <v>151</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="3">
+        <v>324</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" s="3">
+        <v>340</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="3">
+        <v>324</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D94" s="3">
+        <v>31</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J76" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J76">
-      <sortCondition ref="B2:B76"/>
-      <sortCondition ref="A2:A76"/>
-      <sortCondition ref="D2:D76"/>
-      <sortCondition ref="C2:C76"/>
+  <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J93">
+      <sortCondition ref="B2:B93"/>
+      <sortCondition ref="A2:A93"/>
+      <sortCondition ref="D2:D93"/>
+      <sortCondition ref="C2:C93"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{88E5C103-F4AE-0E48-A72A-7FA7A8B97876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82FF77B4-F2AB-2F4A-AC3F-B3D41B3F170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1264" uniqueCount="250">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1318" uniqueCount="259">
   <si>
     <t>reviewer</t>
   </si>
@@ -783,6 +783,33 @@
   </si>
   <si>
     <t>The checksum design is heavily inspired by Bech32 defined in BIP-0173.</t>
+  </si>
+  <si>
+    <t>Proposed-Replacement: 323</t>
+  </si>
+  <si>
+    <t>Sixteen bits from the block header nVersion field [...] are reserved for general use and removed from BIP8 and BIP9 specifications. [...] References BIP8</t>
+  </si>
+  <si>
+    <t>Sixteen bits from the block header nVersion field [...] are reserved for general use and removed from BIP8 and BIP9 specifications. [...] References [...] BIP9</t>
+  </si>
+  <si>
+    <t>Compute h = TaggedHash("Tx Relay Salting", salt1, salt2), where the two salts are encoded in 64-bit little-endian byte order, and TaggedHash is specified by BIP-340.</t>
+  </si>
+  <si>
+    <t>Let s = SipHash-2-4((k0,k1),wtxid), where wtxid is the transaction hash including witness data as defined by BIP141.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since sketches are based on the WTXIDs, the negotiation and support of Erlay should be enabled only if both peers signal BIP-339 support. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> a node cannot use txid to deduplicate transactions it has already downloaded or validated. Ideally, two nodes that both support BIP339 wtxid-based transaction relay shouldn't ever need to use txid-based transaction relay. </t>
+  </si>
+  <si>
+    <t>If the peers are using BIP133 fee filters [...] This does not mean BIP133 is required for package relay to work, [...]</t>
+  </si>
+  <si>
+    <t>Clients implementing this protocol will only attempt to send and request packages if agreed upon during the version handshake. [13] [14] [...] [14] Is Package Erlay possible? A client using BIP330 reconciliation-based transaction relay (Erlay) is able to use package relay [...]</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1322,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1322,6 +1349,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3336,6 +3366,9 @@
       <c r="C33" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D33" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E33" s="7" t="s">
         <v>17</v>
       </c>
@@ -3431,7 +3464,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>33</v>
@@ -3480,6 +3513,9 @@
       <c r="C36" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D36" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E36" s="7" t="s">
         <v>17</v>
       </c>
@@ -3526,6 +3562,9 @@
       </c>
       <c r="C37" s="7" t="s">
         <v>15</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>17</v>
@@ -4175,7 +4214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J237"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -4249,7 +4288,7 @@
       <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4261,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D3" s="3">
         <v>39</v>
@@ -4278,7 +4317,7 @@
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4290,7 +4329,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D4" s="3">
         <v>39</v>
@@ -4307,7 +4346,7 @@
       <c r="I4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4336,7 +4375,7 @@
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4365,7 +4404,7 @@
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4394,7 +4433,7 @@
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4423,7 +4462,7 @@
       <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4452,7 +4491,7 @@
       <c r="I9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4481,7 +4520,7 @@
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4513,7 +4552,7 @@
       <c r="I11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4545,7 +4584,7 @@
       <c r="I12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4577,7 +4616,7 @@
       <c r="I13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4606,7 +4645,7 @@
       <c r="I14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4635,7 +4674,7 @@
       <c r="I15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4664,7 +4703,7 @@
       <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4693,7 +4732,7 @@
       <c r="I17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4722,7 +4761,7 @@
       <c r="I18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="J18" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4751,7 +4790,7 @@
       <c r="I19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="J19" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4783,7 +4822,7 @@
       <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4815,7 +4854,7 @@
       <c r="I21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4844,7 +4883,7 @@
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -4876,7 +4915,7 @@
       <c r="I23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4908,7 +4947,7 @@
       <c r="I24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4937,7 +4976,7 @@
       <c r="I25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4966,7 +5005,7 @@
       <c r="I26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="J26" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4995,7 +5034,7 @@
       <c r="I27" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="J27" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5024,7 +5063,7 @@
       <c r="I28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="J28" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5056,7 +5095,7 @@
       <c r="I29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5088,7 +5127,7 @@
       <c r="I30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5120,7 +5159,7 @@
       <c r="I31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5152,7 +5191,7 @@
       <c r="I32" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="J32" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5181,7 +5220,7 @@
       <c r="I33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J33" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5210,7 +5249,7 @@
       <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J34" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5242,7 +5281,7 @@
       <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J35" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5271,7 +5310,7 @@
       <c r="I36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5300,7 +5339,7 @@
       <c r="I37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J37" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5329,7 +5368,7 @@
       <c r="I38" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5358,7 +5397,7 @@
       <c r="I39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="J39" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5390,7 +5429,7 @@
       <c r="I40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="J40" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5422,7 +5461,7 @@
       <c r="I41" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5454,7 +5493,7 @@
       <c r="I42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J42" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5486,7 +5525,7 @@
       <c r="I43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J43" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5518,7 +5557,7 @@
       <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J44" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5550,7 +5589,7 @@
       <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J45" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5582,7 +5621,7 @@
       <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5611,7 +5650,7 @@
       <c r="I47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="J47" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5640,7 +5679,7 @@
       <c r="I48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J48" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5672,7 +5711,7 @@
       <c r="I49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -5701,7 +5740,7 @@
       <c r="I50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="J50" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5733,7 +5772,7 @@
       <c r="I51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="J51" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5765,7 +5804,7 @@
       <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="J52" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5794,7 +5833,7 @@
       <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5826,7 +5865,7 @@
       <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="J54" s="10" t="s">
         <v>44</v>
       </c>
     </row>
@@ -5858,7 +5897,7 @@
       <c r="I55" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="J55" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5890,7 +5929,7 @@
       <c r="I56" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="J56" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5922,7 +5961,7 @@
       <c r="I57" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="J57" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5954,7 +5993,7 @@
       <c r="I58" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="J58" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5983,7 +6022,7 @@
       <c r="I59" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="J59" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6015,7 +6054,7 @@
       <c r="I60" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="J60" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6047,7 +6086,7 @@
       <c r="I61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="J61" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6076,7 +6115,7 @@
       <c r="I62" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="J62" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6105,7 +6144,7 @@
       <c r="I63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="J63" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6134,7 +6173,7 @@
       <c r="I64" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="J64" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6166,7 +6205,7 @@
       <c r="I65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6198,7 +6237,7 @@
       <c r="I66" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="J66" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6230,7 +6269,7 @@
       <c r="I67" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="J67" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6259,7 +6298,7 @@
       <c r="I68" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="3" t="s">
+      <c r="J68" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6288,7 +6327,7 @@
       <c r="I69" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="J69" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6317,7 +6356,7 @@
       <c r="I70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="J70" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6346,7 +6385,7 @@
       <c r="I71" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="J71" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6375,7 +6414,7 @@
       <c r="I72" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="3" t="s">
+      <c r="J72" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6404,7 +6443,7 @@
       <c r="I73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="J73" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6436,7 +6475,7 @@
       <c r="I74" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="J74" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6465,7 +6504,7 @@
       <c r="I75" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J75" s="3" t="s">
+      <c r="J75" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6497,7 +6536,7 @@
       <c r="I76" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J76" s="3" t="s">
+      <c r="J76" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6529,7 +6568,7 @@
       <c r="I77" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="J77" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6561,7 +6600,7 @@
       <c r="I78" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="J78" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6593,7 +6632,7 @@
       <c r="I79" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J79" s="3" t="s">
+      <c r="J79" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6625,7 +6664,7 @@
       <c r="I80" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="J80" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6654,7 +6693,7 @@
       <c r="I81" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J81" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6686,7 +6725,7 @@
       <c r="I82" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="J82" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6715,7 +6754,7 @@
       <c r="I83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="J83" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6744,7 +6783,7 @@
       <c r="I84" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="J84" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6773,7 +6812,7 @@
       <c r="I85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J85" s="3" t="s">
+      <c r="J85" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6802,7 +6841,7 @@
       <c r="I86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J86" s="3" t="s">
+      <c r="J86" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6831,22 +6870,22 @@
       <c r="I87" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="J87" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B88" s="3">
-        <v>321</v>
-      </c>
-      <c r="C88" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D88" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>128</v>
@@ -6855,71 +6894,71 @@
         <v>20</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J88" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B89" s="3">
-        <v>321</v>
-      </c>
-      <c r="C89" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D89" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J89" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B90" s="3">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D90" s="3">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>50</v>
+      <c r="J90" s="10" t="d">
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -6929,40 +6968,40 @@
       <c r="B91" s="3">
         <v>321</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D91" s="3">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="J91" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B92" s="3">
-        <v>324</v>
-      </c>
-      <c r="C92" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D92" s="3">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>140</v>
@@ -6971,30 +7010,27 @@
         <v>37</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>143</v>
+        <v>240</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="3" t="s">
+      <c r="J92" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B93" s="3">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D93" s="3">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>128</v>
@@ -7003,15 +7039,12 @@
         <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>145</v>
+        <v>242</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J93" s="3" t="s">
+      <c r="J93" s="10" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7020,29 +7053,698 @@
         <v>219</v>
       </c>
       <c r="B94" s="3">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D94" s="3">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F94" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B95" s="3">
+        <v>324</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D95" s="3">
+        <v>31</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G95" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="I95" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B96" s="3">
+        <v>324</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D96" s="3">
+        <v>151</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" s="3">
+        <v>324</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D97" s="3">
+        <v>340</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="3">
+        <v>330</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D98" s="3">
+        <v>340</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="3">
+        <v>330</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D99" s="3">
+        <v>141</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J99" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="3">
+        <v>330</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D100" s="3">
+        <v>339</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J100" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="3">
+        <v>331</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D101" s="3">
+        <v>339</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J101" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B102" s="3">
+        <v>331</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D102" s="3">
+        <v>133</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B103" s="3">
+        <v>331</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D103" s="3">
+        <v>330</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J104" s="10"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J105" s="10"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J106" s="10"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J107" s="10"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J108" s="10"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J109" s="10"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J110" s="10"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J111" s="10"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J112" s="10"/>
+    </row>
+    <row r="113" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J113" s="10"/>
+    </row>
+    <row r="114" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J114" s="10"/>
+    </row>
+    <row r="115" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J115" s="10"/>
+    </row>
+    <row r="116" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J116" s="10"/>
+    </row>
+    <row r="117" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J117" s="10"/>
+    </row>
+    <row r="118" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J118" s="10"/>
+    </row>
+    <row r="119" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J119" s="10"/>
+    </row>
+    <row r="120" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J120" s="10"/>
+    </row>
+    <row r="121" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J121" s="10"/>
+    </row>
+    <row r="122" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J122" s="10"/>
+    </row>
+    <row r="123" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J123" s="10"/>
+    </row>
+    <row r="124" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J124" s="10"/>
+    </row>
+    <row r="125" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J125" s="10"/>
+    </row>
+    <row r="126" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J126" s="10"/>
+    </row>
+    <row r="127" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J127" s="10"/>
+    </row>
+    <row r="128" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J128" s="10"/>
+    </row>
+    <row r="129" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J129" s="10"/>
+    </row>
+    <row r="130" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J130" s="10"/>
+    </row>
+    <row r="131" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J131" s="10"/>
+    </row>
+    <row r="132" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J132" s="10"/>
+    </row>
+    <row r="133" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J133" s="10"/>
+    </row>
+    <row r="134" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J134" s="10"/>
+    </row>
+    <row r="135" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J135" s="10"/>
+    </row>
+    <row r="136" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J136" s="10"/>
+    </row>
+    <row r="137" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J137" s="10"/>
+    </row>
+    <row r="138" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J138" s="10"/>
+    </row>
+    <row r="139" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J139" s="10"/>
+    </row>
+    <row r="140" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J140" s="10"/>
+    </row>
+    <row r="141" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J141" s="10"/>
+    </row>
+    <row r="142" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J142" s="10"/>
+    </row>
+    <row r="143" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J143" s="10"/>
+    </row>
+    <row r="144" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J144" s="10"/>
+    </row>
+    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J145" s="10"/>
+    </row>
+    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J146" s="10"/>
+    </row>
+    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J147" s="10"/>
+    </row>
+    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J148" s="10"/>
+    </row>
+    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J149" s="10"/>
+    </row>
+    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J150" s="10"/>
+    </row>
+    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J151" s="10"/>
+    </row>
+    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J152" s="10"/>
+    </row>
+    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J153" s="10"/>
+    </row>
+    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J154" s="10"/>
+    </row>
+    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J155" s="10"/>
+    </row>
+    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J156" s="10"/>
+    </row>
+    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J157" s="10"/>
+    </row>
+    <row r="158" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J158" s="10"/>
+    </row>
+    <row r="159" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J159" s="10"/>
+    </row>
+    <row r="160" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J160" s="10"/>
+    </row>
+    <row r="161" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J161" s="10"/>
+    </row>
+    <row r="162" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J162" s="10"/>
+    </row>
+    <row r="163" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J163" s="10"/>
+    </row>
+    <row r="164" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J164" s="10"/>
+    </row>
+    <row r="165" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J165" s="10"/>
+    </row>
+    <row r="166" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J166" s="10"/>
+    </row>
+    <row r="167" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J167" s="10"/>
+    </row>
+    <row r="168" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J168" s="10"/>
+    </row>
+    <row r="169" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J169" s="10"/>
+    </row>
+    <row r="170" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J170" s="10"/>
+    </row>
+    <row r="171" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J171" s="10"/>
+    </row>
+    <row r="172" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J172" s="10"/>
+    </row>
+    <row r="173" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J173" s="10"/>
+    </row>
+    <row r="174" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J174" s="10"/>
+    </row>
+    <row r="175" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J175" s="10"/>
+    </row>
+    <row r="176" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J176" s="10"/>
+    </row>
+    <row r="177" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J177" s="10"/>
+    </row>
+    <row r="178" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J178" s="10"/>
+    </row>
+    <row r="179" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J179" s="10"/>
+    </row>
+    <row r="180" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J180" s="10"/>
+    </row>
+    <row r="181" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J181" s="10"/>
+    </row>
+    <row r="182" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J182" s="10"/>
+    </row>
+    <row r="183" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J183" s="10"/>
+    </row>
+    <row r="184" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J184" s="10"/>
+    </row>
+    <row r="185" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J185" s="10"/>
+    </row>
+    <row r="186" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J186" s="10"/>
+    </row>
+    <row r="187" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J187" s="10"/>
+    </row>
+    <row r="188" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J188" s="10"/>
+    </row>
+    <row r="189" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J189" s="10"/>
+    </row>
+    <row r="190" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J190" s="10"/>
+    </row>
+    <row r="191" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J191" s="10"/>
+    </row>
+    <row r="192" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J192" s="10"/>
+    </row>
+    <row r="193" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J193" s="10"/>
+    </row>
+    <row r="194" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J194" s="10"/>
+    </row>
+    <row r="195" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J195" s="10"/>
+    </row>
+    <row r="196" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J196" s="10"/>
+    </row>
+    <row r="197" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J197" s="10"/>
+    </row>
+    <row r="198" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J198" s="10"/>
+    </row>
+    <row r="199" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J199" s="10"/>
+    </row>
+    <row r="200" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J200" s="10"/>
+    </row>
+    <row r="201" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J201" s="10"/>
+    </row>
+    <row r="202" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J202" s="10"/>
+    </row>
+    <row r="203" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J203" s="10"/>
+    </row>
+    <row r="204" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J204" s="10"/>
+    </row>
+    <row r="205" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J205" s="10"/>
+    </row>
+    <row r="206" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J206" s="10"/>
+    </row>
+    <row r="207" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J207" s="10"/>
+    </row>
+    <row r="208" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J208" s="10"/>
+    </row>
+    <row r="209" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J209" s="10"/>
+    </row>
+    <row r="210" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J210" s="10"/>
+    </row>
+    <row r="211" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J211" s="10"/>
+    </row>
+    <row r="212" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J212" s="10"/>
+    </row>
+    <row r="213" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J213" s="10"/>
+    </row>
+    <row r="214" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J214" s="10"/>
+    </row>
+    <row r="215" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J215" s="10"/>
+    </row>
+    <row r="216" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J216" s="10"/>
+    </row>
+    <row r="217" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J217" s="10"/>
+    </row>
+    <row r="218" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J218" s="10"/>
+    </row>
+    <row r="219" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J219" s="10"/>
+    </row>
+    <row r="220" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J220" s="10"/>
+    </row>
+    <row r="221" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J221" s="10"/>
+    </row>
+    <row r="222" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J222" s="10"/>
+    </row>
+    <row r="223" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J223" s="10"/>
+    </row>
+    <row r="224" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J224" s="10"/>
+    </row>
+    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J225" s="10"/>
+    </row>
+    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J226" s="10"/>
+    </row>
+    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J227" s="10"/>
+    </row>
+    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J228" s="10"/>
+    </row>
+    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J229" s="10"/>
+    </row>
+    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J230" s="10"/>
+    </row>
+    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J231" s="10"/>
+    </row>
+    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J232" s="10"/>
+    </row>
+    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J233" s="10"/>
+    </row>
+    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J234" s="10"/>
+    </row>
+    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J235" s="10"/>
+    </row>
+    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J236" s="10"/>
+    </row>
+    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J237" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">
@@ -7053,6 +7755,12 @@
       <sortCondition ref="C2:C93"/>
     </sortState>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J97">
+    <sortCondition ref="B2:B97"/>
+    <sortCondition ref="A2:A97"/>
+    <sortCondition ref="D2:D97"/>
+    <sortCondition ref="C2:C97"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82FF77B4-F2AB-2F4A-AC3F-B3D41B3F170B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{896B9106-0CD7-734A-8D40-00962C587EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1318" uniqueCount="259">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1443" uniqueCount="285">
   <si>
     <t>reviewer</t>
   </si>
@@ -810,6 +810,105 @@
   </si>
   <si>
     <t>Clients implementing this protocol will only attempt to send and request packages if agreed upon during the version handshake. [13] [14] [...] [14] Is Package Erlay possible? A client using BIP330 reconciliation-based transaction relay (Erlay) is able to use package relay [...]</t>
+  </si>
+  <si>
+    <t>Requires: 340, 341, 342</t>
+  </si>
+  <si>
+    <t>Requires: 340, 341, 342 [...] The use of "Nothing Up My Sleeve" (NUMS) points as described in BIP341 to disable the key spend-path</t>
+  </si>
+  <si>
+    <t>Requires: 340, 341, 342 [...] Our decision to reenable OP_CAT by redefining a tapscript OP_SUCCESSx opcode to OP_CAT was motivated to leverage the tapscript softfork opcode upgrade path introduced in BIP342</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BIP347 defines Tapscript, and Tapscript/Taproot validation uses Schnorr signatures, which are defined by BIP340</t>
+  </si>
+  <si>
+    <t>Requires Taproot, as OP_CAT applies only to Taproot (tapscript) outputs</t>
+  </si>
+  <si>
+    <t>BIP347 uses the tapscript OP_SUCCESSx soft fork upgrade mechanism introduced by BIP342 to redefine OP_SUCCESS126 as OP_CAT</t>
+  </si>
+  <si>
+    <t>Made compliant with BIP 3, use cases added.</t>
+  </si>
+  <si>
+    <t>This BIP proposes a standard format for encoding BIP 21 URI schemes in DNS TXT records.</t>
+  </si>
+  <si>
+    <t>Reference implementations for parsing the URI contents can be found in BIP 321.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document proposes additional fields and updated role responsibilities for BIP370 PSBTv2 which adds support for sending to silent payments as described in BIP352. </t>
+  </si>
+  <si>
+    <t>Compute the DLEQ proof for C using BIP374 GenerateProof and passing an as a and Bscan as B. [...] Using BIP374 VerifyProof and passing A as An, B as Bscan, [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sp() descriptors take silent payment key material and describe P2TR outputs when combined with sender input public keys as defined in BIP352. [...] The output scripts produced are BIP341 taproot outputs as specified in BIP352. </t>
+  </si>
+  <si>
+    <t>The spscan key expression encodes the scan private key and spend public key. It is a Bech32m encoding of [...]</t>
+  </si>
+  <si>
+    <t>Bech32m is defined in BIP350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The output scripts produced are BIP341 taproot outputs [...] The scripts produced are BIP341 taproot outputs, making them indistinguishable from other taproot outputs on-chain. </t>
+  </si>
+  <si>
+    <t>The second key expression represents the spend key and may be any key expression as defined in BIP380 or other key expression BIPs (e.g. musig() as defined in BIP390) that represents a single key, public or private. [...] sp() descriptors use the format and general operation specified in BIP380.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The second key expression represents the spend key and may be any key expression as defined in BIP380 or other key expression BIPs (e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>musig()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as defined in BIP390) that represents a single key, public or private.</t>
+    </r>
+  </si>
+  <si>
+    <t>This BIP defines a "varops budget", which generalizes the "sigops budget" introduced in BIP342 to non-signature operations. [...] The signature cost is simply carried across from the existing BIP-342 limit [...]</t>
+  </si>
+  <si>
+    <t>This BIP proposes to add consensus support for a new tapscript opcode that enables a new type of output restrictions: OP_CHECKCONTRACTVERIFY (OP_CCV).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the &lt;pk&gt; is 0, it is replaced with the NUMS x-only pubkey [...] defined in BIP-341. [...] BIP341_NUMS_KEY is the x-only provably unspendable key [...] defined in BIP-341. </t>
+  </si>
+  <si>
+    <t>OP_VAULT[2] is a proposed opcode to implement a 2-step withdrawal process, enabling on-chain reactive security. [...] [2] BIP-345</t>
+  </si>
+  <si>
+    <t>OP_CHECKTEMPLATEVERIFY[3] is a long-proposed opcode to constrain a transaction to a template with a fixed set of outputs.  [...] [3] BIP-119</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> For example, in a multi-party contract, the naked key could be an aggregate key using MuSig2</t>
+  </si>
+  <si>
+    <t>MuSig2 is definied in BIP327</t>
+  </si>
+  <si>
+    <t>BIP443 extends Taproot by constraining P2TR outputs and reuses Taproot key tweaking and internal-key semantics defined in BIP341</t>
+  </si>
+  <si>
+    <t>BIP443 introduces OP_CHECKCONTRACTVERIFY by redefining the tapscript opcode OP_SUCCESS187, using the tapscript opcode upgrade mechanism defined in BIP342</t>
   </si>
 </sst>
 </file>
@@ -819,7 +918,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -967,6 +1066,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="35">
@@ -3613,6 +3718,9 @@
       <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D38" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E38" s="7" t="s">
         <v>17</v>
       </c>
@@ -3660,6 +3768,9 @@
       <c r="C39" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D39" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E39" s="7" t="s">
         <v>17</v>
       </c>
@@ -3707,6 +3818,9 @@
       <c r="C40" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D40" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E40" s="7" t="s">
         <v>17</v>
       </c>
@@ -3754,6 +3868,9 @@
       <c r="C41" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D41" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E41" s="7" t="s">
         <v>17</v>
       </c>
@@ -3801,6 +3918,9 @@
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="D42" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="E42" s="7" t="s">
         <v>17</v>
       </c>
@@ -3847,6 +3967,9 @@
       </c>
       <c r="C43" s="7" t="s">
         <v>15</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>17</v>
@@ -7344,79 +7467,596 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J104" s="10"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J105" s="10"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J106" s="10"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J107" s="10"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J108" s="10"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J109" s="10"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J110" s="10"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J111" s="10"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J112" s="10"/>
-    </row>
-    <row r="113" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J113" s="10"/>
-    </row>
-    <row r="114" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J114" s="10"/>
-    </row>
-    <row r="115" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J115" s="10"/>
-    </row>
-    <row r="116" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J116" s="10"/>
-    </row>
-    <row r="117" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J117" s="10"/>
-    </row>
-    <row r="118" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J118" s="10"/>
-    </row>
-    <row r="119" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J119" s="10"/>
-    </row>
-    <row r="120" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J120" s="10"/>
-    </row>
-    <row r="121" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J121" s="10"/>
-    </row>
-    <row r="122" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J122" s="10"/>
-    </row>
-    <row r="123" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J123" s="10"/>
-    </row>
-    <row r="124" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B104" s="3">
+        <v>347</v>
+      </c>
+      <c r="D104" s="3">
+        <v>340</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B105" s="3">
+        <v>347</v>
+      </c>
+      <c r="D105" s="3">
+        <v>341</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B106" s="3">
+        <v>347</v>
+      </c>
+      <c r="D106" s="3">
+        <v>342</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J106" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B107" s="3">
+        <v>347</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D107" s="3">
+        <v>3</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J107" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B108" s="3">
+        <v>353</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D108" s="3">
+        <v>21</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B109" s="3">
+        <v>353</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D109" s="3">
+        <v>321</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J109" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B110" s="3">
+        <v>375</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D110" s="3">
+        <v>370</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J110" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" s="3">
+        <v>375</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D111" s="3">
+        <v>352</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J111" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B112" s="3">
+        <v>375</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" s="3">
+        <v>374</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J112" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A113" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B113" s="3">
+        <v>392</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" s="3">
+        <v>352</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J113" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B114" s="3">
+        <v>392</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D114" s="3">
+        <v>341</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B115" s="3">
+        <v>392</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" s="3">
+        <v>350</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J115" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B116" s="3">
+        <v>392</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D116" s="3">
+        <v>380</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J116" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B117" s="3">
+        <v>392</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D117" s="3">
+        <v>390</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J117" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B118" s="3">
+        <v>440</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D118" s="3">
+        <v>342</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J118" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119" s="3">
+        <v>443</v>
+      </c>
+      <c r="D119" s="3">
+        <v>342</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J119" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A120" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B120" s="3">
+        <v>443</v>
+      </c>
+      <c r="D120" s="3">
+        <v>341</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J120" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B121" s="3">
+        <v>443</v>
+      </c>
+      <c r="D121" s="3">
+        <v>345</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J121" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B122" s="3">
+        <v>443</v>
+      </c>
+      <c r="D122" s="3">
+        <v>119</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B123" s="3">
+        <v>443</v>
+      </c>
+      <c r="D123" s="3">
+        <v>327</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J123" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J124" s="10"/>
     </row>
-    <row r="125" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J125" s="10"/>
     </row>
-    <row r="126" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J126" s="10"/>
     </row>
-    <row r="127" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J127" s="10"/>
     </row>
-    <row r="128" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J128" s="10"/>
     </row>
     <row r="129" spans="10:10" x14ac:dyDescent="0.2">

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{896B9106-0CD7-734A-8D40-00962C587EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9E94DD37-0E43-C44F-8C17-496CC1576E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1443" uniqueCount="285">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1465" uniqueCount="289">
   <si>
     <t>reviewer</t>
   </si>
@@ -840,9 +840,6 @@
   </si>
   <si>
     <t xml:space="preserve">This document proposes additional fields and updated role responsibilities for BIP370 PSBTv2 which adds support for sending to silent payments as described in BIP352. </t>
-  </si>
-  <si>
-    <t>Compute the DLEQ proof for C using BIP374 GenerateProof and passing an as a and Bscan as B. [...] Using BIP374 VerifyProof and passing A as An, B as Bscan, [...]</t>
   </si>
   <si>
     <t xml:space="preserve">sp() descriptors take silent payment key material and describe P2TR outputs when combined with sender input public keys as defined in BIP352. [...] The output scripts produced are BIP341 taproot outputs as specified in BIP352. </t>
@@ -909,6 +906,21 @@
   </si>
   <si>
     <t>BIP443 introduces OP_CHECKCONTRACTVERIFY by redefining the tapscript opcode OP_SUCCESS187, using the tapscript opcode upgrade mechanism defined in BIP342</t>
+  </si>
+  <si>
+    <t>On-chain addresses which are re-used (i.e. not including schemes like Silent Payments) need to be rotated to avoid contributing substantially to address reuse.</t>
+  </si>
+  <si>
+    <t>Silent payments are defined in BIP352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compute the DLEQ proof for C using BIP374 GenerateProof and passing an as a and Bscan as B. [...] Using BIP374 VerifyProof and passing A as An, B as Bscan, [...] </t>
+  </si>
+  <si>
+    <t>The updater should add a PSBT_IN_BIP32_DERIVATION for any p2wpkh, p2sh-p2wpkh, or p2pkh input [...] Updaters may add two PSBT_OUT_BIP32_DERIVATION key-value-pairs with the corresponding derivation path [...]</t>
+  </si>
+  <si>
+    <t>BIP375 references BIP32 derivation metadata (PSBT_IN_BIP32_DERIVATION and PSBT_OUT_BIP32_DERIVATION) to identify keys and verify silent payment change outputs (metadata named after BIP32)</t>
   </si>
 </sst>
 </file>
@@ -4337,7 +4349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J239"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7474,6 +7486,9 @@
       <c r="B104" s="3">
         <v>347</v>
       </c>
+      <c r="C104" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D104" s="3">
         <v>340</v>
       </c>
@@ -7503,6 +7518,9 @@
       <c r="B105" s="3">
         <v>347</v>
       </c>
+      <c r="C105" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D105" s="3">
         <v>341</v>
       </c>
@@ -7532,6 +7550,9 @@
       <c r="B106" s="3">
         <v>347</v>
       </c>
+      <c r="C106" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D106" s="3">
         <v>342</v>
       </c>
@@ -7646,22 +7667,25 @@
         <v>219</v>
       </c>
       <c r="B110" s="3">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D110" s="3">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>268</v>
+        <v>284</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -7681,7 +7705,7 @@
         <v>219</v>
       </c>
       <c r="D111" s="3">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>118</v>
@@ -7710,7 +7734,7 @@
         <v>219</v>
       </c>
       <c r="D112" s="3">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>118</v>
@@ -7719,7 +7743,7 @@
         <v>37</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -7728,18 +7752,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B113" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D113" s="3">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>118</v>
@@ -7748,7 +7772,7 @@
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -7757,27 +7781,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B114" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D114" s="3">
-        <v>341</v>
+        <v>32</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>273</v>
+        <v>287</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>288</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -7786,7 +7813,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>219</v>
       </c>
@@ -7797,7 +7824,7 @@
         <v>219</v>
       </c>
       <c r="D115" s="3">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>118</v>
@@ -7806,10 +7833,7 @@
         <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -7818,7 +7842,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>219</v>
       </c>
@@ -7829,7 +7853,7 @@
         <v>219</v>
       </c>
       <c r="D116" s="3">
-        <v>380</v>
+        <v>341</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>118</v>
@@ -7838,7 +7862,7 @@
         <v>37</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -7847,7 +7871,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>219</v>
       </c>
@@ -7858,16 +7882,19 @@
         <v>219</v>
       </c>
       <c r="D117" s="3">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>275</v>
+        <v>270</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -7876,27 +7903,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B118" s="3">
-        <v>440</v>
+        <v>392</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D118" s="3">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -7905,27 +7932,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="69" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B119" s="3">
-        <v>443</v>
+        <v>392</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="D119" s="3">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -7934,27 +7961,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B120" s="3">
-        <v>443</v>
+        <v>440</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>219</v>
       </c>
       <c r="D120" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -7963,24 +7990,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B121" s="3">
         <v>443</v>
       </c>
+      <c r="C121" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D121" s="3">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -7996,17 +8029,23 @@
       <c r="B122" s="3">
         <v>443</v>
       </c>
+      <c r="C122" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D122" s="3">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -8022,20 +8061,20 @@
       <c r="B123" s="3">
         <v>443</v>
       </c>
+      <c r="C123" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="D123" s="3">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -8044,11 +8083,66 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J124" s="10"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J125" s="10"/>
+    <row r="124" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A124" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B124" s="3">
+        <v>443</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D124" s="3">
+        <v>119</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J124" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A125" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B125" s="3">
+        <v>443</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D125" s="3">
+        <v>327</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J125" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="J126" s="10"/>
@@ -8385,6 +8479,12 @@
     </row>
     <row r="237" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J237" s="10"/>
+    </row>
+    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J238" s="10"/>
+    </row>
+    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J239" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9E94DD37-0E43-C44F-8C17-496CC1576E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3C382419-C4E6-B641-B399-AB210D290C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1465" uniqueCount="289">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2102" uniqueCount="403">
   <si>
     <t>reviewer</t>
   </si>
@@ -921,6 +921,348 @@
   </si>
   <si>
     <t>BIP375 references BIP32 derivation metadata (PSBT_IN_BIP32_DERIVATION and PSBT_OUT_BIP32_DERIVATION) to identify keys and verify silent payment change outputs (metadata named after BIP32)</t>
+  </si>
+  <si>
+    <t>all_methods</t>
+  </si>
+  <si>
+    <t>M-of-N Standard Transactions</t>
+  </si>
+  <si>
+    <t>2012-01-18</t>
+  </si>
+  <si>
+    <t>OP_CHECKHASHVERIFY (CHV)</t>
+  </si>
+  <si>
+    <t>2012-01-30</t>
+  </si>
+  <si>
+    <t>M-of-N Standard Transactions (Low SigOp)</t>
+  </si>
+  <si>
+    <t>2012-01-29</t>
+  </si>
+  <si>
+    <t>2012-07-06</t>
+  </si>
+  <si>
+    <t>Block v2, Height in Coinbase</t>
+  </si>
+  <si>
+    <t>2012-08-16</t>
+  </si>
+  <si>
+    <t>mempool message</t>
+  </si>
+  <si>
+    <t>2012-10-24</t>
+  </si>
+  <si>
+    <t>Connection Bloom filtering</t>
+  </si>
+  <si>
+    <t>2021-05-13</t>
+  </si>
+  <si>
+    <t>Consensus (hard fork)</t>
+  </si>
+  <si>
+    <t>Durable, Low Energy Bitcoin PoW</t>
+  </si>
+  <si>
+    <t>2014-06-10</t>
+  </si>
+  <si>
+    <t>getutxo message</t>
+  </si>
+  <si>
+    <t>2025-12-03</t>
+  </si>
+  <si>
+    <t>Chain Code Delegation</t>
+  </si>
+  <si>
+    <t>2017-08-24</t>
+  </si>
+  <si>
+    <t>Fast Merkle Trees</t>
+  </si>
+  <si>
+    <t>2015-06-23</t>
+  </si>
+  <si>
+    <t>Block size increase to 2MB</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>'Block75' - Max block size like difficulty</t>
+  </si>
+  <si>
+    <t>2015-08-21</t>
+  </si>
+  <si>
+    <t>Consensus based block size retargeting algorithm</t>
+  </si>
+  <si>
+    <t>2015-09-11</t>
+  </si>
+  <si>
+    <t>Dynamic limit on the block size</t>
+  </si>
+  <si>
+    <t>2016-09-23</t>
+  </si>
+  <si>
+    <t>Generic anti-replay protection using Script</t>
+  </si>
+  <si>
+    <t>2015-12-04</t>
+  </si>
+  <si>
+    <t>Opt-in Full Replace-by-Fee Signaling</t>
+  </si>
+  <si>
+    <t>2019-01-28</t>
+  </si>
+  <si>
+    <t>Simple Proof-of-Reserves Transactions</t>
+  </si>
+  <si>
+    <t>2015-12-21</t>
+  </si>
+  <si>
+    <t>Segregated Witness (Consensus layer)</t>
+  </si>
+  <si>
+    <t>2017-03-12</t>
+  </si>
+  <si>
+    <t>Mandatory activation of segwit deployment</t>
+  </si>
+  <si>
+    <t>2017-05-11</t>
+  </si>
+  <si>
+    <t>NODE_NETWORK_LIMITED service bit</t>
+  </si>
+  <si>
+    <t>2017-03-04</t>
+  </si>
+  <si>
+    <t>Currency/exchange rate information API</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>Hashed Time-Locked Contract transactions</t>
+  </si>
+  <si>
+    <t>2017-08-14</t>
+  </si>
+  <si>
+    <t>Hashrate Escrows (Consensus layer)</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
+  </si>
+  <si>
+    <t>Compressed Transactions</t>
+  </si>
+  <si>
+    <t>2020-01-19</t>
+  </si>
+  <si>
+    <t>Taproot: SegWit version 1 spending rules</t>
+  </si>
+  <si>
+    <t>2021-04-25</t>
+  </si>
+  <si>
+    <t>Mandatory activation of taproot deployment</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>PSBT Version 2</t>
+  </si>
+  <si>
+    <t>2021-06-21</t>
+  </si>
+  <si>
+    <t>Taproot Fields for PSBT</t>
+  </si>
+  <si>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>Dust UTXO Disposal Protocol</t>
+  </si>
+  <si>
+    <t>Address Format for pay-to-script-hash</t>
+  </si>
+  <si>
+    <t>getblocktemplate - Pooled Mining</t>
+  </si>
+  <si>
+    <t>2012-05-15</t>
+  </si>
+  <si>
+    <t>Stratized Nodes</t>
+  </si>
+  <si>
+    <t>2014-04-01</t>
+  </si>
+  <si>
+    <t>A finite monetary supply for Bitcoin</t>
+  </si>
+  <si>
+    <t>2022-04-01</t>
+  </si>
+  <si>
+    <t>Address Scheme for Timelocked Fidelity Bonds</t>
+  </si>
+  <si>
+    <t>2014-06-18</t>
+  </si>
+  <si>
+    <t>Reject P2P message</t>
+  </si>
+  <si>
+    <t>2014-03-12</t>
+  </si>
+  <si>
+    <t>Dealing with malleability</t>
+  </si>
+  <si>
+    <t>2015-01-10</t>
+  </si>
+  <si>
+    <t>Strict DER signatures</t>
+  </si>
+  <si>
+    <t>2015-02-08</t>
+  </si>
+  <si>
+    <t>Deterministic Pay-to-script-hash multi-signature addresses through public key sorting</t>
+  </si>
+  <si>
+    <t>2013-07-29</t>
+  </si>
+  <si>
+    <t>Payment Protocol MIME types</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>Hierarchy for Deterministic Multisig Wallets</t>
+  </si>
+  <si>
+    <t>2017-05-22</t>
+  </si>
+  <si>
+    <t>Reduced threshold Segwit MASF</t>
+  </si>
+  <si>
+    <t>2015-06-11</t>
+  </si>
+  <si>
+    <t>Dynamic maximum block size by miner vote</t>
+  </si>
+  <si>
+    <t>2015-07-21</t>
+  </si>
+  <si>
+    <t>Block size following technological growth</t>
+  </si>
+  <si>
+    <t>2017-08-25</t>
+  </si>
+  <si>
+    <t>Tail Call Execution Semantics</t>
+  </si>
+  <si>
+    <t>2015-05-08</t>
+  </si>
+  <si>
+    <t>sendheaders message</t>
+  </si>
+  <si>
+    <t>2015-11-30</t>
+  </si>
+  <si>
+    <t>"Coalescing Transaction" Specification (wildcard inputs)</t>
+  </si>
+  <si>
+    <t>2016-02-13</t>
+  </si>
+  <si>
+    <t>feefilter message</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>Flexible Transactions</t>
+  </si>
+  <si>
+    <t>2019-02-16</t>
+  </si>
+  <si>
+    <t>Signatures of Messages using Private Keys</t>
+  </si>
+  <si>
+    <t>2016-01-08</t>
+  </si>
+  <si>
+    <t>Segregated Witness (Peer Services)</t>
+  </si>
+  <si>
+    <t>2016-09-02</t>
+  </si>
+  <si>
+    <t>Dealing with dummy stack element malleability</t>
+  </si>
+  <si>
+    <t>2016-03-23</t>
+  </si>
+  <si>
+    <t>Peer Authentication</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>Partially Signed Bitcoin Transaction Format</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>Blind Merged Mining (Consensus layer)</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>24 nVersion bits for general purpose use</t>
+  </si>
+  <si>
+    <t>2024-12-26</t>
+  </si>
+  <si>
+    <t>Discrete Log Equality Proofs</t>
+  </si>
+  <si>
+    <t>2024-12-09</t>
+  </si>
+  <si>
+    <t>OP_PAIRCOMMIT</t>
   </si>
 </sst>
 </file>
@@ -1439,7 +1781,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1470,6 +1812,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1989,14 +2337,8 @@
       <c r="A3" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B3" s="3">
-        <v>12</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
+      <c r="B3" s="11">
+        <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>17</v>
@@ -2004,35 +2346,35 @@
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="12">
         <v>42</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="7">
-        <v>1</v>
+        <v>290</v>
+      </c>
+      <c r="P3" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -2040,7 +2382,7 @@
         <v>219</v>
       </c>
       <c r="B4" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -2061,28 +2403,28 @@
         <v>19</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -2090,34 +2432,28 @@
         <v>219</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G5" s="12">
+        <v>42</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>29</v>
@@ -2126,10 +2462,13 @@
         <v>24</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>36</v>
+        <v>349</v>
+      </c>
+      <c r="P5" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
@@ -2137,7 +2476,7 @@
         <v>219</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
@@ -2158,28 +2497,28 @@
         <v>19</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="P6" s="7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -2187,96 +2526,90 @@
         <v>219</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M7" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="3">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>219</v>
+      </c>
+      <c r="B8" s="11">
+        <v>17</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G8" s="12">
+        <v>42</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="8" t="d">
-        <v>2019-06-25</v>
+        <v>289</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>223</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>224</v>
+        <v>24</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>226</v>
+        <v>292</v>
+      </c>
+      <c r="P8" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
@@ -2284,13 +2617,13 @@
         <v>219</v>
       </c>
       <c r="B9" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>17</v>
@@ -2305,42 +2638,36 @@
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P9" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="3">
-        <v>30</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
+      <c r="B10" s="11">
+        <v>19</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>17</v>
@@ -2348,35 +2675,35 @@
       <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="12">
         <v>42</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>48</v>
+        <v>293</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="P10" s="7">
-        <v>0</v>
+        <v>294</v>
+      </c>
+      <c r="P10" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -2384,87 +2711,81 @@
         <v>219</v>
       </c>
       <c r="B11" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G11" s="7">
+        <v>42</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="P11" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="3">
-        <v>39</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>50</v>
+      <c r="B12" s="11">
+        <v>21</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G12" s="12">
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>53</v>
+        <v>295</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>24</v>
@@ -2473,10 +2794,10 @@
         <v>42</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12" s="7">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="P12" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
@@ -2484,7 +2805,7 @@
         <v>222</v>
       </c>
       <c r="B13" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -2511,7 +2832,7 @@
         <v>34</v>
       </c>
       <c r="K13" s="8" t="d">
-        <v>2017-12-18</v>
+        <v>2019-06-25</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>223</v>
@@ -2523,7 +2844,7 @@
         <v>34</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -2531,34 +2852,34 @@
         <v>219</v>
       </c>
       <c r="B14" s="3">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G14" s="7">
+        <v>42</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>29</v>
@@ -2567,13 +2888,13 @@
         <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="P14" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -2581,13 +2902,7 @@
         <v>219</v>
       </c>
       <c r="B15" s="3">
-        <v>44</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>17</v>
@@ -2595,7 +2910,7 @@
       <c r="F15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="12">
         <v>42</v>
       </c>
       <c r="H15" s="7" t="s">
@@ -2605,10 +2920,10 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>29</v>
@@ -2617,60 +2932,63 @@
         <v>24</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>57</v>
+        <v>350</v>
       </c>
       <c r="P15" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B16" s="3">
+        <v>30</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G16" s="7">
+        <v>42</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K16" s="8" t="d">
-        <v>2014-07-09</v>
+        <v>21</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>224</v>
+        <v>24</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>229</v>
+        <v>49</v>
+      </c>
+      <c r="P16" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -2678,34 +2996,34 @@
         <v>219</v>
       </c>
       <c r="B17" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>29</v>
@@ -2714,13 +3032,13 @@
         <v>24</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="P17" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -2728,13 +3046,7 @@
         <v>219</v>
       </c>
       <c r="B18" s="3">
-        <v>73</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>17</v>
@@ -2742,7 +3054,7 @@
       <c r="F18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="12">
         <v>42</v>
       </c>
       <c r="H18" s="7" t="s">
@@ -2752,22 +3064,22 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>61</v>
+        <v>351</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>62</v>
+        <v>352</v>
       </c>
       <c r="P18" s="7">
         <v>1</v>
@@ -2777,14 +3089,8 @@
       <c r="A19" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B19" s="3">
-        <v>74</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>44</v>
+      <c r="B19" s="11">
+        <v>34</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>17</v>
@@ -2792,120 +3098,108 @@
       <c r="F19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="12">
         <v>42</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>63</v>
+        <v>296</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P19" s="7">
-        <v>1</v>
+        <v>297</v>
+      </c>
+      <c r="P19" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B20" s="3">
-        <v>77</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>50</v>
+      <c r="B20" s="11">
+        <v>35</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G20" s="12">
+        <v>42</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>65</v>
+        <v>298</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="P20" s="7">
-        <v>7</v>
+        <v>299</v>
+      </c>
+      <c r="P20" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="3">
-        <v>78</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>50</v>
+      <c r="B21" s="11">
+        <v>37</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G21" s="12">
+        <v>42</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>29</v>
@@ -2914,13 +3208,13 @@
         <v>24</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="P21" s="7">
-        <v>3</v>
+        <v>301</v>
+      </c>
+      <c r="P21" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -2928,34 +3222,34 @@
         <v>219</v>
       </c>
       <c r="B22" s="3">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>29</v>
@@ -2964,10 +3258,10 @@
         <v>24</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="P22" s="7">
         <v>1</v>
@@ -2975,52 +3269,49 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B23" s="3">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="K23" s="8" t="d">
+        <v>2017-12-18</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>24</v>
+        <v>224</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="P23" s="7">
-        <v>4</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -3028,13 +3319,7 @@
         <v>219</v>
       </c>
       <c r="B24" s="3">
-        <v>113</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>17</v>
@@ -3042,7 +3327,7 @@
       <c r="F24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="12">
         <v>42</v>
       </c>
       <c r="H24" s="7" t="s">
@@ -3052,10 +3337,10 @@
         <v>37</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>72</v>
+        <v>353</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>29</v>
@@ -3067,10 +3352,10 @@
         <v>25</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>74</v>
+        <v>354</v>
       </c>
       <c r="P24" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -3078,49 +3363,49 @@
         <v>219</v>
       </c>
       <c r="B25" s="3">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="P25" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
@@ -3128,13 +3413,13 @@
         <v>219</v>
       </c>
       <c r="B26" s="3">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>17</v>
@@ -3146,81 +3431,78 @@
         <v>42</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="P26" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B27" s="3">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>79</v>
+        <v>34</v>
+      </c>
+      <c r="K27" s="8" t="d">
+        <v>2014-07-09</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>24</v>
+        <v>224</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="P27" s="7">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
@@ -3228,13 +3510,7 @@
         <v>219</v>
       </c>
       <c r="B28" s="3">
-        <v>128</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>17</v>
@@ -3242,7 +3518,7 @@
       <c r="F28" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="12">
         <v>42</v>
       </c>
       <c r="H28" s="7" t="s">
@@ -3252,10 +3528,10 @@
         <v>37</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>66</v>
@@ -3267,10 +3543,10 @@
         <v>42</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="P28" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
@@ -3278,13 +3554,13 @@
         <v>219</v>
       </c>
       <c r="B29" s="3">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>17</v>
@@ -3299,16 +3575,16 @@
         <v>58</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>24</v>
@@ -3317,24 +3593,18 @@
         <v>42</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="P29" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="3">
-        <v>145</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>32</v>
+      <c r="B30" s="11">
+        <v>52</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>17</v>
@@ -3342,35 +3612,35 @@
       <c r="F30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="12">
         <v>42</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>86</v>
+        <v>302</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>46</v>
+        <v>303</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="P30" s="7">
-        <v>4</v>
+        <v>304</v>
+      </c>
+      <c r="P30" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
@@ -3378,13 +3648,7 @@
         <v>219</v>
       </c>
       <c r="B31" s="3">
-        <v>158</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>17</v>
@@ -3392,20 +3656,20 @@
       <c r="F31" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="12">
         <v>42</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>88</v>
+        <v>357</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>29</v>
@@ -3417,10 +3681,10 @@
         <v>30</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>89</v>
+        <v>358</v>
       </c>
       <c r="P31" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
@@ -3428,13 +3692,7 @@
         <v>219</v>
       </c>
       <c r="B32" s="3">
-        <v>197</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>17</v>
@@ -3442,32 +3700,32 @@
       <c r="F32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="12">
         <v>42</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>90</v>
+        <v>359</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>91</v>
+        <v>360</v>
       </c>
       <c r="P32" s="7">
         <v>1</v>
@@ -3477,14 +3735,8 @@
       <c r="A33" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B33" s="3">
-        <v>320</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>32</v>
+      <c r="B33" s="11">
+        <v>64</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>17</v>
@@ -3492,32 +3744,35 @@
       <c r="F33" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="12">
         <v>42</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>92</v>
+        <v>305</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="N33" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="O33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P33" s="7">
-        <v>0</v>
+        <v>306</v>
+      </c>
+      <c r="P33" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
@@ -3525,49 +3780,43 @@
         <v>219</v>
       </c>
       <c r="B34" s="3">
-        <v>321</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G34" s="12">
+        <v>42</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>94</v>
+        <v>361</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
       <c r="P34" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
@@ -3575,46 +3824,40 @@
         <v>219</v>
       </c>
       <c r="B35" s="3">
-        <v>324</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G35" s="12">
+        <v>42</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>95</v>
+        <v>363</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>96</v>
+        <v>364</v>
       </c>
       <c r="P35" s="7">
         <v>3</v>
@@ -3625,13 +3868,7 @@
         <v>219</v>
       </c>
       <c r="B36" s="3">
-        <v>330</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>17</v>
@@ -3639,32 +3876,32 @@
       <c r="F36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="12">
         <v>42</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>27</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>97</v>
+        <v>365</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="P36" s="7">
         <v>0</v>
@@ -3675,13 +3912,13 @@
         <v>219</v>
       </c>
       <c r="B37" s="3">
-        <v>331</v>
+        <v>73</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>17</v>
@@ -3693,7 +3930,7 @@
         <v>42</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>20</v>
@@ -3702,22 +3939,22 @@
         <v>21</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M37" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="P37" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
@@ -3725,13 +3962,13 @@
         <v>219</v>
       </c>
       <c r="B38" s="3">
-        <v>347</v>
+        <v>74</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>17</v>
@@ -3743,31 +3980,31 @@
         <v>42</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="M38" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="P38" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
@@ -3775,37 +4012,37 @@
         <v>219</v>
       </c>
       <c r="B39" s="3">
-        <v>353</v>
+        <v>77</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="M39" s="7" t="s">
         <v>24</v>
@@ -3814,10 +4051,10 @@
         <v>42</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="P39" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
@@ -3825,37 +4062,37 @@
         <v>219</v>
       </c>
       <c r="B40" s="3">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>24</v>
@@ -3864,10 +4101,10 @@
         <v>42</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="P40" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
@@ -3875,13 +4112,7 @@
         <v>219</v>
       </c>
       <c r="B41" s="3">
-        <v>392</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>17</v>
@@ -3889,23 +4120,23 @@
       <c r="F41" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="12">
         <v>42</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>107</v>
+        <v>367</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>24</v>
@@ -3914,24 +4145,18 @@
         <v>42</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>108</v>
+        <v>368</v>
       </c>
       <c r="P41" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B42" s="3">
-        <v>440</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>32</v>
+      <c r="B42" s="11">
+        <v>89</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>17</v>
@@ -3939,20 +4164,20 @@
       <c r="F42" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="12">
         <v>42</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>81</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>109</v>
+        <v>307</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>66</v>
@@ -3961,13 +4186,13 @@
         <v>24</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="P42" s="7">
-        <v>1</v>
+        <v>308</v>
+      </c>
+      <c r="P42" s="12">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
@@ -3975,13 +4200,7 @@
         <v>219</v>
       </c>
       <c r="B43" s="3">
-        <v>443</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>17</v>
@@ -3989,23 +4208,23 @@
       <c r="F43" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="12">
         <v>42</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>111</v>
+        <v>369</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>24</v>
@@ -4014,285 +4233,2731 @@
         <v>25</v>
       </c>
       <c r="O43" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P43" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B44" s="11">
+        <v>98</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="12">
+        <v>42</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="P44" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="12">
+        <v>42</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="P45" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="11">
+        <v>102</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="12">
+        <v>42</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="P46" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" s="3">
+        <v>103</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="12">
+        <v>42</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="P47" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B48" s="11">
+        <v>104</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="12">
+        <v>42</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="P48" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="11">
+        <v>105</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="12">
+        <v>42</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="P49" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="11">
+        <v>107</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="12">
+        <v>42</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="P50" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="3">
+        <v>111</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="7">
+        <v>42</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B52" s="3">
         <v>112</v>
       </c>
-      <c r="P43" s="7">
+      <c r="C52" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="7">
+        <v>42</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P52" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="3">
+        <v>113</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="7">
+        <v>42</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P53" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B54" s="3">
+        <v>114</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="7">
+        <v>42</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P54" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="11">
+        <v>115</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="12">
+        <v>42</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="P55" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="3">
+        <v>117</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="12">
+        <v>42</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="P56" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="3">
+        <v>119</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="7">
+        <v>42</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P57" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="3">
+        <v>122</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="7">
+        <v>42</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P58" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F44" s="8"/>
-      <c r="K44" s="8"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F45" s="8"/>
-      <c r="K45" s="8"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F46" s="8"/>
-      <c r="K46" s="8"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F47" s="8"/>
-      <c r="K47" s="8"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F48" s="8"/>
-      <c r="K48" s="8"/>
-    </row>
-    <row r="49" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F49" s="8"/>
-      <c r="K49" s="8"/>
-    </row>
-    <row r="50" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F50" s="8"/>
-      <c r="K50" s="8"/>
-    </row>
-    <row r="51" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F51" s="8"/>
-      <c r="K51" s="8"/>
-    </row>
-    <row r="52" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F52" s="8"/>
-      <c r="K52" s="8"/>
-    </row>
-    <row r="53" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F53" s="8"/>
-      <c r="K53" s="8"/>
-    </row>
-    <row r="54" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F54" s="8"/>
-      <c r="K54" s="8"/>
-    </row>
-    <row r="55" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F55" s="8"/>
-      <c r="K55" s="8"/>
-    </row>
-    <row r="56" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F56" s="8"/>
-      <c r="K56" s="8"/>
-    </row>
-    <row r="57" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F57" s="8"/>
-      <c r="K57" s="8"/>
-    </row>
-    <row r="58" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F58" s="8"/>
-      <c r="K58" s="8"/>
-    </row>
-    <row r="59" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F59" s="8"/>
-      <c r="K59" s="8"/>
-    </row>
-    <row r="60" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F60" s="8"/>
-      <c r="K60" s="8"/>
-    </row>
-    <row r="61" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F61" s="8"/>
-      <c r="K61" s="8"/>
-    </row>
-    <row r="62" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F62" s="8"/>
-      <c r="K62" s="8"/>
-    </row>
-    <row r="63" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F63" s="8"/>
-      <c r="K63" s="8"/>
-    </row>
-    <row r="64" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F64" s="8"/>
-      <c r="K64" s="8"/>
-    </row>
-    <row r="65" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F65" s="8"/>
-      <c r="K65" s="8"/>
-    </row>
-    <row r="66" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F66" s="8"/>
-      <c r="K66" s="8"/>
-    </row>
-    <row r="67" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F67" s="8"/>
-      <c r="K67" s="8"/>
-    </row>
-    <row r="68" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F68" s="8"/>
-      <c r="K68" s="8"/>
-    </row>
-    <row r="69" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F69" s="8"/>
-      <c r="K69" s="8"/>
-    </row>
-    <row r="70" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F70" s="8"/>
-      <c r="K70" s="8"/>
-    </row>
-    <row r="71" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F71" s="8"/>
-      <c r="K71" s="8"/>
-    </row>
-    <row r="72" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F72" s="8"/>
-      <c r="K72" s="8"/>
-    </row>
-    <row r="73" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F73" s="8"/>
-      <c r="K73" s="8"/>
-    </row>
-    <row r="74" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F74" s="8"/>
-      <c r="K74" s="8"/>
-    </row>
-    <row r="75" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F75" s="8"/>
-      <c r="K75" s="8"/>
-    </row>
-    <row r="76" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F76" s="8"/>
-      <c r="K76" s="8"/>
-    </row>
-    <row r="77" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F77" s="8"/>
-      <c r="K77" s="8"/>
-    </row>
-    <row r="78" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F78" s="8"/>
-      <c r="K78" s="8"/>
-    </row>
-    <row r="79" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F79" s="8"/>
-      <c r="K79" s="8"/>
-    </row>
-    <row r="80" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F80" s="8"/>
-      <c r="K80" s="8"/>
-    </row>
-    <row r="81" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F81" s="8"/>
-      <c r="K81" s="8"/>
-    </row>
-    <row r="82" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F82" s="8"/>
-      <c r="K82" s="8"/>
-    </row>
-    <row r="83" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F83" s="8"/>
-      <c r="K83" s="8"/>
-    </row>
-    <row r="84" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F84" s="8"/>
-      <c r="K84" s="8"/>
-    </row>
-    <row r="85" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F85" s="8"/>
-      <c r="K85" s="8"/>
-    </row>
-    <row r="86" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F86" s="8"/>
-      <c r="K86" s="8"/>
-    </row>
-    <row r="87" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F87" s="8"/>
-      <c r="K87" s="8"/>
-    </row>
-    <row r="88" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F88" s="8"/>
-      <c r="K88" s="8"/>
-    </row>
-    <row r="89" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F89" s="8"/>
-      <c r="K89" s="8"/>
-    </row>
-    <row r="90" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F90" s="8"/>
-      <c r="K90" s="8"/>
-    </row>
-    <row r="91" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F91" s="8"/>
-      <c r="K91" s="8"/>
-    </row>
-    <row r="92" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F92" s="8"/>
-      <c r="K92" s="8"/>
-    </row>
-    <row r="93" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F93" s="8"/>
-      <c r="K93" s="8"/>
-    </row>
-    <row r="94" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F94" s="8"/>
-      <c r="K94" s="8"/>
-    </row>
-    <row r="95" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F95" s="8"/>
-      <c r="K95" s="8"/>
-    </row>
-    <row r="96" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F96" s="8"/>
-      <c r="K96" s="8"/>
-    </row>
-    <row r="97" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F97" s="8"/>
-      <c r="K97" s="8"/>
-    </row>
-    <row r="98" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F98" s="8"/>
-      <c r="K98" s="8"/>
-    </row>
-    <row r="99" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F99" s="8"/>
-      <c r="K99" s="8"/>
-    </row>
-    <row r="100" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F100" s="8"/>
-      <c r="K100" s="8"/>
-    </row>
-    <row r="101" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F101" s="8"/>
-      <c r="K101" s="8"/>
-    </row>
-    <row r="102" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B59" s="11">
+        <v>125</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="12">
+        <v>42</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P59" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="11">
+        <v>127</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="12">
+        <v>42</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="P60" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" s="3">
+        <v>128</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="7">
+        <v>42</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P61" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="3">
+        <v>130</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="12">
+        <v>42</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="P62" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="3">
+        <v>131</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" s="12">
+        <v>42</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="P63" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="3">
+        <v>133</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="12">
+        <v>42</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="P64" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" s="3">
+        <v>134</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="12">
+        <v>42</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="P65" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" s="3">
+        <v>137</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="12">
+        <v>42</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="L66" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="P66" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" s="11">
+        <v>141</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="12">
+        <v>42</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="P67" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B68" s="3">
+        <v>142</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="7">
+        <v>42</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P68" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B69" s="3">
+        <v>144</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" s="12">
+        <v>42</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="P69" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" s="3">
+        <v>145</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" s="7">
+        <v>42</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P70" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B71" s="3">
+        <v>147</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="12">
+        <v>42</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="L71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="P71" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B72" s="11">
+        <v>148</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" s="12">
+        <v>42</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="P72" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" s="3">
+        <v>150</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" s="12">
+        <v>42</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="L73" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="P73" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" s="3">
+        <v>158</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" s="7">
+        <v>42</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I74" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P74" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" s="11">
+        <v>159</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" s="12">
+        <v>42</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="L75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="P75" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" s="11">
+        <v>171</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" s="12">
+        <v>42</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="P76" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" s="3">
+        <v>174</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" s="12">
+        <v>42</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="P77" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B78" s="3">
+        <v>197</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" s="7">
+        <v>42</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P78" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B79" s="11">
+        <v>199</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" s="12">
+        <v>42</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="P79" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B80" s="11">
+        <v>300</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" s="12">
+        <v>42</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="P80" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B81" s="3">
+        <v>301</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="12">
+        <v>42</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M81" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="P81" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B82" s="3">
+        <v>320</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" s="7">
+        <v>42</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P82" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B83" s="3">
+        <v>321</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P83" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B84" s="3">
+        <v>323</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" s="12">
+        <v>42</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="L84" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M84" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="P84" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B85" s="3">
+        <v>324</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="L85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M85" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="P85" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B86" s="3">
+        <v>330</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" s="7">
+        <v>42</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K86" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M86" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P86" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B87" s="3">
+        <v>331</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" s="7">
+        <v>42</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M87" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P87" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B88" s="11">
+        <v>337</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" s="12">
+        <v>42</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K88" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="P88" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="11">
+        <v>341</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" s="12">
+        <v>42</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M89" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="P89" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B90" s="11">
+        <v>343</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" s="12">
+        <v>42</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="L90" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="P90" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B91" s="3">
+        <v>347</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" s="7">
+        <v>42</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="L91" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M91" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P91" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B92" s="3">
+        <v>353</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" s="7">
+        <v>42</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="L92" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="M92" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N92" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="P92" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="11">
+        <v>370</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" s="12">
+        <v>42</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="P93" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="11">
+        <v>371</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" s="12">
+        <v>42</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K94" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="L94" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="P94" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B95" s="3">
+        <v>374</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" s="12">
+        <v>42</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="L95" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M95" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="P95" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B96" s="3">
+        <v>375</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" s="7">
+        <v>42</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M96" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P96" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" s="3">
+        <v>392</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" s="7">
+        <v>42</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="L97" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M97" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="P97" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="3">
+        <v>440</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="7">
+        <v>42</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M98" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="P98" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="3">
+        <v>442</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" s="12">
+        <v>42</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M99" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="P99" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B100" s="3">
+        <v>443</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" s="7">
+        <v>42</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M100" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="P100" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="11">
+        <v>451</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" s="12">
+        <v>42</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M101" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="P101" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F102" s="8"/>
       <c r="K102" s="8"/>
     </row>
-    <row r="103" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F103" s="8"/>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F104" s="8"/>
       <c r="K104" s="8"/>
     </row>
-    <row r="105" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F105" s="8"/>
       <c r="K105" s="8"/>
     </row>
-    <row r="106" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F106" s="8"/>
       <c r="K106" s="8"/>
     </row>
-    <row r="107" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F107" s="8"/>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F108" s="8"/>
       <c r="K108" s="8"/>
     </row>
-    <row r="109" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F109" s="8"/>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F110" s="8"/>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F111" s="8"/>
       <c r="K111" s="8"/>
     </row>
-    <row r="112" spans="6:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="F112" s="8"/>
       <c r="K112" s="8"/>
     </row>
@@ -4338,6 +7003,10 @@
       <sortCondition ref="A2:A43"/>
     </sortState>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q101">
+    <sortCondition ref="B2:B101"/>
+    <sortCondition ref="A2:A101"/>
+  </sortState>
   <conditionalFormatting sqref="E1:E1048576">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="manual">
       <formula>NOT(ISERROR(SEARCH("manual",E1)))</formula>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3C382419-C4E6-B641-B399-AB210D290C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7E4BD3BF-C7A8-8242-ABE4-F1C0707AA318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2102" uniqueCount="403">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2168" uniqueCount="416">
   <si>
     <t>reviewer</t>
   </si>
@@ -1263,6 +1263,45 @@
   </si>
   <si>
     <t>OP_PAIRCOMMIT</t>
+  </si>
+  <si>
+    <t>See Also BIP 12: OP_EVAL, the original P2SH design</t>
+  </si>
+  <si>
+    <t>See Also [...] BIP 16: Pay to Script Hash (aka "/P2SH/")</t>
+  </si>
+  <si>
+    <t>See Also [...] BIP 17: OP_CHECKHASHVERIFY, another P2SH design</t>
+  </si>
+  <si>
+    <t>BIP 13 defines only the address encoding for P2SH. The actual semantics of spending those outputs are defined by BIP 16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP replaces BIP 12 and BIP 16, which propose evaluating a Script from the stack after verifying its hash. </t>
+  </si>
+  <si>
+    <t>See Also [...] M-of-N Multisignature Transactions (BIP 11)</t>
+  </si>
+  <si>
+    <t>See Also The Address format for Pay to Script Hash BIP</t>
+  </si>
+  <si>
+    <t>Address format for P2SH is defined in BIP13</t>
+  </si>
+  <si>
+    <t>OP_NOP2 is used, so existing OP_EVAL (BIP 12) transactions in the block chain can still be redeemed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP_CHECKMULTISIG is already an enabled opcode, and is the most straightforward way to support several important use cases. This is already specified in BIP 0011. </t>
+  </si>
+  <si>
+    <t>BIP 19 explicitly proposes an alternative implementation to BIP 11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed-Replacement: 321 [...] This BIP has been superseded and replaced with BIP 321. Please see BIP 321 instead. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaces: 20 [...] This BIP is a modification of an earlier BIP 0020 by Luke Dashjr. BIP 0020 was based off an earlier document by Nils Schneider. The alternative payment amounts in BIP 0020 have been removed. </t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1820,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1813,11 +1852,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2211,20 +2253,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" style="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.83203125" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -2243,13 +2285,13 @@
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -2264,7 +2306,7 @@
       <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="11" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="6" t="s">
@@ -2296,7 +2338,7 @@
       <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -2337,8 +2379,14 @@
       <c r="A3" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="3">
         <v>11</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>17</v>
@@ -2346,7 +2394,7 @@
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="7">
         <v>42</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -2373,7 +2421,7 @@
       <c r="O3" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2387,7 +2435,7 @@
       <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="7" t="s">
@@ -2434,13 +2482,19 @@
       <c r="B5" s="3">
         <v>13</v>
       </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="7">
         <v>42</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -2481,7 +2535,7 @@
       <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -2531,7 +2585,7 @@
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -2572,8 +2626,14 @@
       <c r="A8" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="3">
         <v>17</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>17</v>
@@ -2581,7 +2641,7 @@
       <c r="F8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="7">
         <v>42</v>
       </c>
       <c r="H8" s="7" t="s">
@@ -2608,7 +2668,7 @@
       <c r="O8" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="7">
         <v>4</v>
       </c>
     </row>
@@ -2622,7 +2682,7 @@
       <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -2666,8 +2726,14 @@
       <c r="A10" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="3">
         <v>19</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>17</v>
@@ -2675,7 +2741,7 @@
       <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="7">
         <v>42</v>
       </c>
       <c r="H10" s="7" t="s">
@@ -2702,7 +2768,7 @@
       <c r="O10" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2716,7 +2782,7 @@
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -2760,8 +2826,14 @@
       <c r="A12" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="3">
         <v>21</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>17</v>
@@ -2769,7 +2841,7 @@
       <c r="F12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="7">
         <v>42</v>
       </c>
       <c r="H12" s="7" t="s">
@@ -2796,7 +2868,7 @@
       <c r="O12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="P12" s="12">
+      <c r="P12" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2810,7 +2882,7 @@
       <c r="C13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -2857,7 +2929,7 @@
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -2910,7 +2982,7 @@
       <c r="F15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="7">
         <v>42</v>
       </c>
       <c r="H15" s="7" t="s">
@@ -2951,7 +3023,7 @@
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -3001,7 +3073,7 @@
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -3054,7 +3126,7 @@
       <c r="F18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="7">
         <v>42</v>
       </c>
       <c r="H18" s="7" t="s">
@@ -3089,7 +3161,7 @@
       <c r="A19" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="3">
         <v>34</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -3098,7 +3170,7 @@
       <c r="F19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="7">
         <v>42</v>
       </c>
       <c r="H19" s="7" t="s">
@@ -3125,7 +3197,7 @@
       <c r="O19" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="P19" s="12">
+      <c r="P19" s="7">
         <v>0</v>
       </c>
     </row>
@@ -3133,7 +3205,7 @@
       <c r="A20" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="3">
         <v>35</v>
       </c>
       <c r="E20" s="7" t="s">
@@ -3142,7 +3214,7 @@
       <c r="F20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="7">
         <v>42</v>
       </c>
       <c r="H20" s="7" t="s">
@@ -3169,7 +3241,7 @@
       <c r="O20" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="P20" s="12">
+      <c r="P20" s="7">
         <v>0</v>
       </c>
     </row>
@@ -3177,7 +3249,7 @@
       <c r="A21" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="3">
         <v>37</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -3186,7 +3258,7 @@
       <c r="F21" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="7">
         <v>42</v>
       </c>
       <c r="H21" s="7" t="s">
@@ -3213,7 +3285,7 @@
       <c r="O21" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="P21" s="12">
+      <c r="P21" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3227,7 +3299,7 @@
       <c r="C22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="7" t="s">
@@ -3277,7 +3349,7 @@
       <c r="C23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="7" t="s">
@@ -3327,7 +3399,7 @@
       <c r="F24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="7">
         <v>42</v>
       </c>
       <c r="H24" s="7" t="s">
@@ -3368,7 +3440,7 @@
       <c r="C25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -3418,7 +3490,7 @@
       <c r="C26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="7" t="s">
@@ -3468,7 +3540,7 @@
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E27" s="7" t="s">
@@ -3518,7 +3590,7 @@
       <c r="F28" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="7">
         <v>42</v>
       </c>
       <c r="H28" s="7" t="s">
@@ -3559,7 +3631,7 @@
       <c r="C29" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E29" s="7" t="s">
@@ -3603,7 +3675,7 @@
       <c r="A30" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="3">
         <v>52</v>
       </c>
       <c r="E30" s="7" t="s">
@@ -3612,7 +3684,7 @@
       <c r="F30" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="7">
         <v>42</v>
       </c>
       <c r="H30" s="7" t="s">
@@ -3639,7 +3711,7 @@
       <c r="O30" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="P30" s="12">
+      <c r="P30" s="7">
         <v>0</v>
       </c>
     </row>
@@ -3656,7 +3728,7 @@
       <c r="F31" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="7">
         <v>42</v>
       </c>
       <c r="H31" s="7" t="s">
@@ -3700,7 +3772,7 @@
       <c r="F32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="7">
         <v>42</v>
       </c>
       <c r="H32" s="7" t="s">
@@ -3735,7 +3807,7 @@
       <c r="A33" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="3">
         <v>64</v>
       </c>
       <c r="E33" s="7" t="s">
@@ -3744,7 +3816,7 @@
       <c r="F33" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="7">
         <v>42</v>
       </c>
       <c r="H33" s="7" t="s">
@@ -3771,7 +3843,7 @@
       <c r="O33" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="P33" s="12">
+      <c r="P33" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3788,7 +3860,7 @@
       <c r="F34" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="7">
         <v>42</v>
       </c>
       <c r="H34" s="7" t="s">
@@ -3832,7 +3904,7 @@
       <c r="F35" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="7">
         <v>42</v>
       </c>
       <c r="H35" s="7" t="s">
@@ -3876,7 +3948,7 @@
       <c r="F36" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="7">
         <v>42</v>
       </c>
       <c r="H36" s="7" t="s">
@@ -3917,7 +3989,7 @@
       <c r="C37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E37" s="7" t="s">
@@ -3967,7 +4039,7 @@
       <c r="C38" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="7" t="s">
@@ -4017,7 +4089,7 @@
       <c r="C39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E39" s="7" t="s">
@@ -4067,7 +4139,7 @@
       <c r="C40" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E40" s="7" t="s">
@@ -4120,7 +4192,7 @@
       <c r="F41" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="7">
         <v>42</v>
       </c>
       <c r="H41" s="7" t="s">
@@ -4155,7 +4227,7 @@
       <c r="A42" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="3">
         <v>89</v>
       </c>
       <c r="E42" s="7" t="s">
@@ -4164,7 +4236,7 @@
       <c r="F42" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="7">
         <v>42</v>
       </c>
       <c r="H42" s="7" t="s">
@@ -4191,7 +4263,7 @@
       <c r="O42" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="P42" s="12">
+      <c r="P42" s="7">
         <v>5</v>
       </c>
     </row>
@@ -4208,7 +4280,7 @@
       <c r="F43" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="7">
         <v>42</v>
       </c>
       <c r="H43" s="7" t="s">
@@ -4243,7 +4315,7 @@
       <c r="A44" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="3">
         <v>98</v>
       </c>
       <c r="E44" s="7" t="s">
@@ -4252,7 +4324,7 @@
       <c r="F44" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="7">
         <v>42</v>
       </c>
       <c r="H44" s="7" t="s">
@@ -4279,7 +4351,7 @@
       <c r="O44" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="P44" s="12">
+      <c r="P44" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4296,7 +4368,7 @@
       <c r="F45" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="7">
         <v>42</v>
       </c>
       <c r="H45" s="7" t="s">
@@ -4331,7 +4403,7 @@
       <c r="A46" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="3">
         <v>102</v>
       </c>
       <c r="E46" s="7" t="s">
@@ -4340,7 +4412,7 @@
       <c r="F46" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="7">
         <v>42</v>
       </c>
       <c r="H46" s="7" t="s">
@@ -4367,7 +4439,7 @@
       <c r="O46" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="P46" s="12">
+      <c r="P46" s="7">
         <v>0</v>
       </c>
     </row>
@@ -4384,7 +4456,7 @@
       <c r="F47" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="7">
         <v>42</v>
       </c>
       <c r="H47" s="7" t="s">
@@ -4419,7 +4491,7 @@
       <c r="A48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="3">
         <v>104</v>
       </c>
       <c r="E48" s="7" t="s">
@@ -4428,7 +4500,7 @@
       <c r="F48" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="7">
         <v>42</v>
       </c>
       <c r="H48" s="7" t="s">
@@ -4455,7 +4527,7 @@
       <c r="O48" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="P48" s="12">
+      <c r="P48" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4463,7 +4535,7 @@
       <c r="A49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="3">
         <v>105</v>
       </c>
       <c r="E49" s="7" t="s">
@@ -4472,7 +4544,7 @@
       <c r="F49" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="7">
         <v>42</v>
       </c>
       <c r="H49" s="7" t="s">
@@ -4499,7 +4571,7 @@
       <c r="O49" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="P49" s="12">
+      <c r="P49" s="7">
         <v>2</v>
       </c>
     </row>
@@ -4507,7 +4579,7 @@
       <c r="A50" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="3">
         <v>107</v>
       </c>
       <c r="E50" s="7" t="s">
@@ -4516,7 +4588,7 @@
       <c r="F50" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="7">
         <v>42</v>
       </c>
       <c r="H50" s="7" t="s">
@@ -4543,7 +4615,7 @@
       <c r="O50" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="P50" s="12">
+      <c r="P50" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4557,7 +4629,7 @@
       <c r="C51" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E51" s="7" t="s">
@@ -4607,7 +4679,7 @@
       <c r="C52" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E52" s="7" t="s">
@@ -4657,7 +4729,7 @@
       <c r="C53" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E53" s="7" t="s">
@@ -4707,7 +4779,7 @@
       <c r="C54" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E54" s="7" t="s">
@@ -4751,7 +4823,7 @@
       <c r="A55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="3">
         <v>115</v>
       </c>
       <c r="E55" s="7" t="s">
@@ -4760,7 +4832,7 @@
       <c r="F55" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="7">
         <v>42</v>
       </c>
       <c r="H55" s="7" t="s">
@@ -4787,7 +4859,7 @@
       <c r="O55" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="P55" s="12">
+      <c r="P55" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4804,7 +4876,7 @@
       <c r="F56" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G56" s="7">
         <v>42</v>
       </c>
       <c r="H56" s="7" t="s">
@@ -4845,7 +4917,7 @@
       <c r="C57" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E57" s="7" t="s">
@@ -4895,7 +4967,7 @@
       <c r="C58" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E58" s="7" t="s">
@@ -4939,7 +5011,7 @@
       <c r="A59" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="3">
         <v>125</v>
       </c>
       <c r="E59" s="7" t="s">
@@ -4948,7 +5020,7 @@
       <c r="F59" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G59" s="12">
+      <c r="G59" s="7">
         <v>42</v>
       </c>
       <c r="H59" s="7" t="s">
@@ -4975,7 +5047,7 @@
       <c r="O59" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="P59" s="12">
+      <c r="P59" s="7">
         <v>2</v>
       </c>
     </row>
@@ -4983,7 +5055,7 @@
       <c r="A60" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="3">
         <v>127</v>
       </c>
       <c r="E60" s="7" t="s">
@@ -4992,7 +5064,7 @@
       <c r="F60" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G60" s="12">
+      <c r="G60" s="7">
         <v>42</v>
       </c>
       <c r="H60" s="7" t="s">
@@ -5019,7 +5091,7 @@
       <c r="O60" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="P60" s="12">
+      <c r="P60" s="7">
         <v>3</v>
       </c>
     </row>
@@ -5033,7 +5105,7 @@
       <c r="C61" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E61" s="7" t="s">
@@ -5086,7 +5158,7 @@
       <c r="F62" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="7">
         <v>42</v>
       </c>
       <c r="H62" s="7" t="s">
@@ -5130,7 +5202,7 @@
       <c r="F63" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G63" s="12">
+      <c r="G63" s="7">
         <v>42</v>
       </c>
       <c r="H63" s="7" t="s">
@@ -5174,7 +5246,7 @@
       <c r="F64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G64" s="12">
+      <c r="G64" s="7">
         <v>42</v>
       </c>
       <c r="H64" s="7" t="s">
@@ -5218,7 +5290,7 @@
       <c r="F65" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G65" s="12">
+      <c r="G65" s="7">
         <v>42</v>
       </c>
       <c r="H65" s="7" t="s">
@@ -5262,7 +5334,7 @@
       <c r="F66" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G66" s="12">
+      <c r="G66" s="7">
         <v>42</v>
       </c>
       <c r="H66" s="7" t="s">
@@ -5297,7 +5369,7 @@
       <c r="A67" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="3">
         <v>141</v>
       </c>
       <c r="E67" s="7" t="s">
@@ -5306,7 +5378,7 @@
       <c r="F67" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="7">
         <v>42</v>
       </c>
       <c r="H67" s="7" t="s">
@@ -5333,7 +5405,7 @@
       <c r="O67" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="P67" s="12">
+      <c r="P67" s="7">
         <v>11</v>
       </c>
     </row>
@@ -5347,7 +5419,7 @@
       <c r="C68" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E68" s="7" t="s">
@@ -5400,7 +5472,7 @@
       <c r="F69" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="7">
         <v>42</v>
       </c>
       <c r="H69" s="7" t="s">
@@ -5441,7 +5513,7 @@
       <c r="C70" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E70" s="7" t="s">
@@ -5494,7 +5566,7 @@
       <c r="F71" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="7">
         <v>42</v>
       </c>
       <c r="H71" s="7" t="s">
@@ -5529,7 +5601,7 @@
       <c r="A72" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="3">
         <v>148</v>
       </c>
       <c r="E72" s="7" t="s">
@@ -5538,7 +5610,7 @@
       <c r="F72" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="7">
         <v>42</v>
       </c>
       <c r="H72" s="7" t="s">
@@ -5565,7 +5637,7 @@
       <c r="O72" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="P72" s="12">
+      <c r="P72" s="7">
         <v>5</v>
       </c>
     </row>
@@ -5582,7 +5654,7 @@
       <c r="F73" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="7">
         <v>42</v>
       </c>
       <c r="H73" s="7" t="s">
@@ -5623,7 +5695,7 @@
       <c r="C74" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E74" s="7" t="s">
@@ -5667,7 +5739,7 @@
       <c r="A75" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="3">
         <v>159</v>
       </c>
       <c r="E75" s="7" t="s">
@@ -5676,7 +5748,7 @@
       <c r="F75" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="7">
         <v>42</v>
       </c>
       <c r="H75" s="7" t="s">
@@ -5703,7 +5775,7 @@
       <c r="O75" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="P75" s="12">
+      <c r="P75" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5711,7 +5783,7 @@
       <c r="A76" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="3">
         <v>171</v>
       </c>
       <c r="E76" s="7" t="s">
@@ -5720,7 +5792,7 @@
       <c r="F76" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="7">
         <v>42</v>
       </c>
       <c r="H76" s="7" t="s">
@@ -5747,7 +5819,7 @@
       <c r="O76" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="P76" s="12">
+      <c r="P76" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5764,7 +5836,7 @@
       <c r="F77" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G77" s="12">
+      <c r="G77" s="7">
         <v>42</v>
       </c>
       <c r="H77" s="7" t="s">
@@ -5805,7 +5877,7 @@
       <c r="C78" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E78" s="7" t="s">
@@ -5849,7 +5921,7 @@
       <c r="A79" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="3">
         <v>199</v>
       </c>
       <c r="E79" s="7" t="s">
@@ -5858,7 +5930,7 @@
       <c r="F79" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G79" s="12">
+      <c r="G79" s="7">
         <v>42</v>
       </c>
       <c r="H79" s="7" t="s">
@@ -5885,7 +5957,7 @@
       <c r="O79" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="P79" s="12">
+      <c r="P79" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5893,7 +5965,7 @@
       <c r="A80" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="3">
         <v>300</v>
       </c>
       <c r="E80" s="7" t="s">
@@ -5902,7 +5974,7 @@
       <c r="F80" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G80" s="12">
+      <c r="G80" s="7">
         <v>42</v>
       </c>
       <c r="H80" s="7" t="s">
@@ -5929,7 +6001,7 @@
       <c r="O80" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="P80" s="12">
+      <c r="P80" s="7">
         <v>1</v>
       </c>
     </row>
@@ -5946,7 +6018,7 @@
       <c r="F81" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G81" s="12">
+      <c r="G81" s="7">
         <v>42</v>
       </c>
       <c r="H81" s="7" t="s">
@@ -5987,7 +6059,7 @@
       <c r="C82" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E82" s="7" t="s">
@@ -6034,7 +6106,7 @@
       <c r="C83" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E83" s="7" t="s">
@@ -6087,7 +6159,7 @@
       <c r="F84" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G84" s="12">
+      <c r="G84" s="7">
         <v>42</v>
       </c>
       <c r="H84" s="7" t="s">
@@ -6125,7 +6197,7 @@
       <c r="C85" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E85" s="7" t="s">
@@ -6175,7 +6247,7 @@
       <c r="C86" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E86" s="7" t="s">
@@ -6225,7 +6297,7 @@
       <c r="C87" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E87" s="7" t="s">
@@ -6269,7 +6341,7 @@
       <c r="A88" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B88" s="11">
+      <c r="B88" s="3">
         <v>337</v>
       </c>
       <c r="E88" s="7" t="s">
@@ -6278,7 +6350,7 @@
       <c r="F88" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G88" s="12">
+      <c r="G88" s="7">
         <v>42</v>
       </c>
       <c r="H88" s="7" t="s">
@@ -6305,7 +6377,7 @@
       <c r="O88" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="P88" s="12">
+      <c r="P88" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6313,7 +6385,7 @@
       <c r="A89" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="3">
         <v>341</v>
       </c>
       <c r="E89" s="7" t="s">
@@ -6322,7 +6394,7 @@
       <c r="F89" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G89" s="12">
+      <c r="G89" s="7">
         <v>42</v>
       </c>
       <c r="H89" s="7" t="s">
@@ -6349,7 +6421,7 @@
       <c r="O89" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="P89" s="12">
+      <c r="P89" s="7">
         <v>10</v>
       </c>
     </row>
@@ -6357,7 +6429,7 @@
       <c r="A90" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B90" s="11">
+      <c r="B90" s="3">
         <v>343</v>
       </c>
       <c r="E90" s="7" t="s">
@@ -6366,7 +6438,7 @@
       <c r="F90" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G90" s="12">
+      <c r="G90" s="7">
         <v>42</v>
       </c>
       <c r="H90" s="7" t="s">
@@ -6393,7 +6465,7 @@
       <c r="O90" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="P90" s="12">
+      <c r="P90" s="7">
         <v>6</v>
       </c>
     </row>
@@ -6407,7 +6479,7 @@
       <c r="C91" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E91" s="7" t="s">
@@ -6457,7 +6529,7 @@
       <c r="C92" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="D92" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E92" s="7" t="s">
@@ -6501,7 +6573,7 @@
       <c r="A93" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="3">
         <v>370</v>
       </c>
       <c r="E93" s="7" t="s">
@@ -6510,7 +6582,7 @@
       <c r="F93" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G93" s="12">
+      <c r="G93" s="7">
         <v>42</v>
       </c>
       <c r="H93" s="7" t="s">
@@ -6537,7 +6609,7 @@
       <c r="O93" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="P93" s="12">
+      <c r="P93" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6545,7 +6617,7 @@
       <c r="A94" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B94" s="11">
+      <c r="B94" s="3">
         <v>371</v>
       </c>
       <c r="E94" s="7" t="s">
@@ -6554,7 +6626,7 @@
       <c r="F94" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G94" s="12">
+      <c r="G94" s="7">
         <v>42</v>
       </c>
       <c r="H94" s="7" t="s">
@@ -6581,7 +6653,7 @@
       <c r="O94" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="P94" s="12">
+      <c r="P94" s="7">
         <v>6</v>
       </c>
     </row>
@@ -6598,7 +6670,7 @@
       <c r="F95" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G95" s="12">
+      <c r="G95" s="7">
         <v>42</v>
       </c>
       <c r="H95" s="7" t="s">
@@ -6639,7 +6711,7 @@
       <c r="C96" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E96" s="7" t="s">
@@ -6689,7 +6761,7 @@
       <c r="C97" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E97" s="7" t="s">
@@ -6739,7 +6811,7 @@
       <c r="C98" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E98" s="7" t="s">
@@ -6792,7 +6864,7 @@
       <c r="F99" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G99" s="12">
+      <c r="G99" s="7">
         <v>42</v>
       </c>
       <c r="H99" s="7" t="s">
@@ -6833,7 +6905,7 @@
       <c r="C100" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="8" t="s">
         <v>32</v>
       </c>
       <c r="E100" s="7" t="s">
@@ -6877,7 +6949,7 @@
       <c r="A101" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="3">
         <v>451</v>
       </c>
       <c r="E101" s="7" t="s">
@@ -6886,7 +6958,7 @@
       <c r="F101" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G101" s="12">
+      <c r="G101" s="7">
         <v>42</v>
       </c>
       <c r="H101" s="7" t="s">
@@ -6913,88 +6985,9 @@
       <c r="O101" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="P101" s="12">
+      <c r="P101" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F102" s="8"/>
-      <c r="K102" s="8"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F103" s="8"/>
-      <c r="K103" s="8"/>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F104" s="8"/>
-      <c r="K104" s="8"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F105" s="8"/>
-      <c r="K105" s="8"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F106" s="8"/>
-      <c r="K106" s="8"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F107" s="8"/>
-      <c r="K107" s="8"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F108" s="8"/>
-      <c r="K108" s="8"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F109" s="8"/>
-      <c r="K109" s="8"/>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F110" s="8"/>
-      <c r="K110" s="8"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F111" s="8"/>
-      <c r="K111" s="8"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="F112" s="8"/>
-      <c r="K112" s="8"/>
-    </row>
-    <row r="113" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F113" s="8"/>
-      <c r="K113" s="8"/>
-    </row>
-    <row r="114" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F114" s="8"/>
-      <c r="K114" s="8"/>
-    </row>
-    <row r="115" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F115" s="8"/>
-      <c r="K115" s="8"/>
-    </row>
-    <row r="116" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F116" s="8"/>
-      <c r="K116" s="8"/>
-    </row>
-    <row r="117" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F117" s="8"/>
-      <c r="K117" s="8"/>
-    </row>
-    <row r="118" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F118" s="8"/>
-      <c r="K118" s="8"/>
-    </row>
-    <row r="119" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F119" s="8"/>
-      <c r="K119" s="8"/>
-    </row>
-    <row r="120" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F120" s="8"/>
-      <c r="K120" s="8"/>
-    </row>
-    <row r="121" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F121" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q43" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -7018,7 +7011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7029,7 +7022,7 @@
     <col min="6" max="6" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="57.6640625" style="4" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -7060,7 +7053,7 @@
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -10813,347 +10806,285 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J126" s="10"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J127" s="10"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="J128" s="10"/>
-    </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J129" s="10"/>
-    </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J130" s="10"/>
-    </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J131" s="10"/>
-    </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J132" s="10"/>
-    </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J133" s="10"/>
-    </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J134" s="10"/>
-    </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J135" s="10"/>
-    </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J136" s="10"/>
-    </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J137" s="10"/>
-    </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J138" s="10"/>
-    </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J139" s="10"/>
-    </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J140" s="10"/>
-    </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J141" s="10"/>
-    </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J142" s="10"/>
-    </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J143" s="10"/>
-    </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J144" s="10"/>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" s="10"/>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" s="10"/>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" s="10"/>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" s="10"/>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" s="10"/>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" s="10"/>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" s="10"/>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" s="10"/>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" s="10"/>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" s="10"/>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" s="10"/>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" s="10"/>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" s="10"/>
-    </row>
-    <row r="158" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J158" s="10"/>
-    </row>
-    <row r="159" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J159" s="10"/>
-    </row>
-    <row r="160" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J160" s="10"/>
-    </row>
-    <row r="161" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J161" s="10"/>
-    </row>
-    <row r="162" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J162" s="10"/>
-    </row>
-    <row r="163" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J163" s="10"/>
-    </row>
-    <row r="164" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J164" s="10"/>
-    </row>
-    <row r="165" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J165" s="10"/>
-    </row>
-    <row r="166" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J166" s="10"/>
-    </row>
-    <row r="167" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J167" s="10"/>
-    </row>
-    <row r="168" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J168" s="10"/>
-    </row>
-    <row r="169" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J169" s="10"/>
-    </row>
-    <row r="170" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J170" s="10"/>
-    </row>
-    <row r="171" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J171" s="10"/>
-    </row>
-    <row r="172" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J172" s="10"/>
-    </row>
-    <row r="173" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J173" s="10"/>
-    </row>
-    <row r="174" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J174" s="10"/>
-    </row>
-    <row r="175" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J175" s="10"/>
-    </row>
-    <row r="176" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J176" s="10"/>
-    </row>
-    <row r="177" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J177" s="10"/>
-    </row>
-    <row r="178" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J178" s="10"/>
-    </row>
-    <row r="179" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J179" s="10"/>
-    </row>
-    <row r="180" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J180" s="10"/>
-    </row>
-    <row r="181" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J181" s="10"/>
-    </row>
-    <row r="182" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J182" s="10"/>
-    </row>
-    <row r="183" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J183" s="10"/>
-    </row>
-    <row r="184" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J184" s="10"/>
-    </row>
-    <row r="185" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J185" s="10"/>
-    </row>
-    <row r="186" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J186" s="10"/>
-    </row>
-    <row r="187" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J187" s="10"/>
-    </row>
-    <row r="188" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J188" s="10"/>
-    </row>
-    <row r="189" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J189" s="10"/>
-    </row>
-    <row r="190" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J190" s="10"/>
-    </row>
-    <row r="191" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J191" s="10"/>
-    </row>
-    <row r="192" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J192" s="10"/>
-    </row>
-    <row r="193" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J193" s="10"/>
-    </row>
-    <row r="194" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J194" s="10"/>
-    </row>
-    <row r="195" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J195" s="10"/>
-    </row>
-    <row r="196" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J196" s="10"/>
-    </row>
-    <row r="197" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J197" s="10"/>
-    </row>
-    <row r="198" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J198" s="10"/>
-    </row>
-    <row r="199" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J199" s="10"/>
-    </row>
-    <row r="200" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J200" s="10"/>
-    </row>
-    <row r="201" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J201" s="10"/>
-    </row>
-    <row r="202" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J202" s="10"/>
-    </row>
-    <row r="203" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J203" s="10"/>
-    </row>
-    <row r="204" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J204" s="10"/>
-    </row>
-    <row r="205" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J205" s="10"/>
-    </row>
-    <row r="206" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J206" s="10"/>
-    </row>
-    <row r="207" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J207" s="10"/>
-    </row>
-    <row r="208" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J208" s="10"/>
-    </row>
-    <row r="209" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J209" s="10"/>
-    </row>
-    <row r="210" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J210" s="10"/>
-    </row>
-    <row r="211" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J211" s="10"/>
-    </row>
-    <row r="212" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J212" s="10"/>
-    </row>
-    <row r="213" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J213" s="10"/>
-    </row>
-    <row r="214" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J214" s="10"/>
-    </row>
-    <row r="215" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J215" s="10"/>
-    </row>
-    <row r="216" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J216" s="10"/>
-    </row>
-    <row r="217" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J217" s="10"/>
-    </row>
-    <row r="218" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J218" s="10"/>
-    </row>
-    <row r="219" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J219" s="10"/>
-    </row>
-    <row r="220" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J220" s="10"/>
-    </row>
-    <row r="221" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J221" s="10"/>
-    </row>
-    <row r="222" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J222" s="10"/>
-    </row>
-    <row r="223" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J223" s="10"/>
-    </row>
-    <row r="224" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J224" s="10"/>
-    </row>
-    <row r="225" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J225" s="10"/>
-    </row>
-    <row r="226" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J226" s="10"/>
-    </row>
-    <row r="227" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J227" s="10"/>
-    </row>
-    <row r="228" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J228" s="10"/>
-    </row>
-    <row r="229" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J229" s="10"/>
-    </row>
-    <row r="230" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J230" s="10"/>
-    </row>
-    <row r="231" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J231" s="10"/>
-    </row>
-    <row r="232" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J232" s="10"/>
-    </row>
-    <row r="233" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J233" s="10"/>
-    </row>
-    <row r="234" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J234" s="10"/>
-    </row>
-    <row r="235" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J235" s="10"/>
-    </row>
-    <row r="236" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J236" s="10"/>
-    </row>
-    <row r="237" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J237" s="10"/>
-    </row>
-    <row r="238" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J238" s="10"/>
-    </row>
-    <row r="239" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J239" s="10"/>
+    <row r="126" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A126" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B126" s="3">
+        <v>13</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D126" s="3">
+        <v>12</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J126" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" s="3">
+        <v>13</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D127" s="3">
+        <v>16</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J127" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B128" s="3">
+        <v>13</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D128" s="3">
+        <v>17</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J128" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B129" s="3">
+        <v>17</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D129" s="3">
+        <v>12</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B130" s="3">
+        <v>17</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" s="3">
+        <v>16</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B131" s="3">
+        <v>17</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D131" s="3">
+        <v>13</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B132" s="3">
+        <v>17</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D132" s="3">
+        <v>11</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B133" s="3">
+        <v>17</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D133" s="3">
+        <v>12</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G133" s="13" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B134" s="3">
+        <v>19</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D134" s="3">
+        <v>11</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="68" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B135" s="3">
+        <v>21</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D135" s="3">
+        <v>20</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B136" s="3">
+        <v>21</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D136" s="3">
+        <v>321</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>414</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7E4BD3BF-C7A8-8242-ABE4-F1C0707AA318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9B4DDF98-275B-9A44-817F-2B14C6C95ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2168" uniqueCount="416">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2163" uniqueCount="416">
   <si>
     <t>reviewer</t>
   </si>
@@ -1289,9 +1289,6 @@
     <t>Address format for P2SH is defined in BIP13</t>
   </si>
   <si>
-    <t>OP_NOP2 is used, so existing OP_EVAL (BIP 12) transactions in the block chain can still be redeemed.</t>
-  </si>
-  <si>
     <t xml:space="preserve">OP_CHECKMULTISIG is already an enabled opcode, and is the most straightforward way to support several important use cases. This is already specified in BIP 0011. </t>
   </si>
   <si>
@@ -1302,6 +1299,9 @@
   </si>
   <si>
     <t xml:space="preserve">Replaces: 20 [...] This BIP is a modification of an earlier BIP 0020 by Luke Dashjr. BIP 0020 was based off an earlier document by Nils Schneider. The alternative payment amounts in BIP 0020 have been removed. </t>
+  </si>
+  <si>
+    <t>This BIP replaces BIP 12 and BIP 16, which propose evaluating a Script from the stack after verifying its hash.  [...] OP_NOP2 is used, so existing OP_EVAL (BIP 12) transactions in the block chain can still be redeemed.</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1820,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1857,9 +1857,6 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -7011,7 +7008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7181,28 +7178,28 @@
         <v>219</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>154</v>
+        <v>403</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="10" t="s">
-        <v>32</v>
+      <c r="J6" s="10" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -7210,57 +7207,60 @@
         <v>219</v>
       </c>
       <c r="B7" s="3">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="3">
         <v>16</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="3">
-        <v>12</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>206</v>
+        <v>404</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J7" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D8" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>207</v>
+        <v>405</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>32</v>
+      <c r="J8" s="10" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -7268,7 +7268,7 @@
         <v>219</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>219</v>
@@ -7280,7 +7280,7 @@
         <v>128</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>154</v>
@@ -7289,7 +7289,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -7297,7 +7297,7 @@
         <v>219</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>219</v>
@@ -7309,24 +7309,24 @@
         <v>140</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J10" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="3">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="3">
-        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>219</v>
@@ -7338,65 +7338,53 @@
         <v>128</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B12" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D12" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B13" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D13" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>140</v>
@@ -7405,85 +7393,67 @@
         <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="3">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="3">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="3">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D15" s="3">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="3">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="3">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="3">
-        <v>21</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D15" s="3">
-        <v>10</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B16" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D16" s="3">
         <v>11</v>
@@ -7492,149 +7462,155 @@
         <v>128</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B17" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D17" s="3">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B18" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D18" s="3">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B19" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D19" s="3">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>150</v>
+        <v>157</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B20" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D20" s="3">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D21" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>128</v>
@@ -7643,132 +7619,108 @@
         <v>37</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>165</v>
+        <v>411</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B22" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D22" s="3">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B23" s="3">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D23" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B24" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D24" s="3">
-        <v>32</v>
+        <v>321</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B25" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D25" s="3">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -7777,27 +7729,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B26" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D26" s="3">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>152</v>
+        <v>248</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
@@ -7806,27 +7758,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>222</v>
       </c>
       <c r="B27" s="3">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D27" s="3">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>15</v>
@@ -7837,25 +7789,25 @@
     </row>
     <row r="28" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B28" s="3">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D28" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
@@ -7866,28 +7818,25 @@
     </row>
     <row r="29" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B29" s="3">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D29" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>244</v>
+        <v>150</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>15</v>
@@ -7896,82 +7845,82 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B30" s="3">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="3">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D30" s="3">
-        <v>32</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B31" s="3">
+        <v>22</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="3">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D31" s="3">
-        <v>43</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B32" s="3">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D32" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>128</v>
@@ -7980,30 +7929,27 @@
         <v>37</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B33" s="3">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D33" s="3">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>118</v>
@@ -8012,7 +7958,10 @@
         <v>37</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>153</v>
+        <v>119</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>15</v>
@@ -8021,41 +7970,44 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B34" s="3">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D34" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>233</v>
+        <v>121</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B35" s="3">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>219</v>
@@ -8070,103 +8022,100 @@
         <v>37</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B36" s="3">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D36" s="3">
+        <v>39</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" s="3">
+        <v>39</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" s="3">
+        <v>173</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" s="3">
         <v>43</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B37" s="3">
-        <v>49</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D37" s="3">
-        <v>44</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="3">
+        <v>32</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B38" s="3">
-        <v>49</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D38" s="3">
-        <v>132</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -8174,74 +8123,77 @@
         <v>219</v>
       </c>
       <c r="B39" s="3">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D39" s="3">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" s="3">
+        <v>44</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" s="3">
+        <v>32</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" s="10" t="s">
+      <c r="F40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B40" s="3">
-        <v>73</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D40" s="3">
-        <v>70</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B41" s="3">
-        <v>74</v>
-      </c>
       <c r="C41" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D41" s="3">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>118</v>
@@ -8250,42 +8202,42 @@
         <v>37</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J41" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B42" s="3">
-        <v>77</v>
-      </c>
       <c r="C42" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D42" s="3">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
@@ -8294,18 +8246,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B43" s="3">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D43" s="3">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>118</v>
@@ -8314,10 +8266,7 @@
         <v>37</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>15</v>
@@ -8326,50 +8275,47 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B44" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D44" s="3">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B45" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D45" s="3">
-        <v>174</v>
+        <v>32</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>118</v>
@@ -8378,138 +8324,132 @@
         <v>37</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B46" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D46" s="3">
-        <v>321</v>
+        <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>132</v>
+        <v>232</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B47" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D47" s="3">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B48" s="3">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D48" s="3">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="3">
+        <v>49</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" s="3">
+        <v>141</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B49" s="3">
-        <v>78</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D49" s="3">
-        <v>79</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J49" s="10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -8517,22 +8457,25 @@
         <v>219</v>
       </c>
       <c r="B50" s="3">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D50" s="3">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
@@ -8541,18 +8484,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B51" s="3">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D51" s="3">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>118</v>
@@ -8561,10 +8504,10 @@
         <v>37</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>15</v>
@@ -8573,50 +8516,50 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B52" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D52" s="3">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B53" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D53" s="3">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>118</v>
@@ -8625,13 +8568,16 @@
         <v>37</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>176</v>
+        <v>133</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -8639,31 +8585,31 @@
         <v>219</v>
       </c>
       <c r="B54" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D54" s="3">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -8671,13 +8617,13 @@
         <v>219</v>
       </c>
       <c r="B55" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D55" s="3">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>118</v>
@@ -8686,234 +8632,231 @@
         <v>37</v>
       </c>
       <c r="G55" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B56" s="3">
+        <v>77</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" s="3">
+        <v>321</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" s="3">
+        <v>77</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" s="3">
+        <v>324</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="3">
+        <v>78</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D58" s="3">
+        <v>21</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B59" s="3">
+        <v>78</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" s="3">
+        <v>79</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="3">
+        <v>111</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" s="3">
+        <v>37</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" s="3">
+        <v>112</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D61" s="3">
+        <v>9</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B56" s="3">
-        <v>113</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D56" s="3">
+      <c r="I61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="3">
+        <v>112</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" s="3">
         <v>65</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B57" s="3">
-        <v>113</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D57" s="3">
-        <v>68</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B58" s="3">
-        <v>113</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D58" s="3">
-        <v>112</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B59" s="3">
-        <v>114</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D59" s="3">
-        <v>9</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B60" s="3">
-        <v>114</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D60" s="3">
-        <v>16</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B61" s="3">
-        <v>114</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D61" s="3">
-        <v>112</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B62" s="3">
-        <v>114</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D62" s="3">
-        <v>141</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -8921,83 +8864,86 @@
         <v>219</v>
       </c>
       <c r="B63" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D63" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B64" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D64" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B65" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D65" s="3">
-        <v>341</v>
+        <v>9</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -9006,30 +8952,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B66" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D66" s="3">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
@@ -9038,30 +8984,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B67" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D67" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
@@ -9075,22 +9021,25 @@
         <v>219</v>
       </c>
       <c r="B68" s="3">
+        <v>113</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" s="3">
+        <v>112</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D68" s="3">
-        <v>68</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F68" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>197</v>
+        <v>180</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
@@ -9099,27 +9048,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B69" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D69" s="3">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
@@ -9128,18 +9077,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B70" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D70" s="3">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>128</v>
@@ -9148,7 +9097,10 @@
         <v>37</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>196</v>
+        <v>182</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
@@ -9157,18 +9109,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B71" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D71" s="3">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>128</v>
@@ -9177,7 +9129,10 @@
         <v>146</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>198</v>
+        <v>185</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
@@ -9186,27 +9141,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B72" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D72" s="3">
-        <v>433</v>
+        <v>141</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>15</v>
@@ -9215,18 +9170,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B73" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D73" s="3">
-        <v>443</v>
+        <v>65</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>128</v>
@@ -9235,7 +9190,7 @@
         <v>37</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
@@ -9249,13 +9204,13 @@
         <v>219</v>
       </c>
       <c r="B74" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D74" s="3">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>128</v>
@@ -9264,10 +9219,7 @@
         <v>37</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H74" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>15</v>
@@ -9276,27 +9228,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B75" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D75" s="3">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>204</v>
+        <v>191</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
@@ -9305,30 +9260,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B76" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D76" s="3">
-        <v>47</v>
+        <v>346</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>15</v>
@@ -9337,18 +9292,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B77" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D77" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>128</v>
@@ -9357,10 +9312,10 @@
         <v>37</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>15</v>
@@ -9369,30 +9324,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B78" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D78" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
@@ -9401,30 +9353,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B79" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D79" s="3">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
@@ -9433,30 +9382,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B80" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D80" s="3">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -9465,27 +9411,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B81" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D81" s="3">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -9494,30 +9440,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B82" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D82" s="3">
-        <v>23</v>
+        <v>433</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -9526,18 +9469,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B83" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="3">
-        <v>141</v>
+        <v>443</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>128</v>
@@ -9546,7 +9489,7 @@
         <v>37</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
@@ -9560,13 +9503,13 @@
         <v>219</v>
       </c>
       <c r="B84" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D84" s="3">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>128</v>
@@ -9575,7 +9518,10 @@
         <v>37</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>216</v>
+        <v>202</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
@@ -9584,27 +9530,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B85" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D85" s="3">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -9613,27 +9559,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B86" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D86" s="3">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>214</v>
+        <v>205</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
@@ -9642,27 +9591,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B87" s="3">
-        <v>197</v>
-      </c>
-      <c r="C87" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D87" s="3">
-        <v>199</v>
+        <v>63</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>215</v>
+        <v>205</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>15</v>
@@ -9671,163 +9623,175 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B88" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D88" s="3">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F88" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B89" s="3">
+        <v>142</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" s="3">
+        <v>141</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B90" s="3">
+        <v>145</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" s="3">
+        <v>9</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G88" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B89" s="3">
-        <v>320</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D89" s="3">
-        <v>9</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B90" s="3">
-        <v>320</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D90" s="3">
-        <v>323</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G90" s="4" t="s">
-        <v>250</v>
+        <v>210</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J90" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B91" s="3">
-        <v>321</v>
-      </c>
-      <c r="C91" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D91" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J91" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B92" s="3">
-        <v>321</v>
-      </c>
-      <c r="C92" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D92" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>240</v>
+        <v>212</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J92" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B93" s="3">
-        <v>321</v>
+        <v>145</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D93" s="3">
-        <v>351</v>
+        <v>141</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>128</v>
@@ -9836,27 +9800,27 @@
         <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J93" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B94" s="3">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D94" s="3">
-        <v>352</v>
+        <v>37</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>128</v>
@@ -9865,13 +9829,13 @@
         <v>37</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J94" s="10" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9879,13 +9843,13 @@
         <v>219</v>
       </c>
       <c r="B95" s="3">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D95" s="3">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>128</v>
@@ -9894,77 +9858,71 @@
         <v>20</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J95" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J95" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B96" s="3">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D96" s="3">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J96" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J96" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B97" s="3">
-        <v>324</v>
-      </c>
-      <c r="C97" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C97" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D97" s="3">
-        <v>340</v>
+        <v>199</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J97" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J97" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -9972,22 +9930,22 @@
         <v>219</v>
       </c>
       <c r="B98" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D98" s="3">
-        <v>340</v>
+        <v>8</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -9996,27 +9954,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B99" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D99" s="3">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -10025,27 +9983,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B100" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D100" s="3">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -10054,33 +10012,33 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B101" s="3">
-        <v>331</v>
-      </c>
-      <c r="C101" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C101" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D101" s="3">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J101" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J101" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10088,57 +10046,57 @@
         <v>219</v>
       </c>
       <c r="B102" s="3">
-        <v>331</v>
-      </c>
-      <c r="C102" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C102" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D102" s="3">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J102" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J102" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B103" s="3">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D103" s="3">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J103" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J103" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10146,31 +10104,28 @@
         <v>219</v>
       </c>
       <c r="B104" s="3">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D104" s="3">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J104" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J104" s="10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10178,25 +10133,22 @@
         <v>219</v>
       </c>
       <c r="B105" s="3">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D105" s="3">
-        <v>341</v>
+        <v>31</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10205,30 +10157,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B106" s="3">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D106" s="3">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>264</v>
+        <v>143</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10237,27 +10189,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B107" s="3">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D107" s="3">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>265</v>
+        <v>144</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -10271,22 +10226,22 @@
         <v>219</v>
       </c>
       <c r="B108" s="3">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D108" s="3">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -10300,22 +10255,22 @@
         <v>219</v>
       </c>
       <c r="B109" s="3">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D109" s="3">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -10329,25 +10284,22 @@
         <v>219</v>
       </c>
       <c r="B110" s="3">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D110" s="3">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -10356,27 +10308,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B111" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D111" s="3">
-        <v>370</v>
+        <v>133</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -10385,27 +10337,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B112" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D112" s="3">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -10414,27 +10366,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B113" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D113" s="3">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10443,30 +10395,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B114" s="3">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D114" s="3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -10475,18 +10424,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B115" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D115" s="3">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>118</v>
@@ -10495,7 +10444,10 @@
         <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>269</v>
+        <v>259</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>262</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -10504,12 +10456,12 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B116" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>219</v>
@@ -10524,7 +10476,10 @@
         <v>37</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>272</v>
+        <v>260</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -10533,18 +10488,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B117" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D117" s="3">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>118</v>
@@ -10553,10 +10508,10 @@
         <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -10565,18 +10520,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B118" s="3">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D118" s="3">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>118</v>
@@ -10585,7 +10540,7 @@
         <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -10594,18 +10549,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B119" s="3">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D119" s="3">
-        <v>390</v>
+        <v>321</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>128</v>
@@ -10614,7 +10569,7 @@
         <v>146</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -10623,27 +10578,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B120" s="3">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D120" s="3">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>275</v>
+        <v>284</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -10652,30 +10610,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B121" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D121" s="3">
-        <v>342</v>
+        <v>32</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -10689,13 +10647,13 @@
         <v>219</v>
       </c>
       <c r="B122" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D122" s="3">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>118</v>
@@ -10704,10 +10662,7 @@
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -10716,27 +10671,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B123" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D123" s="3">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -10750,22 +10705,22 @@
         <v>219</v>
       </c>
       <c r="B124" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D124" s="3">
-        <v>119</v>
+        <v>374</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -10774,30 +10729,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B125" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D125" s="3">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -10806,47 +10758,50 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B126" s="3">
-        <v>13</v>
+        <v>392</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D126" s="3">
-        <v>12</v>
+        <v>350</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>403</v>
+        <v>270</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J126" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B127" s="3">
-        <v>13</v>
+        <v>392</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D127" s="3">
-        <v>16</v>
+        <v>352</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>118</v>
@@ -10855,251 +10810,270 @@
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>406</v>
+        <v>269</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J127" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B128" s="3">
-        <v>13</v>
+        <v>392</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D128" s="3">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="E128" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J128" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A129" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B129" s="3">
+        <v>392</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D129" s="3">
+        <v>390</v>
+      </c>
+      <c r="E129" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F129" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J129" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B130" s="3">
+        <v>440</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" s="3">
+        <v>342</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G128" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="I128" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J128" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A129" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B129" s="3">
-        <v>17</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D129" s="3">
-        <v>12</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B130" s="3">
-        <v>17</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="3">
-        <v>16</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G130" s="4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J130" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B131" s="3">
-        <v>17</v>
+        <v>443</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D131" s="3">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J131" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B132" s="3">
-        <v>17</v>
+        <v>443</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D132" s="3">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J132" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B133" s="3">
-        <v>17</v>
+        <v>443</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D133" s="3">
-        <v>12</v>
+        <v>341</v>
       </c>
       <c r="E133" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J133" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B134" s="3">
+        <v>443</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D134" s="3">
+        <v>342</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" s="10" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B135" s="3">
+        <v>443</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D135" s="3">
+        <v>345</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F133" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G133" s="13" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="51" x14ac:dyDescent="0.2">
-      <c r="A134" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B134" s="3">
-        <v>19</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D134" s="3">
-        <v>11</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F134" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="68" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B135" s="3">
-        <v>21</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D135" s="3">
-        <v>20</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="F135" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A136" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B136" s="3">
-        <v>21</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D136" s="3">
-        <v>321</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>414</v>
+        <v>278</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J135" s="10" t="d">
+        <v>2026-06-29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J93">
-      <sortCondition ref="B2:B93"/>
-      <sortCondition ref="A2:A93"/>
-      <sortCondition ref="D2:D93"/>
-      <sortCondition ref="C2:C93"/>
+  <autoFilter ref="A1:J92" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J92">
+      <sortCondition ref="B2:B92"/>
+      <sortCondition ref="A2:A92"/>
+      <sortCondition ref="D2:D92"/>
+      <sortCondition ref="C2:C92"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J97">
-    <sortCondition ref="B2:B97"/>
-    <sortCondition ref="A2:A97"/>
-    <sortCondition ref="D2:D97"/>
-    <sortCondition ref="C2:C97"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J135">
+    <sortCondition ref="B2:B135"/>
+    <sortCondition ref="A2:A135"/>
+    <sortCondition ref="D2:D135"/>
+    <sortCondition ref="C2:C135"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9B4DDF98-275B-9A44-817F-2B14C6C95ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{678A28BB-CAB4-D245-9C40-C1B134D3820A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2163" uniqueCount="416">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2237" uniqueCount="426">
   <si>
     <t>reviewer</t>
   </si>
@@ -1302,6 +1302,36 @@
   </si>
   <si>
     <t>This BIP replaces BIP 12 and BIP 16, which propose evaluating a Script from the stack after verifying its hash.  [...] OP_NOP2 is used, so existing OP_EVAL (BIP 12) transactions in the block chain can still be redeemed.</t>
+  </si>
+  <si>
+    <t>This BIP describes extensions to the getblocktemplate JSON-RPC call to enhance pooled mining. [...] Note that all sections of this specification are optional extensions on top of BIP 22.</t>
+  </si>
+  <si>
+    <t>A softfork (see BIP16, BIP34, BIP62) will take place on april 1st 2214, permanently setting the subsidy to zero.</t>
+  </si>
+  <si>
+    <t>OP_CHECKLOCKTIMEVERIFY is defined in BIP65</t>
+  </si>
+  <si>
+    <t>Fidelity bonds are used to resist sybil attacks in certain decentralized anonymous protocols. They are created by locking up bitcoins using the `OP_CHECKLOCKTIMEVERIFY` opcode. [...] References [...] BIP65 - OP_CHECKLOCKTIMEVERIFY</t>
+  </si>
+  <si>
+    <t>Specifications This BIP defines the two needed steps to derive multiple deterministic addresses based on a BIP 32 master private key. [...] Reference [...] BIP32 - Hierarchical Deterministic Wallets</t>
+  </si>
+  <si>
+    <t>To derive a public key from the root account, this BIP uses a similar account-structure as defined in BIP 44 but with change set to 2 [...] Reference [...] BIP44 - Multi-Account Hierarchy for Deterministic Wallets</t>
+  </si>
+  <si>
+    <t>We largely use the same approach used in BIPs 49, 84 and 86 for ease of implementation. [...] Reference [...] BIP84 - Derivation scheme for P2WPKH based accounts</t>
+  </si>
+  <si>
+    <t>We largely use the same approach used in BIPs 49, 84 and 86 for ease of implementation. [...] Reference [...] BIP86 - Key Derivation for Single Key P2TR Outputs</t>
+  </si>
+  <si>
+    <t>We largely use the same approach used in BIPs 49, 84 and 86 for ease of implementation. [...] This BIP is not backwards compatible by design as described in the Considerations section of BIP 49. [...] Reference [...] BIP49 - Derivation scheme for P2WPKH-nested-in-P2SH based accounts</t>
+  </si>
+  <si>
+    <t>All inputs MUST set the nSequence to 0xFFFFFFFF (do not signal for BIP 125 RBF). [...] The batch creator MUST add a new dust UTXO input, and the resulting replacement transaction MUST satisfy BIP 125 RBF rules:</t>
   </si>
 </sst>
 </file>
@@ -2973,6 +3003,12 @@
       <c r="B15" s="3">
         <v>23</v>
       </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E15" s="7" t="s">
         <v>17</v>
       </c>
@@ -3117,6 +3153,12 @@
       <c r="B18" s="3">
         <v>33</v>
       </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E18" s="7" t="s">
         <v>17</v>
       </c>
@@ -3161,6 +3203,12 @@
       <c r="B19" s="3">
         <v>34</v>
       </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E19" s="7" t="s">
         <v>17</v>
       </c>
@@ -3205,6 +3253,12 @@
       <c r="B20" s="3">
         <v>35</v>
       </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E20" s="7" t="s">
         <v>17</v>
       </c>
@@ -3248,6 +3302,12 @@
       </c>
       <c r="B21" s="3">
         <v>37</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>17</v>
@@ -3390,6 +3450,12 @@
       <c r="B24" s="3">
         <v>42</v>
       </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E24" s="7" t="s">
         <v>17</v>
       </c>
@@ -3581,6 +3647,12 @@
       <c r="B28" s="3">
         <v>46</v>
       </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E28" s="7" t="s">
         <v>17</v>
       </c>
@@ -6948,6 +7020,12 @@
       </c>
       <c r="B101" s="3">
         <v>451</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>17</v>
@@ -7008,7 +7086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7017,7 +7095,8 @@
     <col min="4" max="4" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="57.6640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="57.6640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.83203125" style="4" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5" style="10" bestFit="1" customWidth="1"/>
   </cols>
@@ -11058,6 +11137,322 @@
       </c>
       <c r="J135" s="10" t="d">
         <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A136" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B136" s="3">
+        <v>23</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D136" s="3">
+        <v>22</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J136" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B137" s="3">
+        <v>42</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D137" s="3">
+        <v>16</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J137" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B138" s="3">
+        <v>42</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" s="3">
+        <v>34</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B139" s="3">
+        <v>42</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D139" s="3">
+        <v>62</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B140" s="3">
+        <v>46</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D140" s="3">
+        <v>65</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J140" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B141" s="3">
+        <v>46</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D141" s="3">
+        <v>32</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J141" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B142" s="3">
+        <v>46</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D142" s="3">
+        <v>44</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J142" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B143" s="3">
+        <v>46</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D143" s="3">
+        <v>49</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J143" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B144" s="3">
+        <v>46</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D144" s="3">
+        <v>84</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J144" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B145" s="3">
+        <v>46</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D145" s="3">
+        <v>86</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J145" s="10" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B146" s="3">
+        <v>451</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D146" s="3">
+        <v>125</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{678A28BB-CAB4-D245-9C40-C1B134D3820A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F5AF51C8-2C12-1D44-8044-7CDEFFA3AFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2237" uniqueCount="426">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2251" uniqueCount="427">
   <si>
     <t>reviewer</t>
   </si>
@@ -1332,6 +1332,9 @@
   </si>
   <si>
     <t>All inputs MUST set the nSequence to 0xFFFFFFFF (do not signal for BIP 125 RBF). [...] The batch creator MUST add a new dust UTXO input, and the resulting replacement transaction MUST satisfy BIP 125 RBF rules:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The counter-argument is that these new multi-signature transactions will be used in combination with OP_EVAL (see the OP_EVAL BIP), </t>
   </si>
 </sst>
 </file>
@@ -1850,7 +1853,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1879,14 +1882,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2312,13 +2312,13 @@
       <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -2333,7 +2333,7 @@
       <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="6" t="s">
@@ -7086,7 +7086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J146"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7098,7 +7098,7 @@
     <col min="7" max="7" width="57.6640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="41.83203125" style="4" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -7129,7 +7129,7 @@
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7219,37 +7219,37 @@
       <c r="I4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="3">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="3">
-        <v>11</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>154</v>
+        <v>426</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>16</v>
+      <c r="J5" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -7257,13 +7257,13 @@
         <v>219</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>128</v>
@@ -7272,16 +7272,16 @@
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>403</v>
+        <v>154</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>219</v>
       </c>
@@ -7292,28 +7292,25 @@
         <v>219</v>
       </c>
       <c r="D7" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="10" t="d">
+      <c r="J7" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>219</v>
       </c>
@@ -7324,21 +7321,24 @@
         <v>219</v>
       </c>
       <c r="D8" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="10" t="d">
+      <c r="J8" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -7347,31 +7347,31 @@
         <v>219</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D9" s="3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>154</v>
+        <v>405</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J9" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>219</v>
       </c>
@@ -7382,25 +7382,25 @@
         <v>219</v>
       </c>
       <c r="D10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>219</v>
       </c>
@@ -7411,36 +7411,36 @@
         <v>219</v>
       </c>
       <c r="D11" s="3">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="3">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="3">
         <v>13</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="3">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D12" s="3">
-        <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>128</v>
@@ -7449,10 +7449,16 @@
         <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>219</v>
       </c>
@@ -7463,19 +7469,25 @@
         <v>219</v>
       </c>
       <c r="D13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>219</v>
       </c>
@@ -7486,22 +7498,25 @@
         <v>219</v>
       </c>
       <c r="D14" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>219</v>
       </c>
@@ -7512,48 +7527,57 @@
         <v>219</v>
       </c>
       <c r="D15" s="3">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B16" s="3">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="3">
         <v>16</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B16" s="3">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="3">
-        <v>11</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J16" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>219</v>
       </c>
@@ -7564,25 +7588,25 @@
         <v>219</v>
       </c>
       <c r="D17" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>219</v>
       </c>
@@ -7593,28 +7617,25 @@
         <v>219</v>
       </c>
       <c r="D18" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>219</v>
       </c>
@@ -7625,24 +7646,24 @@
         <v>219</v>
       </c>
       <c r="D19" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7657,24 +7678,24 @@
         <v>219</v>
       </c>
       <c r="D20" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>140</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7683,80 +7704,95 @@
         <v>219</v>
       </c>
       <c r="B21" s="3">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="3">
+        <v>17</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" s="3">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="C22" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="3">
         <v>11</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B23" s="3">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="C23" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="3">
         <v>21</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="10" t="s">
+      <c r="I23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="3">
-        <v>21</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D23" s="3">
-        <v>20</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>219</v>
       </c>
@@ -7767,48 +7803,54 @@
         <v>219</v>
       </c>
       <c r="D24" s="3">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B25" s="3">
         <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D25" s="3">
-        <v>10</v>
+        <v>321</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>149</v>
+        <v>413</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J25" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>222</v>
       </c>
@@ -7819,25 +7861,25 @@
         <v>222</v>
       </c>
       <c r="D26" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>248</v>
+        <v>149</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>222</v>
       </c>
@@ -7845,28 +7887,28 @@
         <v>21</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D27" s="3">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>149</v>
+        <v>248</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>222</v>
       </c>
@@ -7877,7 +7919,7 @@
         <v>219</v>
       </c>
       <c r="D28" s="3">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>118</v>
@@ -7886,12 +7928,12 @@
         <v>146</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7903,7 +7945,7 @@
         <v>21</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D29" s="3">
         <v>39</v>
@@ -7920,43 +7962,40 @@
       <c r="I29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B30" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D30" s="3">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J30" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J30" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>219</v>
       </c>
@@ -7967,7 +8006,7 @@
         <v>219</v>
       </c>
       <c r="D31" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>128</v>
@@ -7976,15 +8015,15 @@
         <v>37</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="10" t="s">
+      <c r="J31" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7999,7 +8038,7 @@
         <v>219</v>
       </c>
       <c r="D32" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>128</v>
@@ -8008,45 +8047,45 @@
         <v>37</v>
       </c>
       <c r="G32" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="3">
+        <v>22</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="3">
+        <v>34</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="10" t="s">
+      <c r="I33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="3">
-        <v>31</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="3">
-        <v>14</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -8054,13 +8093,13 @@
         <v>219</v>
       </c>
       <c r="B34" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D34" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>118</v>
@@ -8069,30 +8108,27 @@
         <v>37</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>122</v>
+        <v>416</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J34" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B35" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D35" s="3">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>118</v>
@@ -8101,18 +8137,21 @@
         <v>37</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>151</v>
+        <v>119</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3">
         <v>39</v>
@@ -8121,25 +8160,28 @@
         <v>219</v>
       </c>
       <c r="D36" s="3">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>152</v>
+        <v>121</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="10" t="s">
+      <c r="J36" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>222</v>
       </c>
@@ -8150,65 +8192,65 @@
         <v>219</v>
       </c>
       <c r="D37" s="3">
-        <v>173</v>
+        <v>32</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>249</v>
+        <v>151</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J37" s="10" t="s">
+      <c r="J37" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B38" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D38" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B39" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D39" s="3">
-        <v>44</v>
+        <v>173</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>128</v>
@@ -8217,15 +8259,12 @@
         <v>37</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -8234,109 +8273,100 @@
         <v>219</v>
       </c>
       <c r="B40" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D40" s="3">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>125</v>
+        <v>417</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J40" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J40" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B41" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D41" s="3">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>127</v>
+        <v>417</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J41" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J41" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B42" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D42" s="3">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>130</v>
+        <v>417</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J42" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J42" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B43" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D43" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>118</v>
@@ -8345,50 +8375,53 @@
         <v>37</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B44" s="3">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D44" s="3">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>244</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J44" s="10" t="s">
+      <c r="J44" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="3">
         <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B45" s="3">
-        <v>49</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>219</v>
@@ -8403,24 +8436,24 @@
         <v>37</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>231</v>
+        <v>124</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J45" s="10" t="s">
+      <c r="J45" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="3">
         <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" s="3">
-        <v>49</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>219</v>
@@ -8429,91 +8462,97 @@
         <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>232</v>
+        <v>126</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B47" s="3">
-        <v>49</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D47" s="3">
         <v>44</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B48" s="3">
+        <v>44</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" s="3">
+        <v>44</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B48" s="3">
-        <v>49</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D48" s="3">
-        <v>132</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J48" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J48" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B49" s="3">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D49" s="3">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>118</v>
@@ -8522,77 +8561,71 @@
         <v>37</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>167</v>
+        <v>420</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J49" s="10" t="s">
+      <c r="J49" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="3">
         <v>44</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B50" s="3">
-        <v>73</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D50" s="3">
-        <v>70</v>
-      </c>
       <c r="E50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" s="3">
+        <v>49</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="170" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B51" s="3">
-        <v>74</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D51" s="3">
-        <v>70</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F51" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>172</v>
+        <v>424</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="10" t="s">
-        <v>44</v>
+      <c r="J51" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -8600,13 +8633,13 @@
         <v>219</v>
       </c>
       <c r="B52" s="3">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D52" s="3">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>118</v>
@@ -8615,16 +8648,16 @@
         <v>37</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>131</v>
+        <v>419</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>132</v>
+        <v>418</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="10" t="s">
-        <v>50</v>
+      <c r="J52" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -8632,109 +8665,100 @@
         <v>219</v>
       </c>
       <c r="B53" s="3">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D53" s="3">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>134</v>
+        <v>422</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J53" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B54" s="3">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D54" s="3">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>136</v>
+        <v>423</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J54" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J54" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B55" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D55" s="3">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J55" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J55" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B56" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D56" s="3">
-        <v>321</v>
+        <v>32</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>118</v>
@@ -8743,120 +8767,117 @@
         <v>37</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J56" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J56" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B57" s="3">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D57" s="3">
-        <v>324</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J57" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J57" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B58" s="3">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D58" s="3">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J58" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J58" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B59" s="3">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D59" s="3">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H59" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="3">
+        <v>49</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" s="3">
         <v>141</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B60" s="3">
-        <v>111</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D60" s="3">
-        <v>37</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>118</v>
@@ -8865,76 +8886,76 @@
         <v>37</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="J60" s="8" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B61" s="3">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D61" s="3">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E61" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B62" s="3">
+        <v>74</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" s="3">
+        <v>70</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B62" s="3">
-        <v>112</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D62" s="3">
-        <v>65</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="10" t="s">
+      <c r="J62" s="8" t="s">
         <v>44</v>
       </c>
     </row>
@@ -8943,13 +8964,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D63" s="3">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>118</v>
@@ -8958,45 +8979,48 @@
         <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>176</v>
+        <v>131</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J63" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J63" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B64" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D64" s="3">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J64" s="10" t="s">
-        <v>44</v>
+      <c r="J64" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9004,13 +9028,13 @@
         <v>219</v>
       </c>
       <c r="B65" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D65" s="3">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>118</v>
@@ -9019,126 +9043,123 @@
         <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" s="3">
+        <v>77</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" s="3">
         <v>174</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B66" s="3">
-        <v>113</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D66" s="3">
-        <v>65</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J66" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B67" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D67" s="3">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J67" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B68" s="3">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D68" s="3">
-        <v>112</v>
+        <v>324</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J68" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B69" s="3">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D69" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>118</v>
@@ -9147,77 +9168,74 @@
         <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J69" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B70" s="3">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D70" s="3">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J70" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B71" s="3">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D71" s="3">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="10" t="s">
-        <v>32</v>
+      <c r="J71" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9225,13 +9243,13 @@
         <v>219</v>
       </c>
       <c r="B72" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D72" s="3">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>118</v>
@@ -9240,21 +9258,24 @@
         <v>37</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J72" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B73" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>219</v>
@@ -9266,16 +9287,19 @@
         <v>128</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="10" t="s">
-        <v>32</v>
+      <c r="J73" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -9283,100 +9307,100 @@
         <v>219</v>
       </c>
       <c r="B74" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D74" s="3">
+        <v>68</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" s="3">
         <v>112</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B75" s="3">
-        <v>119</v>
-      </c>
       <c r="C75" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D75" s="3">
-        <v>341</v>
+        <v>113</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J75" s="10" t="s">
+      <c r="J75" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" s="3">
+        <v>113</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" s="3">
+        <v>9</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B76" s="3">
-        <v>119</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D76" s="3">
-        <v>346</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B77" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>219</v>
@@ -9388,18 +9412,18 @@
         <v>128</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="10" t="s">
+      <c r="J77" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9408,7 +9432,7 @@
         <v>219</v>
       </c>
       <c r="B78" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>219</v>
@@ -9417,18 +9441,21 @@
         <v>68</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>197</v>
+        <v>180</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J78" s="10" t="s">
+      <c r="J78" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9437,7 +9464,7 @@
         <v>219</v>
       </c>
       <c r="B79" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>219</v>
@@ -9449,44 +9476,47 @@
         <v>128</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>195</v>
+        <v>180</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J79" s="10" t="s">
+      <c r="J79" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B80" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D80" s="3">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J80" s="10" t="s">
+      <c r="J80" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9495,42 +9525,45 @@
         <v>219</v>
       </c>
       <c r="B81" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D81" s="3">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J81" s="10" t="s">
+      <c r="J81" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B82" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D82" s="3">
-        <v>433</v>
+        <v>112</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>128</v>
@@ -9539,41 +9572,44 @@
         <v>146</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>199</v>
+        <v>185</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J82" s="10" t="s">
+      <c r="J82" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B83" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D83" s="3">
-        <v>443</v>
+        <v>141</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J83" s="10" t="s">
+      <c r="J83" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9582,13 +9618,13 @@
         <v>219</v>
       </c>
       <c r="B84" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D84" s="3">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>128</v>
@@ -9597,59 +9633,56 @@
         <v>37</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H84" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J84" s="10" t="s">
+      <c r="J84" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B85" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D85" s="3">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J85" s="10" t="s">
+      <c r="J85" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B86" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D86" s="3">
-        <v>47</v>
+        <v>341</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>128</v>
@@ -9658,62 +9691,62 @@
         <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J86" s="10" t="s">
+      <c r="J86" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B87" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D87" s="3">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J87" s="10" t="s">
+      <c r="J87" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B88" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D88" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>128</v>
@@ -9722,30 +9755,30 @@
         <v>37</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J88" s="10" t="s">
+      <c r="J88" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B89" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D89" s="3">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>118</v>
@@ -9754,15 +9787,12 @@
         <v>37</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J89" s="10" t="s">
+      <c r="J89" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9771,91 +9801,85 @@
         <v>219</v>
       </c>
       <c r="B90" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D90" s="3">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="10" t="s">
+      <c r="J90" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B91" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D91" s="3">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J91" s="10" t="s">
+      <c r="J91" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B92" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D92" s="3">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="10" t="s">
+      <c r="J92" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9864,42 +9888,42 @@
         <v>219</v>
       </c>
       <c r="B93" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D93" s="3">
-        <v>141</v>
+        <v>433</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J93" s="10" t="s">
+      <c r="J93" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B94" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D94" s="3">
-        <v>37</v>
+        <v>443</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>128</v>
@@ -9908,288 +9932,309 @@
         <v>37</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J94" s="10" t="s">
+      <c r="J94" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B95" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D95" s="3">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>239</v>
+        <v>202</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J95" s="10" t="s">
+      <c r="J95" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B96" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D96" s="3">
-        <v>157</v>
+        <v>16</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J96" s="10" t="s">
+      <c r="J96" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B97" s="3">
-        <v>197</v>
-      </c>
-      <c r="C97" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D97" s="3">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>215</v>
+        <v>205</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J97" s="10" t="s">
+      <c r="J97" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B98" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D98" s="3">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>251</v>
+        <v>205</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J98" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J98" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B99" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D99" s="3">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>252</v>
+        <v>205</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J99" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J99" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B100" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D100" s="3">
-        <v>323</v>
+        <v>141</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>250</v>
+        <v>200</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J100" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B101" s="3">
-        <v>321</v>
-      </c>
-      <c r="C101" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D101" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>245</v>
+        <v>210</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J101" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J101" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B102" s="3">
-        <v>321</v>
-      </c>
-      <c r="C102" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D102" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J102" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J102" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B103" s="3">
-        <v>321</v>
+        <v>145</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D103" s="3">
-        <v>351</v>
+        <v>23</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>242</v>
+        <v>212</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J103" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J103" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B104" s="3">
-        <v>321</v>
+        <v>145</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D104" s="3">
-        <v>352</v>
+        <v>141</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>128</v>
@@ -10198,106 +10243,100 @@
         <v>37</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J104" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J104" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B105" s="3">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D105" s="3">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F105" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B106" s="3">
+        <v>158</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D106" s="3">
+        <v>141</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G105" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J105" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B106" s="3">
-        <v>324</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D106" s="3">
-        <v>151</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J106" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J106" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B107" s="3">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D107" s="3">
-        <v>340</v>
+        <v>157</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J107" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J107" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10305,56 +10344,56 @@
         <v>219</v>
       </c>
       <c r="B108" s="3">
-        <v>330</v>
-      </c>
-      <c r="C108" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C108" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D108" s="3">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="E108" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B109" s="3">
+        <v>320</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D109" s="3">
+        <v>8</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J108" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B109" s="3">
-        <v>330</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D109" s="3">
-        <v>339</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F109" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J109" s="10" t="d">
+      <c r="J109" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -10363,144 +10402,144 @@
         <v>219</v>
       </c>
       <c r="B110" s="3">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D110" s="3">
-        <v>340</v>
+        <v>9</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J110" s="10" t="d">
+      <c r="J110" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B111" s="3">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D111" s="3">
-        <v>133</v>
+        <v>323</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J111" s="10" t="d">
+      <c r="J111" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B112" s="3">
-        <v>331</v>
-      </c>
-      <c r="C112" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C112" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D112" s="3">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J112" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J112" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B113" s="3">
-        <v>331</v>
-      </c>
-      <c r="C113" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C113" s="9" t="s">
         <v>219</v>
       </c>
       <c r="D113" s="3">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J113" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J113" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B114" s="3">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D114" s="3">
-        <v>3</v>
+        <v>351</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J114" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J114" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10508,31 +10547,28 @@
         <v>219</v>
       </c>
       <c r="B115" s="3">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D115" s="3">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J115" s="10" t="d">
-        <v>2026-06-29</v>
+      <c r="J115" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10540,91 +10576,91 @@
         <v>219</v>
       </c>
       <c r="B116" s="3">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D116" s="3">
-        <v>341</v>
+        <v>31</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J116" s="10" t="d">
+      <c r="J116" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B117" s="3">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D117" s="3">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>264</v>
+        <v>143</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J117" s="10" t="d">
+      <c r="J117" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B118" s="3">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D118" s="3">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>266</v>
+        <v>144</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J118" s="10" t="d">
+      <c r="J118" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -10633,13 +10669,13 @@
         <v>219</v>
       </c>
       <c r="B119" s="3">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D119" s="3">
-        <v>321</v>
+        <v>141</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>128</v>
@@ -10648,207 +10684,201 @@
         <v>146</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J119" s="10" t="d">
+      <c r="J119" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B120" s="3">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D120" s="3">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J120" s="10" t="d">
+      <c r="J120" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B121" s="3">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D121" s="3">
-        <v>32</v>
+        <v>340</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>288</v>
+        <v>253</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J121" s="10" t="d">
+      <c r="J121" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B122" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D122" s="3">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J122" s="10" t="d">
+      <c r="J122" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B123" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D123" s="3">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J123" s="10" t="d">
+      <c r="J123" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B124" s="3">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D124" s="3">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J124" s="10" t="d">
+      <c r="J124" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B125" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D125" s="3">
-        <v>341</v>
+        <v>3</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J125" s="10" t="d">
+      <c r="J125" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B126" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D126" s="3">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>118</v>
@@ -10857,30 +10887,30 @@
         <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J126" s="10" t="d">
+      <c r="J126" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B127" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D127" s="3">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>118</v>
@@ -10889,27 +10919,30 @@
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>269</v>
+        <v>260</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J127" s="10" t="d">
+      <c r="J127" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B128" s="3">
-        <v>392</v>
+        <v>347</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D128" s="3">
-        <v>380</v>
+        <v>342</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>118</v>
@@ -10918,70 +10951,73 @@
         <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>273</v>
+        <v>261</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>264</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="10" t="d">
+      <c r="J128" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B129" s="3">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D129" s="3">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="E129" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J129" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B130" s="3">
+        <v>353</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" s="3">
+        <v>321</v>
+      </c>
+      <c r="E130" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F130" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G129" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="I129" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J129" s="10" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B130" s="3">
-        <v>440</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="3">
-        <v>342</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G130" s="4" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J130" s="10" t="d">
+      <c r="J130" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -10990,59 +11026,62 @@
         <v>219</v>
       </c>
       <c r="B131" s="3">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D131" s="3">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>279</v>
+        <v>284</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="10" t="d">
+      <c r="J131" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B132" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D132" s="3">
-        <v>327</v>
+        <v>32</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="10" t="d">
+      <c r="J132" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -11051,13 +11090,13 @@
         <v>219</v>
       </c>
       <c r="B133" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D133" s="3">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>118</v>
@@ -11066,15 +11105,12 @@
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J133" s="10" t="d">
+      <c r="J133" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -11083,13 +11119,13 @@
         <v>219</v>
       </c>
       <c r="B134" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D134" s="3">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>118</v>
@@ -11098,44 +11134,41 @@
         <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J134" s="10" t="d">
+      <c r="J134" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B135" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D135" s="3">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J135" s="10" t="d">
+      <c r="J135" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
@@ -11144,13 +11177,13 @@
         <v>219</v>
       </c>
       <c r="B136" s="3">
-        <v>23</v>
+        <v>392</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D136" s="3">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>118</v>
@@ -11159,13 +11192,13 @@
         <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>416</v>
+        <v>272</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J136" s="10" t="d">
-        <v>2026-06-30</v>
+      <c r="J136" s="8" t="d">
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11173,205 +11206,208 @@
         <v>219</v>
       </c>
       <c r="B137" s="3">
-        <v>42</v>
+        <v>392</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D137" s="3">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="E137" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J137" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A138" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B138" s="3">
+        <v>392</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" s="3">
+        <v>352</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B139" s="3">
+        <v>392</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D139" s="3">
+        <v>380</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A140" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B140" s="3">
+        <v>392</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D140" s="3">
+        <v>390</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F137" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J137" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B138" s="3">
-        <v>42</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D138" s="3">
-        <v>34</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J138" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A139" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B139" s="3">
-        <v>42</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D139" s="3">
-        <v>62</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I139" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J139" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A140" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B140" s="3">
-        <v>46</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D140" s="3">
-        <v>65</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F140" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>418</v>
+        <v>274</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J140" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J140" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B141" s="3">
-        <v>46</v>
+        <v>440</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D141" s="3">
-        <v>32</v>
+        <v>342</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>420</v>
+        <v>275</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J141" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J141" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B142" s="3">
-        <v>46</v>
+        <v>443</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D142" s="3">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>421</v>
+        <v>279</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J142" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J142" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B143" s="3">
-        <v>46</v>
+        <v>443</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D143" s="3">
-        <v>49</v>
+        <v>327</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>424</v>
+        <v>280</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>281</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J143" s="10" t="d">
-        <v>2026-06-30</v>
+      <c r="J143" s="8" t="d">
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -11379,96 +11415,137 @@
         <v>219</v>
       </c>
       <c r="B144" s="3">
-        <v>46</v>
+        <v>443</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D144" s="3">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>422</v>
+        <v>277</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J144" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J144" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B145" s="3">
-        <v>46</v>
+        <v>443</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D145" s="3">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>423</v>
+        <v>276</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J145" s="10" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J145" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B146" s="3">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D146" s="3">
-        <v>125</v>
+        <v>345</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F146" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J146" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B147" s="3">
+        <v>451</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D147" s="3">
+        <v>125</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F147" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="G147" s="4" t="s">
         <v>425</v>
       </c>
+      <c r="I147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J147" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J92" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J92">
-      <sortCondition ref="B2:B92"/>
-      <sortCondition ref="A2:A92"/>
-      <sortCondition ref="D2:D92"/>
-      <sortCondition ref="C2:C92"/>
+  <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J93">
+      <sortCondition ref="B2:B93"/>
+      <sortCondition ref="A2:A93"/>
+      <sortCondition ref="D2:D93"/>
+      <sortCondition ref="C2:C93"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J135">
-    <sortCondition ref="B2:B135"/>
-    <sortCondition ref="A2:A135"/>
-    <sortCondition ref="D2:D135"/>
-    <sortCondition ref="C2:C135"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J147">
+    <sortCondition ref="B2:B147"/>
+    <sortCondition ref="A2:A147"/>
+    <sortCondition ref="D2:D147"/>
+    <sortCondition ref="C2:C147"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F5AF51C8-2C12-1D44-8044-7CDEFFA3AFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2186B10A-E0CA-CF43-A5F8-E92BCEE27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41060" yWindow="620" windowWidth="35720" windowHeight="31760" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2251" uniqueCount="427">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2301" uniqueCount="436">
   <si>
     <t>reviewer</t>
   </si>
@@ -681,9 +681,6 @@
   </si>
   <si>
     <t>This BIP describes a script for generalized debt agreement contract based on Hashed Time-Lock Contract (BIP 199) transactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The filter construction proposed is an alternative to Bloom filters, as used in BIP 37 [... ]Bloom Filters are perhaps the best known probabilistic data structure for testing set membership, and were introduced into the Bitcoin protocol with BIP 37. </t>
   </si>
   <si>
     <t>ip_source</t>
@@ -1335,6 +1332,36 @@
   </si>
   <si>
     <t xml:space="preserve">The counter-argument is that these new multi-signature transactions will be used in combination with OP_EVAL (see the OP_EVAL BIP), </t>
+  </si>
+  <si>
+    <t>The same mechanism as in BIP 0034 is used to introduce v3 blocks.</t>
+  </si>
+  <si>
+    <t>When combined with Bloom filtering this can be reasonably efficient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The filter construction proposed is an alternative to Bloom filters, as used in BIP 37 [... ] Bloom Filters are perhaps the best known probabilistic data structure for testing set membership, and were introduced into the Bitcoin protocol with BIP 37. </t>
+  </si>
+  <si>
+    <t>Bloom filtering is defined in BIP37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment We reuse the double-threshold switchover mechanism from BIP 34, with the same thresholds, but for nVersion = 3. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This proposal has the added benefit of reducing transaction malleability (see BIP 62). [...] This document is extracted from the previous BIP62 proposal, which had input from various people, in particular Greg Maxwell and Peter Todd, who gave feedback about this document as well. </t>
+  </si>
+  <si>
+    <t>Pay-to-script-hash (BIP-0011[1]) is a transaction type that allows funding of arbitrary scripts, where the recipient carries the cost of fee's associated with using longer, more complex scripts.  [...] References ^ BIP-0011</t>
+  </si>
+  <si>
+    <t>Multi-signature pay-to-script-hash transactions are defined in BIP-0016[2]. [...] References [...] ^ BIP-0016</t>
+  </si>
+  <si>
+    <t>Usage &amp; Implementations  BIP-0045 - Structure for Deterministic P2SH Multisignature Wallets</t>
+  </si>
+  <si>
+    <t>BIP67 references BIP11 as the original standard for multisignature transactions to provide context, but its specification builds on P2SH redeem scripts defined by BIP16 rather than depending on BIP11.</t>
   </si>
 </sst>
 </file>
@@ -1933,7 +1960,21 @@
     <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2304,10 +2345,10 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>0</v>
@@ -2357,7 +2398,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
@@ -2390,21 +2431,21 @@
         <v>2016-04-26</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3">
         <v>11</v>
@@ -2431,7 +2472,7 @@
         <v>27</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>22</v>
@@ -2446,7 +2487,7 @@
         <v>42</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P3" s="7">
         <v>0</v>
@@ -2454,7 +2495,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3">
         <v>12</v>
@@ -2504,7 +2545,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
@@ -2531,7 +2572,7 @@
         <v>37</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>22</v>
@@ -2546,7 +2587,7 @@
         <v>42</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P5" s="7">
         <v>3</v>
@@ -2554,7 +2595,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -2604,7 +2645,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
@@ -2651,7 +2692,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
@@ -2678,10 +2719,10 @@
         <v>37</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>23</v>
@@ -2693,7 +2734,7 @@
         <v>25</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P8" s="7">
         <v>4</v>
@@ -2701,7 +2742,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3">
         <v>18</v>
@@ -2751,7 +2792,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="3">
         <v>19</v>
@@ -2778,10 +2819,10 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>23</v>
@@ -2793,7 +2834,7 @@
         <v>42</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P10" s="7">
         <v>1</v>
@@ -2801,7 +2842,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="3">
         <v>20</v>
@@ -2851,7 +2892,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3">
         <v>21</v>
@@ -2878,10 +2919,10 @@
         <v>37</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>23</v>
@@ -2901,7 +2942,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B13" s="3">
         <v>21</v>
@@ -2934,21 +2975,21 @@
         <v>2019-06-25</v>
       </c>
       <c r="L13" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="3">
         <v>22</v>
@@ -2998,7 +3039,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B15" s="3">
         <v>23</v>
@@ -3025,7 +3066,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>45</v>
@@ -3040,7 +3081,7 @@
         <v>46</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P15" s="7">
         <v>1</v>
@@ -3048,7 +3089,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3">
         <v>30</v>
@@ -3098,7 +3139,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B17" s="3">
         <v>31</v>
@@ -3148,7 +3189,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" s="3">
         <v>33</v>
@@ -3175,10 +3216,10 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>23</v>
@@ -3190,7 +3231,7 @@
         <v>30</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P18" s="7">
         <v>1</v>
@@ -3198,7 +3239,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B19" s="3">
         <v>34</v>
@@ -3225,10 +3266,10 @@
         <v>27</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>29</v>
@@ -3240,7 +3281,7 @@
         <v>25</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P19" s="7">
         <v>0</v>
@@ -3248,7 +3289,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" s="3">
         <v>35</v>
@@ -3275,10 +3316,10 @@
         <v>27</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>29</v>
@@ -3290,7 +3331,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P20" s="7">
         <v>0</v>
@@ -3298,7 +3339,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B21" s="3">
         <v>37</v>
@@ -3325,10 +3366,10 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>29</v>
@@ -3340,7 +3381,7 @@
         <v>30</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P21" s="7">
         <v>1</v>
@@ -3348,7 +3389,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="3">
         <v>39</v>
@@ -3398,7 +3439,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" s="3">
         <v>39</v>
@@ -3431,21 +3472,21 @@
         <v>2017-12-18</v>
       </c>
       <c r="L23" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" s="3">
         <v>42</v>
@@ -3472,10 +3513,10 @@
         <v>37</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>29</v>
@@ -3487,7 +3528,7 @@
         <v>25</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="P24" s="7">
         <v>3</v>
@@ -3495,7 +3536,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B25" s="3">
         <v>43</v>
@@ -3545,7 +3586,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B26" s="3">
         <v>44</v>
@@ -3595,7 +3636,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B27" s="3">
         <v>44</v>
@@ -3628,21 +3669,21 @@
         <v>2014-07-09</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>34</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B28" s="3">
         <v>46</v>
@@ -3669,10 +3710,10 @@
         <v>37</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>66</v>
@@ -3684,7 +3725,7 @@
         <v>42</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P28" s="7">
         <v>6</v>
@@ -3692,7 +3733,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B29" s="3">
         <v>49</v>
@@ -3742,11 +3783,17 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B30" s="3">
         <v>52</v>
       </c>
+      <c r="C30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E30" s="7" t="s">
         <v>17</v>
       </c>
@@ -3763,10 +3810,10 @@
         <v>27</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>66</v>
@@ -3775,10 +3822,10 @@
         <v>24</v>
       </c>
       <c r="N30" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="O30" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="P30" s="7">
         <v>0</v>
@@ -3786,11 +3833,17 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="3">
         <v>61</v>
       </c>
+      <c r="C31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E31" s="7" t="s">
         <v>17</v>
       </c>
@@ -3807,10 +3860,10 @@
         <v>27</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>29</v>
@@ -3822,7 +3875,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P31" s="7">
         <v>0</v>
@@ -3830,11 +3883,17 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="3">
         <v>62</v>
       </c>
+      <c r="C32" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E32" s="7" t="s">
         <v>17</v>
       </c>
@@ -3851,10 +3910,10 @@
         <v>20</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>23</v>
@@ -3866,7 +3925,7 @@
         <v>25</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P32" s="7">
         <v>1</v>
@@ -3874,11 +3933,17 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="3">
         <v>64</v>
       </c>
+      <c r="C33" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E33" s="7" t="s">
         <v>17</v>
       </c>
@@ -3895,10 +3960,10 @@
         <v>20</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>23</v>
@@ -3910,7 +3975,7 @@
         <v>30</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P33" s="7">
         <v>1</v>
@@ -3918,11 +3983,17 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" s="3">
         <v>66</v>
       </c>
+      <c r="C34" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E34" s="7" t="s">
         <v>17</v>
       </c>
@@ -3939,10 +4010,10 @@
         <v>37</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>29</v>
@@ -3954,7 +4025,7 @@
         <v>25</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P34" s="7">
         <v>2</v>
@@ -3962,11 +4033,17 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="3">
         <v>67</v>
       </c>
+      <c r="C35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E35" s="7" t="s">
         <v>17</v>
       </c>
@@ -3983,10 +4060,10 @@
         <v>37</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>39</v>
@@ -3998,7 +4075,7 @@
         <v>42</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P35" s="7">
         <v>3</v>
@@ -4006,7 +4083,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>71</v>
@@ -4027,10 +4104,10 @@
         <v>27</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>29</v>
@@ -4042,7 +4119,7 @@
         <v>42</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P36" s="7">
         <v>0</v>
@@ -4050,7 +4127,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3">
         <v>73</v>
@@ -4100,7 +4177,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3">
         <v>74</v>
@@ -4150,7 +4227,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B39" s="3">
         <v>77</v>
@@ -4200,7 +4277,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B40" s="3">
         <v>78</v>
@@ -4250,7 +4327,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" s="3">
         <v>87</v>
@@ -4271,10 +4348,10 @@
         <v>37</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>39</v>
@@ -4286,7 +4363,7 @@
         <v>42</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P41" s="7">
         <v>10</v>
@@ -4294,7 +4371,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B42" s="3">
         <v>89</v>
@@ -4315,10 +4392,10 @@
         <v>37</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>66</v>
@@ -4330,7 +4407,7 @@
         <v>42</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P42" s="7">
         <v>5</v>
@@ -4338,7 +4415,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="3">
         <v>91</v>
@@ -4359,10 +4436,10 @@
         <v>37</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>29</v>
@@ -4374,7 +4451,7 @@
         <v>25</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P43" s="7">
         <v>8</v>
@@ -4382,7 +4459,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" s="3">
         <v>98</v>
@@ -4403,10 +4480,10 @@
         <v>20</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>66</v>
@@ -4418,7 +4495,7 @@
         <v>25</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P44" s="7">
         <v>1</v>
@@ -4426,7 +4503,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B45" s="3">
         <v>100</v>
@@ -4447,10 +4524,10 @@
         <v>20</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>23</v>
@@ -4459,10 +4536,10 @@
         <v>24</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P45" s="7">
         <v>1</v>
@@ -4470,7 +4547,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B46" s="3">
         <v>102</v>
@@ -4491,10 +4568,10 @@
         <v>27</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>23</v>
@@ -4503,10 +4580,10 @@
         <v>24</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P46" s="7">
         <v>0</v>
@@ -4514,7 +4591,7 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B47" s="3">
         <v>103</v>
@@ -4535,10 +4612,10 @@
         <v>20</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>23</v>
@@ -4547,10 +4624,10 @@
         <v>24</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P47" s="7">
         <v>1</v>
@@ -4558,7 +4635,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B48" s="3">
         <v>104</v>
@@ -4579,10 +4656,10 @@
         <v>20</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>23</v>
@@ -4591,10 +4668,10 @@
         <v>24</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P48" s="7">
         <v>1</v>
@@ -4602,7 +4679,7 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3">
         <v>105</v>
@@ -4623,10 +4700,10 @@
         <v>37</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>23</v>
@@ -4635,10 +4712,10 @@
         <v>24</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P49" s="7">
         <v>2</v>
@@ -4646,7 +4723,7 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3">
         <v>107</v>
@@ -4667,10 +4744,10 @@
         <v>20</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>23</v>
@@ -4679,10 +4756,10 @@
         <v>24</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P50" s="7">
         <v>1</v>
@@ -4690,7 +4767,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B51" s="3">
         <v>111</v>
@@ -4740,7 +4817,7 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B52" s="3">
         <v>112</v>
@@ -4790,7 +4867,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" s="3">
         <v>113</v>
@@ -4840,7 +4917,7 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B54" s="3">
         <v>114</v>
@@ -4890,7 +4967,7 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B55" s="3">
         <v>115</v>
@@ -4911,10 +4988,10 @@
         <v>20</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>23</v>
@@ -4926,7 +5003,7 @@
         <v>25</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P55" s="7">
         <v>1</v>
@@ -4934,7 +5011,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B56" s="3">
         <v>117</v>
@@ -4955,10 +5032,10 @@
         <v>37</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>66</v>
@@ -4970,7 +5047,7 @@
         <v>25</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P56" s="7">
         <v>6</v>
@@ -4978,7 +5055,7 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B57" s="3">
         <v>119</v>
@@ -5028,7 +5105,7 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B58" s="3">
         <v>122</v>
@@ -5078,7 +5155,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="3">
         <v>125</v>
@@ -5099,10 +5176,10 @@
         <v>37</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>29</v>
@@ -5114,7 +5191,7 @@
         <v>42</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P59" s="7">
         <v>2</v>
@@ -5122,7 +5199,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="3">
         <v>127</v>
@@ -5143,10 +5220,10 @@
         <v>37</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>66</v>
@@ -5158,7 +5235,7 @@
         <v>42</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P60" s="7">
         <v>3</v>
@@ -5166,7 +5243,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B61" s="3">
         <v>128</v>
@@ -5216,7 +5293,7 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="3">
         <v>130</v>
@@ -5237,10 +5314,10 @@
         <v>27</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>29</v>
@@ -5252,7 +5329,7 @@
         <v>30</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P62" s="7">
         <v>0</v>
@@ -5260,7 +5337,7 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B63" s="3">
         <v>131</v>
@@ -5281,10 +5358,10 @@
         <v>27</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>23</v>
@@ -5293,10 +5370,10 @@
         <v>24</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P63" s="7">
         <v>0</v>
@@ -5304,7 +5381,7 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B64" s="3">
         <v>133</v>
@@ -5325,10 +5402,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>29</v>
@@ -5340,7 +5417,7 @@
         <v>30</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P64" s="7">
         <v>1</v>
@@ -5348,7 +5425,7 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B65" s="3">
         <v>134</v>
@@ -5369,10 +5446,10 @@
         <v>20</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L65" s="7" t="s">
         <v>23</v>
@@ -5381,10 +5458,10 @@
         <v>24</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P65" s="7">
         <v>1</v>
@@ -5392,7 +5469,7 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B66" s="3">
         <v>137</v>
@@ -5413,10 +5490,10 @@
         <v>20</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>29</v>
@@ -5428,7 +5505,7 @@
         <v>42</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P66" s="7">
         <v>1</v>
@@ -5436,7 +5513,7 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B67" s="3">
         <v>141</v>
@@ -5457,10 +5534,10 @@
         <v>37</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L67" s="7" t="s">
         <v>29</v>
@@ -5472,7 +5549,7 @@
         <v>25</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P67" s="7">
         <v>11</v>
@@ -5480,7 +5557,7 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="3">
         <v>142</v>
@@ -5530,7 +5607,7 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B69" s="3">
         <v>144</v>
@@ -5551,10 +5628,10 @@
         <v>37</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L69" s="7" t="s">
         <v>29</v>
@@ -5566,7 +5643,7 @@
         <v>30</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P69" s="7">
         <v>2</v>
@@ -5574,7 +5651,7 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B70" s="3">
         <v>145</v>
@@ -5624,7 +5701,7 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B71" s="3">
         <v>147</v>
@@ -5645,10 +5722,10 @@
         <v>37</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>29</v>
@@ -5660,7 +5737,7 @@
         <v>25</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P71" s="7">
         <v>5</v>
@@ -5668,7 +5745,7 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B72" s="3">
         <v>148</v>
@@ -5689,10 +5766,10 @@
         <v>37</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>29</v>
@@ -5704,7 +5781,7 @@
         <v>25</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P72" s="7">
         <v>5</v>
@@ -5712,7 +5789,7 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B73" s="3">
         <v>150</v>
@@ -5733,10 +5810,10 @@
         <v>20</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L73" s="7" t="s">
         <v>23</v>
@@ -5748,7 +5825,7 @@
         <v>30</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="P73" s="7">
         <v>1</v>
@@ -5756,7 +5833,7 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B74" s="3">
         <v>158</v>
@@ -5806,7 +5883,7 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B75" s="3">
         <v>159</v>
@@ -5827,10 +5904,10 @@
         <v>27</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>29</v>
@@ -5842,7 +5919,7 @@
         <v>30</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P75" s="7">
         <v>0</v>
@@ -5850,7 +5927,7 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B76" s="3">
         <v>171</v>
@@ -5871,10 +5948,10 @@
         <v>27</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>23</v>
@@ -5886,7 +5963,7 @@
         <v>42</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P76" s="7">
         <v>0</v>
@@ -5894,7 +5971,7 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B77" s="3">
         <v>174</v>
@@ -5915,10 +5992,10 @@
         <v>37</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L77" s="7" t="s">
         <v>29</v>
@@ -5930,7 +6007,7 @@
         <v>42</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="P77" s="7">
         <v>4</v>
@@ -5938,7 +6015,7 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B78" s="3">
         <v>197</v>
@@ -5988,7 +6065,7 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B79" s="3">
         <v>199</v>
@@ -6009,10 +6086,10 @@
         <v>27</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>23</v>
@@ -6024,7 +6101,7 @@
         <v>42</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P79" s="7">
         <v>0</v>
@@ -6032,7 +6109,7 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B80" s="3">
         <v>300</v>
@@ -6053,10 +6130,10 @@
         <v>20</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L80" s="7" t="s">
         <v>66</v>
@@ -6068,7 +6145,7 @@
         <v>25</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P80" s="7">
         <v>1</v>
@@ -6076,7 +6153,7 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B81" s="3">
         <v>301</v>
@@ -6097,10 +6174,10 @@
         <v>20</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>66</v>
@@ -6112,7 +6189,7 @@
         <v>25</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P81" s="7">
         <v>1</v>
@@ -6120,7 +6197,7 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B82" s="3">
         <v>320</v>
@@ -6167,7 +6244,7 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B83" s="3">
         <v>321</v>
@@ -6217,7 +6294,7 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B84" s="3">
         <v>323</v>
@@ -6238,10 +6315,10 @@
         <v>37</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>66</v>
@@ -6250,7 +6327,7 @@
         <v>24</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P84" s="7">
         <v>3</v>
@@ -6258,7 +6335,7 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B85" s="3">
         <v>324</v>
@@ -6308,7 +6385,7 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B86" s="3">
         <v>330</v>
@@ -6358,7 +6435,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B87" s="3">
         <v>331</v>
@@ -6408,7 +6485,7 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" s="3">
         <v>337</v>
@@ -6429,10 +6506,10 @@
         <v>27</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>66</v>
@@ -6444,7 +6521,7 @@
         <v>46</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P88" s="7">
         <v>0</v>
@@ -6452,7 +6529,7 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B89" s="3">
         <v>341</v>
@@ -6473,10 +6550,10 @@
         <v>37</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>29</v>
@@ -6488,7 +6565,7 @@
         <v>25</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="P89" s="7">
         <v>10</v>
@@ -6496,7 +6573,7 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B90" s="3">
         <v>343</v>
@@ -6517,10 +6594,10 @@
         <v>37</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L90" s="7" t="s">
         <v>29</v>
@@ -6532,7 +6609,7 @@
         <v>25</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P90" s="7">
         <v>6</v>
@@ -6540,7 +6617,7 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B91" s="3">
         <v>347</v>
@@ -6590,7 +6667,7 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B92" s="3">
         <v>353</v>
@@ -6640,7 +6717,7 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B93" s="3">
         <v>370</v>
@@ -6661,10 +6738,10 @@
         <v>20</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L93" s="7" t="s">
         <v>29</v>
@@ -6676,7 +6753,7 @@
         <v>42</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P93" s="7">
         <v>1</v>
@@ -6684,7 +6761,7 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B94" s="3">
         <v>371</v>
@@ -6705,10 +6782,10 @@
         <v>37</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>29</v>
@@ -6720,7 +6797,7 @@
         <v>42</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P94" s="7">
         <v>6</v>
@@ -6728,7 +6805,7 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B95" s="3">
         <v>374</v>
@@ -6749,10 +6826,10 @@
         <v>37</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>66</v>
@@ -6764,7 +6841,7 @@
         <v>42</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P95" s="7">
         <v>3</v>
@@ -6772,7 +6849,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B96" s="3">
         <v>375</v>
@@ -6822,7 +6899,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B97" s="3">
         <v>392</v>
@@ -6872,7 +6949,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B98" s="3">
         <v>440</v>
@@ -6922,7 +6999,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B99" s="3">
         <v>442</v>
@@ -6943,10 +7020,10 @@
         <v>37</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>66</v>
@@ -6958,7 +7035,7 @@
         <v>25</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P99" s="7">
         <v>10</v>
@@ -6966,7 +7043,7 @@
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B100" s="3">
         <v>443</v>
@@ -7016,7 +7093,7 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B101" s="3">
         <v>451</v>
@@ -7043,10 +7120,10 @@
         <v>20</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>66</v>
@@ -7058,7 +7135,7 @@
         <v>42</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P101" s="7">
         <v>1</v>
@@ -7076,8 +7153,13 @@
     <sortCondition ref="A2:A101"/>
   </sortState>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="manual">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="manual">
       <formula>NOT(ISERROR(SEARCH("manual",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"slips"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -7086,7 +7168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7106,13 +7188,13 @@
         <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>115</v>
@@ -7135,13 +7217,13 @@
     </row>
     <row r="2" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D2" s="3">
         <v>32</v>
@@ -7167,13 +7249,13 @@
     </row>
     <row r="3" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B3" s="3">
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D3" s="3">
         <v>39</v>
@@ -7185,7 +7267,7 @@
         <v>37</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>15</v>
@@ -7196,13 +7278,13 @@
     </row>
     <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D4" s="3">
         <v>39</v>
@@ -7214,7 +7296,7 @@
         <v>37</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -7225,13 +7307,13 @@
     </row>
     <row r="5" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3">
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D5" s="3">
         <v>12</v>
@@ -7243,7 +7325,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -7254,13 +7336,13 @@
     </row>
     <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D6" s="3">
         <v>11</v>
@@ -7283,13 +7365,13 @@
     </row>
     <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D7" s="3">
         <v>12</v>
@@ -7301,7 +7383,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
@@ -7312,13 +7394,13 @@
     </row>
     <row r="8" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D8" s="3">
         <v>16</v>
@@ -7330,10 +7412,10 @@
         <v>37</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>15</v>
@@ -7344,13 +7426,13 @@
     </row>
     <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D9" s="3">
         <v>17</v>
@@ -7362,7 +7444,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>15</v>
@@ -7373,13 +7455,13 @@
     </row>
     <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D10" s="3">
         <v>11</v>
@@ -7402,13 +7484,13 @@
     </row>
     <row r="11" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D11" s="3">
         <v>12</v>
@@ -7431,13 +7513,13 @@
     </row>
     <row r="12" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3">
         <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D12" s="3">
         <v>13</v>
@@ -7460,13 +7542,13 @@
     </row>
     <row r="13" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B13" s="3">
         <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D13" s="3">
         <v>11</v>
@@ -7478,7 +7560,7 @@
         <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>15</v>
@@ -7489,13 +7571,13 @@
     </row>
     <row r="14" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="3">
         <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D14" s="3">
         <v>12</v>
@@ -7507,7 +7589,7 @@
         <v>37</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>15</v>
@@ -7518,13 +7600,13 @@
     </row>
     <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B15" s="3">
         <v>17</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D15" s="3">
         <v>13</v>
@@ -7536,10 +7618,10 @@
         <v>37</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>410</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -7550,13 +7632,13 @@
     </row>
     <row r="16" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3">
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" s="3">
         <v>16</v>
@@ -7568,7 +7650,7 @@
         <v>37</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
@@ -7579,13 +7661,13 @@
     </row>
     <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B17" s="3">
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D17" s="3">
         <v>11</v>
@@ -7608,13 +7690,13 @@
     </row>
     <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" s="3">
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D18" s="3">
         <v>12</v>
@@ -7637,13 +7719,13 @@
     </row>
     <row r="19" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B19" s="3">
         <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D19" s="3">
         <v>13</v>
@@ -7669,13 +7751,13 @@
     </row>
     <row r="20" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" s="3">
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D20" s="3">
         <v>16</v>
@@ -7701,13 +7783,13 @@
     </row>
     <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B21" s="3">
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D21" s="3">
         <v>17</v>
@@ -7733,13 +7815,13 @@
     </row>
     <row r="22" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="3">
         <v>19</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D22" s="3">
         <v>11</v>
@@ -7751,10 +7833,10 @@
         <v>37</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
@@ -7765,13 +7847,13 @@
     </row>
     <row r="23" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B23" s="3">
         <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D23" s="3">
         <v>21</v>
@@ -7794,13 +7876,13 @@
     </row>
     <row r="24" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" s="3">
         <v>21</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D24" s="3">
         <v>20</v>
@@ -7812,7 +7894,7 @@
         <v>37</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>15</v>
@@ -7823,13 +7905,13 @@
     </row>
     <row r="25" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B25" s="3">
         <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D25" s="3">
         <v>321</v>
@@ -7841,7 +7923,7 @@
         <v>37</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -7852,13 +7934,13 @@
     </row>
     <row r="26" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B26" s="3">
         <v>21</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D26" s="3">
         <v>10</v>
@@ -7881,13 +7963,13 @@
     </row>
     <row r="27" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B27" s="3">
         <v>21</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D27" s="3">
         <v>11</v>
@@ -7899,7 +7981,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>15</v>
@@ -7910,13 +7992,13 @@
     </row>
     <row r="28" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B28" s="3">
         <v>21</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D28" s="3">
         <v>32</v>
@@ -7939,13 +8021,13 @@
     </row>
     <row r="29" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B29" s="3">
         <v>21</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D29" s="3">
         <v>39</v>
@@ -7968,13 +8050,13 @@
     </row>
     <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B30" s="3">
         <v>21</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D30" s="3">
         <v>39</v>
@@ -7997,13 +8079,13 @@
     </row>
     <row r="31" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="3">
         <v>22</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D31" s="3">
         <v>16</v>
@@ -8029,13 +8111,13 @@
     </row>
     <row r="32" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="3">
         <v>22</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D32" s="3">
         <v>23</v>
@@ -8061,13 +8143,13 @@
     </row>
     <row r="33" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="3">
         <v>22</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D33" s="3">
         <v>34</v>
@@ -8079,7 +8161,7 @@
         <v>37</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>15</v>
@@ -8090,13 +8172,13 @@
     </row>
     <row r="34" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" s="3">
         <v>23</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D34" s="3">
         <v>22</v>
@@ -8108,7 +8190,7 @@
         <v>37</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
@@ -8119,13 +8201,13 @@
     </row>
     <row r="35" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="3">
         <v>31</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D35" s="3">
         <v>14</v>
@@ -8151,13 +8233,13 @@
     </row>
     <row r="36" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3">
         <v>32</v>
@@ -8183,13 +8265,13 @@
     </row>
     <row r="37" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3">
         <v>39</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D37" s="3">
         <v>32</v>
@@ -8212,13 +8294,13 @@
     </row>
     <row r="38" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3">
         <v>39</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D38" s="3">
         <v>39</v>
@@ -8241,13 +8323,13 @@
     </row>
     <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>39</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D39" s="3">
         <v>173</v>
@@ -8259,7 +8341,7 @@
         <v>37</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>15</v>
@@ -8270,13 +8352,13 @@
     </row>
     <row r="40" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B40" s="3">
         <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D40" s="3">
         <v>16</v>
@@ -8288,7 +8370,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>15</v>
@@ -8299,13 +8381,13 @@
     </row>
     <row r="41" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" s="3">
         <v>42</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D41" s="3">
         <v>34</v>
@@ -8317,7 +8399,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>15</v>
@@ -8328,13 +8410,13 @@
     </row>
     <row r="42" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B42" s="3">
         <v>42</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D42" s="3">
         <v>62</v>
@@ -8346,7 +8428,7 @@
         <v>20</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
@@ -8357,13 +8439,13 @@
     </row>
     <row r="43" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="3">
         <v>43</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D43" s="3">
         <v>32</v>
@@ -8386,13 +8468,13 @@
     </row>
     <row r="44" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" s="3">
         <v>43</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D44" s="3">
         <v>44</v>
@@ -8404,10 +8486,10 @@
         <v>37</v>
       </c>
       <c r="G44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="H44" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
@@ -8418,13 +8500,13 @@
     </row>
     <row r="45" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B45" s="3">
         <v>44</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D45" s="3">
         <v>32</v>
@@ -8450,13 +8532,13 @@
     </row>
     <row r="46" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B46" s="3">
         <v>44</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D46" s="3">
         <v>43</v>
@@ -8482,13 +8564,13 @@
     </row>
     <row r="47" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B47" s="3">
         <v>44</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D47" s="3">
         <v>44</v>
@@ -8514,13 +8596,13 @@
     </row>
     <row r="48" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B48" s="3">
         <v>44</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D48" s="3">
         <v>44</v>
@@ -8543,13 +8625,13 @@
     </row>
     <row r="49" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3">
         <v>46</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D49" s="3">
         <v>32</v>
@@ -8561,7 +8643,7 @@
         <v>37</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>15</v>
@@ -8572,13 +8654,13 @@
     </row>
     <row r="50" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B50" s="3">
         <v>46</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D50" s="3">
         <v>44</v>
@@ -8590,7 +8672,7 @@
         <v>37</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
@@ -8601,13 +8683,13 @@
     </row>
     <row r="51" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B51" s="3">
         <v>46</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D51" s="3">
         <v>49</v>
@@ -8619,7 +8701,7 @@
         <v>37</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>15</v>
@@ -8630,13 +8712,13 @@
     </row>
     <row r="52" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B52" s="3">
         <v>46</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D52" s="3">
         <v>65</v>
@@ -8648,10 +8730,10 @@
         <v>37</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
@@ -8662,13 +8744,13 @@
     </row>
     <row r="53" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" s="3">
         <v>46</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D53" s="3">
         <v>84</v>
@@ -8680,7 +8762,7 @@
         <v>37</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
@@ -8691,13 +8773,13 @@
     </row>
     <row r="54" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B54" s="3">
         <v>46</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D54" s="3">
         <v>86</v>
@@ -8709,7 +8791,7 @@
         <v>37</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>15</v>
@@ -8720,13 +8802,13 @@
     </row>
     <row r="55" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B55" s="3">
         <v>49</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D55" s="3">
         <v>16</v>
@@ -8738,7 +8820,7 @@
         <v>146</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
@@ -8749,13 +8831,13 @@
     </row>
     <row r="56" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B56" s="3">
         <v>49</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D56" s="3">
         <v>32</v>
@@ -8767,7 +8849,7 @@
         <v>37</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>168</v>
@@ -8781,13 +8863,13 @@
     </row>
     <row r="57" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B57" s="3">
         <v>49</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D57" s="3">
         <v>43</v>
@@ -8799,7 +8881,7 @@
         <v>146</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>15</v>
@@ -8810,13 +8892,13 @@
     </row>
     <row r="58" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B58" s="3">
         <v>49</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D58" s="3">
         <v>44</v>
@@ -8828,7 +8910,7 @@
         <v>20</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
@@ -8839,13 +8921,13 @@
     </row>
     <row r="59" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="3">
         <v>49</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D59" s="3">
         <v>132</v>
@@ -8857,7 +8939,7 @@
         <v>146</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>15</v>
@@ -8868,13 +8950,13 @@
     </row>
     <row r="60" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="3">
         <v>49</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D60" s="3">
         <v>141</v>
@@ -8897,13 +8979,13 @@
     </row>
     <row r="61" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B61" s="3">
         <v>73</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D61" s="3">
         <v>70</v>
@@ -8929,13 +9011,13 @@
     </row>
     <row r="62" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B62" s="3">
         <v>74</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D62" s="3">
         <v>70</v>
@@ -8961,13 +9043,13 @@
     </row>
     <row r="63" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B63" s="3">
         <v>77</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D63" s="3">
         <v>21</v>
@@ -8993,13 +9075,13 @@
     </row>
     <row r="64" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B64" s="3">
         <v>77</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D64" s="3">
         <v>78</v>
@@ -9025,13 +9107,13 @@
     </row>
     <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B65" s="3">
         <v>77</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D65" s="3">
         <v>173</v>
@@ -9057,13 +9139,13 @@
     </row>
     <row r="66" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B66" s="3">
         <v>77</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D66" s="3">
         <v>174</v>
@@ -9089,13 +9171,13 @@
     </row>
     <row r="67" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B67" s="3">
         <v>77</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D67" s="3">
         <v>321</v>
@@ -9107,7 +9189,7 @@
         <v>37</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>132</v>
@@ -9121,13 +9203,13 @@
     </row>
     <row r="68" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="3">
         <v>77</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D68" s="3">
         <v>324</v>
@@ -9150,13 +9232,13 @@
     </row>
     <row r="69" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B69" s="3">
         <v>78</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D69" s="3">
         <v>21</v>
@@ -9168,7 +9250,7 @@
         <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
@@ -9179,13 +9261,13 @@
     </row>
     <row r="70" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B70" s="3">
         <v>78</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D70" s="3">
         <v>79</v>
@@ -9197,7 +9279,7 @@
         <v>37</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>141</v>
@@ -9211,13 +9293,13 @@
     </row>
     <row r="71" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B71" s="3">
         <v>111</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D71" s="3">
         <v>37</v>
@@ -9240,13 +9322,13 @@
     </row>
     <row r="72" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B72" s="3">
         <v>112</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D72" s="3">
         <v>9</v>
@@ -9272,13 +9354,13 @@
     </row>
     <row r="73" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B73" s="3">
         <v>112</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D73" s="3">
         <v>65</v>
@@ -9304,13 +9386,13 @@
     </row>
     <row r="74" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B74" s="3">
         <v>112</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D74" s="3">
         <v>68</v>
@@ -9333,13 +9415,13 @@
     </row>
     <row r="75" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B75" s="3">
         <v>112</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D75" s="3">
         <v>113</v>
@@ -9365,13 +9447,13 @@
     </row>
     <row r="76" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B76" s="3">
         <v>113</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D76" s="3">
         <v>9</v>
@@ -9397,13 +9479,13 @@
     </row>
     <row r="77" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B77" s="3">
         <v>113</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D77" s="3">
         <v>65</v>
@@ -9429,13 +9511,13 @@
     </row>
     <row r="78" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B78" s="3">
         <v>113</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D78" s="3">
         <v>68</v>
@@ -9461,13 +9543,13 @@
     </row>
     <row r="79" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B79" s="3">
         <v>113</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D79" s="3">
         <v>112</v>
@@ -9493,13 +9575,13 @@
     </row>
     <row r="80" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B80" s="3">
         <v>114</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D80" s="3">
         <v>9</v>
@@ -9522,13 +9604,13 @@
     </row>
     <row r="81" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B81" s="3">
         <v>114</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D81" s="3">
         <v>16</v>
@@ -9554,13 +9636,13 @@
     </row>
     <row r="82" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B82" s="3">
         <v>114</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D82" s="3">
         <v>112</v>
@@ -9586,13 +9668,13 @@
     </row>
     <row r="83" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B83" s="3">
         <v>114</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D83" s="3">
         <v>141</v>
@@ -9615,13 +9697,13 @@
     </row>
     <row r="84" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B84" s="3">
         <v>119</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D84" s="3">
         <v>65</v>
@@ -9644,13 +9726,13 @@
     </row>
     <row r="85" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B85" s="3">
         <v>119</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D85" s="3">
         <v>112</v>
@@ -9673,13 +9755,13 @@
     </row>
     <row r="86" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B86" s="3">
         <v>119</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D86" s="3">
         <v>341</v>
@@ -9705,13 +9787,13 @@
     </row>
     <row r="87" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B87" s="3">
         <v>119</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D87" s="3">
         <v>346</v>
@@ -9737,13 +9819,13 @@
     </row>
     <row r="88" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" s="3">
         <v>128</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D88" s="3">
         <v>65</v>
@@ -9769,13 +9851,13 @@
     </row>
     <row r="89" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B89" s="3">
         <v>128</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D89" s="3">
         <v>68</v>
@@ -9798,13 +9880,13 @@
     </row>
     <row r="90" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B90" s="3">
         <v>128</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D90" s="3">
         <v>112</v>
@@ -9827,13 +9909,13 @@
     </row>
     <row r="91" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B91" s="3">
         <v>128</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D91" s="3">
         <v>119</v>
@@ -9856,13 +9938,13 @@
     </row>
     <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B92" s="3">
         <v>128</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D92" s="3">
         <v>140</v>
@@ -9885,13 +9967,13 @@
     </row>
     <row r="93" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B93" s="3">
         <v>128</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D93" s="3">
         <v>433</v>
@@ -9914,13 +9996,13 @@
     </row>
     <row r="94" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B94" s="3">
         <v>128</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D94" s="3">
         <v>443</v>
@@ -9943,13 +10025,13 @@
     </row>
     <row r="95" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B95" s="3">
         <v>142</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D95" s="3">
         <v>13</v>
@@ -9975,13 +10057,13 @@
     </row>
     <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B96" s="3">
         <v>142</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D96" s="3">
         <v>16</v>
@@ -10004,13 +10086,13 @@
     </row>
     <row r="97" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B97" s="3">
         <v>142</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D97" s="3">
         <v>47</v>
@@ -10036,13 +10118,13 @@
     </row>
     <row r="98" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B98" s="3">
         <v>142</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D98" s="3">
         <v>63</v>
@@ -10068,13 +10150,13 @@
     </row>
     <row r="99" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B99" s="3">
         <v>142</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D99" s="3">
         <v>70</v>
@@ -10100,13 +10182,13 @@
     </row>
     <row r="100" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B100" s="3">
         <v>142</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D100" s="3">
         <v>141</v>
@@ -10132,13 +10214,13 @@
     </row>
     <row r="101" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B101" s="3">
         <v>145</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D101" s="3">
         <v>9</v>
@@ -10164,13 +10246,13 @@
     </row>
     <row r="102" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B102" s="3">
         <v>145</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D102" s="3">
         <v>22</v>
@@ -10193,13 +10275,13 @@
     </row>
     <row r="103" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B103" s="3">
         <v>145</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D103" s="3">
         <v>23</v>
@@ -10225,13 +10307,13 @@
     </row>
     <row r="104" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B104" s="3">
         <v>145</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D104" s="3">
         <v>141</v>
@@ -10254,13 +10336,13 @@
     </row>
     <row r="105" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B105" s="3">
         <v>158</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D105" s="3">
         <v>37</v>
@@ -10272,7 +10354,7 @@
         <v>37</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>216</v>
+        <v>428</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10283,13 +10365,13 @@
     </row>
     <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B106" s="3">
         <v>158</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D106" s="3">
         <v>141</v>
@@ -10301,7 +10383,7 @@
         <v>20</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10312,13 +10394,13 @@
     </row>
     <row r="107" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B107" s="3">
         <v>158</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D107" s="3">
         <v>157</v>
@@ -10341,13 +10423,13 @@
     </row>
     <row r="108" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B108" s="3">
         <v>197</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D108" s="3">
         <v>199</v>
@@ -10370,13 +10452,13 @@
     </row>
     <row r="109" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B109" s="3">
         <v>320</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D109" s="3">
         <v>8</v>
@@ -10388,7 +10470,7 @@
         <v>20</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -10399,13 +10481,13 @@
     </row>
     <row r="110" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B110" s="3">
         <v>320</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D110" s="3">
         <v>9</v>
@@ -10417,7 +10499,7 @@
         <v>20</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -10428,13 +10510,13 @@
     </row>
     <row r="111" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B111" s="3">
         <v>320</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D111" s="3">
         <v>323</v>
@@ -10446,7 +10528,7 @@
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -10457,13 +10539,13 @@
     </row>
     <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B112" s="3">
         <v>321</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D112" s="3">
         <v>20</v>
@@ -10475,7 +10557,7 @@
         <v>20</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -10486,13 +10568,13 @@
     </row>
     <row r="113" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B113" s="3">
         <v>321</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D113" s="3">
         <v>21</v>
@@ -10504,7 +10586,7 @@
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10515,13 +10597,13 @@
     </row>
     <row r="114" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B114" s="3">
         <v>321</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D114" s="3">
         <v>351</v>
@@ -10533,7 +10615,7 @@
         <v>37</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -10544,13 +10626,13 @@
     </row>
     <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B115" s="3">
         <v>321</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D115" s="3">
         <v>352</v>
@@ -10562,7 +10644,7 @@
         <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -10573,13 +10655,13 @@
     </row>
     <row r="116" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B116" s="3">
         <v>324</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D116" s="3">
         <v>31</v>
@@ -10591,7 +10673,7 @@
         <v>20</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -10602,13 +10684,13 @@
     </row>
     <row r="117" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B117" s="3">
         <v>324</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D117" s="3">
         <v>151</v>
@@ -10634,13 +10716,13 @@
     </row>
     <row r="118" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B118" s="3">
         <v>324</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D118" s="3">
         <v>340</v>
@@ -10666,13 +10748,13 @@
     </row>
     <row r="119" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B119" s="3">
         <v>330</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D119" s="3">
         <v>141</v>
@@ -10684,7 +10766,7 @@
         <v>146</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -10695,13 +10777,13 @@
     </row>
     <row r="120" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B120" s="3">
         <v>330</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D120" s="3">
         <v>339</v>
@@ -10713,7 +10795,7 @@
         <v>146</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -10724,13 +10806,13 @@
     </row>
     <row r="121" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B121" s="3">
         <v>330</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D121" s="3">
         <v>340</v>
@@ -10742,7 +10824,7 @@
         <v>146</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -10753,13 +10835,13 @@
     </row>
     <row r="122" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B122" s="3">
         <v>331</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D122" s="3">
         <v>133</v>
@@ -10771,7 +10853,7 @@
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -10782,13 +10864,13 @@
     </row>
     <row r="123" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B123" s="3">
         <v>331</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D123" s="3">
         <v>330</v>
@@ -10800,7 +10882,7 @@
         <v>146</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -10811,13 +10893,13 @@
     </row>
     <row r="124" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B124" s="3">
         <v>331</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D124" s="3">
         <v>339</v>
@@ -10829,7 +10911,7 @@
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -10840,13 +10922,13 @@
     </row>
     <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B125" s="3">
         <v>347</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D125" s="3">
         <v>3</v>
@@ -10858,7 +10940,7 @@
         <v>20</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -10869,13 +10951,13 @@
     </row>
     <row r="126" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B126" s="3">
         <v>347</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D126" s="3">
         <v>340</v>
@@ -10887,10 +10969,10 @@
         <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -10901,13 +10983,13 @@
     </row>
     <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B127" s="3">
         <v>347</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D127" s="3">
         <v>341</v>
@@ -10919,10 +11001,10 @@
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -10933,13 +11015,13 @@
     </row>
     <row r="128" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B128" s="3">
         <v>347</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D128" s="3">
         <v>342</v>
@@ -10951,10 +11033,10 @@
         <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
@@ -10965,13 +11047,13 @@
     </row>
     <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B129" s="3">
         <v>353</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D129" s="3">
         <v>21</v>
@@ -10983,7 +11065,7 @@
         <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -10994,13 +11076,13 @@
     </row>
     <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B130" s="3">
         <v>353</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D130" s="3">
         <v>321</v>
@@ -11012,7 +11094,7 @@
         <v>146</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -11023,13 +11105,13 @@
     </row>
     <row r="131" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B131" s="3">
         <v>353</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D131" s="3">
         <v>352</v>
@@ -11041,10 +11123,10 @@
         <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H131" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -11055,13 +11137,13 @@
     </row>
     <row r="132" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B132" s="3">
         <v>375</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D132" s="3">
         <v>32</v>
@@ -11073,10 +11155,10 @@
         <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H132" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -11087,13 +11169,13 @@
     </row>
     <row r="133" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B133" s="3">
         <v>375</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D133" s="3">
         <v>352</v>
@@ -11105,7 +11187,7 @@
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -11116,13 +11198,13 @@
     </row>
     <row r="134" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B134" s="3">
         <v>375</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D134" s="3">
         <v>370</v>
@@ -11134,7 +11216,7 @@
         <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -11145,13 +11227,13 @@
     </row>
     <row r="135" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B135" s="3">
         <v>375</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D135" s="3">
         <v>374</v>
@@ -11163,7 +11245,7 @@
         <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -11174,13 +11256,13 @@
     </row>
     <row r="136" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B136" s="3">
         <v>392</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D136" s="3">
         <v>341</v>
@@ -11192,7 +11274,7 @@
         <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -11203,13 +11285,13 @@
     </row>
     <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B137" s="3">
         <v>392</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D137" s="3">
         <v>350</v>
@@ -11221,10 +11303,10 @@
         <v>37</v>
       </c>
       <c r="G137" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H137" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -11235,13 +11317,13 @@
     </row>
     <row r="138" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B138" s="3">
         <v>392</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D138" s="3">
         <v>352</v>
@@ -11253,7 +11335,7 @@
         <v>37</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -11264,13 +11346,13 @@
     </row>
     <row r="139" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B139" s="3">
         <v>392</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D139" s="3">
         <v>380</v>
@@ -11282,7 +11364,7 @@
         <v>37</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -11293,13 +11375,13 @@
     </row>
     <row r="140" spans="1:10" ht="69" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B140" s="3">
         <v>392</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D140" s="3">
         <v>390</v>
@@ -11311,7 +11393,7 @@
         <v>146</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -11322,13 +11404,13 @@
     </row>
     <row r="141" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B141" s="3">
         <v>440</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D141" s="3">
         <v>342</v>
@@ -11340,7 +11422,7 @@
         <v>20</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -11351,13 +11433,13 @@
     </row>
     <row r="142" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B142" s="3">
         <v>443</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D142" s="3">
         <v>119</v>
@@ -11369,7 +11451,7 @@
         <v>146</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -11380,13 +11462,13 @@
     </row>
     <row r="143" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B143" s="3">
         <v>443</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D143" s="3">
         <v>327</v>
@@ -11398,10 +11480,10 @@
         <v>20</v>
       </c>
       <c r="G143" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H143" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -11412,13 +11494,13 @@
     </row>
     <row r="144" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B144" s="3">
         <v>443</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D144" s="3">
         <v>341</v>
@@ -11430,10 +11512,10 @@
         <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -11444,13 +11526,13 @@
     </row>
     <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B145" s="3">
         <v>443</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D145" s="3">
         <v>342</v>
@@ -11462,10 +11544,10 @@
         <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -11476,13 +11558,13 @@
     </row>
     <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B146" s="3">
         <v>443</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D146" s="3">
         <v>345</v>
@@ -11494,7 +11576,7 @@
         <v>146</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -11505,13 +11587,13 @@
     </row>
     <row r="147" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B147" s="3">
         <v>451</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D147" s="3">
         <v>125</v>
@@ -11523,12 +11605,221 @@
         <v>20</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J147" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B148" s="3">
+        <v>62</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D148" s="3">
+        <v>34</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G148" t="s">
+        <v>426</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J148" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B149" s="3">
+        <v>64</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D149" s="3">
+        <v>37</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G149" t="s">
+        <v>427</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J149" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B150" s="3">
+        <v>66</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D150" s="3">
+        <v>34</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J150" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B151" s="3">
+        <v>66</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D151" s="3">
+        <v>62</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J151" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B152" s="3">
+        <v>67</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D152" s="3">
+        <v>11</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J152" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B153" s="3">
+        <v>67</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D153" s="3">
+        <v>16</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J153" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A154" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B154" s="9">
+        <v>67</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D154" s="9">
+        <v>45</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J154" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -11547,6 +11838,11 @@
     <sortCondition ref="D2:D147"/>
     <sortCondition ref="C2:C147"/>
   </sortState>
+  <conditionalFormatting sqref="C1:C153 A1:A153 A155:A1048576 C155:C1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"slips"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2186B10A-E0CA-CF43-A5F8-E92BCEE27D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F10195B-41AF-6C4C-8D0F-AFAF0006BA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2301" uniqueCount="436">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2361" uniqueCount="447">
   <si>
     <t>reviewer</t>
   </si>
@@ -1362,6 +1362,39 @@
   </si>
   <si>
     <t>BIP67 references BIP11 as the original standard for multisignature transactions to provide context, but its specification builds on P2SH redeem scripts defined by BIP16 rather than depending on BIP11.</t>
+  </si>
+  <si>
+    <t>Part of motivation behind BIP87</t>
+  </si>
+  <si>
+    <t>The multisig descriptors or descriptor template that is generated from the cosigners' combined key records should be used to generate and discover addresses. Please see BIP-0129 (Bitcoin Secure Multisig Setup) for an introduction on descriptor templates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP defines a sane hierarchy for deterministic multisig wallets based on an algorithm described in BIP-0032 (BIP32 from now on), [...] Specification [...] We define the following 5 levels in the BIP32 path: [...] Accounts are numbered from index 0 in sequentially increasing manner. This number is used as child index in BIP32 derivation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP defines a sane hierarchy for deterministic multisig wallets based on an algorithm described in BIP-0032 (BIP32 from now on), purpose scheme described in BIP-0043 (BIP43 from now on), [...] This BIP is a particular application of BIP43. [...] Purpose is a constant set to 87' following the BIP43 recommendation. It indicates that the subtree of this node is used according to this specification. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP defines a sane hierarchy for deterministic multisig wallets based on an algorithm described in BIP-0032 (BIP32 from now on), purpose scheme described in BIP-0043 (BIP43 from now on), and multi-account hierarchy described in BIP-0044 (BIP44 from now on). [...] This level splits the key space into independent user identities, following the BIP44 pattern, so the wallet never mixes the coins across different accounts. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">With the increase of more user friendly (offline) multisignature wallets, and adoption of new technologies such as the descriptor language and BIP-0174 (Partially Signed Bitcoin Transactions), it is necessary to create a common derivation scheme [...] The descriptor or descriptor template should contain the key origin information for maximum compatibility with BIP-0174. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This too is redundant, as descriptors can set the order of the public keys with multi or have them sorted lexicographically (as described in BIP67) with sortedmulti. [...] Specification [...] Any wallet that supports descriptors inherently supports deterministic key sorting as per BIP67 (through the sortedmulti function) so that all possible multisignature addresses/scripts are derived from deterministically sorted public keys. </t>
+  </si>
+  <si>
+    <t>BIP87 references BIP129 as the standard wallet identifier format for multisig coordination, but its account derivation scheme is defined independently of BIP129.</t>
+  </si>
+  <si>
+    <t>BIP87 cites BIP49 and BIP84 as background to contrast existing wallet derivation schemes</t>
+  </si>
+  <si>
+    <t>Rather than following in BIP 44/49/84's path and having a separate BIP per script after P2SH (BIP45)</t>
+  </si>
+  <si>
+    <t>As background, BIP 44/49/84 specifies [...] Even if the user doesn't recall the derivation used, the wallet implementation can iterate through common schemes (BIP44/49/84)</t>
   </si>
 </sst>
 </file>
@@ -1969,13 +2002,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i/>
@@ -1983,6 +2009,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFDB94"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4088,6 +4121,12 @@
       <c r="B36" s="3">
         <v>71</v>
       </c>
+      <c r="C36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E36" s="7" t="s">
         <v>17</v>
       </c>
@@ -4331,6 +4370,12 @@
       </c>
       <c r="B41" s="3">
         <v>87</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>17</v>
@@ -7152,14 +7197,14 @@
     <sortCondition ref="B2:B101"/>
     <sortCondition ref="A2:A101"/>
   </sortState>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="manual">
-      <formula>NOT(ISERROR(SEARCH("manual",E1)))</formula>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"slips"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"slips"</formula>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="manual">
+      <formula>NOT(ISERROR(SEARCH("manual",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
@@ -7168,7 +7213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -8977,18 +9022,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B61" s="3">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D61" s="3">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>128</v>
@@ -8996,63 +9041,60 @@
       <c r="F61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>170</v>
+      <c r="G61" t="s">
+        <v>426</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J61" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="J61" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B62" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D62" s="3">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>171</v>
+      <c r="G62" t="s">
+        <v>427</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>172</v>
+        <v>429</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J62" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B63" s="3">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D63" s="3">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>118</v>
@@ -9061,80 +9103,74 @@
         <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>132</v>
+        <v>430</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J63" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J63" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="3">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D64" s="3">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>134</v>
+        <v>431</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J64" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J64" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B65" s="3">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D65" s="3">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>135</v>
+        <v>432</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>136</v>
+        <v>435</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J65" s="8" t="s">
-        <v>50</v>
+      <c r="J65" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9142,13 +9178,13 @@
         <v>218</v>
       </c>
       <c r="B66" s="3">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D66" s="3">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>118</v>
@@ -9157,91 +9193,88 @@
         <v>37</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>138</v>
+        <v>433</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B67" s="3">
-        <v>77</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D67" s="3">
-        <v>321</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F67" s="3" t="s">
+      <c r="J66" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A67" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B67" s="9">
+        <v>67</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D67" s="9">
+        <v>45</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F67" s="9" t="s">
         <v>37</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>132</v>
+        <v>434</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J67" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B68" s="3">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D68" s="3">
-        <v>324</v>
+        <v>70</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>139</v>
+        <v>169</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B69" s="3">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D69" s="3">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>118</v>
@@ -9250,39 +9283,42 @@
         <v>37</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>237</v>
+        <v>171</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B70" s="3">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D70" s="3">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>236</v>
+        <v>131</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
@@ -9291,18 +9327,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B71" s="3">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D71" s="3">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>118</v>
@@ -9311,13 +9347,16 @@
         <v>37</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>173</v>
+        <v>133</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9325,13 +9364,13 @@
         <v>218</v>
       </c>
       <c r="B72" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D72" s="3">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>118</v>
@@ -9340,62 +9379,62 @@
         <v>37</v>
       </c>
       <c r="G72" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" s="3">
+        <v>77</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D73" s="3">
         <v>174</v>
       </c>
-      <c r="H72" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B73" s="3">
-        <v>112</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D73" s="3">
-        <v>65</v>
-      </c>
       <c r="E73" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J73" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B74" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D74" s="3">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>118</v>
@@ -9404,13 +9443,16 @@
         <v>37</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>176</v>
+        <v>235</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9418,45 +9460,42 @@
         <v>218</v>
       </c>
       <c r="B75" s="3">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D75" s="3">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B76" s="3">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D76" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>118</v>
@@ -9465,126 +9504,117 @@
         <v>37</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J76" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B77" s="3">
+        <v>78</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D77" s="3">
+        <v>79</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A78" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B78" s="3">
+        <v>87</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" s="3">
         <v>32</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B77" s="3">
-        <v>113</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D77" s="3">
-        <v>65</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B78" s="3">
-        <v>113</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D78" s="3">
-        <v>68</v>
-      </c>
       <c r="E78" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>181</v>
+        <v>438</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J78" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
+      <c r="J78" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A79" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B79" s="3">
-        <v>113</v>
-      </c>
-      <c r="C79" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D79" s="3">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>181</v>
+        <v>439</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J79" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
+      <c r="J79" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A80" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B80" s="3">
-        <v>114</v>
-      </c>
-      <c r="C80" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D80" s="3">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>118</v>
@@ -9593,13 +9623,13 @@
         <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>187</v>
+        <v>440</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J80" s="8" t="s">
-        <v>32</v>
+      <c r="J80" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9607,13 +9637,13 @@
         <v>218</v>
       </c>
       <c r="B81" s="3">
-        <v>114</v>
-      </c>
-      <c r="C81" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D81" s="3">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>128</v>
@@ -9622,16 +9652,13 @@
         <v>37</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>183</v>
+        <v>445</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J81" s="8" t="s">
-        <v>32</v>
+      <c r="J81" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -9639,13 +9666,13 @@
         <v>218</v>
       </c>
       <c r="B82" s="3">
-        <v>114</v>
-      </c>
-      <c r="C82" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C82" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D82" s="3">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>128</v>
@@ -9654,88 +9681,94 @@
         <v>146</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>185</v>
+        <v>446</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>186</v>
+        <v>444</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J82" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
+      <c r="J82" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A83" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B83" s="3">
-        <v>114</v>
-      </c>
-      <c r="C83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D83" s="3">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>184</v>
+        <v>442</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>436</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J83" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J83" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B84" s="3">
-        <v>119</v>
-      </c>
-      <c r="C84" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D84" s="3">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>190</v>
+        <v>446</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J84" s="8" t="s">
-        <v>32</v>
+      <c r="J84" s="8" t="d">
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B85" s="3">
-        <v>119</v>
-      </c>
-      <c r="C85" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C85" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D85" s="3">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>128</v>
@@ -9744,27 +9777,30 @@
         <v>37</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>190</v>
+        <v>437</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J85" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
+      <c r="J85" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A86" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B86" s="3">
-        <v>119</v>
-      </c>
-      <c r="C86" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D86" s="3">
-        <v>341</v>
+        <v>174</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>128</v>
@@ -9773,109 +9809,106 @@
         <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>192</v>
+        <v>441</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J86" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J86" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B87" s="3">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D87" s="3">
-        <v>346</v>
+        <v>37</v>
       </c>
       <c r="E87" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B88" s="3">
+        <v>112</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D88" s="3">
+        <v>9</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="3">
+        <v>112</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D89" s="3">
+        <v>65</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F89" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G87" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J87" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B88" s="3">
-        <v>128</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D88" s="3">
-        <v>65</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B89" s="3">
-        <v>128</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D89" s="3">
-        <v>68</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G89" s="4" t="s">
-        <v>197</v>
+        <v>177</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -9883,57 +9916,60 @@
         <v>218</v>
       </c>
       <c r="B90" s="3">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D90" s="3">
+        <v>68</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B91" s="3">
         <v>112</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B91" s="3">
-        <v>128</v>
-      </c>
       <c r="C91" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D91" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>196</v>
+        <v>179</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -9941,22 +9977,25 @@
         <v>218</v>
       </c>
       <c r="B92" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D92" s="3">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>198</v>
+        <v>174</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
@@ -9970,13 +10009,13 @@
         <v>218</v>
       </c>
       <c r="B93" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D93" s="3">
-        <v>433</v>
+        <v>65</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>128</v>
@@ -9985,7 +10024,10 @@
         <v>146</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>199</v>
+        <v>180</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -9994,27 +10036,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B94" s="3">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D94" s="3">
-        <v>443</v>
+        <v>68</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>196</v>
+        <v>180</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
@@ -10028,25 +10073,25 @@
         <v>218</v>
       </c>
       <c r="B95" s="3">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D95" s="3">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -10055,27 +10100,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B96" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D96" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -10084,18 +10129,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B97" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D97" s="3">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>128</v>
@@ -10104,10 +10149,10 @@
         <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
@@ -10116,30 +10161,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B98" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D98" s="3">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -10148,30 +10193,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B99" s="3">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D99" s="3">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -10180,30 +10222,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B100" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D100" s="3">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -10217,25 +10256,22 @@
         <v>218</v>
       </c>
       <c r="B101" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D101" s="3">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -10249,22 +10285,25 @@
         <v>218</v>
       </c>
       <c r="B102" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D102" s="3">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>208</v>
+        <v>191</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -10273,30 +10312,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B103" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D103" s="3">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
@@ -10305,18 +10344,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D104" s="3">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>128</v>
@@ -10325,7 +10364,10 @@
         <v>37</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -10339,22 +10381,22 @@
         <v>218</v>
       </c>
       <c r="B105" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D105" s="3">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>428</v>
+        <v>197</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10363,27 +10405,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B106" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D106" s="3">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10392,27 +10434,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B107" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D107" s="3">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -10426,22 +10468,22 @@
         <v>218</v>
       </c>
       <c r="B108" s="3">
-        <v>197</v>
-      </c>
-      <c r="C108" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D108" s="3">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -10450,163 +10492,169 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B109" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D109" s="3">
-        <v>8</v>
+        <v>433</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J109" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J109" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B110" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D110" s="3">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J110" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J110" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B111" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D111" s="3">
-        <v>323</v>
+        <v>13</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>249</v>
+        <v>202</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J111" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J111" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B112" s="3">
-        <v>321</v>
-      </c>
-      <c r="C112" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D112" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B113" s="3">
-        <v>321</v>
-      </c>
-      <c r="C113" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D113" s="3">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>239</v>
+        <v>205</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B114" s="3">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D114" s="3">
-        <v>351</v>
+        <v>63</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>128</v>
@@ -10615,27 +10663,30 @@
         <v>37</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B115" s="3">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D115" s="3">
-        <v>352</v>
+        <v>70</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>128</v>
@@ -10644,74 +10695,80 @@
         <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>240</v>
+        <v>205</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B116" s="3">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D116" s="3">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F116" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A117" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B117" s="3">
+        <v>145</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D117" s="3">
+        <v>9</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G116" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J116" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B117" s="3">
-        <v>324</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D117" s="3">
-        <v>151</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G117" s="4" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J117" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J117" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -10719,118 +10776,118 @@
         <v>218</v>
       </c>
       <c r="B118" s="3">
-        <v>324</v>
+        <v>145</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D118" s="3">
-        <v>340</v>
+        <v>22</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H118" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B119" s="3">
         <v>145</v>
       </c>
-      <c r="I118" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J118" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B119" s="3">
-        <v>330</v>
-      </c>
       <c r="C119" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D119" s="3">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>253</v>
+        <v>212</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J119" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J119" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B120" s="3">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D120" s="3">
-        <v>339</v>
+        <v>141</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J120" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J120" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B121" s="3">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D121" s="3">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>252</v>
+        <v>428</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J121" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J121" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10838,100 +10895,100 @@
         <v>218</v>
       </c>
       <c r="B122" s="3">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D122" s="3">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J122" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J122" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B123" s="3">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D123" s="3">
-        <v>330</v>
+        <v>157</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J123" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J123" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B124" s="3">
-        <v>331</v>
-      </c>
-      <c r="C124" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C124" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D124" s="3">
-        <v>339</v>
+        <v>199</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J124" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J124" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B125" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D125" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>128</v>
@@ -10940,7 +10997,7 @@
         <v>20</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -10954,25 +11011,22 @@
         <v>218</v>
       </c>
       <c r="B126" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D126" s="3">
-        <v>340</v>
+        <v>9</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -10981,30 +11035,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B127" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D127" s="3">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -11013,36 +11064,33 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B128" s="3">
-        <v>347</v>
-      </c>
-      <c r="C128" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C128" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D128" s="3">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J128" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11050,28 +11098,28 @@
         <v>218</v>
       </c>
       <c r="B129" s="3">
-        <v>353</v>
-      </c>
-      <c r="C129" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C129" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D129" s="3">
         <v>21</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J129" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J129" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11079,36 +11127,36 @@
         <v>218</v>
       </c>
       <c r="B130" s="3">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D130" s="3">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J130" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J130" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B131" s="3">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>218</v>
@@ -11123,42 +11171,36 @@
         <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J131" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B132" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D132" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -11167,27 +11209,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B133" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D133" s="3">
-        <v>352</v>
+        <v>151</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>267</v>
+        <v>142</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -11201,22 +11246,25 @@
         <v>218</v>
       </c>
       <c r="B134" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D134" s="3">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>267</v>
+        <v>144</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -11225,27 +11273,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B135" s="3">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D135" s="3">
-        <v>374</v>
+        <v>141</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -11254,27 +11302,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B136" s="3">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D136" s="3">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -11283,30 +11331,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B137" s="3">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D137" s="3">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -11315,27 +11360,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B138" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D138" s="3">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -11349,22 +11394,22 @@
         <v>218</v>
       </c>
       <c r="B139" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D139" s="3">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -11373,27 +11418,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B140" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D140" s="3">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -11402,27 +11447,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B141" s="3">
-        <v>440</v>
+        <v>347</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D141" s="3">
-        <v>342</v>
+        <v>3</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -11436,22 +11481,25 @@
         <v>218</v>
       </c>
       <c r="B142" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D142" s="3">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>278</v>
+        <v>258</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -11465,25 +11513,25 @@
         <v>218</v>
       </c>
       <c r="B143" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D143" s="3">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -11492,18 +11540,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B144" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D144" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>118</v>
@@ -11512,10 +11560,10 @@
         <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -11524,18 +11572,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="3">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D145" s="3">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>118</v>
@@ -11544,10 +11592,7 @@
         <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -11561,13 +11606,13 @@
         <v>218</v>
       </c>
       <c r="B146" s="3">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D146" s="3">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>128</v>
@@ -11576,7 +11621,7 @@
         <v>146</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -11585,47 +11630,50 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B147" s="3">
-        <v>451</v>
+        <v>353</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D147" s="3">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>424</v>
+        <v>283</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J147" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B148" s="3">
-        <v>62</v>
+        <v>375</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D148" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>128</v>
@@ -11633,60 +11681,60 @@
       <c r="F148" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G148" t="s">
-        <v>426</v>
+      <c r="G148" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J148" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B149" s="3">
-        <v>64</v>
+        <v>375</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D149" s="3">
-        <v>37</v>
+        <v>352</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G149" t="s">
-        <v>427</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>429</v>
+      <c r="G149" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J149" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B150" s="3">
-        <v>66</v>
+        <v>375</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D150" s="3">
-        <v>34</v>
+        <v>370</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>118</v>
@@ -11695,74 +11743,71 @@
         <v>37</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J150" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B151" s="3">
-        <v>66</v>
+        <v>375</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D151" s="3">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>431</v>
+        <v>285</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J151" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B152" s="3">
-        <v>67</v>
+        <v>392</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D152" s="3">
-        <v>11</v>
+        <v>341</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>435</v>
+        <v>271</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J152" s="8" t="d">
-        <v>2026-06-30</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11770,13 +11815,13 @@
         <v>218</v>
       </c>
       <c r="B153" s="3">
-        <v>67</v>
+        <v>392</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D153" s="3">
-        <v>16</v>
+        <v>350</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>118</v>
@@ -11785,41 +11830,314 @@
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>433</v>
+        <v>269</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J153" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A154" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B154" s="9">
-        <v>67</v>
-      </c>
-      <c r="C154" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D154" s="9">
-        <v>45</v>
-      </c>
-      <c r="E154" s="9" t="s">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B154" s="3">
+        <v>392</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D154" s="3">
+        <v>352</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J154" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B155" s="3">
+        <v>392</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D155" s="3">
+        <v>380</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J155" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B156" s="3">
+        <v>392</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D156" s="3">
+        <v>390</v>
+      </c>
+      <c r="E156" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F154" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="I154" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J154" s="8" t="d">
+      <c r="F156" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J156" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B157" s="3">
+        <v>440</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D157" s="3">
+        <v>342</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J157" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B158" s="3">
+        <v>443</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D158" s="3">
+        <v>119</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J158" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B159" s="3">
+        <v>443</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D159" s="3">
+        <v>327</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J159" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B160" s="3">
+        <v>443</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D160" s="3">
+        <v>341</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J160" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A161" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B161" s="3">
+        <v>443</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D161" s="3">
+        <v>342</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J161" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B162" s="3">
+        <v>443</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D162" s="3">
+        <v>345</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B163" s="3">
+        <v>451</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D163" s="3">
+        <v>125</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J163" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -11832,13 +12150,13 @@
       <sortCondition ref="C2:C93"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J147">
-    <sortCondition ref="B2:B147"/>
-    <sortCondition ref="A2:A147"/>
-    <sortCondition ref="D2:D147"/>
-    <sortCondition ref="C2:C147"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J163">
+    <sortCondition ref="B2:B163"/>
+    <sortCondition ref="A2:A163"/>
+    <sortCondition ref="D2:D163"/>
+    <sortCondition ref="C2:C163"/>
   </sortState>
-  <conditionalFormatting sqref="C1:C153 A1:A153 A155:A1048576 C155:C1048576">
+  <conditionalFormatting sqref="A1:A153 C1:C153 C164:C1048576 A161:A1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9F10195B-41AF-6C4C-8D0F-AFAF0006BA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADFD3004-9C1E-D349-9462-BBF4ED315B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2361" uniqueCount="447">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2369" uniqueCount="450">
   <si>
     <t>reviewer</t>
   </si>
@@ -1395,6 +1395,15 @@
   </si>
   <si>
     <t>As background, BIP 44/49/84 specifies [...] Even if the user doesn't recall the derivation used, the wallet implementation can iterate through common schemes (BIP44/49/84)</t>
+  </si>
+  <si>
+    <t>OP_EVAL is defined in BIP12</t>
+  </si>
+  <si>
+    <t>Why propose this structure only for multisignature wallets? Currently, single-sig wallets are able to restore funds using just the master private key data (in the format of BIP39 usually).</t>
+  </si>
+  <si>
+    <t>Just a footnote</t>
   </si>
 </sst>
 </file>
@@ -7213,7 +7222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7372,6 +7381,9 @@
       <c r="G5" s="4" t="s">
         <v>425</v>
       </c>
+      <c r="H5" s="4" t="s">
+        <v>447</v>
+      </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
@@ -9574,7 +9586,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="9" t="s">
         <v>218</v>
       </c>
@@ -9585,16 +9597,19 @@
         <v>218</v>
       </c>
       <c r="D79" s="3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>439</v>
+        <v>448</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>449</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
@@ -9603,7 +9618,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
         <v>218</v>
       </c>
@@ -9614,7 +9629,7 @@
         <v>218</v>
       </c>
       <c r="D80" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>118</v>
@@ -9623,7 +9638,7 @@
         <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -9632,8 +9647,8 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A81" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B81" s="3">
@@ -9643,16 +9658,16 @@
         <v>218</v>
       </c>
       <c r="D81" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -9661,7 +9676,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>218</v>
       </c>
@@ -9672,19 +9687,16 @@
         <v>218</v>
       </c>
       <c r="D82" s="3">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -9693,8 +9705,8 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
+    <row r="83" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B83" s="3">
@@ -9704,19 +9716,19 @@
         <v>218</v>
       </c>
       <c r="D83" s="3">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
@@ -9725,8 +9737,8 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A84" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B84" s="3">
@@ -9736,19 +9748,19 @@
         <v>218</v>
       </c>
       <c r="D84" s="3">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
@@ -9757,8 +9769,8 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A85" s="9" t="s">
+    <row r="85" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B85" s="3">
@@ -9768,19 +9780,19 @@
         <v>218</v>
       </c>
       <c r="D85" s="3">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -9789,7 +9801,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A86" s="9" t="s">
         <v>218</v>
       </c>
@@ -9800,7 +9812,7 @@
         <v>218</v>
       </c>
       <c r="D86" s="3">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>128</v>
@@ -9809,7 +9821,10 @@
         <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>441</v>
+        <v>437</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
@@ -9818,47 +9833,47 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A87" s="9" t="s">
         <v>218</v>
       </c>
       <c r="B87" s="3">
+        <v>87</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87" s="3">
+        <v>174</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B88" s="3">
         <v>111</v>
       </c>
-      <c r="C87" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D87" s="3">
-        <v>37</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J87" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B88" s="3">
-        <v>112</v>
-      </c>
       <c r="C88" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D88" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>118</v>
@@ -9867,10 +9882,7 @@
         <v>37</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
@@ -9879,7 +9891,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>218</v>
       </c>
@@ -9890,19 +9902,19 @@
         <v>218</v>
       </c>
       <c r="D89" s="3">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
@@ -9911,7 +9923,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>218</v>
       </c>
@@ -9922,16 +9934,19 @@
         <v>218</v>
       </c>
       <c r="D90" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
@@ -9940,7 +9955,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>218</v>
       </c>
@@ -9951,19 +9966,16 @@
         <v>218</v>
       </c>
       <c r="D91" s="3">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
@@ -9977,34 +9989,34 @@
         <v>218</v>
       </c>
       <c r="B92" s="3">
+        <v>112</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92" s="3">
         <v>113</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D92" s="3">
-        <v>9</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>218</v>
       </c>
@@ -10015,19 +10027,19 @@
         <v>218</v>
       </c>
       <c r="D93" s="3">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -10047,7 +10059,7 @@
         <v>218</v>
       </c>
       <c r="D94" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>128</v>
@@ -10079,7 +10091,7 @@
         <v>218</v>
       </c>
       <c r="D95" s="3">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>128</v>
@@ -10100,27 +10112,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B96" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D96" s="3">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>187</v>
+        <v>180</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -10140,19 +10155,16 @@
         <v>218</v>
       </c>
       <c r="D97" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H97" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
@@ -10161,7 +10173,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>218</v>
       </c>
@@ -10172,19 +10184,19 @@
         <v>218</v>
       </c>
       <c r="D98" s="3">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -10193,7 +10205,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>218</v>
       </c>
@@ -10204,16 +10216,19 @@
         <v>218</v>
       </c>
       <c r="D99" s="3">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -10222,27 +10237,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B100" s="3">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D100" s="3">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -10262,7 +10277,7 @@
         <v>218</v>
       </c>
       <c r="D101" s="3">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>128</v>
@@ -10280,7 +10295,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>218</v>
       </c>
@@ -10291,7 +10306,7 @@
         <v>218</v>
       </c>
       <c r="D102" s="3">
-        <v>341</v>
+        <v>112</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>128</v>
@@ -10300,10 +10315,7 @@
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -10312,7 +10324,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>218</v>
       </c>
@@ -10323,19 +10335,19 @@
         <v>218</v>
       </c>
       <c r="D103" s="3">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
@@ -10344,30 +10356,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D104" s="3">
-        <v>65</v>
+        <v>346</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -10376,7 +10388,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>218</v>
       </c>
@@ -10387,16 +10399,19 @@
         <v>218</v>
       </c>
       <c r="D105" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10416,16 +10431,16 @@
         <v>218</v>
       </c>
       <c r="D106" s="3">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10434,7 +10449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>218</v>
       </c>
@@ -10445,7 +10460,7 @@
         <v>218</v>
       </c>
       <c r="D107" s="3">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>128</v>
@@ -10454,7 +10469,7 @@
         <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -10463,7 +10478,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>218</v>
       </c>
@@ -10474,16 +10489,16 @@
         <v>218</v>
       </c>
       <c r="D108" s="3">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -10492,7 +10507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
@@ -10503,7 +10518,7 @@
         <v>218</v>
       </c>
       <c r="D109" s="3">
-        <v>433</v>
+        <v>140</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>128</v>
@@ -10512,7 +10527,7 @@
         <v>146</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -10521,7 +10536,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>218</v>
       </c>
@@ -10532,16 +10547,16 @@
         <v>218</v>
       </c>
       <c r="D110" s="3">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -10550,18 +10565,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B111" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D111" s="3">
-        <v>13</v>
+        <v>443</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>128</v>
@@ -10570,10 +10585,7 @@
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -10582,7 +10594,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>218</v>
       </c>
@@ -10593,16 +10605,19 @@
         <v>218</v>
       </c>
       <c r="D112" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -10611,7 +10626,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>218</v>
       </c>
@@ -10622,19 +10637,16 @@
         <v>218</v>
       </c>
       <c r="D113" s="3">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10654,7 +10666,7 @@
         <v>218</v>
       </c>
       <c r="D114" s="3">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>128</v>
@@ -10686,7 +10698,7 @@
         <v>218</v>
       </c>
       <c r="D115" s="3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>128</v>
@@ -10718,19 +10730,19 @@
         <v>218</v>
       </c>
       <c r="D116" s="3">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -10739,30 +10751,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B117" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D117" s="3">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -10771,7 +10783,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>218</v>
       </c>
@@ -10782,16 +10794,19 @@
         <v>218</v>
       </c>
       <c r="D118" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -10800,7 +10815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>218</v>
       </c>
@@ -10811,19 +10826,16 @@
         <v>218</v>
       </c>
       <c r="D119" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -10832,7 +10844,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>218</v>
       </c>
@@ -10843,16 +10855,19 @@
         <v>218</v>
       </c>
       <c r="D120" s="3">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -10866,13 +10881,13 @@
         <v>218</v>
       </c>
       <c r="B121" s="3">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D121" s="3">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>128</v>
@@ -10881,7 +10896,7 @@
         <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>428</v>
+        <v>209</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -10890,7 +10905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>218</v>
       </c>
@@ -10901,16 +10916,16 @@
         <v>218</v>
       </c>
       <c r="D122" s="3">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>238</v>
+        <v>428</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -10930,16 +10945,16 @@
         <v>218</v>
       </c>
       <c r="D123" s="3">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -10953,13 +10968,13 @@
         <v>218</v>
       </c>
       <c r="B124" s="3">
-        <v>197</v>
-      </c>
-      <c r="C124" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D124" s="3">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>118</v>
@@ -10968,7 +10983,7 @@
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -10977,33 +10992,33 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B125" s="3">
-        <v>320</v>
-      </c>
-      <c r="C125" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C125" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D125" s="3">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J125" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J125" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -11017,7 +11032,7 @@
         <v>218</v>
       </c>
       <c r="D126" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>128</v>
@@ -11026,7 +11041,7 @@
         <v>20</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -11035,7 +11050,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>218</v>
       </c>
@@ -11046,16 +11061,16 @@
         <v>218</v>
       </c>
       <c r="D127" s="3">
-        <v>323</v>
+        <v>9</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -11064,33 +11079,33 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B128" s="3">
-        <v>321</v>
-      </c>
-      <c r="C128" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D128" s="3">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="8" t="s">
-        <v>50</v>
+      <c r="J128" s="8" t="d">
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11104,16 +11119,16 @@
         <v>218</v>
       </c>
       <c r="D129" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -11129,20 +11144,20 @@
       <c r="B130" s="3">
         <v>321</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D130" s="3">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -11162,7 +11177,7 @@
         <v>218</v>
       </c>
       <c r="D131" s="3">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
@@ -11171,7 +11186,7 @@
         <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -11185,31 +11200,31 @@
         <v>218</v>
       </c>
       <c r="B132" s="3">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D132" s="3">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J132" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>218</v>
       </c>
@@ -11220,19 +11235,16 @@
         <v>218</v>
       </c>
       <c r="D133" s="3">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -11241,7 +11253,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>218</v>
       </c>
@@ -11252,19 +11264,19 @@
         <v>218</v>
       </c>
       <c r="D134" s="3">
-        <v>340</v>
+        <v>151</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -11273,27 +11285,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B135" s="3">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D135" s="3">
-        <v>141</v>
+        <v>340</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>253</v>
+        <v>144</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -11313,16 +11328,16 @@
         <v>218</v>
       </c>
       <c r="D136" s="3">
-        <v>339</v>
+        <v>141</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -11331,7 +11346,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>218</v>
       </c>
@@ -11342,16 +11357,16 @@
         <v>218</v>
       </c>
       <c r="D137" s="3">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -11360,27 +11375,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B138" s="3">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D138" s="3">
-        <v>133</v>
+        <v>340</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -11389,7 +11404,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>218</v>
       </c>
@@ -11400,16 +11415,16 @@
         <v>218</v>
       </c>
       <c r="D139" s="3">
-        <v>330</v>
+        <v>133</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -11418,7 +11433,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>218</v>
       </c>
@@ -11429,16 +11444,16 @@
         <v>218</v>
       </c>
       <c r="D140" s="3">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -11447,27 +11462,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B141" s="3">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D141" s="3">
-        <v>3</v>
+        <v>339</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -11476,7 +11491,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>218</v>
       </c>
@@ -11487,19 +11502,16 @@
         <v>218</v>
       </c>
       <c r="D142" s="3">
-        <v>340</v>
+        <v>3</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -11508,7 +11520,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>218</v>
       </c>
@@ -11519,7 +11531,7 @@
         <v>218</v>
       </c>
       <c r="D143" s="3">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>118</v>
@@ -11528,10 +11540,10 @@
         <v>37</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -11540,7 +11552,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>218</v>
       </c>
@@ -11551,7 +11563,7 @@
         <v>218</v>
       </c>
       <c r="D144" s="3">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>118</v>
@@ -11560,10 +11572,10 @@
         <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -11572,18 +11584,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="3">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D145" s="3">
-        <v>21</v>
+        <v>342</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>118</v>
@@ -11592,7 +11604,10 @@
         <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -11612,16 +11627,16 @@
         <v>218</v>
       </c>
       <c r="D146" s="3">
-        <v>321</v>
+        <v>21</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -11630,7 +11645,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>218</v>
       </c>
@@ -11641,19 +11656,16 @@
         <v>218</v>
       </c>
       <c r="D147" s="3">
-        <v>352</v>
+        <v>321</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="H147" s="4" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -11662,18 +11674,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B148" s="3">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D148" s="3">
-        <v>32</v>
+        <v>352</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>128</v>
@@ -11682,10 +11694,10 @@
         <v>37</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
@@ -11694,7 +11706,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>218</v>
       </c>
@@ -11705,16 +11717,19 @@
         <v>218</v>
       </c>
       <c r="D149" s="3">
-        <v>352</v>
+        <v>32</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>267</v>
+        <v>286</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
@@ -11734,7 +11749,7 @@
         <v>218</v>
       </c>
       <c r="D150" s="3">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>118</v>
@@ -11763,7 +11778,7 @@
         <v>218</v>
       </c>
       <c r="D151" s="3">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>118</v>
@@ -11772,7 +11787,7 @@
         <v>37</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
@@ -11786,13 +11801,13 @@
         <v>218</v>
       </c>
       <c r="B152" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D152" s="3">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>118</v>
@@ -11801,7 +11816,7 @@
         <v>37</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
@@ -11810,7 +11825,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>218</v>
       </c>
@@ -11821,7 +11836,7 @@
         <v>218</v>
       </c>
       <c r="D153" s="3">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>118</v>
@@ -11830,10 +11845,7 @@
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
@@ -11842,7 +11854,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>218</v>
       </c>
@@ -11853,7 +11865,7 @@
         <v>218</v>
       </c>
       <c r="D154" s="3">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>118</v>
@@ -11862,7 +11874,10 @@
         <v>37</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -11871,7 +11886,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>218</v>
       </c>
@@ -11882,7 +11897,7 @@
         <v>218</v>
       </c>
       <c r="D155" s="3">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>118</v>
@@ -11891,7 +11906,7 @@
         <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -11900,7 +11915,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>218</v>
       </c>
@@ -11911,16 +11926,16 @@
         <v>218</v>
       </c>
       <c r="D156" s="3">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -11929,27 +11944,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" ht="69" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B157" s="3">
-        <v>440</v>
+        <v>392</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D157" s="3">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -11958,27 +11973,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B158" s="3">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D158" s="3">
-        <v>119</v>
+        <v>342</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -11987,7 +12002,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>218</v>
       </c>
@@ -11998,19 +12013,16 @@
         <v>218</v>
       </c>
       <c r="D159" s="3">
-        <v>327</v>
+        <v>119</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -12019,7 +12031,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>218</v>
       </c>
@@ -12030,19 +12042,19 @@
         <v>218</v>
       </c>
       <c r="D160" s="3">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -12051,7 +12063,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>218</v>
       </c>
@@ -12062,7 +12074,7 @@
         <v>218</v>
       </c>
       <c r="D161" s="3">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>118</v>
@@ -12071,10 +12083,10 @@
         <v>37</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -12083,7 +12095,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>218</v>
       </c>
@@ -12094,16 +12106,19 @@
         <v>218</v>
       </c>
       <c r="D162" s="3">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -12112,51 +12127,80 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B163" s="3">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D163" s="3">
-        <v>125</v>
+        <v>345</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F163" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J163" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B164" s="3">
+        <v>451</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D164" s="3">
+        <v>125</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F164" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G164" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="I163" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J163" s="8" t="d">
+      <c r="I164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J164" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J93" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J93">
-      <sortCondition ref="B2:B93"/>
-      <sortCondition ref="A2:A93"/>
-      <sortCondition ref="D2:D93"/>
-      <sortCondition ref="C2:C93"/>
+  <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J94">
+      <sortCondition ref="B2:B94"/>
+      <sortCondition ref="A2:A94"/>
+      <sortCondition ref="D2:D94"/>
+      <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J163">
-    <sortCondition ref="B2:B163"/>
-    <sortCondition ref="A2:A163"/>
-    <sortCondition ref="D2:D163"/>
-    <sortCondition ref="C2:C163"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J164">
+    <sortCondition ref="B2:B164"/>
+    <sortCondition ref="A2:A164"/>
+    <sortCondition ref="D2:D164"/>
+    <sortCondition ref="C2:C164"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A153 C1:C153 C164:C1048576 A161:A1048576">
+  <conditionalFormatting sqref="A162:A1048576 C165:C1048576 A1:A154 C1:C154">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADFD3004-9C1E-D349-9462-BBF4ED315B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{077508F4-9B17-1940-B9D2-E35B9EB2AC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2369" uniqueCount="450">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2402" uniqueCount="457">
   <si>
     <t>reviewer</t>
   </si>
@@ -1404,6 +1404,27 @@
   </si>
   <si>
     <t>Just a footnote</t>
+  </si>
+  <si>
+    <t>Requires: 32 [...] Chain Code Delegation (CCD) is a method for multi-signature wallets in which a privileged participant withholds BIP32 chain codes from one or more non-privileged participants [...] CCD operates by having Delegatees deprive Delegators of BIP32 chain codes during setup [...]</t>
+  </si>
+  <si>
+    <t>Requires: [...] 340 [...] This BIP supports two modes:  [...] Both modes produce valid BIP340 signatures. [...] The delegator learns neither the message, the challenge, or the public key used in the BIP340 signature, only a blinded challenge e'.  This blind‑signing protocol specifies how a delegator can produce a blind partial Schnorr signature that a delegatee can unblind into a standard BIP340 signature under a possibly tweaked X‑only public key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The notation, algorithmic patterns, and test‑vector style are adapted from [BIP‑327] </t>
+  </si>
+  <si>
+    <t>The transport that carries this bundle is out of scope for this proposal; implementers MAY use PSBT proprietary keys [...] The transport that carries this bundle is out of scope for this proposal; implementers MAY use PSBT proprietary keys, [...]</t>
+  </si>
+  <si>
+    <t>BIP174 defines PSBT, mentioned in BIP89 only as a possible transport/protocol context</t>
+  </si>
+  <si>
+    <t>Requires: [...] 341 [...]  The output signature is a BIP340 Schnorr signature valid under an X‑only key obtained by applying a sequence of plain (e.g. BIP32) and X‑only (e.g. Tapscript) tweaks to the signer’s plain public key. Consequently the protocol is compatible with BIP341.</t>
+  </si>
+  <si>
+    <t>BIP89 references BIP341 because its signing protocol is designed to be compatible with Taproot’s X-only key and tweak semantics, without requiring Taproot to define CCD itself.</t>
   </si>
 </sst>
 </file>
@@ -4430,6 +4451,12 @@
       <c r="B42" s="3">
         <v>89</v>
       </c>
+      <c r="C42" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E42" s="7" t="s">
         <v>17</v>
       </c>
@@ -7222,7 +7249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -8166,7 +8193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>218</v>
       </c>
@@ -9867,13 +9894,13 @@
         <v>218</v>
       </c>
       <c r="B88" s="3">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D88" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>118</v>
@@ -9882,91 +9909,88 @@
         <v>37</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J88" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J88" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B89" s="3">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D89" s="3">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>174</v>
+        <v>453</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>175</v>
+        <v>454</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J89" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J89" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B90" s="3">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D90" s="3">
-        <v>65</v>
+        <v>327</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>178</v>
+        <v>452</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J90" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B91" s="3">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D91" s="3">
-        <v>68</v>
+        <v>340</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>118</v>
@@ -9975,59 +9999,59 @@
         <v>37</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>176</v>
+        <v>451</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J91" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J91" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B92" s="3">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D92" s="3">
-        <v>113</v>
+        <v>341</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>179</v>
+        <v>455</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>178</v>
+        <v>456</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J92" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B93" s="3">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D93" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>118</v>
@@ -10036,80 +10060,77 @@
         <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" s="3">
+        <v>112</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" s="3">
+        <v>9</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G94" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H94" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I93" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B94" s="3">
-        <v>113</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="3">
+        <v>112</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D95" s="3">
         <v>65</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="3">
-        <v>113</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D95" s="3">
-        <v>68</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -10117,31 +10138,28 @@
         <v>218</v>
       </c>
       <c r="B96" s="3">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D96" s="3">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10149,28 +10167,31 @@
         <v>218</v>
       </c>
       <c r="B97" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D97" s="3">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10178,25 +10199,25 @@
         <v>218</v>
       </c>
       <c r="B98" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D98" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -10205,18 +10226,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B99" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D99" s="3">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>128</v>
@@ -10225,10 +10246,10 @@
         <v>146</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -10237,27 +10258,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B100" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D100" s="3">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -10271,22 +10295,25 @@
         <v>218</v>
       </c>
       <c r="B101" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D101" s="3">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -10295,27 +10322,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B102" s="3">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D102" s="3">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -10324,18 +10351,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B103" s="3">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D103" s="3">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>128</v>
@@ -10344,10 +10371,10 @@
         <v>37</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
@@ -10356,30 +10383,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="3">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D104" s="3">
-        <v>346</v>
+        <v>112</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -10388,30 +10415,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B105" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D105" s="3">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10425,22 +10449,22 @@
         <v>218</v>
       </c>
       <c r="B106" s="3">
+        <v>119</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D106" s="3">
+        <v>65</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D106" s="3">
-        <v>68</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F106" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10454,7 +10478,7 @@
         <v>218</v>
       </c>
       <c r="B107" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>218</v>
@@ -10469,7 +10493,7 @@
         <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -10478,18 +10502,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B108" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D108" s="3">
-        <v>119</v>
+        <v>341</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>128</v>
@@ -10498,7 +10522,10 @@
         <v>37</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -10507,27 +10534,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B109" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D109" s="3">
-        <v>140</v>
+        <v>346</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -10536,7 +10566,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>218</v>
       </c>
@@ -10547,16 +10577,19 @@
         <v>218</v>
       </c>
       <c r="D110" s="3">
-        <v>433</v>
+        <v>65</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -10565,7 +10598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>218</v>
       </c>
@@ -10576,16 +10609,16 @@
         <v>218</v>
       </c>
       <c r="D111" s="3">
-        <v>443</v>
+        <v>68</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -10599,13 +10632,13 @@
         <v>218</v>
       </c>
       <c r="B112" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D112" s="3">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>128</v>
@@ -10614,10 +10647,7 @@
         <v>37</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -10626,27 +10656,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B113" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D113" s="3">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10655,30 +10685,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B114" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D114" s="3">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -10687,30 +10714,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B115" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D115" s="3">
-        <v>63</v>
+        <v>433</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -10724,13 +10748,13 @@
         <v>218</v>
       </c>
       <c r="B116" s="3">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D116" s="3">
-        <v>70</v>
+        <v>443</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>128</v>
@@ -10739,10 +10763,7 @@
         <v>37</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -10751,7 +10772,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>218</v>
       </c>
@@ -10762,19 +10783,19 @@
         <v>218</v>
       </c>
       <c r="D117" s="3">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -10783,30 +10804,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B118" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D118" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -10815,27 +10833,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B119" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D119" s="3">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -10844,30 +10865,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B120" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D120" s="3">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -10876,18 +10897,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B121" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D121" s="3">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>128</v>
@@ -10896,7 +10917,10 @@
         <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -10905,27 +10929,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B122" s="3">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D122" s="3">
-        <v>37</v>
+        <v>141</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>428</v>
+        <v>200</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -10934,27 +10961,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B123" s="3">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D123" s="3">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>238</v>
+        <v>210</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -10963,18 +10993,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B124" s="3">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D124" s="3">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>118</v>
@@ -10983,7 +11013,7 @@
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -10992,27 +11022,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B125" s="3">
-        <v>197</v>
-      </c>
-      <c r="C125" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D125" s="3">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -11021,91 +11054,91 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B126" s="3">
-        <v>320</v>
+        <v>145</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D126" s="3">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J126" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J126" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B127" s="3">
-        <v>320</v>
+        <v>158</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D127" s="3">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F127" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B128" s="3">
+        <v>158</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D128" s="3">
+        <v>141</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G127" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="I127" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J127" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B128" s="3">
-        <v>320</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D128" s="3">
-        <v>323</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G128" s="4" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J128" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11113,28 +11146,28 @@
         <v>218</v>
       </c>
       <c r="B129" s="3">
-        <v>321</v>
-      </c>
-      <c r="C129" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D129" s="3">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J129" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11142,109 +11175,109 @@
         <v>218</v>
       </c>
       <c r="B130" s="3">
-        <v>321</v>
+        <v>197</v>
       </c>
       <c r="C130" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D130" s="3">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J130" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B131" s="3">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D131" s="3">
-        <v>351</v>
+        <v>8</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J131" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B132" s="3">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D132" s="3">
-        <v>352</v>
+        <v>9</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J132" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B133" s="3">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D133" s="3">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -11253,68 +11286,62 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B134" s="3">
-        <v>324</v>
-      </c>
-      <c r="C134" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C134" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D134" s="3">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E134" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A135" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B135" s="3">
+        <v>321</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D135" s="3">
+        <v>21</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F134" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J134" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B135" s="3">
-        <v>324</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D135" s="3">
-        <v>340</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F135" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J135" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J135" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11322,28 +11349,28 @@
         <v>218</v>
       </c>
       <c r="B136" s="3">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D136" s="3">
-        <v>141</v>
+        <v>351</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J136" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J136" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11351,51 +11378,51 @@
         <v>218</v>
       </c>
       <c r="B137" s="3">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D137" s="3">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J137" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J137" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B138" s="3">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D138" s="3">
-        <v>340</v>
+        <v>31</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -11404,27 +11431,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B139" s="3">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D139" s="3">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>256</v>
+        <v>142</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -11433,27 +11463,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B140" s="3">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D140" s="3">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>257</v>
+        <v>144</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -11462,27 +11495,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B141" s="3">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D141" s="3">
-        <v>339</v>
+        <v>141</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -11491,27 +11524,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B142" s="3">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D142" s="3">
-        <v>3</v>
+        <v>339</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -11525,7 +11558,7 @@
         <v>218</v>
       </c>
       <c r="B143" s="3">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>218</v>
@@ -11534,16 +11567,13 @@
         <v>340</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -11557,25 +11587,22 @@
         <v>218</v>
       </c>
       <c r="B144" s="3">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D144" s="3">
-        <v>341</v>
+        <v>133</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -11584,30 +11611,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="3">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D145" s="3">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -11616,27 +11640,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B146" s="3">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D146" s="3">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -11645,27 +11669,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B147" s="3">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D147" s="3">
-        <v>321</v>
+        <v>3</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -11679,25 +11703,25 @@
         <v>218</v>
       </c>
       <c r="B148" s="3">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D148" s="3">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="H148" s="4" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
@@ -11706,30 +11730,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B149" s="3">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D149" s="3">
-        <v>32</v>
+        <v>341</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
@@ -11738,18 +11762,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B150" s="3">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D150" s="3">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>118</v>
@@ -11758,7 +11782,10 @@
         <v>37</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>267</v>
+        <v>260</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
@@ -11767,18 +11794,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B151" s="3">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D151" s="3">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>118</v>
@@ -11787,7 +11814,7 @@
         <v>37</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
@@ -11796,27 +11823,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B152" s="3">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D152" s="3">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
@@ -11830,22 +11857,25 @@
         <v>218</v>
       </c>
       <c r="B153" s="3">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D153" s="3">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>271</v>
+        <v>283</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
@@ -11854,30 +11884,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B154" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D154" s="3">
-        <v>350</v>
+        <v>32</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -11886,12 +11916,12 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B155" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>218</v>
@@ -11906,7 +11936,7 @@
         <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -11915,18 +11945,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B156" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D156" s="3">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>118</v>
@@ -11935,7 +11965,7 @@
         <v>37</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -11944,27 +11974,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B157" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D157" s="3">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -11973,27 +12003,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B158" s="3">
-        <v>440</v>
+        <v>392</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D158" s="3">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -12002,27 +12032,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B159" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D159" s="3">
-        <v>119</v>
+        <v>350</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>278</v>
+        <v>269</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -12031,30 +12064,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B160" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D160" s="3">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H160" s="4" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -12063,18 +12093,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B161" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D161" s="3">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>118</v>
@@ -12083,10 +12113,7 @@
         <v>37</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -12095,30 +12122,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" ht="69" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B162" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D162" s="3">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -12127,27 +12151,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B163" s="3">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D163" s="3">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>15</v>
@@ -12156,32 +12180,186 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B164" s="3">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D164" s="3">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F164" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J164" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B165" s="3">
+        <v>443</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D165" s="3">
+        <v>327</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F165" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G165" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J165" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B166" s="3">
+        <v>443</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D166" s="3">
+        <v>341</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J166" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B167" s="3">
+        <v>443</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D167" s="3">
+        <v>342</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J167" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B168" s="3">
+        <v>443</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D168" s="3">
+        <v>345</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J168" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B169" s="3">
+        <v>451</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D169" s="3">
+        <v>125</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="I164" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J164" s="8" t="d">
+      <c r="I169" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J169" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -12194,13 +12372,13 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J164">
-    <sortCondition ref="B2:B164"/>
-    <sortCondition ref="A2:A164"/>
-    <sortCondition ref="D2:D164"/>
-    <sortCondition ref="C2:C164"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J169">
+    <sortCondition ref="B2:B169"/>
+    <sortCondition ref="A2:A169"/>
+    <sortCondition ref="D2:D169"/>
+    <sortCondition ref="C2:C169"/>
   </sortState>
-  <conditionalFormatting sqref="A162:A1048576 C165:C1048576 A1:A154 C1:C154">
+  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A1048576 C165:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{077508F4-9B17-1940-B9D2-E35B9EB2AC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C44DBA6C-DDE4-E646-8A11-C5631D1D29DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2402" uniqueCount="457">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2448" uniqueCount="466">
   <si>
     <t>reviewer</t>
   </si>
@@ -1328,9 +1328,6 @@
     <t>We largely use the same approach used in BIPs 49, 84 and 86 for ease of implementation. [...] This BIP is not backwards compatible by design as described in the Considerations section of BIP 49. [...] Reference [...] BIP49 - Derivation scheme for P2WPKH-nested-in-P2SH based accounts</t>
   </si>
   <si>
-    <t>All inputs MUST set the nSequence to 0xFFFFFFFF (do not signal for BIP 125 RBF). [...] The batch creator MUST add a new dust UTXO input, and the resulting replacement transaction MUST satisfy BIP 125 RBF rules:</t>
-  </si>
-  <si>
     <t xml:space="preserve">The counter-argument is that these new multi-signature transactions will be used in combination with OP_EVAL (see the OP_EVAL BIP), </t>
   </si>
   <si>
@@ -1425,6 +1422,36 @@
   </si>
   <si>
     <t>BIP89 references BIP341 because its signing protocol is designed to be compatible with Taproot’s X-only key and tweak semantics, without requiring Taproot to define CCD itself.</t>
+  </si>
+  <si>
+    <t>All inputs MUST set the nSequence to 0xFFFFFFFF (do not signal for BIP 125 RBF). [...] The batch creator MUST add a new dust UTXO input, and the resulting replacement transaction MUST satisfy BIP 125 RBF rules [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147.  </t>
+  </si>
+  <si>
+    <t>"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147.  [...] timeout on midnight November 15th 2017 (epoch time 1510704000). This BIP will cease to be active when segwit (BIP141) is locked-in, active, or failed  [...] References [...] BIP141 Segregated Witness (Consensus Layer)</t>
+  </si>
+  <si>
+    <t>This document specifies a method to activate the existing BIP9 segwit deployment with a majority hashpower less than 95%. [...] "existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1 [...]  References [...] BIP9 Version bits with timeout and delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> References [...]  BIP16 Pay to Script Hash</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> References [...] BIP148 Mandatory activation of segwit deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> References [...] BIP149 Segregated Witness (second deployment)</t>
+  </si>
+  <si>
+    <t>BIP91's only purpose is to trigger activation of BIP141’s deployment.</t>
+  </si>
+  <si>
+    <t>Mentioned because it is bundled into the SegWit deployment.</t>
   </si>
 </sst>
 </file>
@@ -4501,6 +4528,12 @@
       <c r="B43" s="3">
         <v>91</v>
       </c>
+      <c r="C43" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
       <c r="E43" s="7" t="s">
         <v>17</v>
       </c>
@@ -7249,7 +7282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -7406,10 +7439,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -7476,7 +7509,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>218</v>
       </c>
@@ -7865,7 +7898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>218</v>
       </c>
@@ -9061,7 +9094,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>218</v>
       </c>
@@ -9080,8 +9113,8 @@
       <c r="F61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G61" t="s">
-        <v>426</v>
+      <c r="G61" s="4" t="s">
+        <v>425</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>15</v>
@@ -9109,11 +9142,11 @@
       <c r="F62" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G62" t="s">
-        <v>427</v>
+      <c r="G62" s="4" t="s">
+        <v>426</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
@@ -9142,7 +9175,7 @@
         <v>37</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
@@ -9171,7 +9204,7 @@
         <v>37</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
@@ -9200,10 +9233,10 @@
         <v>37</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>15</v>
@@ -9232,7 +9265,7 @@
         <v>37</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>15</v>
@@ -9261,7 +9294,7 @@
         <v>37</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
@@ -9604,7 +9637,7 @@
         <v>37</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
@@ -9633,10 +9666,10 @@
         <v>37</v>
       </c>
       <c r="G79" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="H79" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
@@ -9665,7 +9698,7 @@
         <v>37</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -9694,7 +9727,7 @@
         <v>37</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -9723,7 +9756,7 @@
         <v>37</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -9752,10 +9785,10 @@
         <v>146</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>15</v>
@@ -9784,10 +9817,10 @@
         <v>37</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>15</v>
@@ -9816,10 +9849,10 @@
         <v>146</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>15</v>
@@ -9848,10 +9881,10 @@
         <v>37</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>15</v>
@@ -9880,7 +9913,7 @@
         <v>37</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>15</v>
@@ -9909,7 +9942,7 @@
         <v>37</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>15</v>
@@ -9938,10 +9971,10 @@
         <v>146</v>
       </c>
       <c r="G89" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
@@ -9970,7 +10003,7 @@
         <v>37</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
@@ -9999,7 +10032,7 @@
         <v>37</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
@@ -10028,10 +10061,10 @@
         <v>37</v>
       </c>
       <c r="G92" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="H92" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>456</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
@@ -11103,7 +11136,7 @@
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -12354,12 +12387,224 @@
         <v>20</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J169" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B170" s="3">
+        <v>91</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D170" s="3">
+        <v>9</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J170" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B171" s="3">
+        <v>91</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D171" s="3">
+        <v>141</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J171" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B172" s="3">
+        <v>91</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D172" s="3">
+        <v>143</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J172" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B173" s="3">
+        <v>91</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D173" s="3">
+        <v>147</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J173" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B174" s="3">
+        <v>91</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D174" s="3">
+        <v>16</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J174" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B175" s="3">
+        <v>91</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D175" s="3">
+        <v>148</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J175" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B176" s="3">
+        <v>91</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D176" s="3">
+        <v>149</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J176" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -12378,7 +12623,7 @@
     <sortCondition ref="D2:D169"/>
     <sortCondition ref="C2:C169"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A1048576 C165:C1048576">
+  <conditionalFormatting sqref="A1:A154 C1:C154 C165:C1048576 A162:A1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C44DBA6C-DDE4-E646-8A11-C5631D1D29DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8FA51CC6-B842-BC4A-80D2-FFED6148D405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="39360" yWindow="960" windowWidth="37140" windowHeight="30960" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2448" uniqueCount="466">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2520" uniqueCount="482">
   <si>
     <t>reviewer</t>
   </si>
@@ -1452,6 +1452,54 @@
   </si>
   <si>
     <t>Mentioned because it is bundled into the SegWit deployment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bips </t>
+  </si>
+  <si>
+    <t>This BIP is used by BIP116 (MERKLEBRANCHVERIFY)[4] to add Merkle inclusion proof verification to script by means of a soft-fork NOP expansion opcode. Deployment of MERKLEBRANCHVERIFY would make the contents of this BIP consensus critical. The deployment plan for BIP116 is covered in the text of that BIP.</t>
+  </si>
+  <si>
+    <t>MERKLEBRANCHVERIFY</t>
+  </si>
+  <si>
+    <t>Although BIP16 (Pay to Script Hash)[2] and BIP141 (Segregated Witness)[3] both allow the redeem script to be kept out of the scriptPubKey and therefore out of the UTXO set, the entire spending conditions for a coin must nevertheless be revealed when that coin is spent.</t>
+  </si>
+  <si>
+    <t>The MERKLEBRANCHVERIFY opcode uses fast Merkle hash trees as specified by BIP98[1] rather than the construct used by Satoshi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However the more familiar NOP-expansion soft-fork mechanism used by BIP65 (CHECKLOCKTIMEVERIFY)[5] and BIP112 (CHECKSEQUENCEVERIFY)[6] was chosen over script versioning for the following two reasons: </t>
+  </si>
+  <si>
+    <t>Although BIP16 (Pay to Script Hash)[2] and BIP141 (Segregated Witness)[3] both allow the redeem script to be kept out of the scriptPubKey and therefore out of the UTXO set, the entire spending conditions for a coin must nevertheless be revealed when that coin is spent. [...] Additionally, script feature versioning should arguably be specified in the witness and the BIP141 script versioning only be used to specify the structure of the witness, however no such protocol exists as of yet.</t>
+  </si>
+  <si>
+    <t>results in standard P2SH or P2WSH-nested-in-P2SH addresses without the need for BIP143[7] signing code. This allows MERKLEBRANCHVERIFY to be used immediately by services that need it rather than wait on support for script versioning and/or BIP-143[7] signatures in tools and libraries.</t>
+  </si>
+  <si>
+    <t>This BIP will be deployed by BIP8 (Version bits with lock-in by height)[10] with the name "merklebranchverify" and using bit 2. For Bitcoin mainnet, the BIP8 startheight will be at height M to be determined and BIP8 timeout activation will occur on height M + 50,400 blocks. For Bitcoin testnet, the BIP8 startheight will be at height T to be determined and BIP8 timeout activation will occur on height T + 50,400 blocks.</t>
+  </si>
+  <si>
+    <t>We note that DISCOURAGE_UPGRADABLE_NOPS means that transactions which use this feature are already considered non-standard by the rules of the network, making deployment easier than was the case with, for example, with BIP68 (Relative lock-time using consensus-enforced sequence numbers)[9].</t>
+  </si>
+  <si>
+    <t>BIP16 is cited only as motivation/background for hiding redeem scripts from the UTXO set</t>
+  </si>
+  <si>
+    <t>BIP141 is solely discussed as motivation and as an alternative script-upgrade path</t>
+  </si>
+  <si>
+    <t>BIP65 is cited only as precedent for the NOP-expansion soft-fork pattern. BIP116 does not rely on CHECKLOCKTIMEVERIFY behavior.</t>
+  </si>
+  <si>
+    <t>BIP112 is cited only as precedent for the NOP-expansion soft-fork pattern. BIP116 does not rely on CHECKSEQUENCEVERIFY behavior.</t>
+  </si>
+  <si>
+    <t>BIP143 is mentioned only to explain that BIP116 avoids needing v0 witness signing support.</t>
+  </si>
+  <si>
+    <t>BIP68 is used only as a deployment comparison. BIP116 does not use relative lock-time semantics.</t>
   </si>
 </sst>
 </file>
@@ -2411,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
@@ -4578,6 +4626,12 @@
       <c r="B44" s="3">
         <v>98</v>
       </c>
+      <c r="C44" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
       <c r="E44" s="7" t="s">
         <v>17</v>
       </c>
@@ -5128,28 +5182,34 @@
         <v>218</v>
       </c>
       <c r="B56" s="3">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="8" t="d">
+        <v>2026-07-01</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>374</v>
+        <v>34</v>
+      </c>
+      <c r="K56" s="8" t="d">
+        <v>2017-08-25</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>66</v>
@@ -5161,10 +5221,10 @@
         <v>25</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>375</v>
+        <v>468</v>
       </c>
       <c r="P56" s="7">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
@@ -5172,13 +5232,7 @@
         <v>218</v>
       </c>
       <c r="B57" s="3">
-        <v>119</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>17</v>
@@ -5196,10 +5250,10 @@
         <v>37</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>66</v>
@@ -5211,10 +5265,10 @@
         <v>25</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c r="P57" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
@@ -5222,7 +5276,7 @@
         <v>218</v>
       </c>
       <c r="B58" s="3">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>15</v>
@@ -5240,16 +5294,16 @@
         <v>42</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J58" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>66</v>
@@ -5258,13 +5312,13 @@
         <v>24</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P58" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
@@ -5272,7 +5326,13 @@
         <v>218</v>
       </c>
       <c r="B59" s="3">
-        <v>125</v>
+        <v>122</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>17</v>
@@ -5287,16 +5347,16 @@
         <v>19</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M59" s="7" t="s">
         <v>24</v>
@@ -5305,10 +5365,10 @@
         <v>42</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="P59" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
@@ -5316,7 +5376,7 @@
         <v>218</v>
       </c>
       <c r="B60" s="3">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>17</v>
@@ -5328,7 +5388,7 @@
         <v>42</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>37</v>
@@ -5337,10 +5397,10 @@
         <v>288</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M60" s="7" t="s">
         <v>24</v>
@@ -5349,10 +5409,10 @@
         <v>42</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P60" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
@@ -5360,13 +5420,7 @@
         <v>218</v>
       </c>
       <c r="B61" s="3">
-        <v>128</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>17</v>
@@ -5378,16 +5432,16 @@
         <v>42</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>66</v>
@@ -5399,10 +5453,10 @@
         <v>42</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="P61" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
@@ -5410,7 +5464,13 @@
         <v>218</v>
       </c>
       <c r="B62" s="3">
-        <v>130</v>
+        <v>128</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>17</v>
@@ -5422,31 +5482,31 @@
         <v>42</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M62" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="P62" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
@@ -5454,7 +5514,7 @@
         <v>218</v>
       </c>
       <c r="B63" s="3">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>17</v>
@@ -5475,19 +5535,19 @@
         <v>288</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M63" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P63" s="7">
         <v>0</v>
@@ -5498,7 +5558,7 @@
         <v>218</v>
       </c>
       <c r="B64" s="3">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>17</v>
@@ -5510,31 +5570,31 @@
         <v>42</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J64" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M64" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>30</v>
+        <v>302</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P64" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.2">
@@ -5542,7 +5602,7 @@
         <v>218</v>
       </c>
       <c r="B65" s="3">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>17</v>
@@ -5563,19 +5623,19 @@
         <v>288</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M65" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>302</v>
+        <v>30</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P65" s="7">
         <v>1</v>
@@ -5586,7 +5646,7 @@
         <v>218</v>
       </c>
       <c r="B66" s="3">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>17</v>
@@ -5607,19 +5667,19 @@
         <v>288</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M66" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P66" s="7">
         <v>1</v>
@@ -5630,7 +5690,7 @@
         <v>218</v>
       </c>
       <c r="B67" s="3">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>17</v>
@@ -5645,13 +5705,13 @@
         <v>58</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J67" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="L67" s="7" t="s">
         <v>29</v>
@@ -5660,13 +5720,13 @@
         <v>24</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="P67" s="7">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
@@ -5674,13 +5734,7 @@
         <v>218</v>
       </c>
       <c r="B68" s="3">
-        <v>142</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>17</v>
@@ -5695,28 +5749,28 @@
         <v>58</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M68" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>85</v>
+        <v>325</v>
       </c>
       <c r="P68" s="7">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
@@ -5724,7 +5778,13 @@
         <v>218</v>
       </c>
       <c r="B69" s="3">
-        <v>144</v>
+        <v>142</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>17</v>
@@ -5736,31 +5796,31 @@
         <v>42</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M69" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>387</v>
+        <v>85</v>
       </c>
       <c r="P69" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
@@ -5768,13 +5828,7 @@
         <v>218</v>
       </c>
       <c r="B70" s="3">
-        <v>145</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>17</v>
@@ -5786,16 +5840,16 @@
         <v>42</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>37</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>86</v>
+        <v>386</v>
       </c>
       <c r="L70" s="7" t="s">
         <v>29</v>
@@ -5804,13 +5858,13 @@
         <v>24</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>87</v>
+        <v>387</v>
       </c>
       <c r="P70" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
@@ -5818,7 +5872,13 @@
         <v>218</v>
       </c>
       <c r="B71" s="3">
-        <v>147</v>
+        <v>145</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>17</v>
@@ -5836,10 +5896,10 @@
         <v>37</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>388</v>
+        <v>86</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>29</v>
@@ -5848,13 +5908,13 @@
         <v>24</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>389</v>
+        <v>87</v>
       </c>
       <c r="P71" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
@@ -5862,7 +5922,7 @@
         <v>218</v>
       </c>
       <c r="B72" s="3">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>17</v>
@@ -5883,7 +5943,7 @@
         <v>288</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>326</v>
+        <v>388</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>29</v>
@@ -5895,7 +5955,7 @@
         <v>25</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="P72" s="7">
         <v>5</v>
@@ -5906,7 +5966,7 @@
         <v>218</v>
       </c>
       <c r="B73" s="3">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>17</v>
@@ -5921,28 +5981,28 @@
         <v>58</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>390</v>
+        <v>326</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M73" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="P73" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
@@ -5950,13 +6010,7 @@
         <v>218</v>
       </c>
       <c r="B74" s="3">
-        <v>158</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>17</v>
@@ -5974,13 +6028,13 @@
         <v>20</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>88</v>
+        <v>390</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M74" s="7" t="s">
         <v>24</v>
@@ -5989,10 +6043,10 @@
         <v>30</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>89</v>
+        <v>391</v>
       </c>
       <c r="P74" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
@@ -6000,7 +6054,13 @@
         <v>218</v>
       </c>
       <c r="B75" s="3">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>17</v>
@@ -6015,13 +6075,13 @@
         <v>58</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>328</v>
+        <v>88</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>29</v>
@@ -6033,10 +6093,10 @@
         <v>30</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>329</v>
+        <v>89</v>
       </c>
       <c r="P75" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
@@ -6044,7 +6104,7 @@
         <v>218</v>
       </c>
       <c r="B76" s="3">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>17</v>
@@ -6065,19 +6125,19 @@
         <v>288</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M76" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="P76" s="7">
         <v>0</v>
@@ -6088,7 +6148,7 @@
         <v>218</v>
       </c>
       <c r="B77" s="3">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>17</v>
@@ -6103,16 +6163,16 @@
         <v>58</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M77" s="7" t="s">
         <v>24</v>
@@ -6121,10 +6181,10 @@
         <v>42</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>393</v>
+        <v>331</v>
       </c>
       <c r="P77" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.2">
@@ -6132,13 +6192,7 @@
         <v>218</v>
       </c>
       <c r="B78" s="3">
-        <v>197</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>17</v>
@@ -6153,16 +6207,16 @@
         <v>58</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>90</v>
+        <v>392</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M78" s="7" t="s">
         <v>24</v>
@@ -6171,10 +6225,10 @@
         <v>42</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>91</v>
+        <v>393</v>
       </c>
       <c r="P78" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.2">
@@ -6182,7 +6236,13 @@
         <v>218</v>
       </c>
       <c r="B79" s="3">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>17</v>
@@ -6197,16 +6257,16 @@
         <v>58</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>332</v>
+        <v>90</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="M79" s="7" t="s">
         <v>24</v>
@@ -6215,10 +6275,10 @@
         <v>42</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="P79" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.2">
@@ -6226,7 +6286,7 @@
         <v>218</v>
       </c>
       <c r="B80" s="3">
-        <v>300</v>
+        <v>199</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>17</v>
@@ -6241,28 +6301,28 @@
         <v>58</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M80" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P80" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.2">
@@ -6270,7 +6330,7 @@
         <v>218</v>
       </c>
       <c r="B81" s="3">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>17</v>
@@ -6291,7 +6351,7 @@
         <v>288</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>394</v>
+        <v>334</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>66</v>
@@ -6303,7 +6363,7 @@
         <v>25</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="P81" s="7">
         <v>1</v>
@@ -6314,13 +6374,7 @@
         <v>218</v>
       </c>
       <c r="B82" s="3">
-        <v>320</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>32</v>
+        <v>301</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>17</v>
@@ -6335,13 +6389,13 @@
         <v>58</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>92</v>
+        <v>394</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>66</v>
@@ -6349,11 +6403,14 @@
       <c r="M82" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="N82" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="O82" s="3" t="s">
-        <v>93</v>
+        <v>395</v>
       </c>
       <c r="P82" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.2">
@@ -6361,49 +6418,46 @@
         <v>218</v>
       </c>
       <c r="B83" s="3">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G83" s="7">
+        <v>42</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="M83" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="O83" s="3" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="P83" s="7">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.2">
@@ -6411,40 +6465,49 @@
         <v>218</v>
       </c>
       <c r="B84" s="3">
-        <v>323</v>
+        <v>321</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G84" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>396</v>
+        <v>94</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="M84" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="N84" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="O84" s="3" t="s">
-        <v>397</v>
+        <v>43</v>
       </c>
       <c r="P84" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.2">
@@ -6452,46 +6515,37 @@
         <v>218</v>
       </c>
       <c r="B85" s="3">
-        <v>324</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>32</v>
+        <v>323</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="G85" s="7">
+        <v>42</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>95</v>
+        <v>396</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M85" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N85" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="O85" s="3" t="s">
-        <v>96</v>
+        <v>397</v>
       </c>
       <c r="P85" s="7">
         <v>3</v>
@@ -6502,7 +6556,7 @@
         <v>218</v>
       </c>
       <c r="B86" s="3">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>15</v>
@@ -6511,28 +6565,28 @@
         <v>32</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G86" s="7">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M86" s="7" t="s">
         <v>24</v>
@@ -6541,10 +6595,10 @@
         <v>30</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="P86" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
@@ -6552,7 +6606,7 @@
         <v>218</v>
       </c>
       <c r="B87" s="3">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>15</v>
@@ -6570,16 +6624,16 @@
         <v>42</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J87" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L87" s="7" t="s">
         <v>66</v>
@@ -6591,10 +6645,10 @@
         <v>30</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P87" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
@@ -6602,7 +6656,13 @@
         <v>218</v>
       </c>
       <c r="B88" s="3">
-        <v>337</v>
+        <v>331</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>17</v>
@@ -6617,13 +6677,13 @@
         <v>81</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>336</v>
+        <v>99</v>
       </c>
       <c r="L88" s="7" t="s">
         <v>66</v>
@@ -6632,13 +6692,13 @@
         <v>24</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>337</v>
+        <v>100</v>
       </c>
       <c r="P88" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
@@ -6646,7 +6706,7 @@
         <v>218</v>
       </c>
       <c r="B89" s="3">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>17</v>
@@ -6658,31 +6718,31 @@
         <v>42</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="M89" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P89" s="7">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
@@ -6690,7 +6750,7 @@
         <v>218</v>
       </c>
       <c r="B90" s="3">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>17</v>
@@ -6702,7 +6762,7 @@
         <v>42</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>37</v>
@@ -6711,7 +6771,7 @@
         <v>288</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L90" s="7" t="s">
         <v>29</v>
@@ -6723,10 +6783,10 @@
         <v>25</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="P90" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
@@ -6734,13 +6794,7 @@
         <v>218</v>
       </c>
       <c r="B91" s="3">
-        <v>347</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>32</v>
+        <v>343</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>17</v>
@@ -6755,16 +6809,16 @@
         <v>81</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>101</v>
+        <v>340</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M91" s="7" t="s">
         <v>24</v>
@@ -6773,10 +6827,10 @@
         <v>25</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>102</v>
+        <v>341</v>
       </c>
       <c r="P91" s="7">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
@@ -6784,7 +6838,7 @@
         <v>218</v>
       </c>
       <c r="B92" s="3">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>15</v>
@@ -6805,13 +6859,13 @@
         <v>81</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J92" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L92" s="7" t="s">
         <v>39</v>
@@ -6820,13 +6874,13 @@
         <v>24</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P92" s="7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
@@ -6834,7 +6888,13 @@
         <v>218</v>
       </c>
       <c r="B93" s="3">
-        <v>370</v>
+        <v>353</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>17</v>
@@ -6849,16 +6909,16 @@
         <v>81</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>342</v>
+        <v>103</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="M93" s="7" t="s">
         <v>24</v>
@@ -6867,10 +6927,10 @@
         <v>42</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>343</v>
+        <v>104</v>
       </c>
       <c r="P93" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
@@ -6878,7 +6938,7 @@
         <v>218</v>
       </c>
       <c r="B94" s="3">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>17</v>
@@ -6893,13 +6953,13 @@
         <v>81</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J94" s="7" t="s">
         <v>288</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>29</v>
@@ -6911,10 +6971,10 @@
         <v>42</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P94" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
@@ -6922,7 +6982,7 @@
         <v>218</v>
       </c>
       <c r="B95" s="3">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>17</v>
@@ -6943,10 +7003,10 @@
         <v>288</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="M95" s="7" t="s">
         <v>24</v>
@@ -6955,10 +7015,10 @@
         <v>42</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="P95" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
@@ -6966,13 +7026,7 @@
         <v>218</v>
       </c>
       <c r="B96" s="3">
-        <v>375</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>32</v>
+        <v>374</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>17</v>
@@ -6990,10 +7044,10 @@
         <v>37</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>105</v>
+        <v>398</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>66</v>
@@ -7005,10 +7059,10 @@
         <v>42</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="P96" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
@@ -7016,7 +7070,7 @@
         <v>218</v>
       </c>
       <c r="B97" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>15</v>
@@ -7043,7 +7097,7 @@
         <v>21</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L97" s="7" t="s">
         <v>66</v>
@@ -7055,10 +7109,10 @@
         <v>42</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P97" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
@@ -7066,7 +7120,7 @@
         <v>218</v>
       </c>
       <c r="B98" s="3">
-        <v>440</v>
+        <v>392</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>15</v>
@@ -7087,13 +7141,13 @@
         <v>81</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J98" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L98" s="7" t="s">
         <v>66</v>
@@ -7102,13 +7156,13 @@
         <v>24</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P98" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
@@ -7116,7 +7170,13 @@
         <v>218</v>
       </c>
       <c r="B99" s="3">
-        <v>442</v>
+        <v>440</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>17</v>
@@ -7131,13 +7191,13 @@
         <v>81</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>400</v>
+        <v>109</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>66</v>
@@ -7149,10 +7209,10 @@
         <v>25</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>401</v>
+        <v>110</v>
       </c>
       <c r="P99" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.2">
@@ -7160,13 +7220,7 @@
         <v>218</v>
       </c>
       <c r="B100" s="3">
-        <v>443</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>32</v>
+        <v>442</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>17</v>
@@ -7181,13 +7235,13 @@
         <v>81</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>111</v>
+        <v>400</v>
       </c>
       <c r="L100" s="7" t="s">
         <v>66</v>
@@ -7199,10 +7253,10 @@
         <v>25</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>112</v>
+        <v>401</v>
       </c>
       <c r="P100" s="7">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.2">
@@ -7210,13 +7264,13 @@
         <v>218</v>
       </c>
       <c r="B101" s="3">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D101" s="8" t="d">
-        <v>2026-06-30</v>
+      <c r="D101" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>17</v>
@@ -7231,13 +7285,13 @@
         <v>81</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>66</v>
@@ -7246,12 +7300,62 @@
         <v>24</v>
       </c>
       <c r="N101" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="P101" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B102" s="3">
+        <v>451</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" s="7">
         <v>42</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="H102" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M102" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="P101" s="7">
+      <c r="P102" s="7">
         <v>1</v>
       </c>
     </row>
@@ -7262,9 +7366,9 @@
       <sortCondition ref="A2:A43"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q101">
-    <sortCondition ref="B2:B101"/>
-    <sortCondition ref="A2:A101"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q102">
+    <sortCondition ref="B2:B102"/>
+    <sortCondition ref="A2:A102"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
@@ -7282,7 +7386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -10073,18 +10177,18 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B93" s="3">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D93" s="3">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>118</v>
@@ -10093,266 +10197,254 @@
         <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>173</v>
+        <v>460</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J93" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J93" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B94" s="3">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D94" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E94" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="3">
+        <v>91</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D95" s="3">
+        <v>141</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B95" s="3">
-        <v>112</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D95" s="3">
-        <v>65</v>
-      </c>
-      <c r="E95" s="3" t="s">
+      <c r="F95" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96" s="3">
+        <v>91</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D96" s="3">
+        <v>143</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B96" s="3">
-        <v>112</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D96" s="3">
-        <v>68</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>176</v>
+        <v>458</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>465</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J96" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J96" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B97" s="3">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D97" s="3">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>179</v>
+        <v>457</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>178</v>
+        <v>465</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J97" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J97" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B98" s="3">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D98" s="3">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>175</v>
+        <v>462</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J98" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J98" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B99" s="3">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D99" s="3">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>181</v>
+        <v>463</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J99" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J99" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B100" s="3">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D100" s="3">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J100" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B101" s="3">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D101" s="3">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10360,7 +10452,7 @@
         <v>218</v>
       </c>
       <c r="B102" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>218</v>
@@ -10375,77 +10467,77 @@
         <v>37</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B103" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D103" s="3">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D104" s="3">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10453,51 +10545,57 @@
         <v>218</v>
       </c>
       <c r="B105" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D105" s="3">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B106" s="3">
+        <v>113</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D106" s="3">
+        <v>9</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B106" s="3">
-        <v>119</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D106" s="3">
-        <v>65</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F106" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>190</v>
+        <v>174</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10511,22 +10609,25 @@
         <v>218</v>
       </c>
       <c r="B107" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D107" s="3">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -10535,30 +10636,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B108" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D108" s="3">
-        <v>341</v>
+        <v>68</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -10567,30 +10668,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B109" s="3">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D109" s="3">
-        <v>346</v>
+        <v>112</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -10599,30 +10700,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B110" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D110" s="3">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -10631,27 +10729,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B111" s="3">
+        <v>114</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D111" s="3">
+        <v>16</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D111" s="3">
-        <v>68</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F111" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>197</v>
+        <v>182</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -10660,12 +10761,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B112" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>218</v>
@@ -10677,10 +10778,13 @@
         <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -10689,27 +10793,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B113" s="3">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D113" s="3">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10718,198 +10822,201 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B114" s="3">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D114" s="3">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>198</v>
+        <v>474</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J114" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J114" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B115" s="3">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D115" s="3">
-        <v>433</v>
+        <v>16</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>199</v>
+        <v>469</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J115" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J115" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B116" s="3">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D116" s="3">
-        <v>443</v>
+        <v>65</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>196</v>
+        <v>471</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>478</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J116" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J116" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B117" s="3">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D117" s="3">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>202</v>
+        <v>475</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>203</v>
+        <v>481</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J117" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J117" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B118" s="3">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D118" s="3">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>204</v>
+        <v>470</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J118" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J118" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B119" s="3">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D119" s="3">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>205</v>
+        <v>146</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>203</v>
+        <v>479</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J119" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J119" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B120" s="3">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D120" s="3">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>128</v>
@@ -10918,16 +11025,16 @@
         <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>205</v>
+        <v>472</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>203</v>
+        <v>477</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J120" s="8" t="s">
-        <v>32</v>
+      <c r="J120" s="8" t="d">
+        <v>2026-07-01</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -10935,13 +11042,13 @@
         <v>218</v>
       </c>
       <c r="B121" s="3">
-        <v>142</v>
+        <v>116</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D121" s="3">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>128</v>
@@ -10950,42 +11057,39 @@
         <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>205</v>
+        <v>473</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>203</v>
+        <v>480</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J121" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J121" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B122" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D122" s="3">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -10999,25 +11103,22 @@
         <v>218</v>
       </c>
       <c r="B123" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D123" s="3">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -11031,22 +11132,25 @@
         <v>218</v>
       </c>
       <c r="B124" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D124" s="3">
-        <v>22</v>
+        <v>341</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>208</v>
+        <v>191</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -11055,30 +11159,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B125" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D125" s="3">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -11087,18 +11191,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B126" s="3">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D126" s="3">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>128</v>
@@ -11107,7 +11211,10 @@
         <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>209</v>
+        <v>193</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -11121,22 +11228,22 @@
         <v>218</v>
       </c>
       <c r="B127" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D127" s="3">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>427</v>
+        <v>197</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -11145,27 +11252,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B128" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D128" s="3">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
@@ -11174,27 +11281,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B129" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D129" s="3">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -11208,22 +11315,22 @@
         <v>218</v>
       </c>
       <c r="B130" s="3">
-        <v>197</v>
-      </c>
-      <c r="C130" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D130" s="3">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -11232,163 +11339,169 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B131" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D131" s="3">
-        <v>8</v>
+        <v>433</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>250</v>
+        <v>199</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J131" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B132" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D132" s="3">
-        <v>9</v>
+        <v>443</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J132" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B133" s="3">
-        <v>320</v>
+        <v>142</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D133" s="3">
-        <v>323</v>
+        <v>13</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>249</v>
+        <v>202</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J133" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J133" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B134" s="3">
-        <v>321</v>
-      </c>
-      <c r="C134" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D134" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B135" s="3">
-        <v>321</v>
-      </c>
-      <c r="C135" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D135" s="3">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>239</v>
+        <v>205</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B136" s="3">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D136" s="3">
-        <v>351</v>
+        <v>63</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>128</v>
@@ -11397,27 +11510,30 @@
         <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J136" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B137" s="3">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D137" s="3">
-        <v>352</v>
+        <v>70</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>128</v>
@@ -11426,74 +11542,80 @@
         <v>37</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>240</v>
+        <v>205</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B138" s="3">
-        <v>324</v>
+        <v>142</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D138" s="3">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F138" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A139" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B139" s="3">
+        <v>145</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D139" s="3">
+        <v>9</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F139" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G138" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J138" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A139" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B139" s="3">
-        <v>324</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D139" s="3">
-        <v>151</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G139" s="4" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J139" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J139" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -11501,118 +11623,118 @@
         <v>218</v>
       </c>
       <c r="B140" s="3">
-        <v>324</v>
+        <v>145</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D140" s="3">
-        <v>340</v>
+        <v>22</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H140" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J140" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B141" s="3">
         <v>145</v>
       </c>
-      <c r="I140" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J140" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B141" s="3">
-        <v>330</v>
-      </c>
       <c r="C141" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D141" s="3">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>253</v>
+        <v>212</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J141" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J141" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B142" s="3">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D142" s="3">
-        <v>339</v>
+        <v>141</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J142" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J142" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B143" s="3">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D143" s="3">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>252</v>
+        <v>427</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J143" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J143" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11620,100 +11742,100 @@
         <v>218</v>
       </c>
       <c r="B144" s="3">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D144" s="3">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J144" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J144" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="3">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D145" s="3">
-        <v>330</v>
+        <v>157</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J145" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J145" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B146" s="3">
-        <v>331</v>
-      </c>
-      <c r="C146" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C146" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D146" s="3">
-        <v>339</v>
+        <v>199</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J146" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J146" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B147" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D147" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>128</v>
@@ -11722,7 +11844,7 @@
         <v>20</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -11736,25 +11858,22 @@
         <v>218</v>
       </c>
       <c r="B148" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D148" s="3">
-        <v>340</v>
+        <v>9</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H148" s="4" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
@@ -11763,30 +11882,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B149" s="3">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D149" s="3">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H149" s="4" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
@@ -11795,36 +11911,33 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B150" s="3">
-        <v>347</v>
-      </c>
-      <c r="C150" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C150" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D150" s="3">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J150" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J150" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11832,28 +11945,28 @@
         <v>218</v>
       </c>
       <c r="B151" s="3">
-        <v>353</v>
-      </c>
-      <c r="C151" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C151" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D151" s="3">
         <v>21</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J151" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J151" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -11861,36 +11974,36 @@
         <v>218</v>
       </c>
       <c r="B152" s="3">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D152" s="3">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J152" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J152" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B153" s="3">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>218</v>
@@ -11905,42 +12018,36 @@
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J153" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J153" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B154" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D154" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -11949,27 +12056,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B155" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D155" s="3">
-        <v>352</v>
+        <v>151</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>267</v>
+        <v>142</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -11983,22 +12093,25 @@
         <v>218</v>
       </c>
       <c r="B156" s="3">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D156" s="3">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>267</v>
+        <v>144</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -12007,27 +12120,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B157" s="3">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D157" s="3">
-        <v>374</v>
+        <v>141</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -12036,27 +12149,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B158" s="3">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D158" s="3">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -12065,30 +12178,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B159" s="3">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D159" s="3">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -12097,27 +12207,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B160" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D160" s="3">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -12131,22 +12241,22 @@
         <v>218</v>
       </c>
       <c r="B161" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D161" s="3">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -12155,27 +12265,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B162" s="3">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D162" s="3">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -12184,27 +12294,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B163" s="3">
-        <v>440</v>
+        <v>347</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D163" s="3">
-        <v>342</v>
+        <v>3</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>15</v>
@@ -12218,22 +12328,25 @@
         <v>218</v>
       </c>
       <c r="B164" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D164" s="3">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>278</v>
+        <v>258</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>15</v>
@@ -12247,25 +12360,25 @@
         <v>218</v>
       </c>
       <c r="B165" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D165" s="3">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>15</v>
@@ -12274,18 +12387,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B166" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D166" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>118</v>
@@ -12294,10 +12407,10 @@
         <v>37</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>15</v>
@@ -12306,18 +12419,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B167" s="3">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D167" s="3">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>118</v>
@@ -12326,10 +12439,7 @@
         <v>37</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H167" s="4" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>15</v>
@@ -12343,13 +12453,13 @@
         <v>218</v>
       </c>
       <c r="B168" s="3">
-        <v>443</v>
+        <v>353</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D168" s="3">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>128</v>
@@ -12358,7 +12468,7 @@
         <v>146</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>15</v>
@@ -12367,76 +12477,82 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B169" s="3">
-        <v>451</v>
+        <v>353</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D169" s="3">
-        <v>125</v>
+        <v>352</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>456</v>
+        <v>283</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J169" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B170" s="3">
-        <v>91</v>
+        <v>375</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D170" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>460</v>
+        <v>286</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="I170" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J170" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B171" s="3">
-        <v>91</v>
+        <v>375</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D171" s="3">
-        <v>141</v>
+        <v>352</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>118</v>
@@ -12445,16 +12561,13 @@
         <v>37</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="H171" s="4" t="s">
-        <v>464</v>
+        <v>267</v>
       </c>
       <c r="I171" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J171" s="8" t="d">
-        <v>2026-06-30</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -12462,31 +12575,28 @@
         <v>218</v>
       </c>
       <c r="B172" s="3">
-        <v>91</v>
+        <v>375</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D172" s="3">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="H172" s="4" t="s">
-        <v>465</v>
+        <v>267</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J172" s="8" t="d">
-        <v>2026-06-30</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -12494,117 +12604,387 @@
         <v>218</v>
       </c>
       <c r="B173" s="3">
-        <v>91</v>
+        <v>375</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D173" s="3">
-        <v>147</v>
+        <v>374</v>
       </c>
       <c r="E173" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J173" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B174" s="3">
+        <v>392</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D174" s="3">
+        <v>341</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J174" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B175" s="3">
+        <v>392</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D175" s="3">
+        <v>350</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J175" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B176" s="3">
+        <v>392</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D176" s="3">
+        <v>352</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J176" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B177" s="3">
+        <v>392</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D177" s="3">
+        <v>380</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J177" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B178" s="3">
+        <v>392</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D178" s="3">
+        <v>390</v>
+      </c>
+      <c r="E178" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F173" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G173" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="H173" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="I173" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J173" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B174" s="3">
-        <v>91</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D174" s="3">
-        <v>16</v>
-      </c>
-      <c r="E174" s="3" t="s">
+      <c r="F178" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J178" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B179" s="3">
+        <v>440</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D179" s="3">
+        <v>342</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J179" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B180" s="3">
+        <v>443</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D180" s="3">
+        <v>119</v>
+      </c>
+      <c r="E180" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F174" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G174" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="I174" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J174" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B175" s="3">
-        <v>91</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D175" s="3">
-        <v>148</v>
-      </c>
-      <c r="E175" s="3" t="s">
+      <c r="F180" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J180" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B181" s="3">
+        <v>443</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D181" s="3">
+        <v>327</v>
+      </c>
+      <c r="E181" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F175" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="I175" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J175" s="8" t="d">
-        <v>2026-06-30</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B176" s="3">
-        <v>91</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D176" s="3">
-        <v>149</v>
-      </c>
-      <c r="E176" s="3" t="s">
+      <c r="F181" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J181" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B182" s="3">
+        <v>443</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D182" s="3">
+        <v>341</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J182" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B183" s="3">
+        <v>443</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D183" s="3">
+        <v>342</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J183" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B184" s="3">
+        <v>443</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D184" s="3">
+        <v>345</v>
+      </c>
+      <c r="E184" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F176" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G176" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="I176" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J176" s="8" t="d">
+      <c r="F184" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J184" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B185" s="3">
+        <v>451</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D185" s="3">
+        <v>125</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J185" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -12617,11 +12997,11 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J169">
-    <sortCondition ref="B2:B169"/>
-    <sortCondition ref="A2:A169"/>
-    <sortCondition ref="D2:D169"/>
-    <sortCondition ref="C2:C169"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J185">
+    <sortCondition ref="B2:B185"/>
+    <sortCondition ref="A2:A185"/>
+    <sortCondition ref="D2:D185"/>
+    <sortCondition ref="C2:C185"/>
   </sortState>
   <conditionalFormatting sqref="A1:A154 C1:C154 C165:C1048576 A162:A1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8FA51CC6-B842-BC4A-80D2-FFED6148D405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5651D7EF-4F3D-5745-A121-89A17706583F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39360" yWindow="960" windowWidth="37140" windowHeight="30960" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51200" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2520" uniqueCount="482">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2757" uniqueCount="537">
   <si>
     <t>reviewer</t>
   </si>
@@ -1500,6 +1500,171 @@
   </si>
   <si>
     <t>BIP68 is used only as a deployment comparison. BIP116 does not use relative lock-time semantics.</t>
+  </si>
+  <si>
+    <t>If the block height is encoded at the start of the coinbase scriptSig, as per BIP34, it is ignored.</t>
+  </si>
+  <si>
+    <t>Miner vote approach defined in BIP100</t>
+  </si>
+  <si>
+    <t>Hard-coded increase defined in BIP102</t>
+  </si>
+  <si>
+    <t>Allow miners to vote for max block size, rejected because: [...]</t>
+  </si>
+  <si>
+    <t>A hardcoded increase to max block size (2MB, 8MB, etc.), rejected because: [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivation Blocks are already too full and cannot support further transaction growth. While SegWit and Lightning (and other off-chain solutions) will help, they will not solve this problem. </t>
+  </si>
+  <si>
+    <t>SegWit is defined in BIP141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free voting as suggested by BIP100 allows miners to sell their votes out of band at no risk, and enable the sponsor the ability to manipulate the blocksize. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votes are cast using the block's coinbase transaction scriptSig. As per BIP34, the coinbase transaction scriptSig starts with a push of the block height. The next push is a little-endian number representing the preferred block size in bytes. [...] References BIP34 </t>
+  </si>
+  <si>
+    <t>Deployment Similar deployment model to BIP101: [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP will be deployed by "version bits" BIP9 with the name "cbah" and using bit TBD. </t>
+  </si>
+  <si>
+    <t>BIP16 (Pay to Script Hash)[1] and BIP141 (Segregated Witness)[2] provide mechanisms by which script policy can be revealed at spend time as part of the execution witness. In both cases only a single script can be committed to by the construct. [...] References [1]  BIP16: Pay to Script Hash [...]</t>
+  </si>
+  <si>
+    <t>BIP16 (Pay to Script Hash)[1] and BIP141 (Segregated Witness)[2] provide mechanisms by which script policy can be revealed at spend time as part of the execution witness. In both cases only a single script can be committed to by the construct. [...] References [... ] [2] BIP141: Segregated Witness (Consensus Layer) [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP, in conjunction with BIP116 (MERKLEBRANCHVERIFY)[3] allows for a script to commit to a practically unbounded number of code pathways, and then reveal the actual code pathway used at spend time. [...] BIP116 (MERKLEBRANCHVERIFY)[3] allows multiple data elements to be committed to while only revealing those necessary at the time of spend. The MERKLEBRANCHVERIFY opcode is only able to provide commitments to a preselected set of data values, and does not by itself allow for executing code.  [...] References [... ] [3] BIP116: MERKLEBRANCHVERIFY [...] </t>
+  </si>
+  <si>
+    <t>Comparison with BIP114 BIP114 (Merkelized Abstract Syntax Tree)[5] specifies an explicit MAST scheme activated by BIP141 script versioning[2]. Unlike BIP114, the scheme proposed by this BIP in conjunction with BIP116 (MERKLEBRANCHVERIFY)[3] implicitly enables MAST constructs using script itself to validate membership of the policy script in the MAST. [...] References [... ] [5] BIP114: Merkelized Abstract Syntax Tree [...]</t>
+  </si>
+  <si>
+    <t>This BIP will be deployed by BIP8 (Version bits with lock-in by height)[9] with the name "tailcall" and using bit 3.  [...] References [... ] [9] BIP8: Version bits with lock-in by height [...]</t>
+  </si>
+  <si>
+    <t>We note that CLEANSTACK means that transactions which use this feature are already considered non-standard by the rules of the network, making deployment easier than was the case with, for example, with BIP68 (Relative lock-time using consensus-enforced sequence numbers)[6]. [...] References [... ] [6] BIP68: Relative lock-time using consensus-enforced sequence numbers [...]</t>
+  </si>
+  <si>
+    <t>BIP117 is explicitly designed to be used “in conjunction with BIP116” to enable generalized MAST</t>
+  </si>
+  <si>
+    <t>BIP117's usable consensus semantics depend on SegWit script execution context.</t>
+  </si>
+  <si>
+    <t>BIP117 uses BIP16/P2SH as prior art for delayed revelation of script policy, but tail-call execution is explicitly not enabled from P2SH redeem scripts and does not depend on BIP16.</t>
+  </si>
+  <si>
+    <t>BIP117 solely compares its BIP116-based programmable MAST construction against BIP114’s explicit MAST scheme, but it does not implement or require BIP114.</t>
+  </si>
+  <si>
+    <t>BIP117 mentions BIP68 only as a deployment comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There are no known problematic interactions between opt-in full-RBF and other uses of nSequence. Specifically, opt-in full-RBF is compatible with consensus-enforced locktime as provided in the Bitcoin 0.1 implementation, BIP68 (Relative lock-time using consensus-enforced sequence numbers), and BIP112 (CHECKSEQUENCEVERIFY). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It relies on existing standards such as regular Bitcoin transaction serialization/validation and the BIP 174 PSBT format. [...] PSBT (BIP 174) extension The "commitment input" detailed in the proof format section does not spend an existing UTXO and thus shouldn't be signed (empty scriptSig and witness). [...] An addition to the BIP 174 PSBT format could help signing devices to recognize proof-of-reserve transactions. The following field is added to the BIP 174 INPUT map:</t>
+  </si>
+  <si>
+    <t>BIP127 explicitly relies on the BIP174 PSBT format and defines a Partially Signed Bitcoin Transaction Format (PSBT) input-map extension, so PSBT support is required for the standardized signing/UX part of the proposal.</t>
+  </si>
+  <si>
+    <t>Specification [...] The fee filter is additive with a bloom filter for transactions so if an SPV client were to load a bloom filter and send a feefilter message, transactions would only be relayed if they passed both filters.</t>
+  </si>
+  <si>
+    <t>Bloom filter is defined in BIP37, so BIP37 is relevant interoperability context, but feefilter can be implemented without bloom filtering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This protocol upgrade cleans up past soft fork changes like BIP68 which reuse existing fields and do them in a better to maintain and easier to parse system. It creates the building blocks to allow new features to be added much cleaner in the future. </t>
+  </si>
+  <si>
+    <t>BIP134 explicitly describes Flexible Transactions as cleaning up prior soft-fork changes such as (e.g.) BIP68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document describes a signature format for signing messages with Bitcoin private keys. The specification is intended to describe the standard for signatures of messages that can be signed and verified between different clients [...]. See BIP 322 [1] for full details on the new signature scheme. </t>
+  </si>
+  <si>
+    <t>BIP137 points to BIP322 as a newer message-signing scheme with advantages, but BIP137 defines a backwards-compatible legacy signature format that can be implemented independently of BIP322.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While there was no BIP written for how to digitally sign messages with Bitcoin private keys with P2PKH addresses it is a fairly well understood process, however with the introduction of Segwit (both in the form of P2SH and bech32) addresses, it is unclear how to distinguish a P2PKH, P2SH, or bech32 address from one another. This BIP proposes a standard signature format that will allow clients to distinguish between the different address formats. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If the header value is between 35 and 38 inclusive, it is a p2sh segwit address [...] So, you have the following ranges:  27-30: P2PKH uncompressed, 31-34: P2PKH compressed, 35-38: Segwit P2SH, 39-42: Segwit Bech32</t>
+  </si>
+  <si>
+    <t>BIP137 assigns message-signature header ranges for SegWit address types, including P2SH-wrapped SegWit and native witness addresses. BIP141 is relevant because it defines the SegWit witness-program semantics, but BIP137 only labels/verifies message signatures and does not require SegWit consensus validation.</t>
+  </si>
+  <si>
+    <t>BIP137 assigns header values 39-42 to “Segwit Bech32” message signatures. BIP173 is relevant because it defines Bech32 address encoding for native SegWit addresses, but BIP137 does not depend on Bech32 except when mapping the recovered key to an address string.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP will be deployed by "version bits" BIP9 with the name "segwit" and using bit 1. </t>
+  </si>
+  <si>
+    <t>BIP141 defines P2SH-wrapped witness programs, where a BIP16 redeemScript pushed in scriptSig triggers SegWit witness validation. This nested witness form depends on P2SH semantics.</t>
+  </si>
+  <si>
+    <t>BIP141 delegates the consensus-critical signature digest algorithm for version-0 witness programs to BIP143, making BIP143 required for validating SegWit v0 spends.</t>
+  </si>
+  <si>
+    <t>BIP141 defines block and transaction weight using total size serialized as described in BIP144, so the witness transaction serialization format is part of the consensus accounting model.</t>
+  </si>
+  <si>
+    <t>New script semantics [...] Despite that the script language for P2WPKH and P2WSH looks very similar to pre-segregated witness script, there are several notable differences. Users MUST NOT assume that a script spendable in pre-segregated witness system would also be spendable as a P2WPKH or P2WSH script. Before large-scale deployment in the production network, developers should test the scripts on testnet with the default relay policy turned on, and with a small amount of money after BIP141 is activated on mainnet. A major difference at consensus level is described in BIP143, as a new transaction digest algorithm for signature verification in version 0 witness program. [...] users MUST observe the new semantics carefully: Only compressed public keys are accepted in P2WPKH and P2WSH (See BIP143) [...] References [... ] BIP143 Transaction Signature Verification for Version 0 Witness Program [...]</t>
+  </si>
+  <si>
+    <t>Total size is the block size in bytes with transactions serialized as described in BIP144, including base data and witness data. [...] References [... ] BIP144 Segregated Witness (Peer Services) [...]</t>
+  </si>
+  <si>
+    <t>References [... ] BIP173 Base32 address format for native v0-16 witness outputs</t>
+  </si>
+  <si>
+    <t>BIP141 lists BIP173 as the address format for native witness outputs, but SegWit consensus defines witness programs independently of Bech32 address encoding.</t>
+  </si>
+  <si>
+    <t>BIP141 compares SegWit’s malleability fix against BIP62 and argues it is more complete, but it does not use or require BIP62.</t>
+  </si>
+  <si>
+    <t>As a solution of transaction malleability, this is superior to the canonical signature approach (BIP62): [...] In the case of an m-of-n CHECKMULTISIG script, a transaction is malleable only with agreement of m private key holders (as opposed to only 1 private key holder with BIP62) [...] Such setups are not possible with BIP62 as the malleability fix</t>
+  </si>
+  <si>
+    <t>Mentions BIP146 as a likely future soft-fork policy around NULLFAIL signatures, but BIP146 is not required for SegWit’s witness structure or v0 validation.</t>
+  </si>
+  <si>
+    <t>Signature(s) must be null vector(s) if an OP_CHECKSIG or OP_CHECKMULTISIG is failed (for both pre-segregated witness script and P2WSH. See BIP146)</t>
+  </si>
+  <si>
+    <t>Per-input lock-time and relative-lock-time Currently there is only one nLockTime field in a transaction and all inputs must share the same value. BIP68 enables per-input relative-lock-time using the nSequence field, however, with a limited lock-time period and resolution. [...]</t>
+  </si>
+  <si>
+    <t>BIP141 just links BIP68 as an existing relative-locktime mechanism and future extension context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With a soft fork, it is possible to introduce a separate witness structure to allow per-input lock-time and relative-lock-time, and a new script system that could sign and manipulate the new data (like BIP65 and BIP112). </t>
+  </si>
+  <si>
+    <t>BIP141 mentions BIP112 only as an example of relative-locktime script functionality for possible future witness extensions, not as a prerequisite.</t>
+  </si>
+  <si>
+    <t>BIP141 mentions BIP65 only as an example of script-level locktime functionality that future witness extensions could manipulate, not as a prerequisite.</t>
+  </si>
+  <si>
+    <t>Backward compatibility [...] What a non-upgraded wallet can do [...] Sending bitcoin to upgraded wallets using a native witness program through BIP70 payment protocol [...]</t>
+  </si>
+  <si>
+    <t>Witness program A scriptPubKey (or redeemScript as defined in BIP16/P2SH) that consists of a 1-byte push opcode (one of OP_0,OP_1,OP_2,...,OP_16) followed by a direct data push between 2 and 40 bytes gets a new special meaning. The value of the first push is called the "version byte". The following byte vector pushed is called the "witness program". [...] References [... ] BIP16 Pay to Script Hash [...]</t>
   </si>
 </sst>
 </file>
@@ -4676,6 +4841,12 @@
       <c r="B45" s="3">
         <v>100</v>
       </c>
+      <c r="C45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E45" s="7" t="s">
         <v>17</v>
       </c>
@@ -4720,6 +4891,12 @@
       <c r="B46" s="3">
         <v>102</v>
       </c>
+      <c r="C46" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E46" s="7" t="s">
         <v>17</v>
       </c>
@@ -4764,6 +4941,12 @@
       <c r="B47" s="3">
         <v>103</v>
       </c>
+      <c r="C47" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E47" s="7" t="s">
         <v>17</v>
       </c>
@@ -4808,6 +4991,12 @@
       <c r="B48" s="3">
         <v>104</v>
       </c>
+      <c r="C48" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E48" s="7" t="s">
         <v>17</v>
       </c>
@@ -4852,6 +5041,12 @@
       <c r="B49" s="3">
         <v>105</v>
       </c>
+      <c r="C49" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E49" s="7" t="s">
         <v>17</v>
       </c>
@@ -4896,6 +5091,12 @@
       <c r="B50" s="3">
         <v>107</v>
       </c>
+      <c r="C50" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E50" s="7" t="s">
         <v>17</v>
       </c>
@@ -5140,6 +5341,12 @@
       <c r="B55" s="3">
         <v>115</v>
       </c>
+      <c r="C55" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E55" s="7" t="s">
         <v>17</v>
       </c>
@@ -5234,6 +5441,12 @@
       <c r="B57" s="3">
         <v>117</v>
       </c>
+      <c r="C57" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E57" s="7" t="s">
         <v>17</v>
       </c>
@@ -5378,6 +5591,12 @@
       <c r="B60" s="3">
         <v>125</v>
       </c>
+      <c r="C60" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E60" s="7" t="s">
         <v>17</v>
       </c>
@@ -5422,6 +5641,12 @@
       <c r="B61" s="3">
         <v>127</v>
       </c>
+      <c r="C61" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E61" s="7" t="s">
         <v>17</v>
       </c>
@@ -5516,6 +5741,12 @@
       <c r="B63" s="3">
         <v>130</v>
       </c>
+      <c r="C63" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E63" s="7" t="s">
         <v>17</v>
       </c>
@@ -5560,6 +5791,12 @@
       <c r="B64" s="3">
         <v>131</v>
       </c>
+      <c r="C64" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E64" s="7" t="s">
         <v>17</v>
       </c>
@@ -5604,6 +5841,12 @@
       <c r="B65" s="3">
         <v>133</v>
       </c>
+      <c r="C65" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E65" s="7" t="s">
         <v>17</v>
       </c>
@@ -5648,6 +5891,12 @@
       <c r="B66" s="3">
         <v>134</v>
       </c>
+      <c r="C66" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E66" s="7" t="s">
         <v>17</v>
       </c>
@@ -5692,6 +5941,12 @@
       <c r="B67" s="3">
         <v>137</v>
       </c>
+      <c r="C67" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E67" s="7" t="s">
         <v>17</v>
       </c>
@@ -5735,6 +5990,12 @@
       </c>
       <c r="B68" s="3">
         <v>141</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>17</v>
@@ -7386,7 +7647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -10418,33 +10679,33 @@
         <v>2026-07-01</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B101" s="3">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D101" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>173</v>
+        <v>482</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J101" s="8" t="s">
-        <v>44</v>
+      <c r="J101" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10452,31 +10713,31 @@
         <v>218</v>
       </c>
       <c r="B102" s="3">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D102" s="3">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>174</v>
+        <v>486</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>175</v>
+        <v>483</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J102" s="8" t="s">
-        <v>44</v>
+      <c r="J102" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -10484,313 +10745,304 @@
         <v>218</v>
       </c>
       <c r="B103" s="3">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D103" s="3">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>177</v>
+        <v>485</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>178</v>
+        <v>484</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J103" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J103" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="3">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D104" s="3">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="E104" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" s="3">
+        <v>105</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D105" s="3">
+        <v>34</v>
+      </c>
+      <c r="E105" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F104" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J104" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A105" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B105" s="3">
-        <v>112</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D105" s="3">
-        <v>113</v>
-      </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B106" s="3">
+        <v>105</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D106" s="3">
+        <v>100</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J105" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B106" s="3">
-        <v>113</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D106" s="3">
-        <v>9</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F106" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>175</v>
+        <v>489</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J106" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J106" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B107" s="3">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D107" s="3">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>181</v>
+        <v>491</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J107" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J107" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B108" s="3">
+        <v>111</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D108" s="3">
+        <v>37</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="3">
+        <v>112</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D109" s="3">
+        <v>9</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" s="3">
+        <v>112</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="3">
+        <v>65</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A111" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B111" s="3">
+        <v>112</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D111" s="3">
+        <v>68</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J111" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A112" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B112" s="3">
+        <v>112</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D112" s="3">
         <v>113</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D108" s="3">
-        <v>68</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J108" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A109" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B109" s="3">
-        <v>113</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D109" s="3">
-        <v>112</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A110" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B110" s="3">
-        <v>114</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D110" s="3">
-        <v>9</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J110" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A111" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B111" s="3">
-        <v>114</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D111" s="3">
-        <v>16</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A112" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B112" s="3">
-        <v>114</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D112" s="3">
-        <v>112</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10798,13 +11050,13 @@
         <v>218</v>
       </c>
       <c r="B113" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D113" s="3">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>118</v>
@@ -10813,7 +11065,10 @@
         <v>37</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>184</v>
+        <v>174</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -10822,65 +11077,68 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B114" s="3">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D114" s="3">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>474</v>
+        <v>180</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J114" s="8" t="d">
-        <v>2026-07-01</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J114" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B115" s="3">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D115" s="3">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>469</v>
+        <v>180</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>476</v>
+        <v>181</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J115" s="8" t="d">
-        <v>2026-07-01</v>
+      <c r="J115" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -10888,13 +11146,13 @@
         <v>218</v>
       </c>
       <c r="B116" s="3">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D116" s="3">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>128</v>
@@ -10903,48 +11161,45 @@
         <v>146</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>471</v>
+        <v>180</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>478</v>
+        <v>181</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J116" s="8" t="d">
-        <v>2026-07-01</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J116" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B117" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D117" s="3">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>481</v>
+        <v>187</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J117" s="8" t="d">
-        <v>2026-07-01</v>
+      <c r="J117" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10952,28 +11207,31 @@
         <v>218</v>
       </c>
       <c r="B118" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D118" s="3">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>470</v>
+        <v>182</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J118" s="8" t="d">
-        <v>2026-07-01</v>
+      <c r="J118" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -10981,10 +11239,10 @@
         <v>218</v>
       </c>
       <c r="B119" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D119" s="3">
         <v>112</v>
@@ -10995,121 +11253,118 @@
       <c r="F119" s="3" t="s">
         <v>146</v>
       </c>
+      <c r="G119" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="H119" s="4" t="s">
-        <v>479</v>
+        <v>186</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J119" s="8" t="d">
-        <v>2026-07-01</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="J119" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B120" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="D120" s="3">
         <v>141</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>477</v>
+        <v>184</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J120" s="8" t="d">
+      <c r="J120" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B121" s="3">
+        <v>115</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D121" s="3">
+        <v>9</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J121" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B122" s="3">
+        <v>116</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D122" s="3">
+        <v>8</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J122" s="8" t="d">
         <v>2026-07-01</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A121" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B121" s="3">
+    <row r="123" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A123" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B123" s="3">
         <v>116</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D121" s="3">
-        <v>143</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G121" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="I121" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J121" s="8" t="d">
-        <v>2026-07-01</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A122" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B122" s="3">
-        <v>119</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D122" s="3">
-        <v>65</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A123" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B123" s="3">
-        <v>119</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="D123" s="3">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>128</v>
@@ -11118,152 +11373,152 @@
         <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>190</v>
+        <v>469</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>476</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J123" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J123" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B124" s="3">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D124" s="3">
-        <v>341</v>
+        <v>65</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>191</v>
+        <v>471</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>192</v>
+        <v>478</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J124" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J124" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B125" s="3">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D125" s="3">
-        <v>346</v>
+        <v>68</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>188</v>
+        <v>475</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>189</v>
+        <v>481</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J125" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="J125" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B126" s="3">
+        <v>116</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D126" s="3">
+        <v>98</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J126" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B127" s="3">
+        <v>116</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D127" s="3">
+        <v>112</v>
+      </c>
+      <c r="E127" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D126" s="3">
-        <v>65</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I126" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J126" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B127" s="3">
-        <v>128</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D127" s="3">
-        <v>68</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="F127" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>197</v>
+        <v>146</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>479</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J127" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J127" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B128" s="3">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D128" s="3">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>128</v>
@@ -11272,13 +11527,16 @@
         <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>195</v>
+        <v>472</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="8" t="s">
-        <v>32</v>
+      <c r="J128" s="8" t="d">
+        <v>2026-07-01</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -11286,13 +11544,13 @@
         <v>218</v>
       </c>
       <c r="B129" s="3">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>218</v>
+        <v>466</v>
       </c>
       <c r="D129" s="3">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>128</v>
@@ -11301,85 +11559,91 @@
         <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>196</v>
+        <v>473</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>480</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J129" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J129" s="8" t="d">
+        <v>2026-07-01</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B130" s="3">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D130" s="3">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>198</v>
+        <v>497</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J130" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J130" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B131" s="3">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D131" s="3">
-        <v>433</v>
+        <v>16</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>199</v>
+        <v>493</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>501</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J131" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B132" s="3">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D132" s="3">
-        <v>443</v>
+        <v>68</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>128</v>
@@ -11388,27 +11652,30 @@
         <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>196</v>
+        <v>498</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J132" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B133" s="3">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D133" s="3">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>128</v>
@@ -11417,45 +11684,48 @@
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>202</v>
+        <v>496</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>203</v>
+        <v>502</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J133" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J133" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="153" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B134" s="3">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D134" s="3">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>204</v>
+        <v>495</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J134" s="8" t="s">
-        <v>32</v>
+      <c r="J134" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -11463,13 +11733,13 @@
         <v>218</v>
       </c>
       <c r="B135" s="3">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D135" s="3">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>128</v>
@@ -11478,30 +11748,30 @@
         <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>205</v>
+        <v>494</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>203</v>
+        <v>500</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J135" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="J135" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B136" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D136" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>128</v>
@@ -11510,10 +11780,7 @@
         <v>37</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H136" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -11522,18 +11789,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B137" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D137" s="3">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>128</v>
@@ -11542,10 +11809,7 @@
         <v>37</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H137" s="4" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -11554,30 +11818,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B138" s="3">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D138" s="3">
-        <v>141</v>
+        <v>341</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -11586,30 +11850,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B139" s="3">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D139" s="3">
-        <v>9</v>
+        <v>346</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -11618,108 +11882,108 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B140" s="3">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D140" s="3">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E140" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J140" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B141" s="3">
+        <v>125</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D141" s="3">
+        <v>112</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J141" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B142" s="3">
+        <v>127</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D142" s="3">
+        <v>174</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F140" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="I140" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J140" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B141" s="3">
-        <v>145</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D141" s="3">
-        <v>23</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F141" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G141" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="I141" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J141" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B142" s="3">
-        <v>145</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D142" s="3">
-        <v>141</v>
-      </c>
-      <c r="E142" s="3" t="s">
+      <c r="F142" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J142" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B143" s="3">
         <v>128</v>
       </c>
-      <c r="F142" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="I142" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J142" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A143" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B143" s="3">
-        <v>158</v>
-      </c>
       <c r="C143" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D143" s="3">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>128</v>
@@ -11728,7 +11992,10 @@
         <v>37</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>427</v>
+        <v>193</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -11737,27 +12004,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B144" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D144" s="3">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -11766,27 +12033,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="3">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D145" s="3">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -11795,27 +12062,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B146" s="3">
-        <v>197</v>
-      </c>
-      <c r="C146" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D146" s="3">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -11824,163 +12091,169 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B147" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D147" s="3">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J147" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J147" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B148" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D148" s="3">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J148" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="J148" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B149" s="3">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D149" s="3">
-        <v>323</v>
+        <v>443</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J149" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J149" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B150" s="3">
-        <v>321</v>
-      </c>
-      <c r="C150" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C150" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D150" s="3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>20</v>
+        <v>509</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>244</v>
+        <v>507</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>508</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J150" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J150" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B151" s="3">
-        <v>321</v>
-      </c>
-      <c r="C151" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C151" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D151" s="3">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>37</v>
+        <v>509</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>239</v>
+        <v>510</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>511</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J151" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J151" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B152" s="3">
-        <v>321</v>
+        <v>137</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D152" s="3">
-        <v>351</v>
+        <v>141</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>128</v>
@@ -11989,27 +12262,30 @@
         <v>37</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>241</v>
+        <v>515</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>516</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J152" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J152" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B153" s="3">
-        <v>321</v>
+        <v>137</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D153" s="3">
-        <v>352</v>
+        <v>173</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>128</v>
@@ -12018,178 +12294,187 @@
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>240</v>
+        <v>514</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>517</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J153" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J153" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B154" s="3">
-        <v>324</v>
+        <v>137</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D154" s="3">
-        <v>31</v>
+        <v>322</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>245</v>
+        <v>512</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>513</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J154" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B155" s="3">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D155" s="3">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>143</v>
+        <v>518</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J155" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B156" s="3">
-        <v>324</v>
-      </c>
-      <c r="C156" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A156" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B156" s="9">
+        <v>141</v>
+      </c>
+      <c r="C156" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D156" s="3">
-        <v>340</v>
+        <v>16</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>144</v>
+        <v>536</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>145</v>
+        <v>519</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J156" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B157" s="3">
-        <v>330</v>
-      </c>
-      <c r="C157" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A157" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B157" s="9">
+        <v>141</v>
+      </c>
+      <c r="C157" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D157" s="3">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>253</v>
+        <v>527</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>526</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J157" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B158" s="3">
-        <v>330</v>
-      </c>
-      <c r="C158" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A158" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B158" s="9">
+        <v>141</v>
+      </c>
+      <c r="C158" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D158" s="3">
-        <v>339</v>
+        <v>65</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>254</v>
+        <v>532</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>534</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J158" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B159" s="3">
-        <v>330</v>
-      </c>
-      <c r="C159" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A159" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B159" s="9">
+        <v>141</v>
+      </c>
+      <c r="C159" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D159" s="3">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>128</v>
@@ -12198,193 +12483,205 @@
         <v>146</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>252</v>
+        <v>530</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>531</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J159" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B160" s="3">
-        <v>331</v>
-      </c>
-      <c r="C160" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A160" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B160" s="9">
+        <v>141</v>
+      </c>
+      <c r="C160" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D160" s="3">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>256</v>
+        <v>535</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J160" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B161" s="3">
-        <v>331</v>
-      </c>
-      <c r="C161" s="3" t="s">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A161" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B161" s="9">
+        <v>141</v>
+      </c>
+      <c r="C161" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D161" s="3">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F161" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J161" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="238" x14ac:dyDescent="0.2">
+      <c r="A162" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B162" s="9">
+        <v>141</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D162" s="3">
+        <v>143</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A163" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B163" s="9">
+        <v>141</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D163" s="3">
+        <v>144</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J163" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A164" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B164" s="9">
+        <v>141</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D164" s="3">
         <v>146</v>
       </c>
-      <c r="G161" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I161" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J161" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B162" s="3">
-        <v>331</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D162" s="3">
-        <v>339</v>
-      </c>
-      <c r="E162" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F162" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="I162" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J162" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B163" s="3">
-        <v>347</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D163" s="3">
-        <v>3</v>
-      </c>
-      <c r="E163" s="3" t="s">
+      <c r="F164" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J164" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A165" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B165" s="9">
+        <v>141</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D165" s="3">
+        <v>173</v>
+      </c>
+      <c r="E165" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="F165" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G163" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="I163" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J163" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B164" s="3">
-        <v>347</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D164" s="3">
-        <v>340</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="I164" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J164" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B165" s="3">
-        <v>347</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D165" s="3">
-        <v>341</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G165" s="4" t="s">
-        <v>259</v>
+        <v>524</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>262</v>
+        <v>525</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J165" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -12392,103 +12689,106 @@
         <v>218</v>
       </c>
       <c r="B166" s="3">
-        <v>347</v>
+        <v>142</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D166" s="3">
-        <v>342</v>
+        <v>13</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J166" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J166" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B167" s="3">
-        <v>353</v>
+        <v>142</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D167" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J167" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J167" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B168" s="3">
-        <v>353</v>
+        <v>142</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D168" s="3">
-        <v>321</v>
+        <v>47</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>266</v>
+        <v>205</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J168" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J168" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B169" s="3">
-        <v>353</v>
+        <v>142</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D169" s="3">
-        <v>352</v>
+        <v>63</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>128</v>
@@ -12497,16 +12797,16 @@
         <v>37</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>283</v>
+        <v>205</v>
       </c>
       <c r="H169" s="4" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="I169" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J169" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J169" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -12514,13 +12814,13 @@
         <v>218</v>
       </c>
       <c r="B170" s="3">
-        <v>375</v>
+        <v>142</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D170" s="3">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>128</v>
@@ -12529,30 +12829,30 @@
         <v>37</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>286</v>
+        <v>205</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="I170" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J170" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J170" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B171" s="3">
-        <v>375</v>
+        <v>142</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D171" s="3">
-        <v>352</v>
+        <v>141</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>118</v>
@@ -12561,42 +12861,48 @@
         <v>37</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>267</v>
+        <v>200</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="I171" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J171" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J171" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B172" s="3">
-        <v>375</v>
+        <v>145</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D172" s="3">
-        <v>370</v>
+        <v>9</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>267</v>
+        <v>210</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J172" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J172" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -12604,13 +12910,13 @@
         <v>218</v>
       </c>
       <c r="B173" s="3">
-        <v>375</v>
+        <v>145</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D173" s="3">
-        <v>374</v>
+        <v>22</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>118</v>
@@ -12619,74 +12925,74 @@
         <v>37</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>285</v>
+        <v>208</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J173" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J173" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B174" s="3">
-        <v>392</v>
+        <v>145</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D174" s="3">
-        <v>341</v>
+        <v>23</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>271</v>
+        <v>212</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J174" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J174" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B175" s="3">
-        <v>392</v>
+        <v>145</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D175" s="3">
-        <v>350</v>
+        <v>141</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="H175" s="4" t="s">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J175" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J175" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -12694,115 +13000,115 @@
         <v>218</v>
       </c>
       <c r="B176" s="3">
-        <v>392</v>
+        <v>158</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D176" s="3">
-        <v>352</v>
+        <v>37</v>
       </c>
       <c r="E176" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J176" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B177" s="3">
+        <v>158</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D177" s="3">
+        <v>141</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J177" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B178" s="3">
+        <v>158</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D178" s="3">
+        <v>157</v>
+      </c>
+      <c r="E178" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F176" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G176" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="I176" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J176" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B177" s="3">
-        <v>392</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D177" s="3">
-        <v>380</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G177" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I177" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J177" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" ht="69" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B178" s="3">
-        <v>392</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D178" s="3">
-        <v>390</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F178" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J178" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J178" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B179" s="3">
-        <v>440</v>
-      </c>
-      <c r="C179" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C179" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D179" s="3">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>274</v>
+        <v>215</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J179" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J179" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -12810,22 +13116,22 @@
         <v>218</v>
       </c>
       <c r="B180" s="3">
-        <v>443</v>
+        <v>320</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D180" s="3">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
@@ -12834,18 +13140,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B181" s="3">
-        <v>443</v>
+        <v>320</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D181" s="3">
-        <v>327</v>
+        <v>9</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>128</v>
@@ -12854,10 +13160,7 @@
         <v>20</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
@@ -12866,30 +13169,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B182" s="3">
-        <v>443</v>
+        <v>320</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D182" s="3">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H182" s="4" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>15</v>
@@ -12898,36 +13198,33 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B183" s="3">
-        <v>443</v>
-      </c>
-      <c r="C183" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C183" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D183" s="3">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H183" s="4" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J183" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J183" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="184" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -12935,56 +13232,1046 @@
         <v>218</v>
       </c>
       <c r="B184" s="3">
-        <v>443</v>
-      </c>
-      <c r="C184" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C184" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D184" s="3">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J184" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J184" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B185" s="3">
-        <v>451</v>
+        <v>321</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D185" s="3">
-        <v>125</v>
+        <v>351</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F185" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B186" s="3">
+        <v>321</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D186" s="3">
+        <v>352</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J186" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B187" s="3">
+        <v>324</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D187" s="3">
+        <v>31</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F187" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G185" s="4" t="s">
+      <c r="G187" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J187" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A188" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B188" s="3">
+        <v>324</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D188" s="3">
+        <v>151</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J188" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B189" s="3">
+        <v>324</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D189" s="3">
+        <v>340</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J189" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B190" s="3">
+        <v>330</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D190" s="3">
+        <v>141</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J190" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B191" s="3">
+        <v>330</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D191" s="3">
+        <v>339</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J191" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B192" s="3">
+        <v>330</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D192" s="3">
+        <v>340</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J192" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B193" s="3">
+        <v>331</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D193" s="3">
+        <v>133</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J193" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B194" s="3">
+        <v>331</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D194" s="3">
+        <v>330</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J194" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B195" s="3">
+        <v>331</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D195" s="3">
+        <v>339</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J195" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A196" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B196" s="3">
+        <v>347</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D196" s="3">
+        <v>3</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J196" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B197" s="3">
+        <v>347</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D197" s="3">
+        <v>340</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J197" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A198" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B198" s="3">
+        <v>347</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D198" s="3">
+        <v>341</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J198" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A199" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B199" s="3">
+        <v>347</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D199" s="3">
+        <v>342</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J199" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A200" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B200" s="3">
+        <v>353</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D200" s="3">
+        <v>21</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A201" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B201" s="3">
+        <v>353</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D201" s="3">
+        <v>321</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J201" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A202" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B202" s="3">
+        <v>353</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D202" s="3">
+        <v>352</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J202" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B203" s="3">
+        <v>375</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D203" s="3">
+        <v>32</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J203" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A204" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B204" s="3">
+        <v>375</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D204" s="3">
+        <v>352</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J204" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A205" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B205" s="3">
+        <v>375</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D205" s="3">
+        <v>370</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J205" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A206" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B206" s="3">
+        <v>375</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D206" s="3">
+        <v>374</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J206" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B207" s="3">
+        <v>392</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D207" s="3">
+        <v>341</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J207" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A208" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B208" s="3">
+        <v>392</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D208" s="3">
+        <v>350</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J208" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A209" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B209" s="3">
+        <v>392</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D209" s="3">
+        <v>352</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J209" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A210" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B210" s="3">
+        <v>392</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D210" s="3">
+        <v>380</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J210" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="3">
+        <v>392</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D211" s="3">
+        <v>390</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J211" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A212" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" s="3">
+        <v>440</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D212" s="3">
+        <v>342</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J212" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B213" s="3">
+        <v>443</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D213" s="3">
+        <v>119</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J213" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A214" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B214" s="3">
+        <v>443</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D214" s="3">
+        <v>327</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J214" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="3">
+        <v>443</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D215" s="3">
+        <v>341</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J215" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A216" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B216" s="3">
+        <v>443</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D216" s="3">
+        <v>342</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J216" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B217" s="3">
+        <v>443</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D217" s="3">
+        <v>345</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J217" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A218" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="3">
+        <v>451</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D218" s="3">
+        <v>125</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G218" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="I185" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J185" s="8" t="d">
+      <c r="I218" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J218" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -12997,13 +14284,13 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J185">
-    <sortCondition ref="B2:B185"/>
-    <sortCondition ref="A2:A185"/>
-    <sortCondition ref="D2:D185"/>
-    <sortCondition ref="C2:C185"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J218">
+    <sortCondition ref="B2:B218"/>
+    <sortCondition ref="A2:A218"/>
+    <sortCondition ref="D2:D218"/>
+    <sortCondition ref="C2:C218"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A154 C1:C154 C165:C1048576 A162:A1048576">
+  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 C219:C1048576 A219:A1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5651D7EF-4F3D-5745-A121-89A17706583F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{77473137-7AEB-4D46-B800-BBA4B2CB16DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2757" uniqueCount="537">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2962" uniqueCount="589">
   <si>
     <t>reviewer</t>
   </si>
@@ -1421,9 +1421,6 @@
     <t>Requires: [...] 341 [...]  The output signature is a BIP340 Schnorr signature valid under an X‑only key obtained by applying a sequence of plain (e.g. BIP32) and X‑only (e.g. Tapscript) tweaks to the signer’s plain public key. Consequently the protocol is compatible with BIP341.</t>
   </si>
   <si>
-    <t>BIP89 references BIP341 because its signing protocol is designed to be compatible with Taproot’s X-only key and tweak semantics, without requiring Taproot to define CCD itself.</t>
-  </si>
-  <si>
     <t>All inputs MUST set the nSequence to 0xFFFFFFFF (do not signal for BIP 125 RBF). [...] The batch creator MUST add a new dust UTXO input, and the resulting replacement transaction MUST satisfy BIP 125 RBF rules [...]</t>
   </si>
   <si>
@@ -1665,6 +1662,177 @@
   </si>
   <si>
     <t>Witness program A scriptPubKey (or redeemScript as defined in BIP16/P2SH) that consists of a 1-byte push opcode (one of OP_0,OP_1,OP_2,...,OP_16) followed by a direct data push between 2 and 40 bytes gets a new special meaning. The value of the first push is called the "version byte". The following byte vector pushed is called the "witness program". [...] References [... ] BIP16 Pay to Script Hash [...]</t>
+  </si>
+  <si>
+    <t>Although BIP89 lists BIP341 in its Requires field, the CCD mechanism described in the body does not appear to require Taproot consensus validation. BIP341 is still relevant because CCD is designed to interoperate with Taproot-style X-only output keys and tweak semantics, but it is better treated as compatibility context than as a technical dependency.</t>
+  </si>
+  <si>
+    <t>BIP144 defines the peer-services serialization, service-bit signaling, and relay mechanisms for SegWit witness data, which depends on BIP141’s consensus definition of witness structures and witness commitments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition to defining witness structures and requiring commitments in future blocks (BIP141 - Consensus segwit BIP), new mechanisms must be defined to allow peers to advertise support for segregated witness and to relay the witness structures and request them from other peers without breaking compatibility with older nodes. </t>
+  </si>
+  <si>
+    <t>BIP144 mentions BIP130 sendheaders only to explain why witness support is not advertised in inv messages.</t>
+  </si>
+  <si>
+    <t>Relay [...] Rationale for not advertizing witnessness in invs: we don't always use invs anymore (with 'sendheaders' BIP 130), plus it's not useful: implicitly, every transaction and block have a witness, old ones just have empty ones.</t>
+  </si>
+  <si>
+    <t>This BIP will be deployed by "version bits" BIP9 using the same parameters for BIP141 and BIP143, with the name "segwit" and using bit 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledgements Peter Todd is the original author of NULLDUMMY. This document is extracted from the previous BIP62 proposal, which was composed by Pieter Wuille and had input from various people. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This BIP will be deployed by "version bits" BIP9 using the same parameters for BIP141 and BIP143, with the name "segwit" and using bit 1. </t>
+  </si>
+  <si>
+    <t>Motivation [...] Although the txid of segregated witness (BIP141) transactions is not third party malleable, this malleability vector will change the wtxid and may reduce the efficiency of compact block relay (BIP152). [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivation [...] Although the txid of segregated witness (BIP141) transactions is not third party malleable, this malleability vector will change the wtxid and may reduce the efficiency of compact block relay (BIP152). [...] Specification To fix the dummy element malleability, a new consensus rule ("NULLDUMMY") is deployed to require that the dummy element MUST be the empty byte array. Anything else makes the script evaluate to false immediately. The NULLDUMMY rule applies to OP_CHECKMULTISIG and OP_CHECKMULTISIGVERIFY in pre-segregated scripts, and also pay-to-witness-script-hash scripts described in BIP141. </t>
+  </si>
+  <si>
+    <t>Shares segwit deployment parameters only.</t>
+  </si>
+  <si>
+    <t>Motivation-only reference: BIP152 is affected by the malleability vector but not required to define or implement NULLDUMMY.</t>
+  </si>
+  <si>
+    <t>Historical/design provenance only. BIP147 narrows out one rule from BIP62 but does not require BIP62.</t>
+  </si>
+  <si>
+    <t>BIP147 extends its consensus rule to BIP141 witness script contexts, so BIP141 is part of the rule’s applicability.</t>
+  </si>
+  <si>
+    <t>This document specifies a BIP16 like soft fork flag day activation of the segregated witness BIP9 deployment known as "segwit".  [...] "existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147. [...] References [... ] BIP9 Version bits with timeout and delay [...]</t>
+  </si>
+  <si>
+    <t>This document specifies a BIP16 like soft fork flag day activation of the segregated witness BIP9 deployment known as "segwit".  [...] Historically, the P2SH soft fork (BIP16) was activated using a predetermined flag day where nodes began enforcing the new rules. P2SH was successfully activated with relatively few issues [...] References [... ] BIP16 Pay to Script Hash [...]</t>
+  </si>
+  <si>
+    <t>"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147. [...] References [... ] BIP141 Segregated Witness (Consensus layer) [...]</t>
+  </si>
+  <si>
+    <t>"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147. [...] References [... ] BIP143 Transaction Signature Verification for Version 0 Witness Program [...]</t>
+  </si>
+  <si>
+    <t>"existing segwit deployment" refer to the BIP9 "segwit" deployment using bit 1, between November 15th 2016 and November 15th 2017 to activate BIP141, BIP143 and BIP147. [...] References [... ] BIP147 Dealing with dummy stack element malleability [...]</t>
+  </si>
+  <si>
+    <t>Reuses BIP9 segwit deployment state and signalling.</t>
+  </si>
+  <si>
+    <t>BIP148’s purpose is mandatory activation of segwit, whose consensus rules are defined in BIP141.</t>
+  </si>
+  <si>
+    <t>BIP143 is part of the existing segwit deployment that BIP148 forces toward activation.</t>
+  </si>
+  <si>
+    <t>BIP147 is part of the existing segwit deployment that BIP148 forces toward activation.</t>
+  </si>
+  <si>
+    <t>BIP16 is only cited as historical precedent for flag-day soft fork activation.</t>
+  </si>
+  <si>
+    <t>Specification The authentication scheme proposed in this BIP uses ECDSA, secrets will never be transmitted. Authentication initialization must only happen if encrypted channels have been established (according to BIP-151 [1]). The encryption-session-ID is available once channels are encrypted (according to BIP-151 [1]).  [...] After the second AUTHREPLY message (requesting peer's signature -&gt; responding peer), both clients must re-key the symmetric encryption according to BIP151 while using a slightly different re-key key derivation hash. [...] Encryption    Encrypted channels must be established (according to BIP-151 [1]) [...] References [1] BIP 151: Peer-to-Peer Communication Encryption</t>
+  </si>
+  <si>
+    <t>BIP150 authentication is only allowed after BIP151 encrypted channels are established and uses the BIP151 encryption-session-ID.</t>
+  </si>
+  <si>
+    <t>Risks [...] Light clients (and such) who are not checking the nServiceFlags (service bits) from a relayed addr-message may unwittingly connect to a pruned peer and ask for (filtered) blocks at a depth below the peer’s pruned depth. Light clients should therefore check the service bits and either (1) connect to peers signaling NODE_NETWORK_LIMITED that preferably do not also signal serving the full block chain, [...]</t>
+  </si>
+  <si>
+    <t>“Filtered blocks” points to BIP37 bloom-filter light-client behavior, but BIP159 only warns such clients to check service bits.</t>
+  </si>
+  <si>
+    <t>[...] The Updater must only accept a PSBT. The Updater adds information to the PSBT that it has access to. If it has the UTXO for an input, it should add it to the PSBT. The Updater should also add redeemScripts, witnessScripts, and BIP 32 derivation paths to the input and output data if it knows them. [...] In order to detect change, a signer can use the BIP 32 derivation paths provided in inputs and outputs as well as the extended public keys provided globally.</t>
+  </si>
+  <si>
+    <t>PSBT (BIP174) defines optional xpub and derivation-path fields using BIP32 fingerprints, xpub serialization, and path indexes. PSBT can exist without xpubs or derivation paths, BIP32 metadata is supported by the format, not required for the format to function.</t>
+  </si>
+  <si>
+    <t>BIP143 is cited for segwit sighash behavior and the reason some signers require full previous transactions for segwit inputs.</t>
+  </si>
+  <si>
+    <t>PSBT handles redeemScripts and P2SH-embedded witness cases, but P2SH itself is not the purpose of the format.</t>
+  </si>
+  <si>
+    <t>The entire transaction output in network serialization which the current input spends from. This should only be present for inputs which spend segwit outputs, including P2SH embedded ones. [...] Case: PSBT with one P2PKH input and one P2SH-P2WPKH input.</t>
+  </si>
+  <si>
+    <t>NULLDUMMY is mentioned only as an example of an invalid signature-like value.</t>
+  </si>
+  <si>
+    <t>The signature as would be pushed to the stack from a scriptSig or witness. The signature should be a valid ECDSA signature corresponding to the pubkey that would return true when verified and not a value that would return false or be invalid otherwise (such as a NULLDUMMY)</t>
+  </si>
+  <si>
+    <t>[...] else:
+            script = witness_utxo.scriptPubKey
+        if IsP2WPKH(script):
+            sign_witness(P2PKH(script[2:22]), i)
+        else if IsP2WSH(script):
+            assert(script == P2WSH(witnessScript))
+            sign_witness(witnessScript, i)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why would non-witness UTXOs be provided for segwit inputs? The sighash algorithm for Segwit specified in BIP 143 is known to have an issue where an attacker could trick a user to sending Bitcoin to fees if they are able to convince the user to sign a malicious transaction multiple times. </t>
+  </si>
+  <si>
+    <t>PSBT includes witness UTXO, witnessScript, scriptWitness, P2WPKH/P2WSH handling, and segwit input signing/finalization behavior. While, however, BIP174 supports segwit, a valid PSBT can be entirely legacy P2PKH/P2SH, thus no technical dependency.</t>
+  </si>
+  <si>
+    <t>Changelog [...] Mark Final (Later updated to "Deployed" with adoption of BIP3)</t>
+  </si>
+  <si>
+    <t>Hashed Time-Locked Contract (HTLC) funds are sent to a P2SH address, so the script is meant to be wrapped and spent through BIP16 P2SH.</t>
+  </si>
+  <si>
+    <t>A Hashed Time-Locked Contract (HTLC) is a script that permits a designated party (the "seller") to spend funds by disclosing the preimage of a hash. [...] Interaction Victor (the "buyer") and Peggy (the "seller") exchange public keys and mutually agree upon a timeout threshold. Peggy provides a hash digest. Both parties can now construct the script and P2SH address for the HTLC. Victor sends funds to the P2SH address.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[TIMEOUTOP] is either OP_CHECKSEQUENCEVERIFY or OP_CHECKLOCKTIMEVERIFY. </t>
+  </si>
+  <si>
+    <t>BIP199 allows OP_CHECKLOCKTIMEVERIFY, defined in BIP65, as one of the timeout mechanisms.</t>
+  </si>
+  <si>
+    <t>BIP199 allows OP_CHECKSEQUENCEVERIFY, defined in BIP112, as one of the timeout mechanisms.</t>
+  </si>
+  <si>
+    <t>On the L2 side, individual withdrawal requests are periodically combined into a single CoinJoin-like withdrawal bundle. This bundle is hashed in a particular way (on both L2 and L1) -- this "blinded hash" commits to its own L1 fee, but (notably) it does not commit to its first tx-input (in that way, it is like BIP-118). [...]</t>
+  </si>
+  <si>
+    <t>BIP118 is cited only as an analogy for the blinded withdrawal hash not committing to the first transaction input, no technical dependency.</t>
+  </si>
+  <si>
+    <t>BMM Accept To "Accept" a BMM proposal (endorsing Simon's side:block, and allowing Mary to accept Simon's money later in the block), Mary places an OP_RETURN output into the main:coinbase as follows:
+    1-byte - OP_RETURN (0x6a)
+    4-bytes - Message header (0xD1617368)
+    1-byte - Sidechain number (0-255)
+    32-bytes - h* (obtained from Simon) [...]
+Reference Implementation 
+The enforcer is [https://github.com/LayerTwo-Labs/bip300301_enforcer/ here].</t>
+  </si>
+  <si>
+    <t>BIP301 assumes numbered sidechains compatible with BIP300’s sidechain-slot model, but does not explicitly require BIP300.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaces: 320 [...] BIP 320 defined 16 bits of nVersion as nonce space for additional nonce space. It turns out that this isn't enough, as some devices have started using 7 bits from nTime for extra nonce space [...] </t>
+  </si>
+  <si>
+    <t>Specification 24 bits from the block header nVersion field, starting from 5 and ending at 28 inclusive (0x1fffffe0), are reserved for nonce use and removed from BIP8 and BIP9 specifications.</t>
+  </si>
+  <si>
+    <t>BIP323 expands BIP320's nVersion nonce-space reservation from 16 bits to 24 bits.</t>
+  </si>
+  <si>
+    <t>BIP323 removes bits 5–28 from BIP8 soft-fork signalling and warning interpretation.</t>
+  </si>
+  <si>
+    <t>BIP323 removes bits 5–28 from BIP9 soft-fork signalling and warning interpretation.</t>
   </si>
 </sst>
 </file>
@@ -2183,7 +2351,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2217,6 +2385,9 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -5428,7 +5599,7 @@
         <v>25</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P56" s="7">
         <v>0</v>
@@ -6091,6 +6262,12 @@
       <c r="B70" s="3">
         <v>144</v>
       </c>
+      <c r="C70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E70" s="7" t="s">
         <v>17</v>
       </c>
@@ -6185,6 +6362,12 @@
       <c r="B72" s="3">
         <v>147</v>
       </c>
+      <c r="C72" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E72" s="7" t="s">
         <v>17</v>
       </c>
@@ -6229,6 +6412,12 @@
       <c r="B73" s="3">
         <v>148</v>
       </c>
+      <c r="C73" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E73" s="7" t="s">
         <v>17</v>
       </c>
@@ -6273,6 +6462,12 @@
       <c r="B74" s="3">
         <v>150</v>
       </c>
+      <c r="C74" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E74" s="7" t="s">
         <v>17</v>
       </c>
@@ -6367,6 +6562,12 @@
       <c r="B76" s="3">
         <v>159</v>
       </c>
+      <c r="C76" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E76" s="7" t="s">
         <v>17</v>
       </c>
@@ -6411,6 +6612,12 @@
       <c r="B77" s="3">
         <v>171</v>
       </c>
+      <c r="C77" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E77" s="7" t="s">
         <v>17</v>
       </c>
@@ -6455,6 +6662,12 @@
       <c r="B78" s="3">
         <v>174</v>
       </c>
+      <c r="C78" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E78" s="7" t="s">
         <v>17</v>
       </c>
@@ -6549,6 +6762,12 @@
       <c r="B80" s="3">
         <v>199</v>
       </c>
+      <c r="C80" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E80" s="7" t="s">
         <v>17</v>
       </c>
@@ -6593,6 +6812,12 @@
       <c r="B81" s="3">
         <v>300</v>
       </c>
+      <c r="C81" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E81" s="7" t="s">
         <v>17</v>
       </c>
@@ -6637,6 +6862,12 @@
       <c r="B82" s="3">
         <v>301</v>
       </c>
+      <c r="C82" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E82" s="7" t="s">
         <v>17</v>
       </c>
@@ -6777,6 +7008,12 @@
       </c>
       <c r="B85" s="3">
         <v>323</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>17</v>
@@ -7647,7 +7884,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J218"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -10406,7 +10643,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>218</v>
       </c>
@@ -10429,7 +10666,7 @@
         <v>454</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>455</v>
+        <v>536</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
@@ -10458,7 +10695,7 @@
         <v>37</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -10487,7 +10724,7 @@
         <v>37</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
@@ -10516,10 +10753,10 @@
         <v>37</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -10548,10 +10785,10 @@
         <v>37</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -10580,10 +10817,10 @@
         <v>37</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
@@ -10612,7 +10849,7 @@
         <v>37</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -10641,7 +10878,7 @@
         <v>37</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -10658,7 +10895,7 @@
         <v>98</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D100" s="3">
         <v>116</v>
@@ -10670,7 +10907,7 @@
         <v>37</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -10699,7 +10936,7 @@
         <v>37</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -10728,10 +10965,10 @@
         <v>146</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -10760,10 +10997,10 @@
         <v>146</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
@@ -10792,10 +11029,10 @@
         <v>37</v>
       </c>
       <c r="G104" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -10824,7 +11061,7 @@
         <v>37</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -10853,7 +11090,7 @@
         <v>37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -10882,7 +11119,7 @@
         <v>37</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -11315,7 +11552,7 @@
         <v>37</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -11332,7 +11569,7 @@
         <v>116</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D122" s="3">
         <v>8</v>
@@ -11344,7 +11581,7 @@
         <v>37</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -11361,7 +11598,7 @@
         <v>116</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D123" s="3">
         <v>16</v>
@@ -11373,10 +11610,10 @@
         <v>37</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -11393,7 +11630,7 @@
         <v>116</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D124" s="3">
         <v>65</v>
@@ -11405,10 +11642,10 @@
         <v>146</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -11425,7 +11662,7 @@
         <v>116</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D125" s="3">
         <v>68</v>
@@ -11437,10 +11674,10 @@
         <v>146</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -11457,7 +11694,7 @@
         <v>116</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D126" s="3">
         <v>98</v>
@@ -11469,7 +11706,7 @@
         <v>37</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -11486,7 +11723,7 @@
         <v>116</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D127" s="3">
         <v>112</v>
@@ -11498,7 +11735,7 @@
         <v>146</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -11515,7 +11752,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D128" s="3">
         <v>141</v>
@@ -11527,10 +11764,10 @@
         <v>37</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
@@ -11547,7 +11784,7 @@
         <v>116</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D129" s="3">
         <v>143</v>
@@ -11559,10 +11796,10 @@
         <v>37</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -11591,7 +11828,7 @@
         <v>37</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -11620,10 +11857,10 @@
         <v>37</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -11652,10 +11889,10 @@
         <v>37</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -11684,10 +11921,10 @@
         <v>37</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -11716,10 +11953,10 @@
         <v>37</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -11748,10 +11985,10 @@
         <v>37</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -11902,7 +12139,7 @@
         <v>37</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -11931,7 +12168,7 @@
         <v>37</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -11960,10 +12197,10 @@
         <v>37</v>
       </c>
       <c r="G142" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="H142" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -12195,13 +12432,13 @@
         <v>128</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G150" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="H150" s="4" t="s">
         <v>507</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>508</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
@@ -12227,13 +12464,13 @@
         <v>128</v>
       </c>
       <c r="F151" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="G151" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="H151" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
@@ -12262,10 +12499,10 @@
         <v>37</v>
       </c>
       <c r="G152" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
@@ -12294,10 +12531,10 @@
         <v>37</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
@@ -12326,10 +12563,10 @@
         <v>37</v>
       </c>
       <c r="G154" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="H154" s="4" t="s">
         <v>512</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>513</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -12358,7 +12595,7 @@
         <v>37</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -12387,10 +12624,10 @@
         <v>37</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -12419,10 +12656,10 @@
         <v>37</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -12451,10 +12688,10 @@
         <v>20</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -12483,10 +12720,10 @@
         <v>146</v>
       </c>
       <c r="G159" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="H159" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>531</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -12515,7 +12752,7 @@
         <v>20</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -12544,10 +12781,10 @@
         <v>37</v>
       </c>
       <c r="G161" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="H161" s="4" t="s">
         <v>532</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -12576,10 +12813,10 @@
         <v>37</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H162" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -12608,10 +12845,10 @@
         <v>37</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H163" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>15</v>
@@ -12640,10 +12877,10 @@
         <v>146</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>15</v>
@@ -12672,10 +12909,10 @@
         <v>20</v>
       </c>
       <c r="G165" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="H165" s="4" t="s">
         <v>524</v>
-      </c>
-      <c r="H165" s="4" t="s">
-        <v>525</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>15</v>
@@ -12878,45 +13115,45 @@
         <v>218</v>
       </c>
       <c r="B172" s="3">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D172" s="3">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="H172" s="4" t="s">
-        <v>211</v>
+        <v>539</v>
       </c>
       <c r="I172" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J172" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J172" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B173" s="3">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D173" s="3">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>118</v>
@@ -12925,16 +13162,19 @@
         <v>37</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>208</v>
+        <v>538</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>537</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J173" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="J173" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
         <v>218</v>
       </c>
@@ -12945,19 +13185,19 @@
         <v>218</v>
       </c>
       <c r="D174" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>15</v>
@@ -12966,7 +13206,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
         <v>218</v>
       </c>
@@ -12977,16 +13217,16 @@
         <v>218</v>
       </c>
       <c r="D175" s="3">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>15</v>
@@ -12995,27 +13235,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B176" s="3">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D176" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>427</v>
+        <v>212</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>15</v>
@@ -13024,12 +13267,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B177" s="3">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>218</v>
@@ -13041,10 +13284,10 @@
         <v>128</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>15</v>
@@ -13053,18 +13296,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B178" s="3">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D178" s="3">
-        <v>157</v>
+        <v>9</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>118</v>
@@ -13073,71 +13316,77 @@
         <v>37</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>214</v>
+        <v>541</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J178" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J178" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B179" s="3">
-        <v>197</v>
-      </c>
-      <c r="C179" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C179" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D179" s="3">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="E179" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J179" s="8" t="d">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B180" s="3">
+        <v>147</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D180" s="3">
+        <v>141</v>
+      </c>
+      <c r="E180" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F179" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J179" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B180" s="3">
-        <v>320</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D180" s="3">
-        <v>8</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F180" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>250</v>
+        <v>545</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>549</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J180" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-06-30</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -13145,248 +13394,269 @@
         <v>218</v>
       </c>
       <c r="B181" s="3">
-        <v>320</v>
+        <v>147</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D181" s="3">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>251</v>
+        <v>543</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>546</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J181" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B182" s="3">
-        <v>320</v>
+        <v>147</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D182" s="3">
-        <v>323</v>
+        <v>152</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>249</v>
+        <v>544</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>547</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J182" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B183" s="3">
-        <v>321</v>
-      </c>
-      <c r="C183" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C183" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D183" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E183" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J183" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B184" s="3">
+        <v>148</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D184" s="3">
+        <v>16</v>
+      </c>
+      <c r="E184" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F183" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G183" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="I183" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J183" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B184" s="3">
-        <v>321</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="D184" s="3">
-        <v>21</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="F184" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>239</v>
+        <v>551</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>559</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J184" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J184" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A185" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B185" s="3">
-        <v>321</v>
+        <v>148</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D185" s="3">
-        <v>351</v>
+        <v>141</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>241</v>
+        <v>552</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>556</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J185" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J185" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B186" s="3">
-        <v>321</v>
+        <v>148</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D186" s="3">
-        <v>352</v>
+        <v>143</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>240</v>
+        <v>553</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>557</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J186" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J186" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B187" s="3">
-        <v>324</v>
+        <v>148</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D187" s="3">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>245</v>
+        <v>554</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>558</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J187" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="187" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B188" s="3">
-        <v>324</v>
-      </c>
-      <c r="C188" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C188" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D188" s="3">
         <v>151</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>142</v>
+        <v>560</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>143</v>
+        <v>561</v>
       </c>
       <c r="I188" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J188" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B189" s="3">
-        <v>324</v>
+        <v>158</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D189" s="3">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>128</v>
@@ -13395,16 +13665,13 @@
         <v>37</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="H189" s="4" t="s">
-        <v>145</v>
+        <v>427</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J189" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J189" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="190" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -13412,7 +13679,7 @@
         <v>218</v>
       </c>
       <c r="B190" s="3">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>218</v>
@@ -13424,16 +13691,16 @@
         <v>128</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J190" s="8" t="d">
-        <v>2026-06-29</v>
+      <c r="J190" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -13441,42 +13708,42 @@
         <v>218</v>
       </c>
       <c r="B191" s="3">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D191" s="3">
-        <v>339</v>
+        <v>157</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>118</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J191" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="J191" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B192" s="3">
-        <v>330</v>
+        <v>159</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D192" s="3">
-        <v>340</v>
+        <v>37</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>128</v>
@@ -13485,13 +13752,16 @@
         <v>146</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>252</v>
+        <v>562</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>563</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J192" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="193" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -13499,13 +13769,13 @@
         <v>218</v>
       </c>
       <c r="B193" s="3">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D193" s="3">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>128</v>
@@ -13514,27 +13784,27 @@
         <v>37</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>256</v>
+        <v>574</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J193" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B194" s="3">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D194" s="3">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>128</v>
@@ -13543,27 +13813,30 @@
         <v>146</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>257</v>
+        <v>568</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>567</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J194" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B195" s="3">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D195" s="3">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>128</v>
@@ -13572,120 +13845,126 @@
         <v>37</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>255</v>
+        <v>564</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>565</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J195" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B196" s="3">
-        <v>347</v>
+        <v>174</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D196" s="3">
-        <v>3</v>
+        <v>141</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F196" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J196" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B197" s="3">
+        <v>174</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D197" s="3">
+        <v>143</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J197" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A198" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B198" s="3">
+        <v>174</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D198" s="3">
+        <v>147</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F198" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G196" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="I196" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J196" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B197" s="3">
-        <v>347</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D197" s="3">
-        <v>340</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G197" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H197" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="I197" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J197" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A198" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B198" s="3">
-        <v>347</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D198" s="3">
-        <v>341</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G198" s="4" t="s">
-        <v>259</v>
+        <v>570</v>
       </c>
       <c r="H198" s="4" t="s">
-        <v>262</v>
+        <v>569</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J198" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B199" s="3">
-        <v>347</v>
-      </c>
-      <c r="C199" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C199" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D199" s="3">
-        <v>342</v>
+        <v>199</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>118</v>
@@ -13694,30 +13973,27 @@
         <v>37</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H199" s="4" t="s">
-        <v>263</v>
+        <v>215</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J199" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="J199" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B200" s="3">
-        <v>353</v>
+        <v>199</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D200" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>118</v>
@@ -13726,42 +14002,48 @@
         <v>37</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>265</v>
+        <v>576</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>575</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J200" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B201" s="3">
-        <v>353</v>
+        <v>199</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D201" s="3">
-        <v>321</v>
+        <v>65</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>266</v>
+        <v>577</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>578</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J201" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -13769,31 +14051,31 @@
         <v>218</v>
       </c>
       <c r="B202" s="3">
-        <v>353</v>
+        <v>199</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D202" s="3">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>283</v>
+        <v>577</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>284</v>
+        <v>579</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J202" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="203" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -13801,13 +14083,13 @@
         <v>218</v>
       </c>
       <c r="B203" s="3">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D203" s="3">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>128</v>
@@ -13816,45 +14098,48 @@
         <v>37</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>286</v>
+        <v>580</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>287</v>
+        <v>581</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J203" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="187" x14ac:dyDescent="0.2">
       <c r="A204" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B204" s="3">
-        <v>375</v>
+        <v>301</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D204" s="3">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>267</v>
+        <v>582</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="I204" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J204" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="205" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -13862,22 +14147,22 @@
         <v>218</v>
       </c>
       <c r="B205" s="3">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D205" s="3">
-        <v>370</v>
+        <v>8</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>15</v>
@@ -13891,22 +14176,22 @@
         <v>218</v>
       </c>
       <c r="B206" s="3">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D206" s="3">
-        <v>374</v>
+        <v>9</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>15</v>
@@ -13915,27 +14200,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B207" s="3">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D207" s="3">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="I207" s="3" t="s">
         <v>15</v>
@@ -13949,147 +14234,147 @@
         <v>218</v>
       </c>
       <c r="B208" s="3">
-        <v>392</v>
-      </c>
-      <c r="C208" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C208" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D208" s="3">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="H208" s="4" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J208" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J208" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B209" s="3">
-        <v>392</v>
-      </c>
-      <c r="C209" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C209" s="9" t="s">
         <v>218</v>
       </c>
       <c r="D209" s="3">
+        <v>21</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A210" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B210" s="3">
+        <v>321</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D210" s="3">
+        <v>351</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J210" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="3">
+        <v>321</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D211" s="3">
         <v>352</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G209" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="I209" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J209" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="85" x14ac:dyDescent="0.2">
-      <c r="A210" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B210" s="3">
-        <v>392</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D210" s="3">
-        <v>380</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G210" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I210" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J210" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="69" x14ac:dyDescent="0.2">
-      <c r="A211" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B211" s="3">
-        <v>392</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D211" s="3">
-        <v>390</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J211" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="212" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="J211" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B212" s="3">
-        <v>440</v>
+        <v>323</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D212" s="3">
-        <v>342</v>
+        <v>8</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>274</v>
+        <v>585</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J212" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="213" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -14097,86 +14382,86 @@
         <v>218</v>
       </c>
       <c r="B213" s="3">
-        <v>443</v>
+        <v>323</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D213" s="3">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>278</v>
+        <v>585</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>588</v>
       </c>
       <c r="I213" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J213" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="214" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B214" s="3">
-        <v>443</v>
+        <v>323</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D214" s="3">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E214" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J214" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215" s="3">
+        <v>324</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D215" s="3">
+        <v>31</v>
+      </c>
+      <c r="E215" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F214" s="3" t="s">
+      <c r="F215" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G214" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H214" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J214" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="215" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A215" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B215" s="3">
-        <v>443</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D215" s="3">
-        <v>341</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G215" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H215" s="4" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="I215" s="3" t="s">
         <v>15</v>
@@ -14185,30 +14470,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B216" s="3">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D216" s="3">
-        <v>342</v>
+        <v>151</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>282</v>
+        <v>143</v>
       </c>
       <c r="I216" s="3" t="s">
         <v>15</v>
@@ -14217,27 +14502,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B217" s="3">
-        <v>443</v>
+        <v>324</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D217" s="3">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>277</v>
+        <v>144</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="I217" s="3" t="s">
         <v>15</v>
@@ -14246,32 +14534,871 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B218" s="3">
-        <v>451</v>
+        <v>330</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D218" s="3">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F218" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J218" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B219" s="3">
+        <v>330</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D219" s="3">
+        <v>339</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J219" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A220" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B220" s="3">
+        <v>330</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D220" s="3">
+        <v>340</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J220" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B221" s="3">
+        <v>331</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D221" s="3">
+        <v>133</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J221" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B222" s="3">
+        <v>331</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D222" s="3">
+        <v>330</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J222" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B223" s="3">
+        <v>331</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D223" s="3">
+        <v>339</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J223" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B224" s="3">
+        <v>347</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D224" s="3">
+        <v>3</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F224" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G218" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="I218" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J218" s="8" t="d">
+      <c r="G224" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J224" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B225" s="3">
+        <v>347</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D225" s="3">
+        <v>340</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J225" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B226" s="3">
+        <v>347</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D226" s="3">
+        <v>341</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J226" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B227" s="3">
+        <v>347</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D227" s="3">
+        <v>342</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J227" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B228" s="3">
+        <v>353</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D228" s="3">
+        <v>21</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J228" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B229" s="3">
+        <v>353</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D229" s="3">
+        <v>321</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G229" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J229" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B230" s="3">
+        <v>353</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D230" s="3">
+        <v>352</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H230" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J230" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A231" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B231" s="3">
+        <v>375</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D231" s="3">
+        <v>32</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H231" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J231" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A232" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B232" s="3">
+        <v>375</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D232" s="3">
+        <v>352</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J232" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B233" s="3">
+        <v>375</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D233" s="3">
+        <v>370</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G233" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J233" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A234" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B234" s="3">
+        <v>375</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D234" s="3">
+        <v>374</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G234" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J234" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A235" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B235" s="3">
+        <v>392</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D235" s="3">
+        <v>341</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J235" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A236" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B236" s="3">
+        <v>392</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D236" s="3">
+        <v>350</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G236" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J236" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A237" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B237" s="3">
+        <v>392</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D237" s="3">
+        <v>352</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J237" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A238" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B238" s="3">
+        <v>392</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D238" s="3">
+        <v>380</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A239" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B239" s="3">
+        <v>392</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D239" s="3">
+        <v>390</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J239" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A240" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B240" s="3">
+        <v>440</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D240" s="3">
+        <v>342</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J240" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A241" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B241" s="3">
+        <v>443</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D241" s="3">
+        <v>119</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J241" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A242" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B242" s="3">
+        <v>443</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D242" s="3">
+        <v>327</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J242" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A243" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B243" s="3">
+        <v>443</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D243" s="3">
+        <v>341</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J243" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A244" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B244" s="3">
+        <v>443</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D244" s="3">
+        <v>342</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H244" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J244" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A245" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B245" s="3">
+        <v>443</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D245" s="3">
+        <v>345</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G245" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J245" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A246" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B246" s="3">
+        <v>451</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D246" s="3">
+        <v>125</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J246" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -14284,13 +15411,13 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J218">
-    <sortCondition ref="B2:B218"/>
-    <sortCondition ref="A2:A218"/>
-    <sortCondition ref="D2:D218"/>
-    <sortCondition ref="C2:C218"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J246">
+    <sortCondition ref="B2:B246"/>
+    <sortCondition ref="A2:A246"/>
+    <sortCondition ref="D2:D246"/>
+    <sortCondition ref="C2:C246"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 C219:C1048576 A219:A1048576">
+  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 A247:A1048576 C247:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{77473137-7AEB-4D46-B800-BBA4B2CB16DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADFF2802-AD0F-F948-A39F-CC2D07708A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2962" uniqueCount="589">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3103" uniqueCount="626">
   <si>
     <t>reviewer</t>
   </si>
@@ -1833,6 +1833,117 @@
   </si>
   <si>
     <t>BIP323 removes bits 5–28 from BIP9 soft-fork signalling and warning interpretation.</t>
+  </si>
+  <si>
+    <t>BIP337 handles P2TR outputs / Taproot key-spend signatures (BIP341), but Taproot is an existing script/output type being recognized for compression, not a protocol dependency introduced by BIP337.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Boolean to determine if this input's signature hash type is standard (0x00 for Taproot, 0x01 for Legacy/Segwit). [...] </t>
+  </si>
+  <si>
+    <t>A Boolean to determine if this input's signature is compressed. The signature is only compressed for P2TR on a key spend and for P2SH when it is a wrapped P2SH-WPKH. [...] A Boolean to determine if this input's signature hash type is standard (0x00 for Taproot, 0x01 for Legacy/Segwit).</t>
+  </si>
+  <si>
+    <t>A Boolean to determine if this input's signature is compressed. The signature is only compressed for P2TR on a key spend and for P2SH when it is a wrapped P2SH-WPKH. [...] A Boolean to determine if this input's signature hash type is standard (0x00 for Taproot, 0x01 for Legacy/Segwit). [...]</t>
+  </si>
+  <si>
+    <t>Using compressed signatures and public key recovery upon decompression. [...] A Boolean to determine if this input's signature is compressed. The signature is only compressed for P2TR on a key spend and for P2SH when it is a wrapped P2SH-WPKH. [...] Signature || 64 Bytes || Contains the 64 Byte signature.</t>
+  </si>
+  <si>
+    <t>A Boolean to determine if this input's signature is compressed. The signature is only compressed for P2TR on a key spend and for P2SH when it is a wrapped P2SH-WPKH. [...]</t>
+  </si>
+  <si>
+    <t>BIP337 points to BIP141 because its compression format recognizes SegWit transaction/script forms and SegWit sighash conventions. BIP337 uses those existing forms as inputs to compress, but does not redefine SegWit or require a new SegWit deployment.</t>
+  </si>
+  <si>
+    <t>Taproot key-spend compression relies on the fixed 64-byte Schnorr signature format associated with BIP340. The link is explanatory, since BIP337 only serializes/compresses existing signatures rather than changing signature validation.</t>
+  </si>
+  <si>
+    <t>BIP337 support P2SH, including wrapped P2SH-P2WPKH, as one of the script patterns it can recognize and compress.</t>
+  </si>
+  <si>
+    <t>BIP337 references BIP143 because it uses the standard SegWit sighash byte convention when deciding whether a signature hash type can be omitted or compressed. This is contextual to signature serialization, not a direct dependency on BIP143’s transaction digest algorithm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A number of related ideas for improving Bitcoin's scripting capabilities have been previously proposed: Schnorr signatures (BIP340), Merkle branches ("MAST", BIP114, BIP117), new sighash modes (BIP118), new opcodes like CHECKSIGFROMSTACK, Taproot, Graftroot, G'root, and cross-input aggregation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Taproot output is a native SegWit output (see BIP141) with version number 1, and a 32-byte witness program. [...] The following function, taproot_output_script, returns a byte array with the scriptPubKey (see BIP141). ser_script refers to a function that prefixes its input with a CompactSize-encoded length. </t>
+  </si>
+  <si>
+    <t>Requires: 340 [...] The notation below follows that of BIP340.  [...] Let q be the 32-byte array containing the witness program (the second push in the scriptPubKey) which represents a public key according to BIP340. [...] A Taproot signature is a 64-byte Schnorr signature, as defined in BIP340, with the sighash byte appended in the usual Bitcoin fashion. [...] These algorithms take advantage of helper functions from the BIP340 reference code for integer conversion, point multiplication, and tagged hashes. [...] All signatures are created with an all-zero (0x0000...0000) BIP340 auxiliary randomness array. [...]</t>
+  </si>
+  <si>
+    <t>Why not use a more efficient hash construction for inner Merkle nodes? The chosen construction does require two invocations of the SHA256 compression functions, one of which can be avoided in theory (see BIP98). [...]</t>
+  </si>
+  <si>
+    <t>In summary, the semantics of the BIP143 sighash types remain unchanged, except the following: [...] Why does the signature message commit to the scriptPubKey? This prevents lying to offline signing devices about output being spent, even when the actually executed script (scriptCode in BIP143) is correct. [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the applicable script rules in script path spends? BIP342 specifies validity rules that apply for leaf version 0xc0, but future proposals can introduce rules for other leaf versions. [...] What extensions use the ext_flag mechanism? BIP342 reuses the same common signature message algorithm, but adds BIP342-specific data at the end, which is indicated using ext_flag = 1. [...] This BIP is deployed concurrently with BIP342. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Bitcoin mainnet and testnet3, these BIPs are deployed by "version bits" with the name "taproot" and bit 2, using BIP9 modified to use a lower threshold, with an additional min_activation_height parameter and replacing the state transition logic for the DEFINED, STARTED and LOCKED_IN states as follows: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test vectors for wallet operation (scriptPubKey computation, key path spending, control block construction) can be found here. It consists of two sets of vectors. The first "scriptPubKey" tests concern computing the scriptPubKey and (mainnet) BIP350 address given an internal public key, and a script tree. [...] Depending on the implementation non-upgraded wallets may be able to send to Segwit version 1 programs if they support sending to BIP350 Bech32m addresses. </t>
+  </si>
+  <si>
+    <t>BIP341 directly depends on BIP340 because Taproot output keys, public-key interpretation, and signature validation are defined using BIP340 Schnorr keys and signatures.</t>
+  </si>
+  <si>
+    <t>BIP341 depends on BIP141 because Taproot is defined as a new native SegWit witness version. Without the SegWit witness-program framework, BIP341’s output type is meaningless.</t>
+  </si>
+  <si>
+    <t>BIP341 provides the Taproot structure, while BIP342 defines the main script language used inside it.</t>
+  </si>
+  <si>
+    <t>BIP341 references BIP143 because it reuses the existing SegWit sighash-type semantics as a baseline, then defines Taproot-specific changes to the signature message format.</t>
+  </si>
+  <si>
+    <t>BIP341 references BIP117 as prior Merkle-branch/MAST-related work.</t>
+  </si>
+  <si>
+    <t>BIP341 references BIP118 as related sighash-design background, while explicitly excluding those new sighash features from Taproot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A number of related ideas for improving Bitcoin's scripting capabilities have been previously proposed: Schnorr signatures (BIP340), Merkle branches ("MAST", BIP114, BIP117), new sighash modes (BIP118), new opcodes like CHECKSIGFROMSTACK, Taproot, Graftroot, G'root, and cross-input aggregation. [...] For things like sighashes and opcodes we include fixes for known problems, but exclude new features that can be added independently with no downsides. </t>
+  </si>
+  <si>
+    <t>BIP341 references BIP98 only as an alternative Merkle hashing construction considered in rationale</t>
+  </si>
+  <si>
+    <t>Wallets use Bech32m addresses, defined in BIP350, to encode/send to SegWit version 1 Taproot outputs. Taproot consensus does not depend on Bech32m existing. One can create/spend Taproot outputs from raw scripts without addresses.</t>
+  </si>
+  <si>
+    <t>BIP341 references BIP114 as prior Merkle-branch/MAST-related work.</t>
+  </si>
+  <si>
+    <t>This document specifies a BIP8 (LOT=true) deployment to activate taproot. [...]  The mandatory signaling is only required if miners have failed to meet the signaling threshold during the BIP8 deployment. [...] The BIP8(LOT=true) deployment is compatible with the “Speedy Trial” deployment in Bitcoin Core as there was not a discrepancy between MTP and block height for the defined start heights. The BIP8 (LOT=true) deployment has also been deliberately designed to be compatible with a future BIP8(LOT=false) or BIP8(LOT=true) deployment in Bitcoin Core assuming Bitcoin Core releases one of these activation mechanisms in the event of the Speedy Trial deployment failing to activate. [...] References [... ] BIP8 Version bits with lock-in by height [...]</t>
+  </si>
+  <si>
+    <t>The Taproot soft fork upgrade has been assessed to have overwhelming community consensus and hence should attempt to be activated. Lessons have been learned from the BIP148 and BIP91 deployments in 2017 with regards to giving many months of advance warning before the mandatory signaling is attempted. [...] The deployment of BIP148 demonstrated that multiple implementations with different activation mechanisms can incentivize the necessary actors to act so that the different deployments activate in sync. [...] References [... ] BIP148 Mandatory activation of segwit deployment [...]</t>
+  </si>
+  <si>
+    <t>It is effectively a BIP8 activation mechanism with one exception: start height and timeout height were defined using median time past (MTP) rather than block heights. It uses signaling bit 2, was deployed between midnight April 24th 2021 and midnight August 11th 2021, has a minimum activation height of 709632 and intends to activate BIPs 340, 341, and 342. [...] References [... ] BIP340 Schnorr Signatures for secp256k1 [...]</t>
+  </si>
+  <si>
+    <t>It is effectively a BIP8 activation mechanism with one exception: start height and timeout height were defined using median time past (MTP) rather than block heights. It uses signaling bit 2, was deployed between midnight April 24th 2021 and midnight August 11th 2021, has a minimum activation height of 709632 and intends to activate BIPs 340, 341, and 342. [...] References [... ] BIP341 Taproot: SegWit version 1 spending rules [...]</t>
+  </si>
+  <si>
+    <t>It is effectively a BIP8 activation mechanism with one exception: start height and timeout height were defined using median time past (MTP) rather than block heights. It uses signaling bit 2, was deployed between midnight April 24th 2021 and midnight August 11th 2021, has a minimum activation height of 709632 and intends to activate BIPs 340, 341, and 342. [...] References [... ] BIP342 Validation of Taproot Scripts [...]</t>
+  </si>
+  <si>
+    <t>BIP343 references BIP148 as historical precedent for mandatory activation signaling, but it does not reuse BIP148’s SegWit-specific deployment rules.</t>
+  </si>
+  <si>
+    <t>Just references BIP340 as one of the Taproot soft-fork components it intended to activate.</t>
+  </si>
+  <si>
+    <t>Just references BIP341 as one of the Taproot soft-fork components it intended to activate.</t>
+  </si>
+  <si>
+    <t>Just references BIP342 as one of the Taproot soft-fork components it intended to activate.</t>
   </si>
 </sst>
 </file>
@@ -2351,7 +2462,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2385,9 +2496,6 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -7206,6 +7314,12 @@
       <c r="B89" s="3">
         <v>337</v>
       </c>
+      <c r="C89" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E89" s="7" t="s">
         <v>17</v>
       </c>
@@ -7250,6 +7364,12 @@
       <c r="B90" s="3">
         <v>341</v>
       </c>
+      <c r="C90" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E90" s="7" t="s">
         <v>17</v>
       </c>
@@ -7293,6 +7413,12 @@
       </c>
       <c r="B91" s="3">
         <v>343</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>17</v>
@@ -7884,7 +8010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J246"/>
+  <dimension ref="A1:J266"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -13164,7 +13290,7 @@
       <c r="G173" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="H173" s="12" t="s">
+      <c r="H173" s="4" t="s">
         <v>537</v>
       </c>
       <c r="I173" s="3" t="s">
@@ -14708,201 +14834,207 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B224" s="3">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D224" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>264</v>
+        <v>594</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>597</v>
       </c>
       <c r="I224" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J224" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="225" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B225" s="3">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D225" s="3">
+        <v>141</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J225" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B226" s="3">
+        <v>337</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D226" s="3">
+        <v>143</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J226" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B227" s="3">
+        <v>337</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D227" s="3">
         <v>340</v>
       </c>
-      <c r="E225" s="3" t="s">
+      <c r="E227" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J227" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B228" s="3">
+        <v>337</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D228" s="3">
+        <v>341</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J228" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B229" s="3">
+        <v>341</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D229" s="3">
+        <v>9</v>
+      </c>
+      <c r="E229" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F225" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G225" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H225" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="I225" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J225" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A226" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B226" s="3">
-        <v>347</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D226" s="3">
+      <c r="F229" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G229" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J229" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B230" s="3">
         <v>341</v>
       </c>
-      <c r="E226" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H226" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I226" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J226" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="227" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A227" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B227" s="3">
-        <v>347</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D227" s="3">
-        <v>342</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G227" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="H227" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="I227" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J227" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A228" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B228" s="3">
-        <v>353</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D228" s="3">
-        <v>21</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G228" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="I228" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J228" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="229" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A229" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B229" s="3">
-        <v>353</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D229" s="3">
-        <v>321</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G229" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="I229" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J229" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A230" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B230" s="3">
-        <v>353</v>
-      </c>
       <c r="C230" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D230" s="3">
-        <v>352</v>
+        <v>98</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>128</v>
@@ -14911,16 +15043,16 @@
         <v>37</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>283</v>
+        <v>602</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>284</v>
+        <v>614</v>
       </c>
       <c r="I230" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J230" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="231" spans="1:10" ht="85" x14ac:dyDescent="0.2">
@@ -14928,13 +15060,13 @@
         <v>218</v>
       </c>
       <c r="B231" s="3">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D231" s="3">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>128</v>
@@ -14943,88 +15075,94 @@
         <v>37</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>286</v>
+        <v>599</v>
       </c>
       <c r="H231" s="4" t="s">
-        <v>287</v>
+        <v>616</v>
       </c>
       <c r="I231" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J231" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B232" s="3">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D232" s="3">
-        <v>352</v>
+        <v>117</v>
       </c>
       <c r="E232" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="H232" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J232" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A233" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B233" s="3">
+        <v>341</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D233" s="3">
         <v>118</v>
       </c>
-      <c r="F232" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G232" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="I232" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J232" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A233" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B233" s="3">
-        <v>375</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D233" s="3">
-        <v>370</v>
-      </c>
       <c r="E233" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>267</v>
+        <v>613</v>
+      </c>
+      <c r="H233" s="4" t="s">
+        <v>612</v>
       </c>
       <c r="I233" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J233" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B234" s="3">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D234" s="3">
-        <v>374</v>
+        <v>141</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>118</v>
@@ -15033,56 +15171,62 @@
         <v>37</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>285</v>
+        <v>600</v>
+      </c>
+      <c r="H234" s="4" t="s">
+        <v>608</v>
       </c>
       <c r="I234" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J234" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B235" s="3">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D235" s="3">
+        <v>143</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J235" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+      <c r="A236" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B236" s="3">
         <v>341</v>
       </c>
-      <c r="E235" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G235" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="I235" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J235" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A236" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B236" s="3">
-        <v>392</v>
-      </c>
       <c r="C236" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D236" s="3">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>118</v>
@@ -15091,30 +15235,30 @@
         <v>37</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>269</v>
+        <v>601</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>270</v>
+        <v>607</v>
       </c>
       <c r="I236" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J236" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="237" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B237" s="3">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D237" s="3">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>118</v>
@@ -15123,219 +15267,228 @@
         <v>37</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>268</v>
+        <v>604</v>
+      </c>
+      <c r="H237" s="4" t="s">
+        <v>609</v>
       </c>
       <c r="I237" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J237" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B238" s="3">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D238" s="3">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="E238" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H238" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="A239" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B239" s="3">
+        <v>343</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D239" s="3">
+        <v>8</v>
+      </c>
+      <c r="E239" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F238" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G238" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I238" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J238" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="239" spans="1:10" ht="69" x14ac:dyDescent="0.2">
-      <c r="A239" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B239" s="3">
-        <v>392</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D239" s="3">
-        <v>390</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="F239" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>273</v>
+        <v>617</v>
       </c>
       <c r="I239" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J239" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B240" s="3">
-        <v>440</v>
+        <v>343</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D240" s="3">
+        <v>148</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="H240" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J240" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A241" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B241" s="3">
+        <v>343</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D241" s="3">
+        <v>340</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="H241" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J241" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A242" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B242" s="3">
+        <v>343</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D242" s="3">
+        <v>341</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G242" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="H242" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J242" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+      <c r="A243" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B243" s="3">
+        <v>343</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D243" s="3">
         <v>342</v>
       </c>
-      <c r="E240" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F240" s="3" t="s">
+      <c r="E243" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J243" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A244" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B244" s="3">
+        <v>347</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D244" s="3">
+        <v>3</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F244" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G240" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="I240" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J240" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A241" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B241" s="3">
-        <v>443</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D241" s="3">
-        <v>119</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G241" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="I241" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J241" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A242" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B242" s="3">
-        <v>443</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D242" s="3">
-        <v>327</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G242" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H242" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I242" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J242" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A243" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B243" s="3">
-        <v>443</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D243" s="3">
-        <v>341</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G243" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H243" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I243" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J243" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A244" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B244" s="3">
-        <v>443</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D244" s="3">
-        <v>342</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="G244" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H244" s="4" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="I244" s="3" t="s">
         <v>15</v>
@@ -15344,27 +15497,30 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A245" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B245" s="3">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D245" s="3">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>277</v>
+        <v>258</v>
+      </c>
+      <c r="H245" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="I245" s="3" t="s">
         <v>15</v>
@@ -15373,32 +15529,636 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A246" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B246" s="3">
+        <v>347</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D246" s="3">
+        <v>341</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G246" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H246" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J246" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A247" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B247" s="3">
+        <v>347</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D247" s="3">
+        <v>342</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G247" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H247" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J247" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A248" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B248" s="3">
+        <v>353</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D248" s="3">
+        <v>21</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J248" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A249" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B249" s="3">
+        <v>353</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D249" s="3">
+        <v>321</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J249" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A250" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B250" s="3">
+        <v>353</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D250" s="3">
+        <v>352</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="H250" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J250" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A251" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B251" s="3">
+        <v>375</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D251" s="3">
+        <v>32</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H251" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J251" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A252" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B252" s="3">
+        <v>375</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D252" s="3">
+        <v>352</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J252" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A253" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B253" s="3">
+        <v>375</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D253" s="3">
+        <v>370</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J253" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A254" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B254" s="3">
+        <v>375</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D254" s="3">
+        <v>374</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G254" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J254" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A255" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B255" s="3">
+        <v>392</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D255" s="3">
+        <v>341</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G255" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J255" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A256" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B256" s="3">
+        <v>392</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D256" s="3">
+        <v>350</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G256" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H256" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J256" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A257" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B257" s="3">
+        <v>392</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D257" s="3">
+        <v>352</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J257" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A258" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B258" s="3">
+        <v>392</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D258" s="3">
+        <v>380</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J258" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A259" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B259" s="3">
+        <v>392</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D259" s="3">
+        <v>390</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J259" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A260" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B260" s="3">
+        <v>440</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D260" s="3">
+        <v>342</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G260" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J260" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A261" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B261" s="3">
+        <v>443</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D261" s="3">
+        <v>119</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J261" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A262" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B262" s="3">
+        <v>443</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D262" s="3">
+        <v>327</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J262" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A263" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B263" s="3">
+        <v>443</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D263" s="3">
+        <v>341</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G263" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H263" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J263" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A264" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B264" s="3">
+        <v>443</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D264" s="3">
+        <v>342</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J264" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A265" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B265" s="3">
+        <v>443</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D265" s="3">
+        <v>345</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J265" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A266" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B266" s="3">
         <v>451</v>
       </c>
-      <c r="C246" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D246" s="3">
+      <c r="C266" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D266" s="3">
         <v>125</v>
       </c>
-      <c r="E246" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F246" s="3" t="s">
+      <c r="E266" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F266" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G246" s="4" t="s">
+      <c r="G266" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I246" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J246" s="8" t="d">
+      <c r="I266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J266" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -15411,13 +16171,13 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J246">
-    <sortCondition ref="B2:B246"/>
-    <sortCondition ref="A2:A246"/>
-    <sortCondition ref="D2:D246"/>
-    <sortCondition ref="C2:C246"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J266">
+    <sortCondition ref="B2:B266"/>
+    <sortCondition ref="A2:A266"/>
+    <sortCondition ref="D2:D266"/>
+    <sortCondition ref="C2:C266"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 A247:A1048576 C247:C1048576">
+  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 A267:A1048576 C267:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ADFF2802-AD0F-F948-A39F-CC2D07708A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA88378A-AC0D-CA48-A44F-A5ADC5A21E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3103" uniqueCount="626">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3234" uniqueCount="659">
   <si>
     <t>reviewer</t>
   </si>
@@ -1944,6 +1944,109 @@
   </si>
   <si>
     <t>Just references BIP342 as one of the Taproot soft-fork components it intended to activate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document proposes a second version of the Partially Signed Bitcoin Transaction format described in BIP 174 which allows for inputs and outputs to be added to the PSBT after creation. [...] Partially Signed Bitcoin Transaction Version 0 as described in BIP 174 is unable to have new inputs and outputs be added to the transaction. The fixed global unsigned transaction cannot be changed which prevents any additional inputs or outputs to be added. PSBT Version 2 is intended to rectify this problem.  [...] PSBT Version 2 (PSBTv2) only specifies new fields and field inclusion/exclusion requirements. </t>
+  </si>
+  <si>
+    <t>BIP371's Taproot fields are explicitly defined for PSBTv2 (BIP370) as well as PSBTv0 (BIP174), and the field tables specify inclusion support for version 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document proposes additional fields for BIP 174 PSBTv0 and BIP 370 PSBTv2 that allow for BIP 340/341/342 Taproot data to be included in a PSBT of any version. These will be fields for signatures and scripts that are relevant to the creation of Taproot inputs.  [...] BIP 174 recommends using PSBT_IN_NON_WITNESS_UTXO for all inputs because of potential attacks involving an updater lying about the amounts in an output. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This document proposes additional fields for BIP 174 PSBTv0 and BIP 370 PSBTv2 that allow for BIP 340/341/342 Taproot data to be included in a PSBT of any version. These will be fields for signatures and scripts that are relevant to the creation of Taproot inputs. </t>
+  </si>
+  <si>
+    <t>This document proposes additional fields [...] that allow for BIP 340/341/342 Taproot data to be included in a PSBT of any version. These will be fields for signatures and scripts that are relevant to the creation of Taproot inputs. [...] Motivation BIPs 340, 341, and 342 specify Taproot which provides a wholly new way to create and spend Bitcoin outputs. [...]</t>
+  </si>
+  <si>
+    <t>BIP371 defines PSBT fields for carrying Taproot signing data specified by BIP340.</t>
+  </si>
+  <si>
+    <t>BIP371 defines PSBT fields for carrying Taproot spending data specified by BIP341.</t>
+  </si>
+  <si>
+    <t>BIP371 defines PSBT fields for carrying Taproot script-path data specified by BIP342.</t>
+  </si>
+  <si>
+    <t>Motivation BIP352 requires senders to compute output scripts using ECDH shared secrets from the same secret keys used to sign the inputs. Generating an incorrect signature will produce an invalid transaction that will be rejected by consensus. [...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specification All conventions and notations are used as defined in BIP327. </t>
+  </si>
+  <si>
+    <t>Why include auxiliary random data? The auxiliary random data should be set to fresh randomness for each proof. The same rationale and recommendations from BIP340 should be applied.</t>
+  </si>
+  <si>
+    <t>BIP374 explicitly reuses BIP327’s elliptic-curve conventions and notation for defining DLEQ proof generation and verification.</t>
+  </si>
+  <si>
+    <t>BIP374 references BIP352 as the motivating use case for DLEQ proofs in Silent Payments, but the DLEQ proof format itself is general and not limited to BIP352.</t>
+  </si>
+  <si>
+    <t>BIP374 references BIP340 for nonce/auxiliary-randomness rationale, but does not use BIP340 Schnorr signature validation directly.</t>
+  </si>
+  <si>
+    <t>[...] References [...] OP_CHECKCONTRACTVERIFY: BIP-443</t>
+  </si>
+  <si>
+    <t>[...] References [...] OP_INTERNALKEY: BIP-349, BIN-2024-0004</t>
+  </si>
+  <si>
+    <t>[...] References [...] OP_TEMPLATEHASH: BIP-446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For taproot script spends with leaf version 0xc0 (see BIP-342), OP_PAIRCOMMIT replaces OP_SUCCESS205 (0xcd). </t>
+  </si>
+  <si>
+    <t>Specification Notation follows BIP-340, including the tagged hash notation: hashtag(x) = SHA256(SHA256(tag) || SHA256(tag) || x) [...] References [...] Tagged hash: BIP-340</t>
+  </si>
+  <si>
+    <t>Lightning Symmetry contracts require data availability for contested closes. 3 By forcing parties to include settlement transaction hashes in the witness, later updates can reconstruct scripts of intermediate states while only keeping the latest state.
+# S: 500000000
+# internal-key: BIP-327 aggregate key of channel participants
+# state-n-hash:  { nLockTime(S+n), out(contract, amount(A)+amount(B)) } 
+[...] References [...] MuSig2: BIP-327</t>
+  </si>
+  <si>
+    <t>Alternative approaches considered and rejected: OP_CAT67 [...] 'Kitty' CAT: OP_CAT with size limits [...] References [...] OP_CAT: BIP-347, BIN-2024-0001</t>
+  </si>
+  <si>
+    <t>Alternative approaches considered and rejected: [...] OP_CHECKTEMPLATEVERIFY committing to the taproot annex8 [...] References [...] OP_CHECKTEMPLATEVERIFY: BIP-119</t>
+  </si>
+  <si>
+    <t>Alternative approaches considered and rejected: [...] OP_CHECKSIGFROMSTACK on n elements [...] References [...] OP_CHECKSIGFROMSTACK: BIP-348, BIN-2024-0003</t>
+  </si>
+  <si>
+    <t>BIP442 depends on BIP342 because OP_PAIRCOMMIT is defined as a new Tapscript opcode replacing an OP_SUCCESS opcode under BIP342 leaf-version 0xc0 rules.</t>
+  </si>
+  <si>
+    <t>BIP442 depends on BIP340 for the tagged-hash construction used to define PairCommit hashing.</t>
+  </si>
+  <si>
+    <t>BIP442' Lightning Symmetry example uses a MuSig2 aggregate key, but OP_PAIRCOMMIT itself does not require MuSig2, defined in 327.</t>
+  </si>
+  <si>
+    <t>BIP442's examples and cost comparisons use OP_CHECKTEMPLATEVERIFY together with OP_PAIRCOMMIT, but BIP119 is not required for the opcode’s standalone semantics.</t>
+  </si>
+  <si>
+    <t>’</t>
+  </si>
+  <si>
+    <t>BIP442 references BIP348 because OP_CHECKSIGFROMSTACK is a major motivating companion opcode in its delegation and Lightning Symmetry examples.</t>
+  </si>
+  <si>
+    <t>BIP442 references BIP349 because OP_INTERNALKEY is used in the Lightning Symmetry example alongside OP_PAIRCOMMIT and OP_CHECKSIGFROMSTACK.</t>
+  </si>
+  <si>
+    <t>OP_CAT, defined in BIP347, is discussed as an alternative commitment-building opcode that OP_PAIRCOMMIT aims to avoid or improve on.</t>
+  </si>
+  <si>
+    <t>BIP442 references BIP443 as a related covenant/contract opcode considered in the broader design space, not as a dependency.</t>
+  </si>
+  <si>
+    <t>OP_TEMPLATEHASH, defined in BIP446, appears in the Lightning Symmetry cost comparison as an alternative construction.</t>
   </si>
 </sst>
 </file>
@@ -7564,6 +7667,12 @@
       <c r="B94" s="3">
         <v>370</v>
       </c>
+      <c r="C94" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E94" s="7" t="s">
         <v>17</v>
       </c>
@@ -7608,6 +7717,12 @@
       <c r="B95" s="3">
         <v>371</v>
       </c>
+      <c r="C95" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E95" s="7" t="s">
         <v>17</v>
       </c>
@@ -7652,6 +7767,12 @@
       <c r="B96" s="3">
         <v>374</v>
       </c>
+      <c r="C96" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
       <c r="E96" s="7" t="s">
         <v>17</v>
       </c>
@@ -7845,6 +7966,12 @@
       </c>
       <c r="B100" s="3">
         <v>442</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>17</v>
@@ -8010,7 +8137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J266"/>
+  <dimension ref="A1:J291"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -15683,50 +15810,47 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" ht="153" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B251" s="3">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D251" s="3">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="H251" s="4" t="s">
-        <v>287</v>
+        <v>626</v>
       </c>
       <c r="I251" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J251" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A252" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B252" s="3">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D252" s="3">
-        <v>352</v>
+        <v>174</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>118</v>
@@ -15735,27 +15859,30 @@
         <v>37</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>267</v>
+        <v>628</v>
+      </c>
+      <c r="H252" s="4" t="s">
+        <v>627</v>
       </c>
       <c r="I252" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J252" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B253" s="3">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D253" s="3">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>118</v>
@@ -15764,27 +15891,30 @@
         <v>37</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>267</v>
+        <v>630</v>
+      </c>
+      <c r="H253" s="4" t="s">
+        <v>631</v>
       </c>
       <c r="I253" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J253" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B254" s="3">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D254" s="3">
-        <v>374</v>
+        <v>341</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>118</v>
@@ -15793,27 +15923,30 @@
         <v>37</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>285</v>
+        <v>630</v>
+      </c>
+      <c r="H254" s="4" t="s">
+        <v>632</v>
       </c>
       <c r="I254" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J254" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A255" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B255" s="3">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D255" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>118</v>
@@ -15822,27 +15955,30 @@
         <v>37</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>271</v>
+        <v>630</v>
+      </c>
+      <c r="H255" s="4" t="s">
+        <v>633</v>
       </c>
       <c r="I255" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J255" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B256" s="3">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D256" s="3">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>118</v>
@@ -15851,30 +15987,30 @@
         <v>37</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>269</v>
+        <v>629</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>270</v>
+        <v>627</v>
       </c>
       <c r="I256" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J256" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B257" s="3">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D257" s="3">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>118</v>
@@ -15883,94 +16019,106 @@
         <v>37</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>268</v>
+        <v>635</v>
+      </c>
+      <c r="H257" s="4" t="s">
+        <v>637</v>
       </c>
       <c r="I257" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J257" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B258" s="3">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D258" s="3">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>272</v>
+        <v>636</v>
+      </c>
+      <c r="H258" s="4" t="s">
+        <v>639</v>
       </c>
       <c r="I258" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J258" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B259" s="3">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D259" s="3">
-        <v>390</v>
+        <v>352</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>128</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>273</v>
+        <v>634</v>
+      </c>
+      <c r="H259" s="4" t="s">
+        <v>638</v>
       </c>
       <c r="I259" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J259" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A260" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B260" s="3">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D260" s="3">
-        <v>342</v>
+        <v>32</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>274</v>
+        <v>286</v>
+      </c>
+      <c r="H260" s="4" t="s">
+        <v>287</v>
       </c>
       <c r="I260" s="3" t="s">
         <v>15</v>
@@ -15984,22 +16132,22 @@
         <v>218</v>
       </c>
       <c r="B261" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D261" s="3">
-        <v>119</v>
+        <v>352</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="I261" s="3" t="s">
         <v>15</v>
@@ -16008,30 +16156,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B262" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D262" s="3">
-        <v>327</v>
+        <v>370</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="H262" s="4" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="I262" s="3" t="s">
         <v>15</v>
@@ -16045,13 +16190,13 @@
         <v>218</v>
       </c>
       <c r="B263" s="3">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D263" s="3">
-        <v>341</v>
+        <v>374</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>118</v>
@@ -16060,10 +16205,7 @@
         <v>37</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H263" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I263" s="3" t="s">
         <v>15</v>
@@ -16072,18 +16214,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B264" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D264" s="3">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>118</v>
@@ -16092,10 +16234,7 @@
         <v>37</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="H264" s="4" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="I264" s="3" t="s">
         <v>15</v>
@@ -16109,22 +16248,25 @@
         <v>218</v>
       </c>
       <c r="B265" s="3">
-        <v>443</v>
+        <v>392</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D265" s="3">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>277</v>
+        <v>269</v>
+      </c>
+      <c r="H265" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="I265" s="3" t="s">
         <v>15</v>
@@ -16138,28 +16280,596 @@
         <v>218</v>
       </c>
       <c r="B266" s="3">
+        <v>392</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D266" s="3">
+        <v>352</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J266" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A267" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B267" s="3">
+        <v>392</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D267" s="3">
+        <v>380</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G267" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J267" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A268" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B268" s="3">
+        <v>392</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D268" s="3">
+        <v>390</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J268" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A269" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B269" s="3">
+        <v>440</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D269" s="3">
+        <v>342</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J269" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A270" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B270" s="3">
+        <v>442</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D270" s="3">
+        <v>119</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="H270" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J270" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+      <c r="A271" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B271" s="3">
+        <v>442</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D271" s="3">
+        <v>327</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G271" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="H271" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J271" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A272" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B272" s="3">
+        <v>442</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D272" s="3">
+        <v>340</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="H272" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J272" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A273" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B273" s="3">
+        <v>442</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D273" s="3">
+        <v>342</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G273" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="H273" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J273" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A274" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B274" s="3">
+        <v>442</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D274" s="3">
+        <v>347</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="H274" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J274" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A275" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B275" s="3">
+        <v>442</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D275" s="3">
+        <v>348</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G275" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="H275" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J275" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A276" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B276" s="3">
+        <v>442</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D276" s="3">
+        <v>349</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G276" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H276" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J276" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A277" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B277" s="3">
+        <v>442</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D277" s="3">
+        <v>443</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G277" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="H277" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J277" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A278" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B278" s="3">
+        <v>442</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D278" s="3">
+        <v>446</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J278" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A279" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B279" s="3">
+        <v>443</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D279" s="3">
+        <v>119</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G279" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J279" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A280" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B280" s="3">
+        <v>443</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D280" s="3">
+        <v>327</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G280" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H280" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J280" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A281" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B281" s="3">
+        <v>443</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D281" s="3">
+        <v>341</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G281" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="H281" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J281" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A282" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B282" s="3">
+        <v>443</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D282" s="3">
+        <v>342</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G282" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="H282" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J282" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A283" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B283" s="3">
+        <v>443</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D283" s="3">
+        <v>345</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G283" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J283" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A284" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B284" s="3">
         <v>451</v>
       </c>
-      <c r="C266" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D266" s="3">
+      <c r="C284" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D284" s="3">
         <v>125</v>
       </c>
-      <c r="E266" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F266" s="3" t="s">
+      <c r="E284" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F284" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G266" s="4" t="s">
+      <c r="G284" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I266" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J266" s="8" t="d">
+      <c r="I284" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J284" s="8" t="d">
         <v>2026-06-30</v>
+      </c>
+    </row>
+    <row r="290" spans="7:7" x14ac:dyDescent="0.2">
+      <c r="G290" s="4" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="291" spans="7:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="G291" s="4" t="s">
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -16171,13 +16881,13 @@
       <sortCondition ref="C2:C94"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J266">
-    <sortCondition ref="B2:B266"/>
-    <sortCondition ref="A2:A266"/>
-    <sortCondition ref="D2:D266"/>
-    <sortCondition ref="C2:C266"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J284">
+    <sortCondition ref="B2:B284"/>
+    <sortCondition ref="A2:A284"/>
+    <sortCondition ref="D2:D284"/>
+    <sortCondition ref="C2:C284"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 A267:A1048576 C267:C1048576">
+  <conditionalFormatting sqref="A1:A154 C1:C154 A162:A208 C165:C208 A285:A1048576 C285:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA88378A-AC0D-CA48-A44F-A5ADC5A21E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D001EF1C-8E77-5149-B717-EFF73BDAA213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$284</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$43</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3234" uniqueCount="659">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3237" uniqueCount="662">
   <si>
     <t>reviewer</t>
   </si>
@@ -2047,6 +2047,15 @@
   </si>
   <si>
     <t>OP_TEMPLATEHASH, defined in BIP446, appears in the Lightning Symmetry cost comparison as an alternative construction.</t>
+  </si>
+  <si>
+    <t>BIP145 depends on BIP141 because it modifies getblocktemplate specifically to support SegWit block construction, using BIP141-defined witness data, sigop/weight accounting, and commitment requirements.</t>
+  </si>
+  <si>
+    <t>SLIP21 can use a BIP39 seed, but does not require BIP39 specifically.</t>
+  </si>
+  <si>
+    <t>SLIP21 can use a SLIP39 master secret, but does not require SLIP39 specifically.</t>
   </si>
 </sst>
 </file>
@@ -8378,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>37</v>
@@ -9005,13 +9014,16 @@
         <v>39</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>150</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>660</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>15</v>
@@ -9034,13 +9046,16 @@
         <v>39</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>150</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>661</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -13520,7 +13535,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
         <v>218</v>
       </c>
@@ -13534,7 +13549,7 @@
         <v>141</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>37</v>
@@ -13542,6 +13557,9 @@
       <c r="G177" s="4" t="s">
         <v>209</v>
       </c>
+      <c r="H177" s="4" t="s">
+        <v>659</v>
+      </c>
       <c r="I177" s="3" t="s">
         <v>15</v>
       </c>
@@ -15138,7 +15156,7 @@
         <v>118</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G229" s="4" t="s">
         <v>605</v>
@@ -15455,7 +15473,7 @@
         <v>118</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="G239" s="4" t="s">
         <v>617</v>
@@ -16862,7 +16880,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.2">
+    <row r="290" spans="7:7" ht="17" x14ac:dyDescent="0.2">
       <c r="G290" s="4" t="s">
         <v>653</v>
       </c>
@@ -16873,7 +16891,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:J284" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J94">
       <sortCondition ref="B2:B94"/>
       <sortCondition ref="A2:A94"/>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{EF40342B-566E-1949-AA4E-B1367BA65FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E66536E1-A331-5744-8AAC-B61DA3273BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35840" yWindow="5380" windowWidth="36000" windowHeight="23380" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51200" yWindow="5380" windowWidth="36000" windowHeight="23380" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -17426,7 +17426,7 @@
     <sortCondition ref="D2:D294"/>
     <sortCondition ref="C2:C294"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A156 C1:C156 A164:A210 C167:C210 C297:C1048576 A289:A1048576">
+  <conditionalFormatting sqref="A1:A156 C1:C156 A164:A210 C167:C210 A289:A1048576 C297:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D6021A39-AA2B-D54C-81F9-AC0F6A649CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{DBE2E72B-9CB5-554F-A670-0EC4B6339A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11080" yWindow="4000" windowWidth="36000" windowHeight="23380" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$307</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3654" uniqueCount="748">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="3835" uniqueCount="771">
   <si>
     <t>reviewer</t>
   </si>
@@ -1379,9 +1379,6 @@
     <t>Requires: [...] 340 [...] This BIP supports two modes:  [...] Both modes produce valid BIP340 signatures. [...] The delegator learns neither the message, the challenge, or the public key used in the BIP340 signature, only a blinded challenge e'.  This blind‑signing protocol specifies how a delegator can produce a blind partial Schnorr signature that a delegatee can unblind into a standard BIP340 signature under a possibly tweaked X‑only public key.</t>
   </si>
   <si>
-    <t xml:space="preserve">The notation, algorithmic patterns, and test‑vector style are adapted from [BIP‑327] </t>
-  </si>
-  <si>
     <t>The transport that carries this bundle is out of scope for this proposal; implementers MAY use PSBT proprietary keys [...] The transport that carries this bundle is out of scope for this proposal; implementers MAY use PSBT proprietary keys, [...]</t>
   </si>
   <si>
@@ -2324,6 +2321,78 @@
   </si>
   <si>
     <t>2014-07-09</t>
+  </si>
+  <si>
+    <t>Edit the BIP for language (spelling, grammar, sentence structure, etc.), markup (for reST BIPs), code style (examples should match BIP 8 &amp; 7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Proposed-Replacement: 2</t>
+  </si>
+  <si>
+    <t>Proposed-Replacement: 3</t>
+  </si>
+  <si>
+    <t>Replaces: 1</t>
+  </si>
+  <si>
+    <t>The Layer header (only for Standards Track BIPs) documents which layer of Bitcoin the BIP applies to. See BIP 123 for definitions of the various BIP layers. Activation of this BIP implies activation of BIP 123.</t>
+  </si>
+  <si>
+    <t>BIP2 adopts the layer definitions established by BIP123 and explicitly links their activation.</t>
+  </si>
+  <si>
+    <t>CCD fundamentally relies on BIP32 chain codes, extended keys, non-hardened derivation, and scalar tweaks.</t>
+  </si>
+  <si>
+    <t>BIP89's signing modes and verification algorithms produce and consume BIP340 Schnorr signatures.</t>
+  </si>
+  <si>
+    <t>The notation, algorithmic patterns, and test‑vector style are adapted from (MuSig2)</t>
+  </si>
+  <si>
+    <t>BIP327 defines 'MuSig2 for BIP340-compatible Multi-Signatures'</t>
+  </si>
+  <si>
+    <t>This document specifies an alternative to BIP9 that corrects for a number of perceived mistakes.</t>
+  </si>
+  <si>
+    <t>A soft-fork BIP strictly requires a clear miner majority expressed by blockchain voting (eg, using BIP 9). [...] BIP8 and BIP9 deployments should not share concurrent active deployment bits. Nodes that only implement BIP9 will not activate a BIP8 soft fork if hashpower threshold is not reached by timeoutheight, [...]</t>
+  </si>
+  <si>
+    <t>Softfork deployment names listed in "rules" or as keys in "vbavailable" may be prefixed by a '!' character. Without this prefix, GBT clients may assume the rule will not impact usage of the template as-is; typical examples of this would be when previously valid transactions cease to be valid, such as BIPs 16, 65, 66, 68, 112, and 113.</t>
+  </si>
+  <si>
+    <t>Due to the constraints set by BIP 34, BIP 66 and BIP 65, we only have 0x7FFFFFFB possible nVersion values available. [...] typical examples of this would be when previously valid transactions cease to be valid, such as BIPs 16, 65, 66, 68, 112, and 113.</t>
+  </si>
+  <si>
+    <t>Due to the constraints set by BIP 34, BIP 66 and BIP 65, we only have 0x7FFFFFFB possible nVersion values available.  [...] examples of this would be BIP 34 (because it modifies coinbase construction) [...]</t>
+  </si>
+  <si>
+    <t>On the other hand, when this prefix is used, it indicates a more subtle change to the block structure or generation transaction; examples of this would be BIP 34 (because it modifies coinbase construction) and 141 (since it modifies the txid hashing and adds a commitment to the generation transaction).</t>
+  </si>
+  <si>
+    <t>The template request Object is extended to include a new item [...] The template Object is also extended.</t>
+  </si>
+  <si>
+    <t>BIP8 extends the getblocktemplate request and response objects defined by BIP 22  'getblocktemplate - Fundamentals'.</t>
+  </si>
+  <si>
+    <t>Without this prefix, GBT clients may assume the rule will not impact usage of the template as-is; typical examples of this would be when previously valid transactions cease to be valid, such as BIPs 16, 65, 66, 68, 112, and 113. If a client does not understand a rule without the prefix, it may use it unmodified for mining.</t>
+  </si>
+  <si>
+    <t>BIP9 extends the getblocktemplate request and response objects defined by BIP 22  'getblocktemplate - Fundamentals'.</t>
+  </si>
+  <si>
+    <t>This approach was later reused in BIP 66 and BIP 65, which further removed nVersions 2 and 3 as valid options. As will be shown further, this is unnecessary. [...] Without this prefix, GBT clients may assume the rule will not impact usage of the template as-is; typical examples of this would be when previously valid transactions cease to be valid, such as BIPs 16, 65, 66, 68, 112, and 113. If a client does not understand a rule without the prefix, it may use it unmodified for mining.</t>
+  </si>
+  <si>
+    <t>Changelog [...] Withdrawn after Armory stopped using BIP10 and no other projects were known to implement support (see bips 125).</t>
+  </si>
+  <si>
+    <t>A solution is for nodes to sync their mempools to each other at startup, however, this requires a memory pool expiry policy to be implemented as currently node restarts are the only way for unconfirmed transactions to be evicted from the system.</t>
+  </si>
+  <si>
+    <t>BIP35 defines the mempool message and explicitly identifies restoring miners' unconfirmed transactions after a restart as a use case.</t>
   </si>
 </sst>
 </file>
@@ -2842,7 +2911,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2876,6 +2945,9 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3283,6 +3355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q136"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3358,18 +3431,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G2" s="7">
         <v>42</v>
@@ -3384,33 +3463,39 @@
         <v>276</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>685</v>
       </c>
       <c r="P2" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
       </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G3" s="7">
         <v>42</v>
@@ -3425,16 +3510,16 @@
         <v>276</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P3" s="7">
         <v>4</v>
@@ -3447,11 +3532,17 @@
       <c r="B4" s="3">
         <v>8</v>
       </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G4" s="7">
         <v>42</v>
@@ -3466,16 +3557,16 @@
         <v>276</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M4" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>690</v>
       </c>
       <c r="P4" s="7">
         <v>8</v>
@@ -3488,11 +3579,17 @@
       <c r="B5" s="3">
         <v>9</v>
       </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G5" s="7">
         <v>42</v>
@@ -3507,16 +3604,16 @@
         <v>276</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="P5" s="7">
         <v>9</v>
@@ -3529,11 +3626,17 @@
       <c r="B6" s="3">
         <v>10</v>
       </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G6" s="7">
         <v>42</v>
@@ -3548,25 +3651,25 @@
         <v>276</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="P6" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>210</v>
       </c>
@@ -3583,7 +3686,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G7" s="7">
         <v>42</v>
@@ -3598,7 +3701,7 @@
         <v>276</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>211</v>
@@ -3613,7 +3716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>207</v>
       </c>
@@ -3663,7 +3766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>207</v>
       </c>
@@ -3713,7 +3816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>207</v>
       </c>
@@ -3763,7 +3866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>207</v>
       </c>
@@ -3813,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>207</v>
       </c>
@@ -3830,7 +3933,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G12" s="7">
         <v>43</v>
@@ -3845,7 +3948,7 @@
         <v>276</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>23</v>
@@ -3857,13 +3960,13 @@
         <v>40</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P12" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>207</v>
       </c>
@@ -3880,7 +3983,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G13" s="7">
         <v>42</v>
@@ -3913,7 +4016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>207</v>
       </c>
@@ -3963,7 +4066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>207</v>
       </c>
@@ -4013,7 +4116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>207</v>
       </c>
@@ -4063,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>207</v>
       </c>
@@ -4113,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>207</v>
       </c>
@@ -4163,7 +4266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>210</v>
       </c>
@@ -4180,7 +4283,7 @@
         <v>17</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G19" s="7">
         <v>42</v>
@@ -4195,7 +4298,7 @@
         <v>276</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>211</v>
@@ -4210,7 +4313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>207</v>
       </c>
@@ -4260,7 +4363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>207</v>
       </c>
@@ -4310,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>207</v>
       </c>
@@ -4360,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>207</v>
       </c>
@@ -4377,7 +4480,7 @@
         <v>17</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G23" s="7">
         <v>42</v>
@@ -4417,11 +4520,17 @@
       <c r="B24" s="3">
         <v>32</v>
       </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E24" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G24" s="7">
         <v>42</v>
@@ -4436,25 +4545,25 @@
         <v>276</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P24" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>207</v>
       </c>
@@ -4504,7 +4613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>207</v>
       </c>
@@ -4554,7 +4663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>207</v>
       </c>
@@ -4604,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>207</v>
       </c>
@@ -4621,7 +4730,7 @@
         <v>17</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G28" s="7">
         <v>43</v>
@@ -4636,7 +4745,7 @@
         <v>276</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>23</v>
@@ -4648,13 +4757,13 @@
         <v>30</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P28" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>207</v>
       </c>
@@ -4704,7 +4813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>207</v>
       </c>
@@ -4721,7 +4830,7 @@
         <v>17</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G30" s="7">
         <v>42</v>
@@ -4754,7 +4863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>210</v>
       </c>
@@ -4771,7 +4880,7 @@
         <v>17</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G31" s="7">
         <v>42</v>
@@ -4786,7 +4895,7 @@
         <v>276</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>211</v>
@@ -4801,7 +4910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>207</v>
       </c>
@@ -4851,7 +4960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>207</v>
       </c>
@@ -4868,7 +4977,7 @@
         <v>17</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G33" s="7">
         <v>42</v>
@@ -4901,7 +5010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>207</v>
       </c>
@@ -4951,7 +5060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>210</v>
       </c>
@@ -4968,7 +5077,7 @@
         <v>17</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G35" s="7">
         <v>42</v>
@@ -4983,7 +5092,7 @@
         <v>276</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>216</v>
@@ -4998,7 +5107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>207</v>
       </c>
@@ -5048,7 +5157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>207</v>
       </c>
@@ -5105,11 +5214,17 @@
       <c r="B38" s="3">
         <v>50</v>
       </c>
+      <c r="C38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E38" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G38" s="7">
         <v>42</v>
@@ -5124,22 +5239,22 @@
         <v>276</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="P38" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>207</v>
       </c>
@@ -5189,7 +5304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>207</v>
       </c>
@@ -5239,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>207</v>
       </c>
@@ -5289,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>207</v>
       </c>
@@ -5339,7 +5454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>207</v>
       </c>
@@ -5389,7 +5504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>207</v>
       </c>
@@ -5446,11 +5561,14 @@
       <c r="B45" s="3">
         <v>69</v>
       </c>
+      <c r="D45" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E45" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G45" s="7">
         <v>42</v>
@@ -5465,25 +5583,25 @@
         <v>276</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="P45" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>207</v>
       </c>
@@ -5533,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>207</v>
       </c>
@@ -5583,7 +5701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>207</v>
       </c>
@@ -5633,7 +5751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>207</v>
       </c>
@@ -5650,7 +5768,7 @@
         <v>17</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G49" s="7">
         <v>42</v>
@@ -5683,7 +5801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>207</v>
       </c>
@@ -5700,7 +5818,7 @@
         <v>17</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G50" s="7">
         <v>42</v>
@@ -5740,11 +5858,14 @@
       <c r="B51" s="3">
         <v>81</v>
       </c>
+      <c r="D51" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E51" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G51" s="7">
         <v>42</v>
@@ -5759,16 +5880,16 @@
         <v>276</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P51" s="7">
         <v>4</v>
@@ -5781,11 +5902,14 @@
       <c r="B52" s="3">
         <v>85</v>
       </c>
+      <c r="D52" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E52" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G52" s="7">
         <v>42</v>
@@ -5800,25 +5924,25 @@
         <v>276</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P52" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>207</v>
       </c>
@@ -5868,7 +5992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>207</v>
       </c>
@@ -5918,7 +6042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>207</v>
       </c>
@@ -5975,11 +6099,14 @@
       <c r="B56" s="3">
         <v>93</v>
       </c>
+      <c r="D56" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E56" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G56" s="7">
         <v>42</v>
@@ -5994,25 +6121,25 @@
         <v>276</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="P56" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>207</v>
       </c>
@@ -6069,11 +6196,14 @@
       <c r="B58" s="3">
         <v>99</v>
       </c>
+      <c r="D58" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E58" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G58" s="7">
         <v>42</v>
@@ -6088,22 +6218,22 @@
         <v>276</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="P58" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>207</v>
       </c>
@@ -6153,7 +6283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>207</v>
       </c>
@@ -6203,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>207</v>
       </c>
@@ -6253,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>207</v>
       </c>
@@ -6303,7 +6433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>207</v>
       </c>
@@ -6353,7 +6483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>207</v>
       </c>
@@ -6403,7 +6533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>207</v>
       </c>
@@ -6453,7 +6583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>207</v>
       </c>
@@ -6503,7 +6633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>207</v>
       </c>
@@ -6553,7 +6683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>207</v>
       </c>
@@ -6603,7 +6733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>207</v>
       </c>
@@ -6653,7 +6783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>207</v>
       </c>
@@ -6664,13 +6794,13 @@
         <v>15</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G70" s="7">
         <v>42</v>
@@ -6697,13 +6827,13 @@
         <v>25</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P70" s="7">
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>207</v>
       </c>
@@ -6753,7 +6883,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>207</v>
       </c>
@@ -6803,7 +6933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>207</v>
       </c>
@@ -6860,11 +6990,14 @@
       <c r="B74" s="3">
         <v>123</v>
       </c>
+      <c r="D74" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E74" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G74" s="7">
         <v>42</v>
@@ -6879,22 +7012,22 @@
         <v>276</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P74" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>207</v>
       </c>
@@ -6951,11 +7084,14 @@
       <c r="B76" s="3">
         <v>126</v>
       </c>
+      <c r="D76" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E76" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G76" s="7">
         <v>42</v>
@@ -6970,22 +7106,22 @@
         <v>276</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="P76" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>207</v>
       </c>
@@ -7035,7 +7171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>207</v>
       </c>
@@ -7085,7 +7221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>207</v>
       </c>
@@ -7135,7 +7271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>207</v>
       </c>
@@ -7185,7 +7321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>207</v>
       </c>
@@ -7235,7 +7371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
         <v>207</v>
       </c>
@@ -7292,11 +7428,14 @@
       <c r="B83" s="3">
         <v>136</v>
       </c>
+      <c r="D83" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E83" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G83" s="7">
         <v>42</v>
@@ -7311,25 +7450,25 @@
         <v>276</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L83" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P83" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>207</v>
       </c>
@@ -7379,7 +7518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
         <v>207</v>
       </c>
@@ -7429,7 +7568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
         <v>207</v>
       </c>
@@ -7479,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
         <v>207</v>
       </c>
@@ -7529,7 +7668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
         <v>207</v>
       </c>
@@ -7579,7 +7718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
         <v>207</v>
       </c>
@@ -7596,7 +7735,7 @@
         <v>17</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G89" s="7">
         <v>43</v>
@@ -7611,7 +7750,7 @@
         <v>276</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>23</v>
@@ -7623,13 +7762,13 @@
         <v>25</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P89" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
         <v>207</v>
       </c>
@@ -7679,7 +7818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
         <v>207</v>
       </c>
@@ -7729,7 +7868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
         <v>207</v>
       </c>
@@ -7779,7 +7918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
         <v>207</v>
       </c>
@@ -7829,7 +7968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>207</v>
       </c>
@@ -7879,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
         <v>207</v>
       </c>
@@ -7936,11 +8075,14 @@
       <c r="B96" s="3">
         <v>172</v>
       </c>
+      <c r="D96" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E96" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G96" s="7">
         <v>42</v>
@@ -7955,19 +8097,19 @@
         <v>276</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M96" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="P96" s="7">
         <v>2</v>
@@ -7980,11 +8122,14 @@
       <c r="B97" s="3">
         <v>173</v>
       </c>
+      <c r="D97" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E97" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G97" s="7">
         <v>42</v>
@@ -7999,25 +8144,25 @@
         <v>276</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="L97" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P97" s="7">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>207</v>
       </c>
@@ -8074,11 +8219,14 @@
       <c r="B99" s="3">
         <v>175</v>
       </c>
+      <c r="D99" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E99" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G99" s="7">
         <v>42</v>
@@ -8093,19 +8241,19 @@
         <v>276</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M99" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P99" s="7">
         <v>3</v>
@@ -8118,11 +8266,14 @@
       <c r="B100" s="3">
         <v>176</v>
       </c>
+      <c r="D100" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E100" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G100" s="7">
         <v>42</v>
@@ -8137,16 +8288,16 @@
         <v>276</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="L100" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P100" s="7">
         <v>0</v>
@@ -8159,11 +8310,14 @@
       <c r="B101" s="3">
         <v>177</v>
       </c>
+      <c r="D101" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E101" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G101" s="7">
         <v>42</v>
@@ -8178,16 +8332,16 @@
         <v>276</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M101" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="P101" s="7">
         <v>1</v>
@@ -8200,11 +8354,14 @@
       <c r="B102" s="3">
         <v>179</v>
       </c>
+      <c r="D102" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E102" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G102" s="7">
         <v>42</v>
@@ -8219,22 +8376,22 @@
         <v>276</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L102" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M102" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="P102" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
         <v>207</v>
       </c>
@@ -8284,7 +8441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
         <v>207</v>
       </c>
@@ -8334,7 +8491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>207</v>
       </c>
@@ -8384,7 +8541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>207</v>
       </c>
@@ -8441,11 +8598,14 @@
       <c r="B107" s="3">
         <v>310</v>
       </c>
+      <c r="D107" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E107" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G107" s="7">
         <v>42</v>
@@ -8460,25 +8620,25 @@
         <v>276</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L107" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M107" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P107" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>207</v>
       </c>
@@ -8525,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>207</v>
       </c>
@@ -8542,7 +8702,7 @@
         <v>17</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G109" s="7">
         <v>42</v>
@@ -8575,7 +8735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>207</v>
       </c>
@@ -8622,7 +8782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
         <v>207</v>
       </c>
@@ -8639,7 +8799,7 @@
         <v>17</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G111" s="7">
         <v>42</v>
@@ -8679,11 +8839,14 @@
       <c r="B112" s="3">
         <v>326</v>
       </c>
+      <c r="D112" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E112" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G112" s="7">
         <v>42</v>
@@ -8698,19 +8861,19 @@
         <v>276</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L112" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="P112" s="7">
         <v>3</v>
@@ -8723,11 +8886,14 @@
       <c r="B113" s="3">
         <v>328</v>
       </c>
+      <c r="D113" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E113" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G113" s="7">
         <v>42</v>
@@ -8742,25 +8908,25 @@
         <v>276</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L113" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P113" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
         <v>207</v>
       </c>
@@ -8810,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
         <v>207</v>
       </c>
@@ -8860,7 +9026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
         <v>207</v>
       </c>
@@ -8910,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
         <v>207</v>
       </c>
@@ -8960,7 +9126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
         <v>207</v>
       </c>
@@ -9010,7 +9176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
         <v>207</v>
       </c>
@@ -9067,11 +9233,14 @@
       <c r="B120" s="3">
         <v>351</v>
       </c>
+      <c r="D120" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E120" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G120" s="7">
         <v>42</v>
@@ -9086,25 +9255,25 @@
         <v>276</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P120" s="7">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>207</v>
       </c>
@@ -9161,11 +9330,14 @@
       <c r="B122" s="3">
         <v>361</v>
       </c>
+      <c r="D122" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E122" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G122" s="7">
         <v>42</v>
@@ -9180,25 +9352,25 @@
         <v>276</v>
       </c>
       <c r="K122" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L122" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M122" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N122" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P122" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>207</v>
       </c>
@@ -9248,7 +9420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
         <v>207</v>
       </c>
@@ -9298,7 +9470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
         <v>207</v>
       </c>
@@ -9348,7 +9520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
         <v>207</v>
       </c>
@@ -9405,11 +9577,14 @@
       <c r="B127" s="3">
         <v>381</v>
       </c>
+      <c r="D127" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E127" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G127" s="7">
         <v>42</v>
@@ -9424,19 +9599,19 @@
         <v>276</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L127" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M127" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N127" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P127" s="7">
         <v>3</v>
@@ -9449,11 +9624,14 @@
       <c r="B128" s="3">
         <v>383</v>
       </c>
+      <c r="D128" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E128" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G128" s="7">
         <v>42</v>
@@ -9468,19 +9646,19 @@
         <v>276</v>
       </c>
       <c r="K128" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L128" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N128" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P128" s="7">
         <v>4</v>
@@ -9493,11 +9671,14 @@
       <c r="B129" s="3">
         <v>385</v>
       </c>
+      <c r="D129" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E129" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G129" s="7">
         <v>42</v>
@@ -9512,19 +9693,19 @@
         <v>276</v>
       </c>
       <c r="K129" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L129" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M129" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="P129" s="7">
         <v>1</v>
@@ -9537,11 +9718,14 @@
       <c r="B130" s="3">
         <v>387</v>
       </c>
+      <c r="D130" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E130" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G130" s="7">
         <v>42</v>
@@ -9556,19 +9740,19 @@
         <v>276</v>
       </c>
       <c r="K130" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L130" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M130" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P130" s="7">
         <v>6</v>
@@ -9581,11 +9765,14 @@
       <c r="B131" s="3">
         <v>390</v>
       </c>
+      <c r="D131" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E131" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G131" s="7">
         <v>42</v>
@@ -9600,25 +9787,25 @@
         <v>276</v>
       </c>
       <c r="K131" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L131" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M131" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N131" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="P131" s="7">
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
         <v>207</v>
       </c>
@@ -9668,7 +9855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>207</v>
       </c>
@@ -9718,7 +9905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
         <v>207</v>
       </c>
@@ -9768,7 +9955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
         <v>207</v>
       </c>
@@ -9818,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
         <v>207</v>
       </c>
@@ -9870,6 +10057,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q136" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters blank="1"/>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q136">
       <sortCondition ref="B1:B136"/>
     </sortState>
@@ -9894,7 +10084,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J294"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -9941,7 +10132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>210</v>
       </c>
@@ -9973,7 +10164,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>210</v>
       </c>
@@ -10002,7 +10193,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>210</v>
       </c>
@@ -10054,7 +10245,7 @@
         <v>412</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -10202,7 +10393,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -10690,7 +10881,7 @@
         <v>2026-06-30</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>210</v>
       </c>
@@ -10719,7 +10910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>210</v>
       </c>
@@ -10748,7 +10939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>210</v>
       </c>
@@ -10777,7 +10968,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>210</v>
       </c>
@@ -10800,7 +10991,7 @@
         <v>145</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -10809,7 +11000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>210</v>
       </c>
@@ -10832,7 +11023,7 @@
         <v>145</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>15</v>
@@ -10864,7 +11055,7 @@
         <v>158</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>15</v>
@@ -10896,7 +11087,7 @@
         <v>159</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>15</v>
@@ -10986,7 +11177,7 @@
         <v>117</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>15</v>
@@ -11015,10 +11206,10 @@
         <v>35</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>15</v>
@@ -11027,7 +11218,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>210</v>
       </c>
@@ -11056,7 +11247,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>210</v>
       </c>
@@ -11085,7 +11276,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>210</v>
       </c>
@@ -11358,7 +11549,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>210</v>
       </c>
@@ -12589,7 +12780,7 @@
         <v>35</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
@@ -12620,6 +12811,9 @@
       <c r="G90" s="4" t="s">
         <v>436</v>
       </c>
+      <c r="H90" s="4" t="s">
+        <v>753</v>
+      </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
       </c>
@@ -12647,10 +12841,10 @@
         <v>141</v>
       </c>
       <c r="G91" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="H91" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
@@ -12679,7 +12873,10 @@
         <v>35</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>438</v>
+        <v>755</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>756</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
@@ -12710,6 +12907,9 @@
       <c r="G93" s="4" t="s">
         <v>437</v>
       </c>
+      <c r="H93" s="4" t="s">
+        <v>754</v>
+      </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
       </c>
@@ -12737,10 +12937,10 @@
         <v>35</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
@@ -12769,7 +12969,7 @@
         <v>35</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -12798,7 +12998,7 @@
         <v>35</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -12827,7 +13027,7 @@
         <v>35</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
@@ -12856,10 +13056,10 @@
         <v>35</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -12888,10 +13088,10 @@
         <v>35</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>15</v>
@@ -12920,10 +13120,10 @@
         <v>35</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>15</v>
@@ -12952,7 +13152,7 @@
         <v>35</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>15</v>
@@ -12981,7 +13181,7 @@
         <v>35</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>15</v>
@@ -12998,7 +13198,7 @@
         <v>98</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D103" s="3">
         <v>116</v>
@@ -13010,7 +13210,7 @@
         <v>35</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>15</v>
@@ -13039,7 +13239,7 @@
         <v>35</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>15</v>
@@ -13068,10 +13268,10 @@
         <v>141</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>15</v>
@@ -13100,10 +13300,10 @@
         <v>141</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>15</v>
@@ -13132,10 +13332,10 @@
         <v>35</v>
       </c>
       <c r="G107" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>471</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>15</v>
@@ -13164,7 +13364,7 @@
         <v>35</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>15</v>
@@ -13193,7 +13393,7 @@
         <v>35</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -13222,7 +13422,7 @@
         <v>35</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -13440,7 +13640,7 @@
         <v>173</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -13472,7 +13672,7 @@
         <v>173</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -13504,7 +13704,7 @@
         <v>173</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -13655,7 +13855,7 @@
         <v>35</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -13672,7 +13872,7 @@
         <v>116</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D125" s="3">
         <v>8</v>
@@ -13684,7 +13884,7 @@
         <v>35</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -13701,7 +13901,7 @@
         <v>116</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D126" s="3">
         <v>16</v>
@@ -13713,10 +13913,10 @@
         <v>35</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -13733,7 +13933,7 @@
         <v>116</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D127" s="3">
         <v>65</v>
@@ -13745,10 +13945,10 @@
         <v>141</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -13765,7 +13965,7 @@
         <v>116</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D128" s="3">
         <v>68</v>
@@ -13777,10 +13977,10 @@
         <v>141</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
@@ -13797,7 +13997,7 @@
         <v>116</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D129" s="3">
         <v>98</v>
@@ -13809,7 +14009,7 @@
         <v>35</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -13826,7 +14026,7 @@
         <v>116</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D130" s="3">
         <v>112</v>
@@ -13838,10 +14038,10 @@
         <v>141</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -13858,7 +14058,7 @@
         <v>116</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D131" s="3">
         <v>141</v>
@@ -13870,10 +14070,10 @@
         <v>35</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -13890,7 +14090,7 @@
         <v>116</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D132" s="3">
         <v>143</v>
@@ -13902,10 +14102,10 @@
         <v>35</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -13934,7 +14134,7 @@
         <v>35</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -13963,10 +14163,10 @@
         <v>35</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -13995,10 +14195,10 @@
         <v>35</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -14027,10 +14227,10 @@
         <v>35</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -14059,10 +14259,10 @@
         <v>35</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -14091,10 +14291,10 @@
         <v>35</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -14216,7 +14416,7 @@
         <v>180</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -14245,7 +14445,7 @@
         <v>35</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -14274,7 +14474,7 @@
         <v>35</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -14303,10 +14503,10 @@
         <v>35</v>
       </c>
       <c r="G145" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="H145" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="H145" s="4" t="s">
-        <v>487</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -14538,13 +14738,13 @@
         <v>123</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G153" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="H153" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
@@ -14570,13 +14770,13 @@
         <v>123</v>
       </c>
       <c r="F154" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="G154" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="H154" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>492</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -14605,10 +14805,10 @@
         <v>35</v>
       </c>
       <c r="G155" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="H155" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>497</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -14637,10 +14837,10 @@
         <v>35</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -14669,10 +14869,10 @@
         <v>35</v>
       </c>
       <c r="G157" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="H157" s="4" t="s">
         <v>493</v>
-      </c>
-      <c r="H157" s="4" t="s">
-        <v>494</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -14701,7 +14901,7 @@
         <v>35</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -14730,10 +14930,10 @@
         <v>35</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -14762,10 +14962,10 @@
         <v>35</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H160" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I160" s="3" t="s">
         <v>15</v>
@@ -14794,10 +14994,10 @@
         <v>20</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H161" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>15</v>
@@ -14826,10 +15026,10 @@
         <v>141</v>
       </c>
       <c r="G162" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="H162" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="H162" s="4" t="s">
-        <v>510</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>15</v>
@@ -14858,7 +15058,7 @@
         <v>20</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I163" s="3" t="s">
         <v>15</v>
@@ -14887,10 +15087,10 @@
         <v>35</v>
       </c>
       <c r="G164" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="H164" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>15</v>
@@ -14919,10 +15119,10 @@
         <v>35</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H165" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I165" s="3" t="s">
         <v>15</v>
@@ -14951,10 +15151,10 @@
         <v>35</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>15</v>
@@ -14983,10 +15183,10 @@
         <v>141</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>15</v>
@@ -15015,10 +15215,10 @@
         <v>20</v>
       </c>
       <c r="G168" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="H168" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="H168" s="4" t="s">
-        <v>506</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>15</v>
@@ -15236,10 +15436,10 @@
         <v>35</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>15</v>
@@ -15268,10 +15468,10 @@
         <v>35</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>15</v>
@@ -15361,10 +15561,10 @@
         <v>141</v>
       </c>
       <c r="G179" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="H179" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="H179" s="4" t="s">
-        <v>644</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>15</v>
@@ -15396,7 +15596,7 @@
         <v>200</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
@@ -15425,7 +15625,7 @@
         <v>35</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
@@ -15454,10 +15654,10 @@
         <v>35</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H182" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>15</v>
@@ -15486,10 +15686,10 @@
         <v>35</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>15</v>
@@ -15518,10 +15718,10 @@
         <v>35</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>15</v>
@@ -15550,10 +15750,10 @@
         <v>35</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>15</v>
@@ -15582,7 +15782,7 @@
         <v>35</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>15</v>
@@ -15611,10 +15811,10 @@
         <v>35</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>15</v>
@@ -15643,10 +15843,10 @@
         <v>35</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H188" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I188" s="3" t="s">
         <v>15</v>
@@ -15675,10 +15875,10 @@
         <v>35</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I189" s="3" t="s">
         <v>15</v>
@@ -15707,10 +15907,10 @@
         <v>35</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H190" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I190" s="3" t="s">
         <v>15</v>
@@ -15739,10 +15939,10 @@
         <v>35</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>15</v>
@@ -15771,10 +15971,10 @@
         <v>35</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H192" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>15</v>
@@ -15803,10 +16003,10 @@
         <v>35</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H193" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>15</v>
@@ -15835,10 +16035,10 @@
         <v>35</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>15</v>
@@ -15867,10 +16067,10 @@
         <v>35</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>15</v>
@@ -15899,10 +16099,10 @@
         <v>35</v>
       </c>
       <c r="G196" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="H196" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="H196" s="4" t="s">
-        <v>538</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>15</v>
@@ -16018,10 +16218,10 @@
         <v>141</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>15</v>
@@ -16050,7 +16250,7 @@
         <v>35</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>15</v>
@@ -16079,10 +16279,10 @@
         <v>141</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>15</v>
@@ -16111,10 +16311,10 @@
         <v>35</v>
       </c>
       <c r="G203" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="H203" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="H203" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>15</v>
@@ -16143,10 +16343,10 @@
         <v>35</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I204" s="3" t="s">
         <v>15</v>
@@ -16175,10 +16375,10 @@
         <v>141</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H205" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>15</v>
@@ -16207,10 +16407,10 @@
         <v>20</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>15</v>
@@ -16268,10 +16468,10 @@
         <v>35</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>15</v>
@@ -16300,10 +16500,10 @@
         <v>141</v>
       </c>
       <c r="G209" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="H209" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="H209" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>15</v>
@@ -16332,10 +16532,10 @@
         <v>141</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>15</v>
@@ -16364,10 +16564,10 @@
         <v>35</v>
       </c>
       <c r="G211" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H211" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="H211" s="4" t="s">
-        <v>557</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>15</v>
@@ -16396,10 +16596,10 @@
         <v>20</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>15</v>
@@ -16631,10 +16831,10 @@
         <v>35</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I220" s="3" t="s">
         <v>15</v>
@@ -16663,10 +16863,10 @@
         <v>35</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I221" s="3" t="s">
         <v>15</v>
@@ -16695,10 +16895,10 @@
         <v>35</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I222" s="3" t="s">
         <v>15</v>
@@ -16994,10 +17194,10 @@
         <v>141</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I232" s="3" t="s">
         <v>15</v>
@@ -17026,10 +17226,10 @@
         <v>35</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="I233" s="3" t="s">
         <v>15</v>
@@ -17058,10 +17258,10 @@
         <v>141</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="I234" s="3" t="s">
         <v>15</v>
@@ -17090,10 +17290,10 @@
         <v>141</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H235" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I235" s="3" t="s">
         <v>15</v>
@@ -17122,10 +17322,10 @@
         <v>35</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="I236" s="3" t="s">
         <v>15</v>
@@ -17154,7 +17354,7 @@
         <v>35</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I237" s="3" t="s">
         <v>15</v>
@@ -17183,10 +17383,10 @@
         <v>35</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I238" s="3" t="s">
         <v>15</v>
@@ -17215,10 +17415,10 @@
         <v>35</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H239" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="I239" s="3" t="s">
         <v>15</v>
@@ -17247,10 +17447,10 @@
         <v>35</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I240" s="3" t="s">
         <v>15</v>
@@ -17279,10 +17479,10 @@
         <v>35</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H241" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I241" s="3" t="s">
         <v>15</v>
@@ -17311,10 +17511,10 @@
         <v>35</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="I242" s="3" t="s">
         <v>15</v>
@@ -17343,10 +17543,10 @@
         <v>35</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H243" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I243" s="3" t="s">
         <v>15</v>
@@ -17375,10 +17575,10 @@
         <v>35</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I244" s="3" t="s">
         <v>15</v>
@@ -17407,10 +17607,10 @@
         <v>35</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H245" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="I245" s="3" t="s">
         <v>15</v>
@@ -17439,10 +17639,10 @@
         <v>35</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I246" s="3" t="s">
         <v>15</v>
@@ -17471,7 +17671,7 @@
         <v>35</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I247" s="3" t="s">
         <v>15</v>
@@ -17500,7 +17700,7 @@
         <v>35</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I248" s="3" t="s">
         <v>15</v>
@@ -17529,10 +17729,10 @@
         <v>35</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="I249" s="3" t="s">
         <v>15</v>
@@ -17561,10 +17761,10 @@
         <v>35</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I250" s="3" t="s">
         <v>15</v>
@@ -17593,10 +17793,10 @@
         <v>35</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H251" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="I251" s="3" t="s">
         <v>15</v>
@@ -17625,10 +17825,10 @@
         <v>35</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I252" s="3" t="s">
         <v>15</v>
@@ -17872,7 +18072,7 @@
         <v>35</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I260" s="3" t="s">
         <v>15</v>
@@ -17901,7 +18101,7 @@
         <v>35</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I261" s="3" t="s">
         <v>15</v>
@@ -17930,10 +18130,10 @@
         <v>35</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I262" s="3" t="s">
         <v>15</v>
@@ -17962,10 +18162,10 @@
         <v>35</v>
       </c>
       <c r="G263" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="H263" s="4" t="s">
         <v>598</v>
-      </c>
-      <c r="H263" s="4" t="s">
-        <v>599</v>
       </c>
       <c r="I263" s="3" t="s">
         <v>15</v>
@@ -17994,10 +18194,10 @@
         <v>35</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="I264" s="3" t="s">
         <v>15</v>
@@ -18026,10 +18226,10 @@
         <v>35</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="I265" s="3" t="s">
         <v>15</v>
@@ -18058,10 +18258,10 @@
         <v>35</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="I266" s="3" t="s">
         <v>15</v>
@@ -18090,10 +18290,10 @@
         <v>35</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="I267" s="3" t="s">
         <v>15</v>
@@ -18122,10 +18322,10 @@
         <v>35</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I268" s="3" t="s">
         <v>15</v>
@@ -18154,10 +18354,10 @@
         <v>35</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I269" s="3" t="s">
         <v>15</v>
@@ -18482,10 +18682,10 @@
         <v>35</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H280" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="I280" s="3" t="s">
         <v>15</v>
@@ -18514,10 +18714,10 @@
         <v>141</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H281" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I281" s="3" t="s">
         <v>15</v>
@@ -18546,10 +18746,10 @@
         <v>35</v>
       </c>
       <c r="G282" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H282" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I282" s="3" t="s">
         <v>15</v>
@@ -18578,10 +18778,10 @@
         <v>35</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H283" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I283" s="3" t="s">
         <v>15</v>
@@ -18610,10 +18810,10 @@
         <v>141</v>
       </c>
       <c r="G284" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H284" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I284" s="3" t="s">
         <v>15</v>
@@ -18642,10 +18842,10 @@
         <v>35</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H285" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I285" s="3" t="s">
         <v>15</v>
@@ -18674,10 +18874,10 @@
         <v>35</v>
       </c>
       <c r="G286" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H286" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I286" s="3" t="s">
         <v>15</v>
@@ -18706,10 +18906,10 @@
         <v>141</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H287" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I287" s="3" t="s">
         <v>15</v>
@@ -18738,10 +18938,10 @@
         <v>35</v>
       </c>
       <c r="G288" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H288" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I288" s="3" t="s">
         <v>15</v>
@@ -18802,7 +19002,7 @@
         <v>268</v>
       </c>
       <c r="H290" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="I290" s="3" t="s">
         <v>15</v>
@@ -18924,7 +19124,7 @@
         <v>35</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I294" s="3" t="s">
         <v>15</v>
@@ -18933,8 +19133,834 @@
         <v>2026-06-30</v>
       </c>
     </row>
+    <row r="295" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A295" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B295" s="3">
+        <v>1</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D295" s="3">
+        <v>8</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G295" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J295" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A296" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B296" s="3">
+        <v>1</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D296" s="3">
+        <v>7</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J296" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A297" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B297" s="3">
+        <v>1</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D297" s="3">
+        <v>2</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J297" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A298" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B298" s="3">
+        <v>2</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D298" s="3">
+        <v>3</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J298" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A299" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B299" s="3">
+        <v>2</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D299" s="3">
+        <v>1</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G299" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J299" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A300" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B300" s="3">
+        <v>2</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D300" s="3">
+        <v>123</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J300" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A301" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B301" s="3">
+        <v>2</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D301" s="3">
+        <v>9</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G301" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J301" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A302" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B302" s="3">
+        <v>8</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D302" s="3">
+        <v>9</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G302" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J302" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A303" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B303" s="3">
+        <v>8</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D303" s="3">
+        <v>34</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G303" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J303" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A304" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B304" s="3">
+        <v>8</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D304" s="3">
+        <v>66</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J304" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A305" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B305" s="3">
+        <v>8</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D305" s="3">
+        <v>65</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G305" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J305" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A306" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B306" s="3">
+        <v>8</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D306" s="3">
+        <v>16</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G306" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J306" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A307" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B307" s="3">
+        <v>8</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D307" s="3">
+        <v>68</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G307" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J307" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A308" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B308" s="3">
+        <v>8</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D308" s="3">
+        <v>112</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J308" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A309" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B309" s="3">
+        <v>8</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D309" s="3">
+        <v>113</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G309" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J309" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A310" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B310" s="3">
+        <v>8</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D310" s="3">
+        <v>141</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G310" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J310" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A311" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B311" s="3">
+        <v>8</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D311" s="3">
+        <v>22</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J311" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A312" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B312" s="3">
+        <v>9</v>
+      </c>
+      <c r="C312" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D312" s="3">
+        <v>66</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="I312" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J312" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A313" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B313" s="3">
+        <v>9</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D313" s="3">
+        <v>65</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G313" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J313" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A314" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B314" s="3">
+        <v>9</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D314" s="3">
+        <v>34</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G314" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J314" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A315" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B315" s="3">
+        <v>9</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D315" s="3">
+        <v>141</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G315" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J315" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A316" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B316" s="3">
+        <v>9</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D316" s="3">
+        <v>16</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G316" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J316" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A317" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B317" s="3">
+        <v>9</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D317" s="3">
+        <v>68</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G317" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J317" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A318" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B318" s="3">
+        <v>9</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D318" s="3">
+        <v>112</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="I318" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J318" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A319" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B319" s="3">
+        <v>9</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D319" s="3">
+        <v>113</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G319" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J319" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A320" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B320" s="3">
+        <v>9</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D320" s="3">
+        <v>22</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="I320" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J320" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A321" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B321" s="3">
+        <v>10</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D321" s="3">
+        <v>125</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G321" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J321" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A322" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B322" s="3">
+        <v>50</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D322" s="3">
+        <v>35</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G322" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="H322" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J322" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J296" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:J307" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters blank="1">
+        <filter val="bips"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J288">
       <sortCondition ref="B2:B288"/>
       <sortCondition ref="A2:A288"/>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7C444D78-45C6-D245-BF84-F55C30E59F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6F6CBE3E-BDEC-634B-B75C-313229F329DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="620" windowWidth="51160" windowHeight="28160" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="4681" uniqueCount="922">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="4913" uniqueCount="982">
   <si>
     <t>reviewer</t>
   </si>
@@ -2846,6 +2846,188 @@
   </si>
   <si>
     <t xml:space="preserve">Let's imagine BIP66 had a crypto backdoor that nobody noticed and allows an evil developer cabal to steal everyone's coins. [...] This can't guarantee the assumption that most miners have upgraded before enforcing the new rules and that's why the voting mechanism and first used for BIP30 and BIP66. </t>
+  </si>
+  <si>
+    <t>For instance, most wallets built since its introduction in 2012 have used BIP-32 to construct deterministic HD wallets which derive Bitcoin keypairs from a seed. Any BIP-32 wallet which uses a hardened derivation step in its key-paths can thus satisfy a rescue protocol which uses BIP-32 hardened key derivation to prove knowledge of a parent XPriv which a quantum attacker would be very unlikely to know.</t>
+  </si>
+  <si>
+    <t>BIP32 hardened derivation is presented as one possible foundation for a Phase-B rescue protocol, not as a mandatory component.</t>
+  </si>
+  <si>
+    <t>This proposal follows the implementation of any post-quantum (PQ) output type and introduces a pre-announced sunset of legacy ECDSA/Schnorr signatures. [...] Specification [...] What Happens [...] At a predetermined block height, nodes tighten requirements on verification of ECDSA/Schnorr.</t>
+  </si>
+  <si>
+    <t>BIP340 defines Bitcoin’s Schnorr signature scheme.</t>
+  </si>
+  <si>
+    <t>To date, no quantum related proposal provides protection against: [...] Long-range attacks against already exposed public keys in P2PK or P2TR outputs.</t>
+  </si>
+  <si>
+    <t>BIP341 defines P2TR outputs. P2PK is an original Bitcoin script template that predates the BIP process.</t>
+  </si>
+  <si>
+    <t>BIP381 extends BIP380</t>
+  </si>
+  <si>
+    <t>The pkh(KEY) expression can be used as a top level expression, or inside of either a sh() or wsh() descriptor.</t>
+  </si>
+  <si>
+    <t>BIP382 defines the wsh() descriptor in which BIP381 permits pkh() to be nested. However, this is optional interoperability.</t>
+  </si>
+  <si>
+    <t>Prior to the activation of Segregated Witness, there were 3 main standard output script formats: P2PK, P2PKH, and P2SH. These expressions allow specifying those formats as a descriptor.</t>
+  </si>
+  <si>
+    <t>BIP141’s Segregated Witness activation is mentioned only as the historical boundary distinguishing these non-Segwit script formats.</t>
+  </si>
+  <si>
+    <t>sh() descriptors take a script and produces a P2SH output script. [...] The output script produced is: OP_HASH160 &lt;SCRIPT_hash160&gt; OP_EQUAL.</t>
+  </si>
+  <si>
+    <t>BIP16 defines P2SH’s validation and spending semantics. BIP381 provides a descriptor expression that constructs the corresponding output script but does not modify those semantics.</t>
+  </si>
+  <si>
+    <t>BIP11 standardized the bare M-of-N OP_CHECKMULTISIG template and its three-key standardness limit.</t>
+  </si>
+  <si>
+    <t>Both functions take a threshold and one or more public keys and produce a multisig output script. [...] When used at the top level, there can only be at most 3 keys. [...] k KEY_1 KEY_2 ... KEY_n n OP_CHECKMULTISIG.</t>
+  </si>
+  <si>
+    <t>When used inside of a sh() expression, the output script produced is the redeem script, which is pushed as a single element in the spending scriptSig.</t>
+  </si>
+  <si>
+    <t>BIP16 defines P2SH’s validation and spending semantics in which BIP383 multisig scripts can serve as redeem scripts.</t>
+  </si>
+  <si>
+    <t>BIP32 defines the extended keys and child-key derivation supported by BIP383.</t>
+  </si>
+  <si>
+    <t>When one or more the key expressions in a multi() or sortedmulti() expression are extended keys, the derived keys use the same child index.</t>
+  </si>
+  <si>
+    <t>Requires: 380 [...] multi(), and sortedmulti() descriptors use the format and general operation specified in 380.</t>
+  </si>
+  <si>
+    <t>BIP381 defines the sh() descriptor used as an optional outer context for BIP383 multisig expressions.</t>
+  </si>
+  <si>
+    <t>BIP382 defines the wsh() descriptor used as another optional outer context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specification [...]  multi() and sortedmulti() expressions can be used as a top level expression, or inside of either a sh() or wsh() descriptor. [...] </t>
+  </si>
+  <si>
+    <t>Requires: 380 [...] Backwards Compatibility raw() and addr() descriptors use the format and general operation specified in 380. As this is a wholly new descriptor, it is not compatible with any implementation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires: 380 [...] Backwards Compatibility pk(), pkh(), and sh() descriptors use the format and general operation specified in 380. </t>
+  </si>
+  <si>
+    <t>Invalid descriptors [...] raw nested in sh [...] addr nested in sh.</t>
+  </si>
+  <si>
+    <t>Invalid descriptors [...] raw nested in wsh [...] addr nested in wsh.</t>
+  </si>
+  <si>
+    <t>BIP385 prohibits nesting its descriptors inside BIP381's sh() descriptor.</t>
+  </si>
+  <si>
+    <t>BIP385 prohibits nesting its descriptors inside BIP382's wsh() descriptor.</t>
+  </si>
+  <si>
+    <t>Requires: 380 [...] Backwards Compatibility multi_a() and sortedmulti_a() descriptors use the format and general operation specified in 380. As these are wholly new descriptors, they are not compatible with any implementation.</t>
+  </si>
+  <si>
+    <t>BIP385 extends BIP380</t>
+  </si>
+  <si>
+    <t>BIP387 extends BIP380</t>
+  </si>
+  <si>
+    <t>Unsupported sh() context: sh(multi_a(...)).</t>
+  </si>
+  <si>
+    <t>Unsupported wsh() context: wsh(multi_a(...)).</t>
+  </si>
+  <si>
+    <t>BIP387 prohibits multi_a() inside BIP381's sh().</t>
+  </si>
+  <si>
+    <t>BIP387 prohibits multi_a() inside BIP382's wsh().</t>
+  </si>
+  <si>
+    <t>Like BIP 383's multi() and sortedmulti(), both functions take a threshold and one or more public keys and produce a multisig script. The primary distinction is that multi_a() and sortedmulti_a() only produce tapscripts and are only allowed in a tapscript context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specification [...] multi_a() and sortedmulti_a() expressions can only be used inside of a tr() descriptor. </t>
+  </si>
+  <si>
+    <t>BIP386 defines the required tr() descriptor.</t>
+  </si>
+  <si>
+    <t>BIP342 defines Tapscript and OP_CHECKSIGADD.</t>
+  </si>
+  <si>
+    <t>The output script produced also depends on the value of k. If k is less than or equal to 16: KEY_1 OP_CHECKSIG KEY_2 OP_CHECKSIGADD ... KEY_n OP_CHECKSIGADD OP_k OP_NUMEQUAL
+if k is greater than 16:
+KEY_1 OP_CHECKSIG KEY_2 OP_CHECKSIGADD ... KEY_n OP_CHECKSIGADD k OP_NUMEQUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The only change for sortedmulti_a() is that the x-only public keys are sorted lexicographically prior to the creation of the output script. </t>
+  </si>
+  <si>
+    <t>BIP340 defines x-only public keys.</t>
+  </si>
+  <si>
+    <t>Multiple Extended Keys When one or more of the key expressions in a multi_a() or sortedmulti_a() expression are extended keys, the derived keys use the same child index.</t>
+  </si>
+  <si>
+    <t>BIP32 defines the optional extended keys.</t>
+  </si>
+  <si>
+    <t>This document specifies a musig() key expression for output script descriptors. musig() expressions take multiple keys and produce an aggregate public key using BIP-327. [...] BIP-327 introduces the MuSig2 Multi-Signature scheme.</t>
+  </si>
+  <si>
+    <t>Then further BIP-32 derivation will be performed on the aggregate public key as described in BIP-328.</t>
+  </si>
+  <si>
+    <t>Requires: 380, 328 [...] Specification [...] Specification A new key expression is defined: musig(). In the following sections, the term KEY refers to key expressions as defined in BIP-380 and BIP-389. [...] Backwards Compatibility musig() expressions use the format and general operation specified in BIP-380.</t>
+  </si>
+  <si>
+    <t>BIP32 is used by the optional derived musig() form.</t>
+  </si>
+  <si>
+    <t>BIP390 restricts use with BIP381 expressions.</t>
+  </si>
+  <si>
+    <t>BIP390 restricts use with BIP382 expressions.</t>
+  </si>
+  <si>
+    <t>musig() is not allowed in combo().</t>
+  </si>
+  <si>
+    <t>BIP390 prohibits use inside BIP384’s combo().</t>
+  </si>
+  <si>
+    <t>KEY refers to key expressions as defined in BIP-380 and BIP-389.</t>
+  </si>
+  <si>
+    <t>The musig(KEY, KEY, ..., KEY) expression can only be used inside of a tr(), rawtr() or sp() expression as a key expression.</t>
+  </si>
+  <si>
+    <t>BIP386 defines tr().</t>
+  </si>
+  <si>
+    <t>BIP390 incorporates BIP389 multipath descriptor key expressions.</t>
+  </si>
+  <si>
+    <t>Requires: 380, 328 [...] Specification [...] A new key expression is defined: musig(). [...] Then further BIP-32 derivation will be performed on the aggregate public key as described in BIP-328.</t>
+  </si>
+  <si>
+    <t>musig() is not allowed in top-level pk() [...] pkh() [...] sh().</t>
+  </si>
+  <si>
+    <t>musig() is not allowed in wpkh() [...] wsh().</t>
   </si>
 </sst>
 </file>
@@ -9836,6 +10018,12 @@
       <c r="B122" s="3">
         <v>361</v>
       </c>
+      <c r="C122" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E122" s="7" t="s">
         <v>17</v>
       </c>
@@ -10080,6 +10268,12 @@
       <c r="B127" s="3">
         <v>381</v>
       </c>
+      <c r="C127" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E127" s="7" t="s">
         <v>17</v>
       </c>
@@ -10124,6 +10318,12 @@
       <c r="B128" s="3">
         <v>383</v>
       </c>
+      <c r="C128" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E128" s="7" t="s">
         <v>17</v>
       </c>
@@ -10168,6 +10368,12 @@
       <c r="B129" s="3">
         <v>385</v>
       </c>
+      <c r="C129" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E129" s="7" t="s">
         <v>17</v>
       </c>
@@ -10212,6 +10418,12 @@
       <c r="B130" s="3">
         <v>387</v>
       </c>
+      <c r="C130" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
       <c r="E130" s="7" t="s">
         <v>17</v>
       </c>
@@ -10255,6 +10467,12 @@
       </c>
       <c r="B131" s="3">
         <v>390</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="8" t="d">
+        <v>2026-08-07</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>17</v>
@@ -10569,7 +10787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J457"/>
+  <dimension ref="A1:J490"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -23326,108 +23544,114 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="423" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A423" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B423" s="3">
+        <v>361</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D423" s="3">
+        <v>32</v>
+      </c>
+      <c r="E423" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F423" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="I423" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J423" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A424" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B424" s="3">
+        <v>361</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D424" s="3">
+        <v>340</v>
+      </c>
+      <c r="E424" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F424" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="H424" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="I424" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J424" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A425" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B425" s="3">
+        <v>361</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D425" s="3">
+        <v>341</v>
+      </c>
+      <c r="E425" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F425" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G425" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="H425" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="I425" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J425" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+      <c r="A426" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B426" s="3">
         <v>370</v>
       </c>
-      <c r="C423" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D423" s="3">
+      <c r="C426" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D426" s="3">
         <v>174</v>
-      </c>
-      <c r="E423" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F423" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G423" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="I423" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J423" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A424" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B424" s="3">
-        <v>371</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D424" s="3">
-        <v>32</v>
-      </c>
-      <c r="E424" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F424" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G424" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="I424" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J424" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" ht="119" x14ac:dyDescent="0.2">
-      <c r="A425" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B425" s="3">
-        <v>371</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D425" s="3">
-        <v>174</v>
-      </c>
-      <c r="E425" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F425" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G425" s="4" t="s">
-        <v>595</v>
-      </c>
-      <c r="H425" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="I425" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J425" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" ht="102" x14ac:dyDescent="0.2">
-      <c r="A426" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B426" s="3">
-        <v>371</v>
-      </c>
-      <c r="C426" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D426" s="3">
-        <v>340</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>116</v>
@@ -23436,10 +23660,7 @@
         <v>35</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="H426" s="4" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I426" s="3" t="s">
         <v>15</v>
@@ -23459,19 +23680,16 @@
         <v>207</v>
       </c>
       <c r="D427" s="3">
-        <v>341</v>
+        <v>32</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G427" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="H427" s="4" t="s">
-        <v>599</v>
+        <v>652</v>
       </c>
       <c r="I427" s="3" t="s">
         <v>15</v>
@@ -23480,7 +23698,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
         <v>207</v>
       </c>
@@ -23491,7 +23709,7 @@
         <v>207</v>
       </c>
       <c r="D428" s="3">
-        <v>342</v>
+        <v>174</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>116</v>
@@ -23500,10 +23718,10 @@
         <v>35</v>
       </c>
       <c r="G428" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H428" s="4" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="I428" s="3" t="s">
         <v>15</v>
@@ -23512,7 +23730,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="429" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
         <v>207</v>
       </c>
@@ -23523,7 +23741,7 @@
         <v>207</v>
       </c>
       <c r="D429" s="3">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>116</v>
@@ -23532,10 +23750,10 @@
         <v>35</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H429" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="I429" s="3" t="s">
         <v>15</v>
@@ -23544,18 +23762,18 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="430" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B430" s="3">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D430" s="3">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>116</v>
@@ -23564,10 +23782,10 @@
         <v>35</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="H430" s="4" t="s">
-        <v>636</v>
+        <v>599</v>
       </c>
       <c r="I430" s="3" t="s">
         <v>15</v>
@@ -23576,30 +23794,30 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A431" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B431" s="3">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D431" s="3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G431" s="4" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="H431" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="I431" s="3" t="s">
         <v>15</v>
@@ -23613,25 +23831,25 @@
         <v>207</v>
       </c>
       <c r="B432" s="3">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D432" s="3">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G432" s="4" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="H432" s="4" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="I432" s="3" t="s">
         <v>15</v>
@@ -23640,36 +23858,36 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="433" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A433" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B433" s="3">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C433" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D433" s="3">
-        <v>32</v>
+        <v>327</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G433" s="4" t="s">
-        <v>274</v>
+        <v>602</v>
       </c>
       <c r="H433" s="4" t="s">
-        <v>275</v>
+        <v>636</v>
       </c>
       <c r="I433" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J433" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="434" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -23677,60 +23895,66 @@
         <v>207</v>
       </c>
       <c r="B434" s="3">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D434" s="3">
+        <v>340</v>
+      </c>
+      <c r="E434" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F434" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G434" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="H434" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="I434" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J434" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A435" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B435" s="3">
+        <v>374</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D435" s="3">
         <v>352</v>
       </c>
-      <c r="E434" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F434" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G434" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I434" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J434" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A435" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B435" s="3">
-        <v>375</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D435" s="3">
-        <v>370</v>
-      </c>
       <c r="E435" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>256</v>
+        <v>601</v>
+      </c>
+      <c r="H435" s="4" t="s">
+        <v>604</v>
       </c>
       <c r="I435" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J435" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A436" s="3" t="s">
         <v>207</v>
       </c>
@@ -23741,16 +23965,19 @@
         <v>207</v>
       </c>
       <c r="D436" s="3">
-        <v>374</v>
+        <v>32</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G436" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
+      </c>
+      <c r="H436" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="I436" s="3" t="s">
         <v>15</v>
@@ -23764,13 +23991,13 @@
         <v>207</v>
       </c>
       <c r="B437" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C437" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D437" s="3">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>116</v>
@@ -23779,7 +24006,7 @@
         <v>35</v>
       </c>
       <c r="G437" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I437" s="3" t="s">
         <v>15</v>
@@ -23788,18 +24015,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="438" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A438" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B438" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D438" s="3">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>116</v>
@@ -23808,10 +24035,7 @@
         <v>35</v>
       </c>
       <c r="G438" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H438" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I438" s="3" t="s">
         <v>15</v>
@@ -23820,18 +24044,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="439" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B439" s="3">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D439" s="3">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="E439" s="3" t="s">
         <v>116</v>
@@ -23840,7 +24064,7 @@
         <v>35</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="I439" s="3" t="s">
         <v>15</v>
@@ -23854,71 +24078,77 @@
         <v>207</v>
       </c>
       <c r="B440" s="3">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D440" s="3">
+        <v>16</v>
+      </c>
+      <c r="E440" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F440" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G440" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="H440" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="I440" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J440" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="441" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A441" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B441" s="3">
+        <v>381</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D441" s="3">
+        <v>141</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F441" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G441" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="H441" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="I441" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J441" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A442" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B442" s="3">
+        <v>381</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D442" s="3">
         <v>380</v>
-      </c>
-      <c r="E440" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F440" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G440" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="I440" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J440" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="441" spans="1:10" ht="69" x14ac:dyDescent="0.2">
-      <c r="A441" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B441" s="3">
-        <v>392</v>
-      </c>
-      <c r="C441" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D441" s="3">
-        <v>390</v>
-      </c>
-      <c r="E441" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F441" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G441" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I441" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J441" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A442" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B442" s="3">
-        <v>440</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D442" s="3">
-        <v>342</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>116</v>
@@ -23927,59 +24157,62 @@
         <v>35</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>263</v>
+        <v>946</v>
+      </c>
+      <c r="H442" s="4" t="s">
+        <v>928</v>
       </c>
       <c r="I442" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J442" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="443" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B443" s="3">
-        <v>442</v>
+        <v>381</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D443" s="3">
-        <v>119</v>
+        <v>382</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F443" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>613</v>
+        <v>929</v>
       </c>
       <c r="H443" s="4" t="s">
-        <v>637</v>
+        <v>930</v>
       </c>
       <c r="I443" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J443" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="444" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="444" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A444" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B444" s="3">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="C444" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D444" s="3">
-        <v>327</v>
+        <v>11</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>123</v>
@@ -23988,341 +24221,341 @@
         <v>141</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>611</v>
+        <v>936</v>
       </c>
       <c r="H444" s="4" t="s">
-        <v>660</v>
+        <v>935</v>
       </c>
       <c r="I444" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J444" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="445" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="445" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B445" s="3">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="C445" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D445" s="3">
+        <v>16</v>
+      </c>
+      <c r="E445" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G445" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="H445" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="I445" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J445" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="446" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A446" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B446" s="3">
+        <v>383</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D446" s="3">
+        <v>32</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F446" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G446" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="H446" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="I446" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J446" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="447" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A447" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B447" s="3">
+        <v>383</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D447" s="3">
+        <v>380</v>
+      </c>
+      <c r="E447" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F447" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G447" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="I447" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J447" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="448" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A448" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B448" s="3">
+        <v>383</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D448" s="3">
+        <v>381</v>
+      </c>
+      <c r="E448" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F448" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G448" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="H448" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="I448" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J448" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A449" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B449" s="3">
+        <v>383</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D449" s="3">
+        <v>382</v>
+      </c>
+      <c r="E449" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F449" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G449" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="I449" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J449" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A450" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B450" s="3">
+        <v>385</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D450" s="3">
+        <v>380</v>
+      </c>
+      <c r="E450" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F450" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G450" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="H450" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I450" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J450" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A451" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B451" s="3">
+        <v>385</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D451" s="3">
+        <v>381</v>
+      </c>
+      <c r="E451" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F451" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G451" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H451" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="I451" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J451" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A452" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B452" s="3">
+        <v>385</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D452" s="3">
+        <v>382</v>
+      </c>
+      <c r="E452" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F452" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G452" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="H452" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="I452" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J452" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A453" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B453" s="3">
+        <v>387</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D453" s="3">
+        <v>32</v>
+      </c>
+      <c r="E453" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F453" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G453" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="H453" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="I453" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J453" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A454" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B454" s="3">
+        <v>387</v>
+      </c>
+      <c r="C454" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D454" s="3">
         <v>340</v>
       </c>
-      <c r="E445" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F445" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G445" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="H445" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="I445" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J445" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="446" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A446" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B446" s="3">
-        <v>442</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D446" s="3">
-        <v>342</v>
-      </c>
-      <c r="E446" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F446" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G446" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="H446" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="I446" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J446" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="447" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A447" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B447" s="3">
-        <v>442</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D447" s="3">
-        <v>347</v>
-      </c>
-      <c r="E447" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F447" s="3" t="s">
+      <c r="E454" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F454" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G447" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="H447" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="I447" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J447" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="448" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A448" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B448" s="3">
-        <v>442</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D448" s="3">
-        <v>348</v>
-      </c>
-      <c r="E448" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F448" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G448" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="H448" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="I448" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J448" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A449" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B449" s="3">
-        <v>442</v>
-      </c>
-      <c r="C449" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D449" s="3">
-        <v>349</v>
-      </c>
-      <c r="E449" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F449" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G449" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="H449" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="I449" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J449" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="450" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A450" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B450" s="3">
-        <v>442</v>
-      </c>
-      <c r="C450" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D450" s="3">
-        <v>443</v>
-      </c>
-      <c r="E450" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F450" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G450" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="H450" s="4" t="s">
-        <v>619</v>
-      </c>
-      <c r="I450" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J450" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="451" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A451" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B451" s="3">
-        <v>442</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D451" s="3">
-        <v>446</v>
-      </c>
-      <c r="E451" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F451" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G451" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="H451" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="I451" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J451" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A452" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B452" s="3">
-        <v>443</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D452" s="3">
-        <v>119</v>
-      </c>
-      <c r="E452" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F452" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G452" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="I452" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J452" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A453" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B453" s="3">
-        <v>443</v>
-      </c>
-      <c r="C453" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D453" s="3">
-        <v>327</v>
-      </c>
-      <c r="E453" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F453" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G453" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="H453" s="4" t="s">
-        <v>659</v>
-      </c>
-      <c r="I453" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J453" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="454" spans="1:10" ht="51" x14ac:dyDescent="0.2">
-      <c r="A454" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B454" s="3">
-        <v>443</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D454" s="3">
-        <v>341</v>
-      </c>
-      <c r="E454" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F454" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G454" s="4" t="s">
-        <v>265</v>
+        <v>963</v>
       </c>
       <c r="H454" s="4" t="s">
-        <v>269</v>
+        <v>964</v>
       </c>
       <c r="I454" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J454" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="455" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="455" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A455" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B455" s="3">
-        <v>443</v>
+        <v>387</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>207</v>
@@ -24337,73 +24570,1099 @@
         <v>35</v>
       </c>
       <c r="G455" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="H455" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="I455" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J455" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A456" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B456" s="3">
+        <v>387</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D456" s="3">
+        <v>380</v>
+      </c>
+      <c r="E456" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F456" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G456" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="H456" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="I456" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J456" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A457" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B457" s="3">
+        <v>387</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D457" s="3">
+        <v>381</v>
+      </c>
+      <c r="E457" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F457" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G457" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="H457" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="I457" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J457" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A458" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B458" s="3">
+        <v>387</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D458" s="3">
+        <v>382</v>
+      </c>
+      <c r="E458" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F458" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G458" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="H458" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="I458" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J458" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A459" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B459" s="3">
+        <v>387</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D459" s="3">
+        <v>383</v>
+      </c>
+      <c r="E459" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F459" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G459" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="I459" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J459" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A460" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B460" s="3">
+        <v>387</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D460" s="3">
+        <v>386</v>
+      </c>
+      <c r="E460" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F460" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="H460" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="I460" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J460" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A461" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B461" s="3">
+        <v>390</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D461" s="3">
+        <v>32</v>
+      </c>
+      <c r="E461" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F461" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="H461" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="I461" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J461" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="462" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A462" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B462" s="3">
+        <v>390</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D462" s="3">
+        <v>327</v>
+      </c>
+      <c r="E462" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F462" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="I462" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J462" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="463" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A463" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B463" s="3">
+        <v>390</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D463" s="3">
+        <v>328</v>
+      </c>
+      <c r="E463" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F463" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="I463" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J463" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="464" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A464" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B464" s="3">
+        <v>390</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D464" s="3">
+        <v>380</v>
+      </c>
+      <c r="E464" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F464" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G464" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="I464" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J464" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A465" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B465" s="3">
+        <v>390</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D465" s="3">
+        <v>381</v>
+      </c>
+      <c r="E465" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F465" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G465" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H465" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="I465" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J465" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A466" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B466" s="3">
+        <v>390</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D466" s="3">
+        <v>382</v>
+      </c>
+      <c r="E466" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F466" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G466" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="H466" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="I466" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J466" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A467" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B467" s="3">
+        <v>390</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D467" s="3">
+        <v>384</v>
+      </c>
+      <c r="E467" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F467" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H467" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="I467" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J467" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A468" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B468" s="3">
+        <v>390</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D468" s="3">
+        <v>386</v>
+      </c>
+      <c r="E468" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F468" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G468" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="H468" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="I468" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J468" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A469" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B469" s="3">
+        <v>390</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D469" s="3">
+        <v>389</v>
+      </c>
+      <c r="E469" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F469" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G469" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="H469" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="I469" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J469" s="8" t="d">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A470" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B470" s="3">
+        <v>392</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D470" s="3">
+        <v>341</v>
+      </c>
+      <c r="E470" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F470" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G470" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I470" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J470" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A471" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B471" s="3">
+        <v>392</v>
+      </c>
+      <c r="C471" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D471" s="3">
+        <v>350</v>
+      </c>
+      <c r="E471" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F471" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G471" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H471" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I471" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J471" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A472" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B472" s="3">
+        <v>392</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D472" s="3">
+        <v>352</v>
+      </c>
+      <c r="E472" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F472" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G472" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I472" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J472" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="A473" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B473" s="3">
+        <v>392</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D473" s="3">
+        <v>380</v>
+      </c>
+      <c r="E473" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F473" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="I473" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J473" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+      <c r="A474" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B474" s="3">
+        <v>392</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D474" s="3">
+        <v>390</v>
+      </c>
+      <c r="E474" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F474" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G474" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I474" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J474" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A475" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B475" s="3">
+        <v>440</v>
+      </c>
+      <c r="C475" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D475" s="3">
+        <v>342</v>
+      </c>
+      <c r="E475" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F475" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G475" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I475" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J475" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A476" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B476" s="3">
+        <v>442</v>
+      </c>
+      <c r="C476" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D476" s="3">
+        <v>119</v>
+      </c>
+      <c r="E476" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F476" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G476" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="H476" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="I476" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J476" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+      <c r="A477" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B477" s="3">
+        <v>442</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D477" s="3">
+        <v>327</v>
+      </c>
+      <c r="E477" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F477" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G477" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="H477" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="I477" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J477" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A478" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B478" s="3">
+        <v>442</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D478" s="3">
+        <v>340</v>
+      </c>
+      <c r="E478" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F478" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G478" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H478" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I478" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J478" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A479" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B479" s="3">
+        <v>442</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D479" s="3">
+        <v>342</v>
+      </c>
+      <c r="E479" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F479" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G479" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="H479" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="I479" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J479" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A480" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B480" s="3">
+        <v>442</v>
+      </c>
+      <c r="C480" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D480" s="3">
+        <v>347</v>
+      </c>
+      <c r="E480" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F480" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="H480" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="I480" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J480" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A481" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B481" s="3">
+        <v>442</v>
+      </c>
+      <c r="C481" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D481" s="3">
+        <v>348</v>
+      </c>
+      <c r="E481" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F481" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G481" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="H481" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="I481" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J481" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A482" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B482" s="3">
+        <v>442</v>
+      </c>
+      <c r="C482" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D482" s="3">
+        <v>349</v>
+      </c>
+      <c r="E482" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F482" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G482" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="H482" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="I482" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J482" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A483" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B483" s="3">
+        <v>442</v>
+      </c>
+      <c r="C483" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D483" s="3">
+        <v>443</v>
+      </c>
+      <c r="E483" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F483" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G483" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="H483" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="I483" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J483" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B484" s="3">
+        <v>442</v>
+      </c>
+      <c r="C484" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D484" s="3">
+        <v>446</v>
+      </c>
+      <c r="E484" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F484" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="H484" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="I484" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J484" s="8" t="d">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A485" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B485" s="3">
+        <v>443</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D485" s="3">
+        <v>119</v>
+      </c>
+      <c r="E485" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F485" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I485" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J485" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A486" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B486" s="3">
+        <v>443</v>
+      </c>
+      <c r="C486" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D486" s="3">
+        <v>327</v>
+      </c>
+      <c r="E486" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F486" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H486" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="I486" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J486" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="A487" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B487" s="3">
+        <v>443</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D487" s="3">
+        <v>341</v>
+      </c>
+      <c r="E487" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F487" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="H487" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I487" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J487" s="8" t="d">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A488" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B488" s="3">
+        <v>443</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D488" s="3">
+        <v>342</v>
+      </c>
+      <c r="E488" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F488" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G488" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="H455" s="4" t="s">
+      <c r="H488" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="I455" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J455" s="8" t="d">
+      <c r="I488" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J488" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="456" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A456" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B456" s="3">
+    <row r="489" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="A489" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B489" s="3">
         <v>443</v>
       </c>
-      <c r="C456" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D456" s="3">
+      <c r="C489" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D489" s="3">
         <v>345</v>
       </c>
-      <c r="E456" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F456" s="3" t="s">
+      <c r="E489" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F489" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G456" s="4" t="s">
+      <c r="G489" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="I456" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J456" s="8" t="d">
+      <c r="I489" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J489" s="8" t="d">
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A457" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B457" s="3">
+    <row r="490" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="A490" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B490" s="3">
         <v>451</v>
       </c>
-      <c r="C457" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D457" s="3">
+      <c r="C490" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D490" s="3">
         <v>125</v>
       </c>
-      <c r="E457" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F457" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G457" s="4" t="s">
+      <c r="E490" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F490" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G490" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="I457" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J457" s="8" t="d">
+      <c r="I490" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J490" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
@@ -24416,13 +25675,13 @@
       <sortCondition ref="C2:C457"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J293">
-    <sortCondition ref="B2:B293"/>
-    <sortCondition ref="A2:A293"/>
-    <sortCondition ref="D2:D293"/>
-    <sortCondition ref="C2:C293"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J490">
+    <sortCondition ref="B2:B490"/>
+    <sortCondition ref="A2:A490"/>
+    <sortCondition ref="D2:D490"/>
+    <sortCondition ref="C2:C490"/>
   </sortState>
-  <conditionalFormatting sqref="A163:A209 C166:C209 A288:A1048576 C296:C1048576 A1:A155 C1:C155">
+  <conditionalFormatting sqref="A1:A155 C1:C155 A163:A209 C166:C209 A288:A1048576 C296:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"slips"</formula>
     </cfRule>

--- a/ip_data/bitcoin/ground_truth/ground_truth.xlsx
+++ b/ip_data/bitcoin/ground_truth/ground_truth.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rbo/Documents/GitHub/cdv-explorer/ip_data/bitcoin/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6F6CBE3E-BDEC-634B-B75C-313229F329DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AC36B496-4951-B340-B3F9-F6C4E0456295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="620" windowWidth="51160" windowHeight="28160" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="1" xr2:uid="{1EC4DC37-AE45-104B-A3B8-42A37703E7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="ips" sheetId="1" r:id="rId1"/>
     <sheet name="interrelations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$457</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">interrelations!$A$1:$J$456</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ips!$A$1:$Q$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="4913" uniqueCount="982">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="4906" uniqueCount="981">
   <si>
     <t>reviewer</t>
   </si>
@@ -741,9 +741,6 @@
   </si>
   <si>
     <t>Example made to demonstrate purpose of BIP43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIP 21 was based on BIP 20, which was, in turn based on an earlier document by Nils Schneider. </t>
   </si>
   <si>
     <t>Assuming a node sends only ping messages every 20 minutes (the timeout interval for post-BIP31 connections) on a connection</t>
@@ -4082,7 +4079,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G2" s="7">
         <v>42</v>
@@ -4094,19 +4091,19 @@
         <v>20</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="P2" s="7">
         <v>2</v>
@@ -4129,7 +4126,7 @@
         <v>17</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G3" s="7">
         <v>42</v>
@@ -4141,19 +4138,19 @@
         <v>35</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P3" s="7">
         <v>4</v>
@@ -4176,7 +4173,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G4" s="7">
         <v>42</v>
@@ -4188,19 +4185,19 @@
         <v>35</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M4" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>689</v>
       </c>
       <c r="P4" s="7">
         <v>8</v>
@@ -4223,7 +4220,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G5" s="7">
         <v>42</v>
@@ -4235,19 +4232,19 @@
         <v>35</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="P5" s="7">
         <v>9</v>
@@ -4270,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G6" s="7">
         <v>42</v>
@@ -4282,22 +4279,22 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="P6" s="7">
         <v>1</v>
@@ -4320,7 +4317,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G7" s="7">
         <v>42</v>
@@ -4332,10 +4329,10 @@
         <v>35</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>211</v>
@@ -4379,7 +4376,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>22</v>
@@ -4394,7 +4391,7 @@
         <v>40</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P8" s="7">
         <v>0</v>
@@ -4479,7 +4476,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>22</v>
@@ -4494,7 +4491,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P10" s="7">
         <v>3</v>
@@ -4567,7 +4564,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G12" s="7">
         <v>43</v>
@@ -4579,10 +4576,10 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L12" s="7" t="s">
         <v>23</v>
@@ -4594,7 +4591,7 @@
         <v>40</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P12" s="7">
         <v>1</v>
@@ -4617,7 +4614,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G13" s="7">
         <v>42</v>
@@ -4629,7 +4626,7 @@
         <v>35</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>33</v>
@@ -4679,10 +4676,10 @@
         <v>35</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>23</v>
@@ -4694,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P14" s="7">
         <v>4</v>
@@ -4779,10 +4776,10 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>23</v>
@@ -4794,7 +4791,7 @@
         <v>40</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P16" s="7">
         <v>1</v>
@@ -4879,10 +4876,10 @@
         <v>35</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L18" s="7" t="s">
         <v>23</v>
@@ -4917,7 +4914,7 @@
         <v>17</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G19" s="7">
         <v>42</v>
@@ -4929,10 +4926,10 @@
         <v>35</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>211</v>
@@ -5026,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>43</v>
@@ -5041,7 +5038,7 @@
         <v>44</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P21" s="7">
         <v>1</v>
@@ -5114,7 +5111,7 @@
         <v>17</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G23" s="7">
         <v>42</v>
@@ -5126,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>49</v>
@@ -5164,7 +5161,7 @@
         <v>17</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G24" s="7">
         <v>42</v>
@@ -5176,22 +5173,22 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="P24" s="7">
         <v>1</v>
@@ -5226,10 +5223,10 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>23</v>
@@ -5241,7 +5238,7 @@
         <v>30</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P25" s="7">
         <v>1</v>
@@ -5276,10 +5273,10 @@
         <v>27</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>29</v>
@@ -5291,7 +5288,7 @@
         <v>25</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P26" s="7">
         <v>0</v>
@@ -5326,10 +5323,10 @@
         <v>27</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>29</v>
@@ -5341,7 +5338,7 @@
         <v>30</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P27" s="7">
         <v>0</v>
@@ -5364,7 +5361,7 @@
         <v>17</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G28" s="7">
         <v>43</v>
@@ -5376,10 +5373,10 @@
         <v>27</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>23</v>
@@ -5391,7 +5388,7 @@
         <v>30</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="P28" s="7">
         <v>0</v>
@@ -5426,10 +5423,10 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>29</v>
@@ -5441,7 +5438,7 @@
         <v>30</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P29" s="7">
         <v>1</v>
@@ -5464,7 +5461,7 @@
         <v>17</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G30" s="7">
         <v>42</v>
@@ -5476,7 +5473,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>51</v>
@@ -5514,7 +5511,7 @@
         <v>17</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G31" s="7">
         <v>42</v>
@@ -5526,10 +5523,10 @@
         <v>35</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>211</v>
@@ -5573,10 +5570,10 @@
         <v>35</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>29</v>
@@ -5588,7 +5585,7 @@
         <v>25</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P32" s="7">
         <v>3</v>
@@ -5611,7 +5608,7 @@
         <v>17</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G33" s="7">
         <v>42</v>
@@ -5623,7 +5620,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>53</v>
@@ -5711,7 +5708,7 @@
         <v>17</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G35" s="7">
         <v>42</v>
@@ -5723,10 +5720,10 @@
         <v>20</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>216</v>
@@ -5770,10 +5767,10 @@
         <v>35</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>64</v>
@@ -5785,7 +5782,7 @@
         <v>40</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P36" s="7">
         <v>6</v>
@@ -5858,7 +5855,7 @@
         <v>17</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G38" s="7">
         <v>42</v>
@@ -5870,19 +5867,19 @@
         <v>27</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P38" s="7">
         <v>0</v>
@@ -5917,10 +5914,10 @@
         <v>27</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>64</v>
@@ -5929,10 +5926,10 @@
         <v>24</v>
       </c>
       <c r="N39" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="O39" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="P39" s="7">
         <v>0</v>
@@ -5967,10 +5964,10 @@
         <v>27</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>29</v>
@@ -5982,7 +5979,7 @@
         <v>30</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P40" s="7">
         <v>0</v>
@@ -6017,10 +6014,10 @@
         <v>20</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>23</v>
@@ -6032,7 +6029,7 @@
         <v>25</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P41" s="7">
         <v>1</v>
@@ -6067,10 +6064,10 @@
         <v>20</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>23</v>
@@ -6082,7 +6079,7 @@
         <v>30</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P42" s="7">
         <v>1</v>
@@ -6117,10 +6114,10 @@
         <v>35</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>29</v>
@@ -6132,7 +6129,7 @@
         <v>25</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P43" s="7">
         <v>2</v>
@@ -6167,10 +6164,10 @@
         <v>35</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>37</v>
@@ -6182,7 +6179,7 @@
         <v>40</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P44" s="7">
         <v>3</v>
@@ -6205,7 +6202,7 @@
         <v>17</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G45" s="7">
         <v>42</v>
@@ -6217,22 +6214,22 @@
         <v>20</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="P45" s="7">
         <v>1</v>
@@ -6267,10 +6264,10 @@
         <v>27</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>29</v>
@@ -6282,7 +6279,7 @@
         <v>40</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P46" s="7">
         <v>0</v>
@@ -6405,7 +6402,7 @@
         <v>17</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G49" s="7">
         <v>42</v>
@@ -6417,7 +6414,7 @@
         <v>35</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K49" s="8" t="s">
         <v>63</v>
@@ -6455,7 +6452,7 @@
         <v>17</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7">
         <v>42</v>
@@ -6467,7 +6464,7 @@
         <v>35</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K50" s="8" t="s">
         <v>66</v>
@@ -6505,7 +6502,7 @@
         <v>17</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G51" s="7">
         <v>42</v>
@@ -6517,19 +6514,19 @@
         <v>35</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P51" s="7">
         <v>4</v>
@@ -6552,7 +6549,7 @@
         <v>17</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G52" s="7">
         <v>42</v>
@@ -6564,22 +6561,22 @@
         <v>35</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="P52" s="7">
         <v>3</v>
@@ -6614,10 +6611,10 @@
         <v>35</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>37</v>
@@ -6629,7 +6626,7 @@
         <v>40</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P53" s="7">
         <v>10</v>
@@ -6664,10 +6661,10 @@
         <v>35</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L54" s="7" t="s">
         <v>64</v>
@@ -6679,7 +6676,7 @@
         <v>40</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P54" s="7">
         <v>5</v>
@@ -6714,10 +6711,10 @@
         <v>35</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L55" s="7" t="s">
         <v>29</v>
@@ -6729,7 +6726,7 @@
         <v>25</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P55" s="7">
         <v>8</v>
@@ -6752,7 +6749,7 @@
         <v>17</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G56" s="7">
         <v>42</v>
@@ -6764,22 +6761,22 @@
         <v>35</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L56" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P56" s="7">
         <v>4</v>
@@ -6814,10 +6811,10 @@
         <v>20</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L57" s="7" t="s">
         <v>64</v>
@@ -6829,7 +6826,7 @@
         <v>25</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P57" s="7">
         <v>1</v>
@@ -6852,7 +6849,7 @@
         <v>17</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G58" s="7">
         <v>42</v>
@@ -6864,19 +6861,19 @@
         <v>35</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L58" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P58" s="7">
         <v>8</v>
@@ -6911,10 +6908,10 @@
         <v>20</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>23</v>
@@ -6923,10 +6920,10 @@
         <v>24</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P59" s="7">
         <v>1</v>
@@ -6961,10 +6958,10 @@
         <v>27</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>23</v>
@@ -6973,10 +6970,10 @@
         <v>24</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P60" s="7">
         <v>0</v>
@@ -7011,10 +7008,10 @@
         <v>20</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>23</v>
@@ -7023,10 +7020,10 @@
         <v>24</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P61" s="7">
         <v>1</v>
@@ -7061,10 +7058,10 @@
         <v>20</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>23</v>
@@ -7073,10 +7070,10 @@
         <v>24</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P62" s="7">
         <v>1</v>
@@ -7111,10 +7108,10 @@
         <v>35</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>23</v>
@@ -7123,10 +7120,10 @@
         <v>24</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P63" s="7">
         <v>2</v>
@@ -7161,10 +7158,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L64" s="7" t="s">
         <v>23</v>
@@ -7173,10 +7170,10 @@
         <v>24</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P64" s="7">
         <v>1</v>
@@ -7411,10 +7408,10 @@
         <v>20</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L69" s="7" t="s">
         <v>23</v>
@@ -7426,7 +7423,7 @@
         <v>25</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P69" s="7">
         <v>1</v>
@@ -7443,13 +7440,13 @@
         <v>15</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G70" s="7">
         <v>42</v>
@@ -7461,10 +7458,10 @@
         <v>35</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L70" s="7" t="s">
         <v>64</v>
@@ -7476,7 +7473,7 @@
         <v>25</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P70" s="7">
         <v>8</v>
@@ -7511,10 +7508,10 @@
         <v>35</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K71" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>64</v>
@@ -7526,7 +7523,7 @@
         <v>25</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P71" s="7">
         <v>6</v>
@@ -7649,7 +7646,7 @@
         <v>17</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G74" s="7">
         <v>42</v>
@@ -7661,19 +7658,19 @@
         <v>35</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P74" s="7">
         <v>86</v>
@@ -7708,10 +7705,10 @@
         <v>35</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L75" s="7" t="s">
         <v>29</v>
@@ -7723,7 +7720,7 @@
         <v>40</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P75" s="7">
         <v>2</v>
@@ -7746,7 +7743,7 @@
         <v>17</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G76" s="7">
         <v>42</v>
@@ -7758,19 +7755,19 @@
         <v>20</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L76" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="P76" s="7">
         <v>1</v>
@@ -7805,10 +7802,10 @@
         <v>35</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L77" s="7" t="s">
         <v>64</v>
@@ -7820,7 +7817,7 @@
         <v>40</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P77" s="7">
         <v>3</v>
@@ -7905,10 +7902,10 @@
         <v>27</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L79" s="7" t="s">
         <v>29</v>
@@ -7920,7 +7917,7 @@
         <v>30</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P79" s="7">
         <v>0</v>
@@ -7955,10 +7952,10 @@
         <v>27</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L80" s="7" t="s">
         <v>23</v>
@@ -7967,10 +7964,10 @@
         <v>24</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P80" s="7">
         <v>0</v>
@@ -8005,10 +8002,10 @@
         <v>20</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L81" s="7" t="s">
         <v>29</v>
@@ -8020,7 +8017,7 @@
         <v>30</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P81" s="7">
         <v>1</v>
@@ -8055,10 +8052,10 @@
         <v>20</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L82" s="7" t="s">
         <v>23</v>
@@ -8067,10 +8064,10 @@
         <v>24</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P82" s="7">
         <v>1</v>
@@ -8093,7 +8090,7 @@
         <v>17</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G83" s="7">
         <v>42</v>
@@ -8105,22 +8102,22 @@
         <v>20</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L83" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O83" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="P83" s="7">
         <v>2</v>
@@ -8155,10 +8152,10 @@
         <v>20</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L84" s="7" t="s">
         <v>29</v>
@@ -8170,7 +8167,7 @@
         <v>40</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="P84" s="7">
         <v>1</v>
@@ -8205,10 +8202,10 @@
         <v>35</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L85" s="7" t="s">
         <v>29</v>
@@ -8220,7 +8217,7 @@
         <v>25</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P85" s="7">
         <v>11</v>
@@ -8305,10 +8302,10 @@
         <v>35</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L87" s="7" t="s">
         <v>29</v>
@@ -8320,7 +8317,7 @@
         <v>30</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P87" s="7">
         <v>2</v>
@@ -8393,7 +8390,7 @@
         <v>17</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G89" s="7">
         <v>43</v>
@@ -8405,10 +8402,10 @@
         <v>35</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L89" s="7" t="s">
         <v>23</v>
@@ -8420,7 +8417,7 @@
         <v>25</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P89" s="7">
         <v>5</v>
@@ -8455,10 +8452,10 @@
         <v>35</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L90" s="7" t="s">
         <v>29</v>
@@ -8470,7 +8467,7 @@
         <v>25</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P90" s="7">
         <v>5</v>
@@ -8505,10 +8502,10 @@
         <v>35</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L91" s="7" t="s">
         <v>29</v>
@@ -8520,7 +8517,7 @@
         <v>25</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P91" s="7">
         <v>5</v>
@@ -8555,10 +8552,10 @@
         <v>20</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L92" s="7" t="s">
         <v>23</v>
@@ -8570,7 +8567,7 @@
         <v>30</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P92" s="7">
         <v>1</v>
@@ -8655,10 +8652,10 @@
         <v>27</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>29</v>
@@ -8670,7 +8667,7 @@
         <v>30</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P94" s="7">
         <v>0</v>
@@ -8705,10 +8702,10 @@
         <v>27</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K95" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>23</v>
@@ -8720,7 +8717,7 @@
         <v>40</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P95" s="7">
         <v>0</v>
@@ -8743,7 +8740,7 @@
         <v>17</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G96" s="7">
         <v>42</v>
@@ -8755,22 +8752,22 @@
         <v>20</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M96" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P96" s="7">
         <v>2</v>
@@ -8793,7 +8790,7 @@
         <v>17</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G97" s="7">
         <v>42</v>
@@ -8805,22 +8802,22 @@
         <v>35</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="L97" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N97" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="P97" s="7">
         <v>7</v>
@@ -8855,10 +8852,10 @@
         <v>35</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L98" s="7" t="s">
         <v>29</v>
@@ -8870,7 +8867,7 @@
         <v>40</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P98" s="7">
         <v>4</v>
@@ -8893,7 +8890,7 @@
         <v>17</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G99" s="7">
         <v>42</v>
@@ -8905,22 +8902,22 @@
         <v>35</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L99" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M99" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P99" s="7">
         <v>3</v>
@@ -8943,7 +8940,7 @@
         <v>17</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G100" s="7">
         <v>42</v>
@@ -8955,19 +8952,19 @@
         <v>27</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L100" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="P100" s="7">
         <v>0</v>
@@ -8990,7 +8987,7 @@
         <v>17</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G101" s="7">
         <v>42</v>
@@ -9002,19 +8999,19 @@
         <v>20</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M101" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="P101" s="7">
         <v>1</v>
@@ -9037,7 +9034,7 @@
         <v>17</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G102" s="7">
         <v>42</v>
@@ -9049,19 +9046,19 @@
         <v>27</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L102" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M102" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="P102" s="7">
         <v>0</v>
@@ -9146,10 +9143,10 @@
         <v>27</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K104" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L104" s="7" t="s">
         <v>23</v>
@@ -9161,7 +9158,7 @@
         <v>40</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P104" s="7">
         <v>0</v>
@@ -9196,10 +9193,10 @@
         <v>20</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L105" s="7" t="s">
         <v>64</v>
@@ -9211,7 +9208,7 @@
         <v>25</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P105" s="7">
         <v>1</v>
@@ -9246,10 +9243,10 @@
         <v>20</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L106" s="7" t="s">
         <v>64</v>
@@ -9261,7 +9258,7 @@
         <v>25</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P106" s="7">
         <v>1</v>
@@ -9284,7 +9281,7 @@
         <v>17</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G107" s="7">
         <v>42</v>
@@ -9296,22 +9293,22 @@
         <v>20</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L107" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M107" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N107" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="P107" s="7">
         <v>1</v>
@@ -9381,7 +9378,7 @@
         <v>17</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G109" s="7">
         <v>42</v>
@@ -9393,7 +9390,7 @@
         <v>35</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K109" s="8" t="s">
         <v>92</v>
@@ -9443,10 +9440,10 @@
         <v>35</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L110" s="7" t="s">
         <v>64</v>
@@ -9455,7 +9452,7 @@
         <v>24</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P110" s="7">
         <v>3</v>
@@ -9478,7 +9475,7 @@
         <v>17</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G111" s="7">
         <v>42</v>
@@ -9490,7 +9487,7 @@
         <v>35</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K111" s="8" t="s">
         <v>93</v>
@@ -9528,7 +9525,7 @@
         <v>17</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G112" s="7">
         <v>42</v>
@@ -9540,22 +9537,22 @@
         <v>35</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L112" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N112" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O112" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P112" s="7">
         <v>3</v>
@@ -9578,7 +9575,7 @@
         <v>17</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G113" s="7">
         <v>42</v>
@@ -9590,22 +9587,22 @@
         <v>20</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L113" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N113" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O113" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P113" s="7">
         <v>2</v>
@@ -9740,10 +9737,10 @@
         <v>27</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K116" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L116" s="7" t="s">
         <v>64</v>
@@ -9755,7 +9752,7 @@
         <v>44</v>
       </c>
       <c r="O116" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P116" s="7">
         <v>0</v>
@@ -9790,10 +9787,10 @@
         <v>35</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K117" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L117" s="7" t="s">
         <v>29</v>
@@ -9805,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="O117" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P117" s="7">
         <v>10</v>
@@ -9840,10 +9837,10 @@
         <v>35</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K118" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L118" s="7" t="s">
         <v>29</v>
@@ -9855,7 +9852,7 @@
         <v>25</v>
       </c>
       <c r="O118" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P118" s="7">
         <v>6</v>
@@ -9928,7 +9925,7 @@
         <v>17</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G120" s="7">
         <v>42</v>
@@ -9940,22 +9937,22 @@
         <v>35</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N120" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O120" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="P120" s="7">
         <v>11</v>
@@ -10028,7 +10025,7 @@
         <v>17</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G122" s="7">
         <v>42</v>
@@ -10040,22 +10037,22 @@
         <v>35</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K122" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L122" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M122" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N122" s="3" t="s">
         <v>25</v>
       </c>
       <c r="O122" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P122" s="7">
         <v>3</v>
@@ -10090,10 +10087,10 @@
         <v>20</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K123" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L123" s="7" t="s">
         <v>29</v>
@@ -10105,7 +10102,7 @@
         <v>40</v>
       </c>
       <c r="O123" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P123" s="7">
         <v>1</v>
@@ -10140,10 +10137,10 @@
         <v>35</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K124" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L124" s="7" t="s">
         <v>29</v>
@@ -10155,7 +10152,7 @@
         <v>40</v>
       </c>
       <c r="O124" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P124" s="7">
         <v>6</v>
@@ -10190,10 +10187,10 @@
         <v>35</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K125" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L125" s="7" t="s">
         <v>64</v>
@@ -10205,7 +10202,7 @@
         <v>40</v>
       </c>
       <c r="O125" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P125" s="7">
         <v>3</v>
@@ -10278,7 +10275,7 @@
         <v>17</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G127" s="7">
         <v>42</v>
@@ -10290,22 +10287,22 @@
         <v>35</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L127" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M127" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N127" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O127" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P127" s="7">
         <v>3</v>
@@ -10328,7 +10325,7 @@
         <v>17</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G128" s="7">
         <v>42</v>
@@ -10340,22 +10337,22 @@
         <v>35</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K128" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L128" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N128" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O128" s="3" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P128" s="7">
         <v>4</v>
@@ -10378,7 +10375,7 @@
         <v>17</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G129" s="7">
         <v>42</v>
@@ -10390,22 +10387,22 @@
         <v>20</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K129" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L129" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M129" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N129" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O129" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P129" s="7">
         <v>1</v>
@@ -10428,7 +10425,7 @@
         <v>17</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G130" s="7">
         <v>42</v>
@@ -10440,22 +10437,22 @@
         <v>35</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K130" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L130" s="7" t="s">
         <v>29</v>
       </c>
       <c r="M130" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N130" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O130" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P130" s="7">
         <v>6</v>
@@ -10478,7 +10475,7 @@
         <v>17</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G131" s="7">
         <v>42</v>
@@ -10490,22 +10487,22 @@
         <v>35</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K131" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L131" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M131" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N131" s="3" t="s">
         <v>40</v>
       </c>
       <c r="O131" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P131" s="7">
         <v>6</v>
@@ -10640,10 +10637,10 @@
         <v>35</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K134" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L134" s="7" t="s">
         <v>64</v>
@@ -10655,7 +10652,7 @@
         <v>25</v>
       </c>
       <c r="O134" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P134" s="7">
         <v>10</v>
@@ -10740,10 +10737,10 @@
         <v>20</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K136" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L136" s="7" t="s">
         <v>64</v>
@@ -10755,7 +10752,7 @@
         <v>40</v>
       </c>
       <c r="O136" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P136" s="7">
         <v>1</v>
@@ -10787,7 +10784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J490"/>
+  <dimension ref="A1:J489"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -10854,7 +10851,7 @@
         <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>15</v>
@@ -10883,7 +10880,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>15</v>
@@ -10912,7 +10909,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -10941,7 +10938,7 @@
         <v>35</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
@@ -10970,7 +10967,7 @@
         <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>15</v>
@@ -10999,7 +10996,7 @@
         <v>35</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>15</v>
@@ -11028,10 +11025,10 @@
         <v>35</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>751</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>752</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>15</v>
@@ -11060,7 +11057,7 @@
         <v>141</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>15</v>
@@ -11089,7 +11086,7 @@
         <v>141</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>15</v>
@@ -11118,10 +11115,10 @@
         <v>35</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>764</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>15</v>
@@ -11150,7 +11147,7 @@
         <v>141</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>15</v>
@@ -11179,7 +11176,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>15</v>
@@ -11208,7 +11205,7 @@
         <v>141</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>15</v>
@@ -11237,7 +11234,7 @@
         <v>141</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>15</v>
@@ -11266,7 +11263,7 @@
         <v>141</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>15</v>
@@ -11295,7 +11292,7 @@
         <v>141</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>15</v>
@@ -11324,7 +11321,7 @@
         <v>141</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>15</v>
@@ -11353,7 +11350,7 @@
         <v>141</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>15</v>
@@ -11382,10 +11379,10 @@
         <v>35</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>15</v>
@@ -11414,7 +11411,7 @@
         <v>141</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>15</v>
@@ -11443,7 +11440,7 @@
         <v>35</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
@@ -11472,7 +11469,7 @@
         <v>35</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>15</v>
@@ -11501,7 +11498,7 @@
         <v>141</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>15</v>
@@ -11530,7 +11527,7 @@
         <v>141</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>15</v>
@@ -11559,7 +11556,7 @@
         <v>141</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>15</v>
@@ -11588,7 +11585,7 @@
         <v>141</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>15</v>
@@ -11614,7 +11611,7 @@
         <v>123</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>15</v>
@@ -11675,7 +11672,7 @@
         <v>35</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>15</v>
@@ -11704,7 +11701,7 @@
         <v>35</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>15</v>
@@ -11733,10 +11730,10 @@
         <v>20</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>15</v>
@@ -11794,7 +11791,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>15</v>
@@ -11823,10 +11820,10 @@
         <v>35</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>15</v>
@@ -11855,7 +11852,7 @@
         <v>20</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>15</v>
@@ -11884,7 +11881,7 @@
         <v>35</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>15</v>
@@ -12000,7 +11997,7 @@
         <v>35</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>15</v>
@@ -12029,7 +12026,7 @@
         <v>35</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>15</v>
@@ -12058,10 +12055,10 @@
         <v>35</v>
       </c>
       <c r="G43" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>397</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>15</v>
@@ -12090,7 +12087,7 @@
         <v>35</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>15</v>
@@ -12273,10 +12270,10 @@
         <v>35</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="H50" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>399</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>15</v>
@@ -12334,7 +12331,7 @@
         <v>35</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>15</v>
@@ -12363,7 +12360,7 @@
         <v>35</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>15</v>
@@ -12421,7 +12418,7 @@
         <v>20</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>15</v>
@@ -12482,7 +12479,7 @@
         <v>145</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>15</v>
@@ -12514,7 +12511,7 @@
         <v>145</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>15</v>
@@ -12546,7 +12543,7 @@
         <v>158</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>15</v>
@@ -12578,7 +12575,7 @@
         <v>159</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>15</v>
@@ -12636,7 +12633,7 @@
         <v>35</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>15</v>
@@ -12668,7 +12665,7 @@
         <v>117</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>15</v>
@@ -12697,10 +12694,10 @@
         <v>35</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>15</v>
@@ -12787,7 +12784,7 @@
         <v>35</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>15</v>
@@ -12816,7 +12813,7 @@
         <v>20</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>15</v>
@@ -12845,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>15</v>
@@ -12874,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>15</v>
@@ -13089,7 +13086,7 @@
         <v>35</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>15</v>
@@ -13118,7 +13115,7 @@
         <v>35</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>15</v>
@@ -13147,7 +13144,7 @@
         <v>35</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>15</v>
@@ -13176,10 +13173,10 @@
         <v>35</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>15</v>
@@ -13208,7 +13205,7 @@
         <v>35</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>15</v>
@@ -13237,7 +13234,7 @@
         <v>35</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>15</v>
@@ -13443,10 +13440,10 @@
         <v>20</v>
       </c>
       <c r="G89" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>769</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>770</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>15</v>
@@ -13475,7 +13472,7 @@
         <v>35</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>15</v>
@@ -13504,10 +13501,10 @@
         <v>35</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>15</v>
@@ -13536,7 +13533,7 @@
         <v>35</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>15</v>
@@ -13565,7 +13562,7 @@
         <v>35</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>15</v>
@@ -13594,10 +13591,10 @@
         <v>35</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>15</v>
@@ -13626,7 +13623,7 @@
         <v>35</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>15</v>
@@ -13655,7 +13652,7 @@
         <v>35</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>15</v>
@@ -13684,7 +13681,7 @@
         <v>35</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>15</v>
@@ -13713,10 +13710,10 @@
         <v>35</v>
       </c>
       <c r="G98" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>772</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>773</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>15</v>
@@ -14059,10 +14056,10 @@
         <v>35</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>15</v>
@@ -14091,10 +14088,10 @@
         <v>35</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>15</v>
@@ -14123,10 +14120,10 @@
         <v>35</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>15</v>
@@ -14155,7 +14152,7 @@
         <v>35</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>15</v>
@@ -14184,10 +14181,10 @@
         <v>35</v>
       </c>
       <c r="G113" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>782</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>15</v>
@@ -14216,7 +14213,7 @@
         <v>35</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>15</v>
@@ -14245,10 +14242,10 @@
         <v>35</v>
       </c>
       <c r="G115" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>784</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>785</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>15</v>
@@ -14277,7 +14274,7 @@
         <v>35</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>15</v>
@@ -14306,10 +14303,10 @@
         <v>35</v>
       </c>
       <c r="G117" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>15</v>
@@ -14338,7 +14335,7 @@
         <v>35</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>15</v>
@@ -14367,7 +14364,7 @@
         <v>35</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>15</v>
@@ -14396,7 +14393,7 @@
         <v>35</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>15</v>
@@ -14425,10 +14422,10 @@
         <v>141</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>15</v>
@@ -14457,10 +14454,10 @@
         <v>35</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>15</v>
@@ -14489,10 +14486,10 @@
         <v>141</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>15</v>
@@ -14521,10 +14518,10 @@
         <v>35</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>15</v>
@@ -14553,7 +14550,7 @@
         <v>35</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>15</v>
@@ -14582,7 +14579,7 @@
         <v>35</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>15</v>
@@ -14611,10 +14608,10 @@
         <v>35</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>15</v>
@@ -14643,10 +14640,10 @@
         <v>141</v>
       </c>
       <c r="G128" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>439</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>15</v>
@@ -14675,10 +14672,10 @@
         <v>35</v>
       </c>
       <c r="G129" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="H129" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>15</v>
@@ -14707,10 +14704,10 @@
         <v>35</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>15</v>
@@ -14739,10 +14736,10 @@
         <v>35</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>15</v>
@@ -14771,7 +14768,7 @@
         <v>35</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>15</v>
@@ -14800,7 +14797,7 @@
         <v>35</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>15</v>
@@ -14829,7 +14826,7 @@
         <v>35</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>15</v>
@@ -14858,10 +14855,10 @@
         <v>35</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>15</v>
@@ -14890,10 +14887,10 @@
         <v>35</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H136" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>15</v>
@@ -14922,10 +14919,10 @@
         <v>35</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H137" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>15</v>
@@ -14954,7 +14951,7 @@
         <v>35</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>15</v>
@@ -14983,7 +14980,7 @@
         <v>35</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>15</v>
@@ -15012,7 +15009,7 @@
         <v>35</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>15</v>
@@ -15041,10 +15038,10 @@
         <v>35</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>15</v>
@@ -15073,7 +15070,7 @@
         <v>35</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>15</v>
@@ -15102,7 +15099,7 @@
         <v>35</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>15</v>
@@ -15119,7 +15116,7 @@
         <v>98</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D144" s="3">
         <v>116</v>
@@ -15131,7 +15128,7 @@
         <v>35</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>15</v>
@@ -15160,10 +15157,10 @@
         <v>35</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>15</v>
@@ -15192,7 +15189,7 @@
         <v>35</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>15</v>
@@ -15221,7 +15218,7 @@
         <v>35</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>15</v>
@@ -15250,7 +15247,7 @@
         <v>35</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>15</v>
@@ -15279,7 +15276,7 @@
         <v>35</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>15</v>
@@ -15308,7 +15305,7 @@
         <v>35</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>15</v>
@@ -15337,7 +15334,7 @@
         <v>35</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>15</v>
@@ -15366,7 +15363,7 @@
         <v>35</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>15</v>
@@ -15395,7 +15392,7 @@
         <v>35</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>15</v>
@@ -15424,10 +15421,10 @@
         <v>141</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>15</v>
@@ -15456,10 +15453,10 @@
         <v>141</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>15</v>
@@ -15488,10 +15485,10 @@
         <v>35</v>
       </c>
       <c r="G156" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H156" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>470</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>15</v>
@@ -15520,7 +15517,7 @@
         <v>35</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>15</v>
@@ -15549,7 +15546,7 @@
         <v>35</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I158" s="3" t="s">
         <v>15</v>
@@ -15578,7 +15575,7 @@
         <v>35</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I159" s="3" t="s">
         <v>15</v>
@@ -15796,7 +15793,7 @@
         <v>173</v>
       </c>
       <c r="H166" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I166" s="3" t="s">
         <v>15</v>
@@ -15828,7 +15825,7 @@
         <v>173</v>
       </c>
       <c r="H167" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I167" s="3" t="s">
         <v>15</v>
@@ -15860,7 +15857,7 @@
         <v>173</v>
       </c>
       <c r="H168" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I168" s="3" t="s">
         <v>15</v>
@@ -16011,7 +16008,7 @@
         <v>35</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>15</v>
@@ -16028,7 +16025,7 @@
         <v>116</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D174" s="3">
         <v>8</v>
@@ -16040,7 +16037,7 @@
         <v>35</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>15</v>
@@ -16057,7 +16054,7 @@
         <v>116</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D175" s="3">
         <v>16</v>
@@ -16069,10 +16066,10 @@
         <v>35</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I175" s="3" t="s">
         <v>15</v>
@@ -16089,7 +16086,7 @@
         <v>116</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D176" s="3">
         <v>65</v>
@@ -16101,10 +16098,10 @@
         <v>141</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>15</v>
@@ -16121,7 +16118,7 @@
         <v>116</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D177" s="3">
         <v>68</v>
@@ -16133,10 +16130,10 @@
         <v>141</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>15</v>
@@ -16153,7 +16150,7 @@
         <v>116</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D178" s="3">
         <v>98</v>
@@ -16165,7 +16162,7 @@
         <v>35</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I178" s="3" t="s">
         <v>15</v>
@@ -16182,7 +16179,7 @@
         <v>116</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D179" s="3">
         <v>112</v>
@@ -16194,10 +16191,10 @@
         <v>141</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H179" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>15</v>
@@ -16214,7 +16211,7 @@
         <v>116</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D180" s="3">
         <v>141</v>
@@ -16226,10 +16223,10 @@
         <v>35</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H180" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>15</v>
@@ -16246,7 +16243,7 @@
         <v>116</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D181" s="3">
         <v>143</v>
@@ -16258,10 +16255,10 @@
         <v>35</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>15</v>
@@ -16290,7 +16287,7 @@
         <v>35</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>15</v>
@@ -16319,10 +16316,10 @@
         <v>35</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H183" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>15</v>
@@ -16351,10 +16348,10 @@
         <v>35</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H184" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>15</v>
@@ -16383,10 +16380,10 @@
         <v>35</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H185" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>15</v>
@@ -16415,10 +16412,10 @@
         <v>35</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>15</v>
@@ -16447,10 +16444,10 @@
         <v>35</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>15</v>
@@ -16572,7 +16569,7 @@
         <v>180</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>15</v>
@@ -16601,7 +16598,7 @@
         <v>35</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>15</v>
@@ -16630,7 +16627,7 @@
         <v>35</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>15</v>
@@ -16659,7 +16656,7 @@
         <v>35</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>15</v>
@@ -16688,7 +16685,7 @@
         <v>35</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I195" s="3" t="s">
         <v>15</v>
@@ -16717,7 +16714,7 @@
         <v>35</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>15</v>
@@ -16746,7 +16743,7 @@
         <v>35</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>15</v>
@@ -16775,7 +16772,7 @@
         <v>35</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>15</v>
@@ -16804,7 +16801,7 @@
         <v>35</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I199" s="3" t="s">
         <v>15</v>
@@ -16833,7 +16830,7 @@
         <v>35</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>15</v>
@@ -16862,7 +16859,7 @@
         <v>35</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="I201" s="3" t="s">
         <v>15</v>
@@ -16891,7 +16888,7 @@
         <v>35</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>15</v>
@@ -16920,7 +16917,7 @@
         <v>35</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>15</v>
@@ -16949,7 +16946,7 @@
         <v>35</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I204" s="3" t="s">
         <v>15</v>
@@ -16978,7 +16975,7 @@
         <v>35</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I205" s="3" t="s">
         <v>15</v>
@@ -17007,7 +17004,7 @@
         <v>35</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I206" s="3" t="s">
         <v>15</v>
@@ -17036,7 +17033,7 @@
         <v>35</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I207" s="3" t="s">
         <v>15</v>
@@ -17065,7 +17062,7 @@
         <v>35</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I208" s="3" t="s">
         <v>15</v>
@@ -17094,7 +17091,7 @@
         <v>35</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>15</v>
@@ -17123,7 +17120,7 @@
         <v>35</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>15</v>
@@ -17152,7 +17149,7 @@
         <v>35</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>15</v>
@@ -17181,7 +17178,7 @@
         <v>35</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I212" s="3" t="s">
         <v>15</v>
@@ -17210,7 +17207,7 @@
         <v>35</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I213" s="3" t="s">
         <v>15</v>
@@ -17239,7 +17236,7 @@
         <v>35</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I214" s="3" t="s">
         <v>15</v>
@@ -17268,7 +17265,7 @@
         <v>35</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I215" s="3" t="s">
         <v>15</v>
@@ -17297,7 +17294,7 @@
         <v>35</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I216" s="3" t="s">
         <v>15</v>
@@ -17326,7 +17323,7 @@
         <v>35</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I217" s="3" t="s">
         <v>15</v>
@@ -17355,7 +17352,7 @@
         <v>35</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I218" s="3" t="s">
         <v>15</v>
@@ -17384,7 +17381,7 @@
         <v>35</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="I219" s="3" t="s">
         <v>15</v>
@@ -17413,7 +17410,7 @@
         <v>35</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="I220" s="3" t="s">
         <v>15</v>
@@ -17442,7 +17439,7 @@
         <v>35</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="I221" s="3" t="s">
         <v>15</v>
@@ -17471,7 +17468,7 @@
         <v>35</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I222" s="3" t="s">
         <v>15</v>
@@ -17500,7 +17497,7 @@
         <v>35</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I223" s="3" t="s">
         <v>15</v>
@@ -17529,7 +17526,7 @@
         <v>35</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I224" s="3" t="s">
         <v>15</v>
@@ -17558,7 +17555,7 @@
         <v>35</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I225" s="3" t="s">
         <v>15</v>
@@ -17587,7 +17584,7 @@
         <v>35</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I226" s="3" t="s">
         <v>15</v>
@@ -17616,7 +17613,7 @@
         <v>35</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I227" s="3" t="s">
         <v>15</v>
@@ -17645,7 +17642,7 @@
         <v>35</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I228" s="3" t="s">
         <v>15</v>
@@ -17674,7 +17671,7 @@
         <v>35</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I229" s="3" t="s">
         <v>15</v>
@@ -17703,7 +17700,7 @@
         <v>35</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I230" s="3" t="s">
         <v>15</v>
@@ -17732,7 +17729,7 @@
         <v>35</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I231" s="3" t="s">
         <v>15</v>
@@ -17761,7 +17758,7 @@
         <v>35</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I232" s="3" t="s">
         <v>15</v>
@@ -17790,7 +17787,7 @@
         <v>35</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="I233" s="3" t="s">
         <v>15</v>
@@ -17819,7 +17816,7 @@
         <v>35</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="I234" s="3" t="s">
         <v>15</v>
@@ -17848,7 +17845,7 @@
         <v>35</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="I235" s="3" t="s">
         <v>15</v>
@@ -17877,7 +17874,7 @@
         <v>35</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I236" s="3" t="s">
         <v>15</v>
@@ -17906,7 +17903,7 @@
         <v>35</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I237" s="3" t="s">
         <v>15</v>
@@ -17935,7 +17932,7 @@
         <v>35</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I238" s="3" t="s">
         <v>15</v>
@@ -17964,7 +17961,7 @@
         <v>35</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="I239" s="3" t="s">
         <v>15</v>
@@ -17993,7 +17990,7 @@
         <v>35</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="I240" s="3" t="s">
         <v>15</v>
@@ -18022,7 +18019,7 @@
         <v>35</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="I241" s="3" t="s">
         <v>15</v>
@@ -18051,7 +18048,7 @@
         <v>35</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="I242" s="3" t="s">
         <v>15</v>
@@ -18080,7 +18077,7 @@
         <v>35</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="I243" s="3" t="s">
         <v>15</v>
@@ -18109,7 +18106,7 @@
         <v>35</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="I244" s="3" t="s">
         <v>15</v>
@@ -18138,7 +18135,7 @@
         <v>35</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="I245" s="3" t="s">
         <v>15</v>
@@ -18167,7 +18164,7 @@
         <v>35</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I246" s="3" t="s">
         <v>15</v>
@@ -18196,7 +18193,7 @@
         <v>35</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I247" s="3" t="s">
         <v>15</v>
@@ -18225,7 +18222,7 @@
         <v>35</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="I248" s="3" t="s">
         <v>15</v>
@@ -18254,7 +18251,7 @@
         <v>35</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="I249" s="3" t="s">
         <v>15</v>
@@ -18283,7 +18280,7 @@
         <v>35</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I250" s="3" t="s">
         <v>15</v>
@@ -18312,7 +18309,7 @@
         <v>35</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I251" s="3" t="s">
         <v>15</v>
@@ -18341,7 +18338,7 @@
         <v>35</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I252" s="3" t="s">
         <v>15</v>
@@ -18370,7 +18367,7 @@
         <v>35</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I253" s="3" t="s">
         <v>15</v>
@@ -18399,7 +18396,7 @@
         <v>35</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="I254" s="3" t="s">
         <v>15</v>
@@ -18428,7 +18425,7 @@
         <v>35</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="I255" s="3" t="s">
         <v>15</v>
@@ -18457,7 +18454,7 @@
         <v>35</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="I256" s="3" t="s">
         <v>15</v>
@@ -18486,7 +18483,7 @@
         <v>35</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="I257" s="3" t="s">
         <v>15</v>
@@ -18515,7 +18512,7 @@
         <v>35</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I258" s="3" t="s">
         <v>15</v>
@@ -18544,7 +18541,7 @@
         <v>35</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I259" s="3" t="s">
         <v>15</v>
@@ -18573,7 +18570,7 @@
         <v>35</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="I260" s="3" t="s">
         <v>15</v>
@@ -18602,7 +18599,7 @@
         <v>35</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I261" s="3" t="s">
         <v>15</v>
@@ -18631,7 +18628,7 @@
         <v>35</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="I262" s="3" t="s">
         <v>15</v>
@@ -18660,7 +18657,7 @@
         <v>35</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I263" s="3" t="s">
         <v>15</v>
@@ -18689,7 +18686,7 @@
         <v>35</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="I264" s="3" t="s">
         <v>15</v>
@@ -18718,7 +18715,7 @@
         <v>35</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="I265" s="3" t="s">
         <v>15</v>
@@ -18747,7 +18744,7 @@
         <v>35</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="I266" s="3" t="s">
         <v>15</v>
@@ -18776,7 +18773,7 @@
         <v>35</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="I267" s="3" t="s">
         <v>15</v>
@@ -18805,7 +18802,7 @@
         <v>35</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="I268" s="3" t="s">
         <v>15</v>
@@ -18834,7 +18831,7 @@
         <v>35</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I269" s="3" t="s">
         <v>15</v>
@@ -18863,7 +18860,7 @@
         <v>35</v>
       </c>
       <c r="G270" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="I270" s="3" t="s">
         <v>15</v>
@@ -18892,7 +18889,7 @@
         <v>35</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I271" s="3" t="s">
         <v>15</v>
@@ -18921,7 +18918,7 @@
         <v>35</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I272" s="3" t="s">
         <v>15</v>
@@ -18950,7 +18947,7 @@
         <v>35</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I273" s="3" t="s">
         <v>15</v>
@@ -18979,7 +18976,7 @@
         <v>35</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I274" s="3" t="s">
         <v>15</v>
@@ -19008,7 +19005,7 @@
         <v>35</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I275" s="3" t="s">
         <v>15</v>
@@ -19037,7 +19034,7 @@
         <v>35</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I276" s="3" t="s">
         <v>15</v>
@@ -19066,7 +19063,7 @@
         <v>35</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I277" s="3" t="s">
         <v>15</v>
@@ -19095,7 +19092,7 @@
         <v>35</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I278" s="3" t="s">
         <v>15</v>
@@ -19124,7 +19121,7 @@
         <v>35</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I279" s="3" t="s">
         <v>15</v>
@@ -19153,10 +19150,10 @@
         <v>35</v>
       </c>
       <c r="G280" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="H280" s="4" t="s">
         <v>883</v>
-      </c>
-      <c r="H280" s="4" t="s">
-        <v>884</v>
       </c>
       <c r="I280" s="3" t="s">
         <v>15</v>
@@ -19185,10 +19182,10 @@
         <v>35</v>
       </c>
       <c r="G281" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="H281" s="4" t="s">
         <v>485</v>
-      </c>
-      <c r="H281" s="4" t="s">
-        <v>486</v>
       </c>
       <c r="I281" s="3" t="s">
         <v>15</v>
@@ -19420,13 +19417,13 @@
         <v>123</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G289" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="H289" s="4" t="s">
         <v>487</v>
-      </c>
-      <c r="H289" s="4" t="s">
-        <v>488</v>
       </c>
       <c r="I289" s="3" t="s">
         <v>15</v>
@@ -19452,13 +19449,13 @@
         <v>123</v>
       </c>
       <c r="F290" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G290" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="G290" s="4" t="s">
+      <c r="H290" s="4" t="s">
         <v>490</v>
-      </c>
-      <c r="H290" s="4" t="s">
-        <v>491</v>
       </c>
       <c r="I290" s="3" t="s">
         <v>15</v>
@@ -19487,7 +19484,7 @@
         <v>35</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="I291" s="3" t="s">
         <v>15</v>
@@ -19516,7 +19513,7 @@
         <v>35</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="I292" s="3" t="s">
         <v>15</v>
@@ -19545,10 +19542,10 @@
         <v>35</v>
       </c>
       <c r="G293" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H293" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="H293" s="4" t="s">
-        <v>496</v>
       </c>
       <c r="I293" s="3" t="s">
         <v>15</v>
@@ -19577,10 +19574,10 @@
         <v>35</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H294" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I294" s="3" t="s">
         <v>15</v>
@@ -19609,10 +19606,10 @@
         <v>35</v>
       </c>
       <c r="G295" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="H295" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="H295" s="4" t="s">
-        <v>493</v>
       </c>
       <c r="I295" s="3" t="s">
         <v>15</v>
@@ -19641,7 +19638,7 @@
         <v>35</v>
       </c>
       <c r="G296" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I296" s="3" t="s">
         <v>15</v>
@@ -19670,10 +19667,10 @@
         <v>35</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H297" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I297" s="3" t="s">
         <v>15</v>
@@ -19702,10 +19699,10 @@
         <v>35</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H298" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I298" s="3" t="s">
         <v>15</v>
@@ -19734,10 +19731,10 @@
         <v>20</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H299" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I299" s="3" t="s">
         <v>15</v>
@@ -19766,10 +19763,10 @@
         <v>141</v>
       </c>
       <c r="G300" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="H300" s="4" t="s">
         <v>508</v>
-      </c>
-      <c r="H300" s="4" t="s">
-        <v>509</v>
       </c>
       <c r="I300" s="3" t="s">
         <v>15</v>
@@ -19798,7 +19795,7 @@
         <v>20</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I301" s="3" t="s">
         <v>15</v>
@@ -19827,10 +19824,10 @@
         <v>35</v>
       </c>
       <c r="G302" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="H302" s="4" t="s">
         <v>510</v>
-      </c>
-      <c r="H302" s="4" t="s">
-        <v>511</v>
       </c>
       <c r="I302" s="3" t="s">
         <v>15</v>
@@ -19859,10 +19856,10 @@
         <v>35</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H303" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I303" s="3" t="s">
         <v>15</v>
@@ -19891,10 +19888,10 @@
         <v>35</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H304" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I304" s="3" t="s">
         <v>15</v>
@@ -19923,10 +19920,10 @@
         <v>141</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H305" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I305" s="3" t="s">
         <v>15</v>
@@ -19955,10 +19952,10 @@
         <v>20</v>
       </c>
       <c r="G306" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H306" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="H306" s="4" t="s">
-        <v>505</v>
       </c>
       <c r="I306" s="3" t="s">
         <v>15</v>
@@ -20176,10 +20173,10 @@
         <v>35</v>
       </c>
       <c r="G313" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H313" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I313" s="3" t="s">
         <v>15</v>
@@ -20208,10 +20205,10 @@
         <v>35</v>
       </c>
       <c r="G314" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H314" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I314" s="3" t="s">
         <v>15</v>
@@ -20301,10 +20298,10 @@
         <v>141</v>
       </c>
       <c r="G317" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="H317" s="4" t="s">
         <v>642</v>
-      </c>
-      <c r="H317" s="4" t="s">
-        <v>643</v>
       </c>
       <c r="I317" s="3" t="s">
         <v>15</v>
@@ -20336,7 +20333,7 @@
         <v>200</v>
       </c>
       <c r="H318" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I318" s="3" t="s">
         <v>15</v>
@@ -20365,7 +20362,7 @@
         <v>35</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="I319" s="3" t="s">
         <v>15</v>
@@ -20394,10 +20391,10 @@
         <v>35</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H320" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="I320" s="3" t="s">
         <v>15</v>
@@ -20426,10 +20423,10 @@
         <v>35</v>
       </c>
       <c r="G321" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H321" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="I321" s="3" t="s">
         <v>15</v>
@@ -20458,10 +20455,10 @@
         <v>35</v>
       </c>
       <c r="G322" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H322" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I322" s="3" t="s">
         <v>15</v>
@@ -20490,10 +20487,10 @@
         <v>35</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H323" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I323" s="3" t="s">
         <v>15</v>
@@ -20522,7 +20519,7 @@
         <v>35</v>
       </c>
       <c r="G324" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I324" s="3" t="s">
         <v>15</v>
@@ -20551,10 +20548,10 @@
         <v>35</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H325" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I325" s="3" t="s">
         <v>15</v>
@@ -20583,10 +20580,10 @@
         <v>35</v>
       </c>
       <c r="G326" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H326" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I326" s="3" t="s">
         <v>15</v>
@@ -20615,10 +20612,10 @@
         <v>35</v>
       </c>
       <c r="G327" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H327" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I327" s="3" t="s">
         <v>15</v>
@@ -20647,10 +20644,10 @@
         <v>35</v>
       </c>
       <c r="G328" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H328" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I328" s="3" t="s">
         <v>15</v>
@@ -20679,10 +20676,10 @@
         <v>35</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H329" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I329" s="3" t="s">
         <v>15</v>
@@ -20711,10 +20708,10 @@
         <v>35</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H330" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I330" s="3" t="s">
         <v>15</v>
@@ -20743,10 +20740,10 @@
         <v>35</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H331" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I331" s="3" t="s">
         <v>15</v>
@@ -20775,10 +20772,10 @@
         <v>35</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H332" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I332" s="3" t="s">
         <v>15</v>
@@ -20807,10 +20804,10 @@
         <v>35</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H333" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I333" s="3" t="s">
         <v>15</v>
@@ -20839,10 +20836,10 @@
         <v>35</v>
       </c>
       <c r="G334" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="H334" s="4" t="s">
         <v>536</v>
-      </c>
-      <c r="H334" s="4" t="s">
-        <v>537</v>
       </c>
       <c r="I334" s="3" t="s">
         <v>15</v>
@@ -20871,7 +20868,7 @@
         <v>35</v>
       </c>
       <c r="G335" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I335" s="3" t="s">
         <v>15</v>
@@ -20958,10 +20955,10 @@
         <v>141</v>
       </c>
       <c r="G338" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H338" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I338" s="3" t="s">
         <v>15</v>
@@ -20990,10 +20987,10 @@
         <v>35</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H339" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I339" s="3" t="s">
         <v>15</v>
@@ -21022,10 +21019,10 @@
         <v>35</v>
       </c>
       <c r="G340" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H340" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I340" s="3" t="s">
         <v>15</v>
@@ -21054,7 +21051,7 @@
         <v>35</v>
       </c>
       <c r="G341" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="I341" s="3" t="s">
         <v>15</v>
@@ -21083,10 +21080,10 @@
         <v>141</v>
       </c>
       <c r="G342" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="H342" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="H342" s="4" t="s">
-        <v>896</v>
       </c>
       <c r="I342" s="3" t="s">
         <v>15</v>
@@ -21112,10 +21109,10 @@
         <v>116</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H343" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="I343" s="3" t="s">
         <v>15</v>
@@ -21144,7 +21141,7 @@
         <v>35</v>
       </c>
       <c r="G344" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I344" s="3" t="s">
         <v>15</v>
@@ -21173,10 +21170,10 @@
         <v>35</v>
       </c>
       <c r="G345" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H345" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="I345" s="3" t="s">
         <v>15</v>
@@ -21205,7 +21202,7 @@
         <v>35</v>
       </c>
       <c r="G346" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I346" s="3" t="s">
         <v>15</v>
@@ -21234,7 +21231,7 @@
         <v>35</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="I347" s="3" t="s">
         <v>15</v>
@@ -21263,7 +21260,7 @@
         <v>35</v>
       </c>
       <c r="G348" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I348" s="3" t="s">
         <v>15</v>
@@ -21292,10 +21289,10 @@
         <v>141</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H349" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I349" s="3" t="s">
         <v>15</v>
@@ -21324,10 +21321,10 @@
         <v>35</v>
       </c>
       <c r="G350" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H350" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="H350" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="I350" s="3" t="s">
         <v>15</v>
@@ -21356,10 +21353,10 @@
         <v>35</v>
       </c>
       <c r="G351" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H351" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I351" s="3" t="s">
         <v>15</v>
@@ -21388,10 +21385,10 @@
         <v>141</v>
       </c>
       <c r="G352" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H352" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I352" s="3" t="s">
         <v>15</v>
@@ -21420,10 +21417,10 @@
         <v>20</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H353" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I353" s="3" t="s">
         <v>15</v>
@@ -21452,7 +21449,7 @@
         <v>35</v>
       </c>
       <c r="G354" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="I354" s="3" t="s">
         <v>15</v>
@@ -21481,7 +21478,7 @@
         <v>35</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I355" s="3" t="s">
         <v>15</v>
@@ -21510,7 +21507,7 @@
         <v>35</v>
       </c>
       <c r="G356" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I356" s="3" t="s">
         <v>15</v>
@@ -21539,10 +21536,10 @@
         <v>35</v>
       </c>
       <c r="G357" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="H357" s="4" t="s">
         <v>903</v>
-      </c>
-      <c r="H357" s="4" t="s">
-        <v>904</v>
       </c>
       <c r="I357" s="3" t="s">
         <v>15</v>
@@ -21600,10 +21597,10 @@
         <v>35</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H359" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I359" s="3" t="s">
         <v>15</v>
@@ -21632,10 +21629,10 @@
         <v>141</v>
       </c>
       <c r="G360" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="H360" s="4" t="s">
         <v>552</v>
-      </c>
-      <c r="H360" s="4" t="s">
-        <v>553</v>
       </c>
       <c r="I360" s="3" t="s">
         <v>15</v>
@@ -21664,10 +21661,10 @@
         <v>141</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H361" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I361" s="3" t="s">
         <v>15</v>
@@ -21696,10 +21693,10 @@
         <v>35</v>
       </c>
       <c r="G362" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="H362" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="H362" s="4" t="s">
-        <v>556</v>
       </c>
       <c r="I362" s="3" t="s">
         <v>15</v>
@@ -21728,10 +21725,10 @@
         <v>20</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H363" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I363" s="3" t="s">
         <v>15</v>
@@ -21760,7 +21757,7 @@
         <v>20</v>
       </c>
       <c r="G364" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I364" s="3" t="s">
         <v>15</v>
@@ -21789,7 +21786,7 @@
         <v>20</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I365" s="3" t="s">
         <v>15</v>
@@ -21818,7 +21815,7 @@
         <v>35</v>
       </c>
       <c r="G366" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I366" s="3" t="s">
         <v>15</v>
@@ -21838,16 +21835,16 @@
         <v>207</v>
       </c>
       <c r="D367" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I367" s="3" t="s">
         <v>15</v>
@@ -21863,20 +21860,20 @@
       <c r="B368" s="3">
         <v>321</v>
       </c>
-      <c r="C368" s="9" t="s">
+      <c r="C368" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D368" s="3">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F368" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G368" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I368" s="3" t="s">
         <v>15</v>
@@ -21896,7 +21893,7 @@
         <v>207</v>
       </c>
       <c r="D369" s="3">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>123</v>
@@ -21905,7 +21902,7 @@
         <v>35</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I369" s="3" t="s">
         <v>15</v>
@@ -21914,18 +21911,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A370" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B370" s="3">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D370" s="3">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>123</v>
@@ -21934,13 +21931,16 @@
         <v>35</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>229</v>
+        <v>558</v>
+      </c>
+      <c r="H370" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="I370" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J370" s="8" t="s">
-        <v>48</v>
+      <c r="J370" s="8" t="d">
+        <v>2026-07-02</v>
       </c>
     </row>
     <row r="371" spans="1:10" ht="51" x14ac:dyDescent="0.2">
@@ -21954,7 +21954,7 @@
         <v>207</v>
       </c>
       <c r="D371" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>123</v>
@@ -21963,7 +21963,7 @@
         <v>35</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H371" s="4" t="s">
         <v>561</v>
@@ -21975,7 +21975,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A372" s="3" t="s">
         <v>207</v>
       </c>
@@ -21986,19 +21986,19 @@
         <v>207</v>
       </c>
       <c r="D372" s="3">
-        <v>9</v>
+        <v>320</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G372" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="H372" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="H372" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="I372" s="3" t="s">
         <v>15</v>
@@ -22007,39 +22007,36 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A373" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B373" s="3">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D373" s="3">
-        <v>320</v>
+        <v>31</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="H373" s="4" t="s">
-        <v>560</v>
+        <v>233</v>
       </c>
       <c r="I373" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J373" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
         <v>207</v>
       </c>
@@ -22050,16 +22047,19 @@
         <v>207</v>
       </c>
       <c r="D374" s="3">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G374" s="4" t="s">
-        <v>234</v>
+        <v>137</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="I374" s="3" t="s">
         <v>15</v>
@@ -22068,7 +22068,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
         <v>207</v>
       </c>
@@ -22079,19 +22079,19 @@
         <v>207</v>
       </c>
       <c r="D375" s="3">
-        <v>151</v>
+        <v>340</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H375" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I375" s="3" t="s">
         <v>15</v>
@@ -22100,36 +22100,36 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A376" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B376" s="3">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D376" s="3">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G376" s="4" t="s">
-        <v>139</v>
+        <v>906</v>
       </c>
       <c r="H376" s="4" t="s">
-        <v>140</v>
+        <v>907</v>
       </c>
       <c r="I376" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J376" s="8" t="d">
-        <v>2026-06-29</v>
+        <v>2026-08-07</v>
       </c>
     </row>
     <row r="377" spans="1:10" ht="68" x14ac:dyDescent="0.2">
@@ -22143,7 +22143,7 @@
         <v>207</v>
       </c>
       <c r="D377" s="3">
-        <v>68</v>
+        <v>341</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>116</v>
@@ -22152,10 +22152,10 @@
         <v>35</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="H377" s="4" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="I377" s="3" t="s">
         <v>15</v>
@@ -22164,18 +22164,18 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A378" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B378" s="3">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D378" s="3">
-        <v>341</v>
+        <v>32</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>116</v>
@@ -22184,10 +22184,7 @@
         <v>35</v>
       </c>
       <c r="G378" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="H378" s="4" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="I378" s="3" t="s">
         <v>15</v>
@@ -22196,7 +22193,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A379" s="3" t="s">
         <v>207</v>
       </c>
@@ -22207,7 +22204,7 @@
         <v>207</v>
       </c>
       <c r="D379" s="3">
-        <v>32</v>
+        <v>327</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>116</v>
@@ -22216,7 +22213,7 @@
         <v>35</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="I379" s="3" t="s">
         <v>15</v>
@@ -22225,33 +22222,33 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A380" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B380" s="3">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D380" s="3">
-        <v>327</v>
+        <v>141</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>909</v>
+        <v>241</v>
       </c>
       <c r="I380" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J380" s="8" t="d">
-        <v>2026-08-07</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="381" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -22265,10 +22262,10 @@
         <v>207</v>
       </c>
       <c r="D381" s="3">
-        <v>141</v>
+        <v>339</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>141</v>
@@ -22283,7 +22280,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
         <v>207</v>
       </c>
@@ -22294,16 +22291,16 @@
         <v>207</v>
       </c>
       <c r="D382" s="3">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>141</v>
       </c>
       <c r="G382" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I382" s="3" t="s">
         <v>15</v>
@@ -22312,27 +22309,27 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B383" s="3">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D383" s="3">
-        <v>340</v>
+        <v>133</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I383" s="3" t="s">
         <v>15</v>
@@ -22341,7 +22338,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
         <v>207</v>
       </c>
@@ -22352,13 +22349,13 @@
         <v>207</v>
       </c>
       <c r="D384" s="3">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G384" s="4" t="s">
         <v>245</v>
@@ -22370,7 +22367,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A385" s="3" t="s">
         <v>207</v>
       </c>
@@ -22381,16 +22378,16 @@
         <v>207</v>
       </c>
       <c r="D385" s="3">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="I385" s="3" t="s">
         <v>15</v>
@@ -22399,36 +22396,39 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="386" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B386" s="3">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D386" s="3">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G386" s="4" t="s">
-        <v>244</v>
+        <v>567</v>
+      </c>
+      <c r="H386" s="4" t="s">
+        <v>570</v>
       </c>
       <c r="I386" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J386" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A387" s="3" t="s">
         <v>207</v>
       </c>
@@ -22439,19 +22439,19 @@
         <v>207</v>
       </c>
       <c r="D387" s="3">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G387" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="H387" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="H387" s="4" t="s">
-        <v>571</v>
       </c>
       <c r="I387" s="3" t="s">
         <v>15</v>
@@ -22471,19 +22471,19 @@
         <v>207</v>
       </c>
       <c r="D388" s="3">
+        <v>143</v>
+      </c>
+      <c r="E388" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F388" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E388" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F388" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G388" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H388" s="4" t="s">
-        <v>569</v>
+        <v>632</v>
       </c>
       <c r="I388" s="3" t="s">
         <v>15</v>
@@ -22492,7 +22492,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A389" s="3" t="s">
         <v>207</v>
       </c>
@@ -22503,7 +22503,7 @@
         <v>207</v>
       </c>
       <c r="D389" s="3">
-        <v>143</v>
+        <v>340</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>123</v>
@@ -22512,10 +22512,10 @@
         <v>141</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="H389" s="4" t="s">
-        <v>633</v>
+        <v>569</v>
       </c>
       <c r="I389" s="3" t="s">
         <v>15</v>
@@ -22535,19 +22535,19 @@
         <v>207</v>
       </c>
       <c r="D390" s="3">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H390" s="4" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="I390" s="3" t="s">
         <v>15</v>
@@ -22561,25 +22561,22 @@
         <v>207</v>
       </c>
       <c r="B391" s="3">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D391" s="3">
-        <v>341</v>
+        <v>9</v>
       </c>
       <c r="E391" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="H391" s="4" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="I391" s="3" t="s">
         <v>15</v>
@@ -22588,7 +22585,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A392" s="3" t="s">
         <v>207</v>
       </c>
@@ -22599,16 +22596,19 @@
         <v>207</v>
       </c>
       <c r="D392" s="3">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G392" s="4" t="s">
-        <v>578</v>
+        <v>574</v>
+      </c>
+      <c r="H392" s="4" t="s">
+        <v>584</v>
       </c>
       <c r="I392" s="3" t="s">
         <v>15</v>
@@ -22617,7 +22617,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
         <v>207</v>
       </c>
@@ -22628,7 +22628,7 @@
         <v>207</v>
       </c>
       <c r="D393" s="3">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E393" s="3" t="s">
         <v>123</v>
@@ -22637,10 +22637,10 @@
         <v>35</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="H393" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I393" s="3" t="s">
         <v>15</v>
@@ -22660,7 +22660,7 @@
         <v>207</v>
       </c>
       <c r="D394" s="3">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>123</v>
@@ -22669,10 +22669,10 @@
         <v>35</v>
       </c>
       <c r="G394" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H394" s="4" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="I394" s="3" t="s">
         <v>15</v>
@@ -22681,7 +22681,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A395" s="3" t="s">
         <v>207</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>207</v>
       </c>
       <c r="D395" s="3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E395" s="3" t="s">
         <v>123</v>
@@ -22701,7 +22701,7 @@
         <v>35</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="H395" s="4" t="s">
         <v>582</v>
@@ -22713,7 +22713,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
         <v>207</v>
       </c>
@@ -22724,19 +22724,19 @@
         <v>207</v>
       </c>
       <c r="D396" s="3">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E396" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G396" s="4" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="H396" s="4" t="s">
-        <v>583</v>
+        <v>633</v>
       </c>
       <c r="I396" s="3" t="s">
         <v>15</v>
@@ -22756,19 +22756,19 @@
         <v>207</v>
       </c>
       <c r="D397" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H397" s="4" t="s">
-        <v>634</v>
+        <v>580</v>
       </c>
       <c r="I397" s="3" t="s">
         <v>15</v>
@@ -22777,7 +22777,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
         <v>207</v>
       </c>
@@ -22788,19 +22788,19 @@
         <v>207</v>
       </c>
       <c r="D398" s="3">
-        <v>143</v>
+        <v>340</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G398" s="4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H398" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="I398" s="3" t="s">
         <v>15</v>
@@ -22809,7 +22809,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="399" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
         <v>207</v>
       </c>
@@ -22820,19 +22820,19 @@
         <v>207</v>
       </c>
       <c r="D399" s="3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H399" s="4" t="s">
-        <v>580</v>
+        <v>643</v>
       </c>
       <c r="I399" s="3" t="s">
         <v>15</v>
@@ -22841,7 +22841,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:10" ht="136" x14ac:dyDescent="0.2">
       <c r="A400" s="3" t="s">
         <v>207</v>
       </c>
@@ -22852,7 +22852,7 @@
         <v>207</v>
       </c>
       <c r="D400" s="3">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>123</v>
@@ -22861,10 +22861,10 @@
         <v>35</v>
       </c>
       <c r="G400" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H400" s="4" t="s">
-        <v>644</v>
+        <v>585</v>
       </c>
       <c r="I400" s="3" t="s">
         <v>15</v>
@@ -22873,30 +22873,27 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="401" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:10" ht="204" x14ac:dyDescent="0.2">
       <c r="A401" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B401" s="3">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D401" s="3">
-        <v>350</v>
+        <v>8</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="H401" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I401" s="3" t="s">
         <v>15</v>
@@ -22905,7 +22902,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="402" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A402" s="3" t="s">
         <v>207</v>
       </c>
@@ -22916,16 +22913,16 @@
         <v>207</v>
       </c>
       <c r="D402" s="3">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G402" s="4" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="I402" s="3" t="s">
         <v>15</v>
@@ -22934,7 +22931,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="403" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:10" ht="170" x14ac:dyDescent="0.2">
       <c r="A403" s="3" t="s">
         <v>207</v>
       </c>
@@ -22945,7 +22942,7 @@
         <v>207</v>
       </c>
       <c r="D403" s="3">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>123</v>
@@ -22954,7 +22951,10 @@
         <v>35</v>
       </c>
       <c r="G403" s="4" t="s">
-        <v>647</v>
+        <v>588</v>
+      </c>
+      <c r="H403" s="4" t="s">
+        <v>634</v>
       </c>
       <c r="I403" s="3" t="s">
         <v>15</v>
@@ -22963,7 +22963,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="404" spans="1:10" ht="170" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A404" s="3" t="s">
         <v>207</v>
       </c>
@@ -22974,10 +22974,10 @@
         <v>207</v>
       </c>
       <c r="D404" s="3">
-        <v>148</v>
+        <v>340</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>35</v>
@@ -22986,7 +22986,7 @@
         <v>589</v>
       </c>
       <c r="H404" s="4" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="I404" s="3" t="s">
         <v>15</v>
@@ -23006,7 +23006,7 @@
         <v>207</v>
       </c>
       <c r="D405" s="3">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E405" s="3" t="s">
         <v>116</v>
@@ -23038,7 +23038,7 @@
         <v>207</v>
       </c>
       <c r="D406" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E406" s="3" t="s">
         <v>116</v>
@@ -23059,39 +23059,36 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="407" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B407" s="3">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D407" s="3">
-        <v>342</v>
+        <v>3</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F407" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G407" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="H407" s="4" t="s">
-        <v>650</v>
+        <v>252</v>
       </c>
       <c r="I407" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J407" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
         <v>207</v>
       </c>
@@ -23102,16 +23099,19 @@
         <v>207</v>
       </c>
       <c r="D408" s="3">
-        <v>3</v>
+        <v>340</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G408" s="4" t="s">
-        <v>253</v>
+        <v>246</v>
+      </c>
+      <c r="H408" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="I408" s="3" t="s">
         <v>15</v>
@@ -23120,7 +23120,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="409" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
         <v>207</v>
       </c>
@@ -23131,7 +23131,7 @@
         <v>207</v>
       </c>
       <c r="D409" s="3">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>116</v>
@@ -23152,7 +23152,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="410" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
         <v>207</v>
       </c>
@@ -23163,7 +23163,7 @@
         <v>207</v>
       </c>
       <c r="D410" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>116</v>
@@ -23184,18 +23184,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="411" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B411" s="3">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D411" s="3">
-        <v>342</v>
+        <v>32</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>116</v>
@@ -23204,19 +23204,19 @@
         <v>35</v>
       </c>
       <c r="G411" s="4" t="s">
-        <v>249</v>
+        <v>914</v>
       </c>
       <c r="H411" s="4" t="s">
-        <v>252</v>
+        <v>915</v>
       </c>
       <c r="I411" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J411" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
         <v>207</v>
       </c>
@@ -23227,19 +23227,16 @@
         <v>207</v>
       </c>
       <c r="D412" s="3">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G412" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="H412" s="4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="I412" s="3" t="s">
         <v>15</v>
@@ -23248,7 +23245,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="413" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A413" s="3" t="s">
         <v>207</v>
       </c>
@@ -23259,13 +23256,13 @@
         <v>207</v>
       </c>
       <c r="D413" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>116</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G413" s="4" t="s">
         <v>913</v>
@@ -23277,7 +23274,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="414" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
         <v>207</v>
       </c>
@@ -23288,16 +23285,16 @@
         <v>207</v>
       </c>
       <c r="D414" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G414" s="4" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="I414" s="3" t="s">
         <v>15</v>
@@ -23306,7 +23303,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="415" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A415" s="3" t="s">
         <v>207</v>
       </c>
@@ -23317,7 +23314,7 @@
         <v>207</v>
       </c>
       <c r="D415" s="3">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>123</v>
@@ -23326,7 +23323,7 @@
         <v>35</v>
       </c>
       <c r="G415" s="4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="I415" s="3" t="s">
         <v>15</v>
@@ -23335,7 +23332,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="416" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A416" s="3" t="s">
         <v>207</v>
       </c>
@@ -23346,7 +23343,7 @@
         <v>207</v>
       </c>
       <c r="D416" s="3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>123</v>
@@ -23355,7 +23352,7 @@
         <v>35</v>
       </c>
       <c r="G416" s="4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="I416" s="3" t="s">
         <v>15</v>
@@ -23364,7 +23361,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="417" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
         <v>207</v>
       </c>
@@ -23375,16 +23372,19 @@
         <v>207</v>
       </c>
       <c r="D417" s="3">
-        <v>158</v>
+        <v>350</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G417" s="4" t="s">
-        <v>918</v>
+        <v>910</v>
+      </c>
+      <c r="H417" s="4" t="s">
+        <v>911</v>
       </c>
       <c r="I417" s="3" t="s">
         <v>15</v>
@@ -23393,7 +23393,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="418" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A418" s="3" t="s">
         <v>207</v>
       </c>
@@ -23404,19 +23404,16 @@
         <v>207</v>
       </c>
       <c r="D418" s="3">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G418" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="H418" s="4" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="I418" s="3" t="s">
         <v>15</v>
@@ -23425,33 +23422,33 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="419" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A419" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B419" s="3">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D419" s="3">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>917</v>
+        <v>253</v>
       </c>
       <c r="I419" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J419" s="8" t="d">
-        <v>2026-08-07</v>
+        <v>2026-06-29</v>
       </c>
     </row>
     <row r="420" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -23465,13 +23462,13 @@
         <v>207</v>
       </c>
       <c r="D420" s="3">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G420" s="4" t="s">
         <v>254</v>
@@ -23483,7 +23480,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="421" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
         <v>207</v>
       </c>
@@ -23494,16 +23491,19 @@
         <v>207</v>
       </c>
       <c r="D421" s="3">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="E421" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G421" s="4" t="s">
-        <v>255</v>
+        <v>270</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="I421" s="3" t="s">
         <v>15</v>
@@ -23512,18 +23512,18 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="422" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B422" s="3">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D422" s="3">
-        <v>352</v>
+        <v>32</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>123</v>
@@ -23532,19 +23532,19 @@
         <v>35</v>
       </c>
       <c r="G422" s="4" t="s">
-        <v>271</v>
+        <v>921</v>
       </c>
       <c r="H422" s="4" t="s">
-        <v>272</v>
+        <v>922</v>
       </c>
       <c r="I422" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J422" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A423" s="3" t="s">
         <v>207</v>
       </c>
@@ -23555,7 +23555,7 @@
         <v>207</v>
       </c>
       <c r="D423" s="3">
-        <v>32</v>
+        <v>340</v>
       </c>
       <c r="E423" s="3" t="s">
         <v>123</v>
@@ -23564,10 +23564,10 @@
         <v>35</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H423" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I423" s="3" t="s">
         <v>15</v>
@@ -23576,7 +23576,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="424" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A424" s="3" t="s">
         <v>207</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>207</v>
       </c>
       <c r="D424" s="3">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>123</v>
@@ -23596,10 +23596,10 @@
         <v>35</v>
       </c>
       <c r="G424" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H424" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I424" s="3" t="s">
         <v>15</v>
@@ -23608,59 +23608,56 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="425" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:10" ht="153" x14ac:dyDescent="0.2">
       <c r="A425" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B425" s="3">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D425" s="3">
-        <v>341</v>
+        <v>174</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>926</v>
-      </c>
-      <c r="H425" s="4" t="s">
-        <v>927</v>
+        <v>592</v>
       </c>
       <c r="I425" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J425" s="8" t="d">
-        <v>2026-08-07</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A426" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B426" s="3">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D426" s="3">
-        <v>174</v>
+        <v>32</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>593</v>
+        <v>651</v>
       </c>
       <c r="I426" s="3" t="s">
         <v>15</v>
@@ -23669,7 +23666,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="427" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:10" ht="119" x14ac:dyDescent="0.2">
       <c r="A427" s="3" t="s">
         <v>207</v>
       </c>
@@ -23680,16 +23677,19 @@
         <v>207</v>
       </c>
       <c r="D427" s="3">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G427" s="4" t="s">
-        <v>652</v>
+        <v>594</v>
+      </c>
+      <c r="H427" s="4" t="s">
+        <v>593</v>
       </c>
       <c r="I427" s="3" t="s">
         <v>15</v>
@@ -23698,7 +23698,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="119" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
         <v>207</v>
       </c>
@@ -23709,7 +23709,7 @@
         <v>207</v>
       </c>
       <c r="D428" s="3">
-        <v>174</v>
+        <v>340</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>116</v>
@@ -23718,10 +23718,10 @@
         <v>35</v>
       </c>
       <c r="G428" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H428" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="I428" s="3" t="s">
         <v>15</v>
@@ -23741,7 +23741,7 @@
         <v>207</v>
       </c>
       <c r="D429" s="3">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>116</v>
@@ -23750,7 +23750,7 @@
         <v>35</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H429" s="4" t="s">
         <v>598</v>
@@ -23773,7 +23773,7 @@
         <v>207</v>
       </c>
       <c r="D430" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>116</v>
@@ -23782,7 +23782,7 @@
         <v>35</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H430" s="4" t="s">
         <v>599</v>
@@ -23794,7 +23794,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A431" s="3" t="s">
         <v>207</v>
       </c>
@@ -23805,7 +23805,7 @@
         <v>207</v>
       </c>
       <c r="D431" s="3">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="E431" s="3" t="s">
         <v>116</v>
@@ -23814,10 +23814,10 @@
         <v>35</v>
       </c>
       <c r="G431" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H431" s="4" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="I431" s="3" t="s">
         <v>15</v>
@@ -23826,18 +23826,18 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="432" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A432" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B432" s="3">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D432" s="3">
-        <v>370</v>
+        <v>327</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>116</v>
@@ -23846,10 +23846,10 @@
         <v>35</v>
       </c>
       <c r="G432" s="4" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="H432" s="4" t="s">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="I432" s="3" t="s">
         <v>15</v>
@@ -23869,10 +23869,10 @@
         <v>207</v>
       </c>
       <c r="D433" s="3">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>35</v>
@@ -23881,7 +23881,7 @@
         <v>602</v>
       </c>
       <c r="H433" s="4" t="s">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="I433" s="3" t="s">
         <v>15</v>
@@ -23890,7 +23890,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="434" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A434" s="3" t="s">
         <v>207</v>
       </c>
@@ -23901,7 +23901,7 @@
         <v>207</v>
       </c>
       <c r="D434" s="3">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E434" s="3" t="s">
         <v>123</v>
@@ -23910,10 +23910,10 @@
         <v>35</v>
       </c>
       <c r="G434" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H434" s="4" t="s">
         <v>603</v>
-      </c>
-      <c r="H434" s="4" t="s">
-        <v>605</v>
       </c>
       <c r="I434" s="3" t="s">
         <v>15</v>
@@ -23922,18 +23922,18 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="435" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A435" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B435" s="3">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D435" s="3">
-        <v>352</v>
+        <v>32</v>
       </c>
       <c r="E435" s="3" t="s">
         <v>123</v>
@@ -23942,19 +23942,19 @@
         <v>35</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>601</v>
+        <v>273</v>
       </c>
       <c r="H435" s="4" t="s">
-        <v>604</v>
+        <v>274</v>
       </c>
       <c r="I435" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J435" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A436" s="3" t="s">
         <v>207</v>
       </c>
@@ -23965,19 +23965,16 @@
         <v>207</v>
       </c>
       <c r="D436" s="3">
-        <v>32</v>
+        <v>352</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G436" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="H436" s="4" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="I436" s="3" t="s">
         <v>15</v>
@@ -23997,7 +23994,7 @@
         <v>207</v>
       </c>
       <c r="D437" s="3">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>116</v>
@@ -24006,7 +24003,7 @@
         <v>35</v>
       </c>
       <c r="G437" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I437" s="3" t="s">
         <v>15</v>
@@ -24026,7 +24023,7 @@
         <v>207</v>
       </c>
       <c r="D438" s="3">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>116</v>
@@ -24035,7 +24032,7 @@
         <v>35</v>
       </c>
       <c r="G438" s="4" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="I438" s="3" t="s">
         <v>15</v>
@@ -24044,36 +24041,39 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="439" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A439" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B439" s="3">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D439" s="3">
-        <v>374</v>
+        <v>16</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>273</v>
+        <v>932</v>
+      </c>
+      <c r="H439" s="4" t="s">
+        <v>933</v>
       </c>
       <c r="I439" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J439" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+        <v>2026-08-07</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A440" s="3" t="s">
         <v>207</v>
       </c>
@@ -24084,19 +24084,19 @@
         <v>207</v>
       </c>
       <c r="D440" s="3">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="H440" s="4" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="I440" s="3" t="s">
         <v>15</v>
@@ -24105,7 +24105,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="441" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A441" s="3" t="s">
         <v>207</v>
       </c>
@@ -24116,19 +24116,19 @@
         <v>207</v>
       </c>
       <c r="D441" s="3">
-        <v>141</v>
+        <v>380</v>
       </c>
       <c r="E441" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G441" s="4" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="H441" s="4" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="I441" s="3" t="s">
         <v>15</v>
@@ -24137,7 +24137,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="442" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
         <v>207</v>
       </c>
@@ -24148,19 +24148,19 @@
         <v>207</v>
       </c>
       <c r="D442" s="3">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="H442" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I442" s="3" t="s">
         <v>15</v>
@@ -24169,18 +24169,18 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="443" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B443" s="3">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D443" s="3">
-        <v>382</v>
+        <v>11</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>123</v>
@@ -24189,10 +24189,10 @@
         <v>141</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>929</v>
+        <v>935</v>
       </c>
       <c r="H443" s="4" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="I443" s="3" t="s">
         <v>15</v>
@@ -24201,7 +24201,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="444" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A444" s="3" t="s">
         <v>207</v>
       </c>
@@ -24212,7 +24212,7 @@
         <v>207</v>
       </c>
       <c r="D444" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>123</v>
@@ -24224,7 +24224,7 @@
         <v>936</v>
       </c>
       <c r="H444" s="4" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="I444" s="3" t="s">
         <v>15</v>
@@ -24244,7 +24244,7 @@
         <v>207</v>
       </c>
       <c r="D445" s="3">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>123</v>
@@ -24253,7 +24253,7 @@
         <v>141</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="H445" s="4" t="s">
         <v>938</v>
@@ -24265,7 +24265,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="446" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A446" s="3" t="s">
         <v>207</v>
       </c>
@@ -24276,20 +24276,17 @@
         <v>207</v>
       </c>
       <c r="D446" s="3">
-        <v>32</v>
+        <v>380</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G446" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="H446" s="4" t="s">
-        <v>939</v>
-      </c>
       <c r="I446" s="3" t="s">
         <v>15</v>
       </c>
@@ -24297,7 +24294,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="447" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A447" s="3" t="s">
         <v>207</v>
       </c>
@@ -24308,15 +24305,18 @@
         <v>207</v>
       </c>
       <c r="D447" s="3">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G447" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="H447" s="4" t="s">
         <v>941</v>
       </c>
       <c r="I447" s="3" t="s">
@@ -24337,7 +24337,7 @@
         <v>207</v>
       </c>
       <c r="D448" s="3">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E448" s="3" t="s">
         <v>123</v>
@@ -24346,7 +24346,7 @@
         <v>35</v>
       </c>
       <c r="G448" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H448" s="4" t="s">
         <v>942</v>
@@ -24358,21 +24358,21 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B449" s="3">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C449" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D449" s="3">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>35</v>
@@ -24381,7 +24381,7 @@
         <v>944</v>
       </c>
       <c r="H449" s="4" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="I449" s="3" t="s">
         <v>15</v>
@@ -24390,7 +24390,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="450" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A450" s="3" t="s">
         <v>207</v>
       </c>
@@ -24401,19 +24401,19 @@
         <v>207</v>
       </c>
       <c r="D450" s="3">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F450" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H450" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="I450" s="3" t="s">
         <v>15</v>
@@ -24433,7 +24433,7 @@
         <v>207</v>
       </c>
       <c r="D451" s="3">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>123</v>
@@ -24454,30 +24454,30 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="452" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A452" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B452" s="3">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C452" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D452" s="3">
-        <v>382</v>
+        <v>32</v>
       </c>
       <c r="E452" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G452" s="4" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="H452" s="4" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="I452" s="3" t="s">
         <v>15</v>
@@ -24486,7 +24486,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="453" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A453" s="3" t="s">
         <v>207</v>
       </c>
@@ -24497,7 +24497,7 @@
         <v>207</v>
       </c>
       <c r="D453" s="3">
-        <v>32</v>
+        <v>340</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>123</v>
@@ -24506,10 +24506,10 @@
         <v>141</v>
       </c>
       <c r="G453" s="4" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H453" s="4" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="I453" s="3" t="s">
         <v>15</v>
@@ -24518,7 +24518,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="454" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:10" ht="102" x14ac:dyDescent="0.2">
       <c r="A454" s="3" t="s">
         <v>207</v>
       </c>
@@ -24529,19 +24529,19 @@
         <v>207</v>
       </c>
       <c r="D454" s="3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F454" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G454" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="H454" s="4" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="I454" s="3" t="s">
         <v>15</v>
@@ -24550,7 +24550,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="455" spans="1:10" ht="102" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A455" s="3" t="s">
         <v>207</v>
       </c>
@@ -24561,7 +24561,7 @@
         <v>207</v>
       </c>
       <c r="D455" s="3">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="E455" s="3" t="s">
         <v>116</v>
@@ -24570,10 +24570,10 @@
         <v>35</v>
       </c>
       <c r="G455" s="4" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="H455" s="4" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="I455" s="3" t="s">
         <v>15</v>
@@ -24582,7 +24582,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="456" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A456" s="3" t="s">
         <v>207</v>
       </c>
@@ -24593,19 +24593,19 @@
         <v>207</v>
       </c>
       <c r="D456" s="3">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G456" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="H456" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="I456" s="3" t="s">
         <v>15</v>
@@ -24625,7 +24625,7 @@
         <v>207</v>
       </c>
       <c r="D457" s="3">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E457" s="3" t="s">
         <v>123</v>
@@ -24646,7 +24646,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="458" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A458" s="3" t="s">
         <v>207</v>
       </c>
@@ -24657,18 +24657,15 @@
         <v>207</v>
       </c>
       <c r="D458" s="3">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E458" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G458" s="4" t="s">
-        <v>955</v>
-      </c>
-      <c r="H458" s="4" t="s">
         <v>957</v>
       </c>
       <c r="I458" s="3" t="s">
@@ -24678,7 +24675,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="459" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A459" s="3" t="s">
         <v>207</v>
       </c>
@@ -24689,10 +24686,10 @@
         <v>207</v>
       </c>
       <c r="D459" s="3">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>35</v>
@@ -24700,6 +24697,9 @@
       <c r="G459" s="4" t="s">
         <v>958</v>
       </c>
+      <c r="H459" s="4" t="s">
+        <v>959</v>
+      </c>
       <c r="I459" s="3" t="s">
         <v>15</v>
       </c>
@@ -24712,25 +24712,25 @@
         <v>207</v>
       </c>
       <c r="B460" s="3">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C460" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D460" s="3">
-        <v>386</v>
+        <v>32</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="H460" s="4" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="I460" s="3" t="s">
         <v>15</v>
@@ -24739,7 +24739,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="461" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A461" s="3" t="s">
         <v>207</v>
       </c>
@@ -24750,19 +24750,16 @@
         <v>207</v>
       </c>
       <c r="D461" s="3">
-        <v>32</v>
+        <v>327</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G461" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="H461" s="4" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="I461" s="3" t="s">
         <v>15</v>
@@ -24771,7 +24768,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="462" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A462" s="3" t="s">
         <v>207</v>
       </c>
@@ -24782,7 +24779,7 @@
         <v>207</v>
       </c>
       <c r="D462" s="3">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E462" s="3" t="s">
         <v>116</v>
@@ -24791,7 +24788,7 @@
         <v>35</v>
       </c>
       <c r="G462" s="4" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="I462" s="3" t="s">
         <v>15</v>
@@ -24800,7 +24797,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="463" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A463" s="3" t="s">
         <v>207</v>
       </c>
@@ -24811,7 +24808,7 @@
         <v>207</v>
       </c>
       <c r="D463" s="3">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="E463" s="3" t="s">
         <v>116</v>
@@ -24820,7 +24817,7 @@
         <v>35</v>
       </c>
       <c r="G463" s="4" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="I463" s="3" t="s">
         <v>15</v>
@@ -24829,7 +24826,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="464" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A464" s="3" t="s">
         <v>207</v>
       </c>
@@ -24840,16 +24837,19 @@
         <v>207</v>
       </c>
       <c r="D464" s="3">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G464" s="4" t="s">
-        <v>969</v>
+        <v>979</v>
+      </c>
+      <c r="H464" s="4" t="s">
+        <v>970</v>
       </c>
       <c r="I464" s="3" t="s">
         <v>15</v>
@@ -24869,7 +24869,7 @@
         <v>207</v>
       </c>
       <c r="D465" s="3">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>123</v>
@@ -24901,7 +24901,7 @@
         <v>207</v>
       </c>
       <c r="D466" s="3">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E466" s="3" t="s">
         <v>123</v>
@@ -24910,10 +24910,10 @@
         <v>141</v>
       </c>
       <c r="G466" s="4" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="H466" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="I466" s="3" t="s">
         <v>15</v>
@@ -24922,7 +24922,7 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="467" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A467" s="3" t="s">
         <v>207</v>
       </c>
@@ -24933,19 +24933,19 @@
         <v>207</v>
       </c>
       <c r="D467" s="3">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E467" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G467" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="H467" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="I467" s="3" t="s">
         <v>15</v>
@@ -24965,16 +24965,16 @@
         <v>207</v>
       </c>
       <c r="D468" s="3">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G468" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H468" s="4" t="s">
         <v>977</v>
@@ -24986,18 +24986,18 @@
         <v>2026-08-07</v>
       </c>
     </row>
-    <row r="469" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A469" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B469" s="3">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C469" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D469" s="3">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="E469" s="3" t="s">
         <v>116</v>
@@ -25006,19 +25006,16 @@
         <v>35</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>975</v>
-      </c>
-      <c r="H469" s="4" t="s">
-        <v>978</v>
+        <v>259</v>
       </c>
       <c r="I469" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J469" s="8" t="d">
-        <v>2026-08-07</v>
-      </c>
-    </row>
-    <row r="470" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A470" s="3" t="s">
         <v>207</v>
       </c>
@@ -25029,7 +25026,7 @@
         <v>207</v>
       </c>
       <c r="D470" s="3">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E470" s="3" t="s">
         <v>116</v>
@@ -25038,7 +25035,10 @@
         <v>35</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
+      </c>
+      <c r="H470" s="4" t="s">
+        <v>258</v>
       </c>
       <c r="I470" s="3" t="s">
         <v>15</v>
@@ -25047,7 +25047,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="471" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A471" s="3" t="s">
         <v>207</v>
       </c>
@@ -25058,7 +25058,7 @@
         <v>207</v>
       </c>
       <c r="D471" s="3">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E471" s="3" t="s">
         <v>116</v>
@@ -25067,10 +25067,7 @@
         <v>35</v>
       </c>
       <c r="G471" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="H471" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I471" s="3" t="s">
         <v>15</v>
@@ -25079,7 +25076,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="472" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:10" ht="85" x14ac:dyDescent="0.2">
       <c r="A472" s="3" t="s">
         <v>207</v>
       </c>
@@ -25090,7 +25087,7 @@
         <v>207</v>
       </c>
       <c r="D472" s="3">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="E472" s="3" t="s">
         <v>116</v>
@@ -25099,7 +25096,7 @@
         <v>35</v>
       </c>
       <c r="G472" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="I472" s="3" t="s">
         <v>15</v>
@@ -25108,7 +25105,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="85" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" ht="69" x14ac:dyDescent="0.2">
       <c r="A473" s="3" t="s">
         <v>207</v>
       </c>
@@ -25119,13 +25116,13 @@
         <v>207</v>
       </c>
       <c r="D473" s="3">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G473" s="4" t="s">
         <v>261</v>
@@ -25137,24 +25134,24 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="474" spans="1:10" ht="69" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A474" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B474" s="3">
-        <v>392</v>
+        <v>440</v>
       </c>
       <c r="C474" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D474" s="3">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G474" s="4" t="s">
         <v>262</v>
@@ -25171,31 +25168,34 @@
         <v>207</v>
       </c>
       <c r="B475" s="3">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C475" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D475" s="3">
-        <v>342</v>
+        <v>119</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G475" s="4" t="s">
-        <v>263</v>
+        <v>612</v>
+      </c>
+      <c r="H475" s="4" t="s">
+        <v>636</v>
       </c>
       <c r="I475" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J475" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="476" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+        <v>2026-07-02</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" ht="153" x14ac:dyDescent="0.2">
       <c r="A476" s="3" t="s">
         <v>207</v>
       </c>
@@ -25206,19 +25206,19 @@
         <v>207</v>
       </c>
       <c r="D476" s="3">
-        <v>119</v>
+        <v>327</v>
       </c>
       <c r="E476" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G476" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="H476" s="4" t="s">
-        <v>637</v>
+        <v>659</v>
       </c>
       <c r="I476" s="3" t="s">
         <v>15</v>
@@ -25227,7 +25227,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="477" spans="1:10" ht="153" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
         <v>207</v>
       </c>
@@ -25238,19 +25238,19 @@
         <v>207</v>
       </c>
       <c r="D477" s="3">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E477" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G477" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H477" s="4" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="I477" s="3" t="s">
         <v>15</v>
@@ -25270,19 +25270,19 @@
         <v>207</v>
       </c>
       <c r="D478" s="3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G478" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H478" s="4" t="s">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="I478" s="3" t="s">
         <v>15</v>
@@ -25291,7 +25291,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="479" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A479" s="3" t="s">
         <v>207</v>
       </c>
@@ -25302,19 +25302,19 @@
         <v>207</v>
       </c>
       <c r="D479" s="3">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G479" s="4" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H479" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I479" s="3" t="s">
         <v>15</v>
@@ -25323,7 +25323,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="480" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
         <v>207</v>
       </c>
@@ -25334,19 +25334,19 @@
         <v>207</v>
       </c>
       <c r="D480" s="3">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E480" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G480" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H480" s="4" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="I480" s="3" t="s">
         <v>15</v>
@@ -25366,7 +25366,7 @@
         <v>207</v>
       </c>
       <c r="D481" s="3">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E481" s="3" t="s">
         <v>123</v>
@@ -25375,7 +25375,7 @@
         <v>35</v>
       </c>
       <c r="G481" s="4" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="H481" s="4" t="s">
         <v>616</v>
@@ -25387,7 +25387,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="482" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
         <v>207</v>
       </c>
@@ -25398,19 +25398,19 @@
         <v>207</v>
       </c>
       <c r="D482" s="3">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="E482" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G482" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H482" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I482" s="3" t="s">
         <v>15</v>
@@ -25419,7 +25419,7 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="483" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="3" t="s">
         <v>207</v>
       </c>
@@ -25430,16 +25430,16 @@
         <v>207</v>
       </c>
       <c r="D483" s="3">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E483" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G483" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H483" s="4" t="s">
         <v>619</v>
@@ -25451,39 +25451,36 @@
         <v>2026-07-02</v>
       </c>
     </row>
-    <row r="484" spans="1:10" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A484" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B484" s="3">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C484" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D484" s="3">
-        <v>446</v>
+        <v>119</v>
       </c>
       <c r="E484" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G484" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="H484" s="4" t="s">
-        <v>620</v>
+        <v>266</v>
       </c>
       <c r="I484" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J484" s="8" t="d">
-        <v>2026-07-02</v>
-      </c>
-    </row>
-    <row r="485" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+        <v>2026-06-29</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A485" s="3" t="s">
         <v>207</v>
       </c>
@@ -25494,17 +25491,20 @@
         <v>207</v>
       </c>
       <c r="D485" s="3">
-        <v>119</v>
+        <v>327</v>
       </c>
       <c r="E485" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="G485" s="4" t="s">
         <v>267</v>
       </c>
+      <c r="H485" s="4" t="s">
+        <v>658</v>
+      </c>
       <c r="I485" s="3" t="s">
         <v>15</v>
       </c>
@@ -25512,7 +25512,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="486" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A486" s="3" t="s">
         <v>207</v>
       </c>
@@ -25523,19 +25523,19 @@
         <v>207</v>
       </c>
       <c r="D486" s="3">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="E486" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G486" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="H486" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="H486" s="4" t="s">
-        <v>659</v>
       </c>
       <c r="I486" s="3" t="s">
         <v>15</v>
@@ -25544,7 +25544,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="487" spans="1:10" ht="51" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A487" s="3" t="s">
         <v>207</v>
       </c>
@@ -25555,7 +25555,7 @@
         <v>207</v>
       </c>
       <c r="D487" s="3">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E487" s="3" t="s">
         <v>116</v>
@@ -25564,7 +25564,7 @@
         <v>35</v>
       </c>
       <c r="G487" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H487" s="4" t="s">
         <v>269</v>
@@ -25576,7 +25576,7 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="488" spans="1:10" ht="68" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
         <v>207</v>
       </c>
@@ -25587,19 +25587,16 @@
         <v>207</v>
       </c>
       <c r="D488" s="3">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="H488" s="4" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I488" s="3" t="s">
         <v>15</v>
@@ -25608,78 +25605,49 @@
         <v>2026-06-29</v>
       </c>
     </row>
-    <row r="489" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:10" ht="68" x14ac:dyDescent="0.2">
       <c r="A489" s="3" t="s">
         <v>207</v>
       </c>
       <c r="B489" s="3">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C489" s="3" t="s">
         <v>207</v>
       </c>
       <c r="D489" s="3">
-        <v>345</v>
+        <v>125</v>
       </c>
       <c r="E489" s="3" t="s">
         <v>123</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>266</v>
+        <v>439</v>
       </c>
       <c r="I489" s="3" t="s">
         <v>15</v>
       </c>
       <c r="J489" s="8" t="d">
-        <v>2026-06-29</v>
-      </c>
-    </row>
-    <row r="490" spans="1:10" ht="68" x14ac:dyDescent="0.2">
-      <c r="A490" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B490" s="3">
-        <v>451</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D490" s="3">
-        <v>125</v>
-      </c>
-      <c r="E490" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F490" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G490" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="I490" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J490" s="8" t="d">
         <v>2026-06-30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J457" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J457">
-      <sortCondition ref="B2:B457"/>
-      <sortCondition ref="A2:A457"/>
-      <sortCondition ref="D2:D457"/>
-      <sortCondition ref="C2:C457"/>
+  <autoFilter ref="A1:J456" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J456">
+      <sortCondition ref="B2:B456"/>
+      <sortCondition ref="A2:A456"/>
+      <sortCondition ref="D2:D456"/>
+      <sortCondition ref="C2:C456"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J490">
-    <sortCondition ref="B2:B490"/>
-    <sortCondition ref="A2:A490"/>
-    <sortCondition ref="D2:D490"/>
-    <sortCondition ref="C2:C490"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J489">
+    <sortCondition ref="B2:B489"/>
+    <sortCondition ref="A2:A489"/>
+    <sortCondition ref="D2:D489"/>
+    <sortCondition ref="C2:C489"/>
   </sortState>
   <conditionalFormatting sqref="A1:A155 C1:C155 A163:A209 C166:C209 A288:A1048576 C296:C1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
